--- a/build/lis/P2437-HV-LIS-001 REV0.xlsx
+++ b/build/lis/P2437-HV-LIS-001 REV0.xlsx
@@ -337,7 +337,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -496,6 +496,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3220,7 +3221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.61328125" customWidth="1" min="1" max="1"/>
@@ -3481,764 +3482,1025 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="61" t="inlineStr">
+        <is>
+          <t>1. Alcance del suministro</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="61" t="inlineStr">
-        <is>
-          <t>1. Alcance del suministro</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, exfiltración, control de presurización, instrumentación y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
+    <row r="17"/>
+    <row r="19">
+      <c r="A19" s="61" t="inlineStr">
+        <is>
+          <t>2. Tabla de equipos y materiales</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="62" t="inlineStr">
+        <is>
+          <t>Tabla 1. BOQ del sistema de presurización positiva (consulta de fuentes 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="inlineStr">
+        <is>
+          <t>Ítem</t>
+        </is>
+      </c>
+      <c r="B21" s="63" t="n"/>
+      <c r="C21" s="63" t="n"/>
+      <c r="D21" s="63" t="inlineStr">
+        <is>
+          <t>Función</t>
+        </is>
+      </c>
+      <c r="E21" s="63" t="n"/>
+      <c r="F21" s="63" t="inlineStr">
+        <is>
+          <t>Especificación clave</t>
+        </is>
+      </c>
+      <c r="G21" s="63" t="n"/>
+      <c r="H21" s="63" t="inlineStr">
+        <is>
+          <t>Material / compatibilidad corrosiva</t>
+        </is>
+      </c>
+      <c r="I21" s="63" t="n"/>
+      <c r="J21" s="63" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="K21" s="63" t="n"/>
+      <c r="L21" s="63" t="inlineStr">
+        <is>
+          <t>Candidatos comerciales (fabricante/modelo)</t>
+        </is>
+      </c>
+      <c r="M21" s="63" t="n"/>
+      <c r="N21" s="63" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="O21" s="63" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="61" t="inlineStr">
-        <is>
-          <t>2. Tabla de equipos y materiales</t>
-        </is>
-      </c>
+      <c r="A22" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="65" t="n"/>
+      <c r="C22" s="65" t="n"/>
+      <c r="D22" s="64" t="inlineStr">
+        <is>
+          <t>Ventilador de impulsión</t>
+        </is>
+      </c>
+      <c r="E22" s="65" t="n"/>
+      <c r="F22" s="64" t="inlineStr">
+        <is>
+          <t>Centrífugo álabes curvados atrás; 3 840 m³/h @ 260 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 190 Pa en sitio; AMCA 210; Spark A</t>
+        </is>
+      </c>
+      <c r="G22" s="65" t="n"/>
+      <c r="H22" s="64" t="inlineStr">
+        <is>
+          <t>PRFV viniléster (ASTM C582/D4167); alternativa PP</t>
+        </is>
+      </c>
+      <c r="I22" s="65" t="n"/>
+      <c r="J22" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="65" t="n"/>
+      <c r="L22" s="64" t="inlineStr">
+        <is>
+          <t>Greenheck BCSW-FRP (vía Prime Lines HVAC, Bogotá); NYB FRP Fume Exhauster; Sodeca CPV; Plastec 25/30; S&amp;P línea PP</t>
+        </is>
+      </c>
+      <c r="M22" s="65" t="n"/>
+      <c r="N22" s="64" t="inlineStr">
+        <is>
+          <t>BCSW-FRP (https://content.greenheck.com/public/DAMProd/Original/10002/BCSWFRP_catalog.pdf); NYB (https://www.nyb.com/frp-fume-exhauster/); Sodeca CPV (https://www.sodeca.com/es/sistemas-de-ventilacion-extraccion/cpv-p1000000071)</t>
+        </is>
+      </c>
+      <c r="O22" s="65" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="62" t="inlineStr">
-        <is>
-          <t>Tabla 1. BOQ del sistema de presurización positiva (consulta de fuentes 2026-07-23).</t>
-        </is>
-      </c>
+      <c r="A23" s="64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="65" t="n"/>
+      <c r="C23" s="65" t="n"/>
+      <c r="D23" s="64" t="inlineStr">
+        <is>
+          <t>Motor del ventilador</t>
+        </is>
+      </c>
+      <c r="E23" s="65" t="n"/>
+      <c r="F23" s="64" t="inlineStr">
+        <is>
+          <t>1.0 HP, TEFC, 1 800 RPM (4 polos), 60 Hz, clase F, IP55 mín., severe duty epóxico; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="G23" s="65" t="n"/>
+      <c r="H23" s="64" t="inlineStr">
+        <is>
+          <t>Pintura epóxica + protección interna anticorrosiva; motor fuera de la corriente</t>
+        </is>
+      </c>
+      <c r="I23" s="65" t="n"/>
+      <c r="J23" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" s="65" t="n"/>
+      <c r="L23" s="64" t="inlineStr">
+        <is>
+          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
+        </is>
+      </c>
+      <c r="M23" s="65" t="n"/>
+      <c r="N23" s="64" t="inlineStr">
+        <is>
+          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
+        </is>
+      </c>
+      <c r="O23" s="65" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="63" t="inlineStr">
-        <is>
-          <t>Ítem</t>
-        </is>
-      </c>
-      <c r="B24" s="63" t="inlineStr">
-        <is>
-          <t>Función</t>
-        </is>
-      </c>
-      <c r="C24" s="63" t="inlineStr">
-        <is>
-          <t>Especificación clave</t>
-        </is>
-      </c>
-      <c r="D24" s="63" t="inlineStr">
-        <is>
-          <t>Material / compatibilidad corrosiva</t>
-        </is>
-      </c>
-      <c r="E24" s="63" t="inlineStr">
-        <is>
-          <t>Cant.</t>
-        </is>
-      </c>
-      <c r="F24" s="63" t="inlineStr">
-        <is>
-          <t>Candidatos comerciales (fabricante/modelo)</t>
-        </is>
-      </c>
-      <c r="G24" s="63" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
+      <c r="A24" s="64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="65" t="n"/>
+      <c r="C24" s="65" t="n"/>
+      <c r="D24" s="64" t="inlineStr">
+        <is>
+          <t>Prefiltro (etapa 1)</t>
+        </is>
+      </c>
+      <c r="E24" s="65" t="n"/>
+      <c r="F24" s="64" t="inlineStr">
+        <is>
+          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
+        </is>
+      </c>
+      <c r="G24" s="65" t="n"/>
+      <c r="H24" s="64" t="inlineStr">
+        <is>
+          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
+        </is>
+      </c>
+      <c r="I24" s="65" t="n"/>
+      <c r="J24" s="64" t="inlineStr">
+        <is>
+          <t>1 (+ repuestos)</t>
+        </is>
+      </c>
+      <c r="K24" s="65" t="n"/>
+      <c r="L24" s="64" t="inlineStr">
+        <is>
+          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
+        </is>
+      </c>
+      <c r="M24" s="65" t="n"/>
+      <c r="N24" s="64" t="inlineStr">
+        <is>
+          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
+        </is>
+      </c>
+      <c r="O24" s="65" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="64" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B25" s="64" t="inlineStr">
-        <is>
-          <t>Ventilador de impulsión</t>
-        </is>
-      </c>
-      <c r="C25" s="64" t="inlineStr">
-        <is>
-          <t>Centrífugo álabes curvados atrás; 3 840 m³/h @ 260 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 190 Pa en sitio; AMCA 210; Spark A</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B25" s="65" t="n"/>
+      <c r="C25" s="65" t="n"/>
       <c r="D25" s="64" t="inlineStr">
         <is>
-          <t>PRFV viniléster (ASTM C582/D4167); alternativa PP</t>
-        </is>
-      </c>
-      <c r="E25" s="64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Filtro final (etapa 2)</t>
+        </is>
+      </c>
+      <c r="E25" s="65" t="n"/>
       <c r="F25" s="64" t="inlineStr">
         <is>
-          <t>Greenheck BCSW-FRP (vía Prime Lines HVAC, Bogotá); NYB FRP Fume Exhauster; Sodeca CPV; Plastec 25/30; S&amp;P línea PP</t>
-        </is>
-      </c>
-      <c r="G25" s="64" t="inlineStr">
-        <is>
-          <t>BCSW-FRP (https://content.greenheck.com/public/DAMProd/Original/10002/BCSWFRP_catalog.pdf); NYB (https://www.nyb.com/frp-fume-exhauster/); Sodeca CPV (https://www.sodeca.com/es/sistemas-de-ventilacion-extraccion/cpv-p1000000071)</t>
-        </is>
-      </c>
+          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
+        </is>
+      </c>
+      <c r="G25" s="65" t="n"/>
+      <c r="H25" s="64" t="inlineStr">
+        <is>
+          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
+        </is>
+      </c>
+      <c r="I25" s="65" t="n"/>
+      <c r="J25" s="64" t="inlineStr">
+        <is>
+          <t>1 (+ repuestos)</t>
+        </is>
+      </c>
+      <c r="K25" s="65" t="n"/>
+      <c r="L25" s="64" t="inlineStr">
+        <is>
+          <t>Camfil Durafil ES2 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
+        </is>
+      </c>
+      <c r="M25" s="65" t="n"/>
+      <c r="N25" s="64" t="inlineStr">
+        <is>
+          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
+        </is>
+      </c>
+      <c r="O25" s="65" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="64" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B26" s="64" t="inlineStr">
-        <is>
-          <t>Motor del ventilador</t>
-        </is>
-      </c>
-      <c r="C26" s="64" t="inlineStr">
-        <is>
-          <t>1.0 HP, TEFC, 1 800 RPM (4 polos), 60 Hz, clase F, IP55 mín., severe duty epóxico; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="65" t="n"/>
+      <c r="C26" s="65" t="n"/>
       <c r="D26" s="64" t="inlineStr">
         <is>
-          <t>Pintura epóxica + protección interna anticorrosiva; motor fuera de la corriente</t>
-        </is>
-      </c>
-      <c r="E26" s="64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Marcos portafiltros</t>
+        </is>
+      </c>
+      <c r="E26" s="65" t="n"/>
       <c r="F26" s="64" t="inlineStr">
         <is>
-          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
-        </is>
-      </c>
-      <c r="G26" s="64" t="inlineStr">
-        <is>
-          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
-        </is>
-      </c>
+          <t>Holding frames para prefiltro + filtro final con junta continua</t>
+        </is>
+      </c>
+      <c r="G26" s="65" t="n"/>
+      <c r="H26" s="64" t="inlineStr">
+        <is>
+          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
+        </is>
+      </c>
+      <c r="I26" s="65" t="n"/>
+      <c r="J26" s="64" t="inlineStr">
+        <is>
+          <t>1 juego</t>
+        </is>
+      </c>
+      <c r="K26" s="65" t="n"/>
+      <c r="L26" s="64" t="inlineStr">
+        <is>
+          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
+        </is>
+      </c>
+      <c r="M26" s="65" t="n"/>
+      <c r="N26" s="64" t="inlineStr">
+        <is>
+          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
+        </is>
+      </c>
+      <c r="O26" s="65" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="64" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="65" t="n"/>
+      <c r="C27" s="65" t="n"/>
+      <c r="D27" s="64" t="inlineStr">
+        <is>
+          <t>Rejillas de exfiltración</t>
+        </is>
+      </c>
+      <c r="E27" s="65" t="n"/>
+      <c r="F27" s="64" t="inlineStr">
+        <is>
+          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio; área libre ≥ 90 %</t>
+        </is>
+      </c>
+      <c r="G27" s="65" t="n"/>
+      <c r="H27" s="64" t="inlineStr">
+        <is>
+          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
+        </is>
+      </c>
+      <c r="I27" s="65" t="n"/>
+      <c r="J27" s="64" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B27" s="64" t="inlineStr">
-        <is>
-          <t>Prefiltro (etapa 1)</t>
-        </is>
-      </c>
-      <c r="C27" s="64" t="inlineStr">
-        <is>
-          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
-        </is>
-      </c>
-      <c r="D27" s="64" t="inlineStr">
-        <is>
-          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
-        </is>
-      </c>
-      <c r="E27" s="64" t="inlineStr">
-        <is>
-          <t>1 (+ repuestos)</t>
-        </is>
-      </c>
-      <c r="F27" s="64" t="inlineStr">
-        <is>
-          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
-        </is>
-      </c>
-      <c r="G27" s="64" t="inlineStr">
-        <is>
-          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
-        </is>
-      </c>
+      <c r="K27" s="65" t="n"/>
+      <c r="L27" s="64" t="inlineStr">
+        <is>
+          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
+        </is>
+      </c>
+      <c r="M27" s="65" t="n"/>
+      <c r="N27" s="64" t="inlineStr">
+        <is>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+        </is>
+      </c>
+      <c r="O27" s="65" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="64" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B28" s="64" t="inlineStr">
-        <is>
-          <t>Filtro final (etapa 2)</t>
-        </is>
-      </c>
-      <c r="C28" s="64" t="inlineStr">
-        <is>
-          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="65" t="n"/>
+      <c r="C28" s="65" t="n"/>
       <c r="D28" s="64" t="inlineStr">
         <is>
-          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
-        </is>
-      </c>
-      <c r="E28" s="64" t="inlineStr">
-        <is>
-          <t>1 (+ repuestos)</t>
-        </is>
-      </c>
+          <t>Malla anti-insectos</t>
+        </is>
+      </c>
+      <c r="E28" s="65" t="n"/>
       <c r="F28" s="64" t="inlineStr">
         <is>
-          <t>Camfil Durafil ES2 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
-        </is>
-      </c>
-      <c r="G28" s="64" t="inlineStr">
-        <is>
-          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
-        </is>
-      </c>
+          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
+        </is>
+      </c>
+      <c r="G28" s="65" t="n"/>
+      <c r="H28" s="64" t="inlineStr">
+        <is>
+          <t>Inox 316</t>
+        </is>
+      </c>
+      <c r="I28" s="65" t="n"/>
+      <c r="J28" s="64" t="inlineStr">
+        <is>
+          <t>3 (una por rejilla)</t>
+        </is>
+      </c>
+      <c r="K28" s="65" t="n"/>
+      <c r="L28" s="64" t="inlineStr">
+        <is>
+          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
+        </is>
+      </c>
+      <c r="M28" s="65" t="n"/>
+      <c r="N28" s="64" t="inlineStr">
+        <is>
+          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
+        </is>
+      </c>
+      <c r="O28" s="65" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="64" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B29" s="64" t="inlineStr">
-        <is>
-          <t>Marcos portafiltros</t>
-        </is>
-      </c>
-      <c r="C29" s="64" t="inlineStr">
-        <is>
-          <t>Holding frames para prefiltro + filtro final con junta continua</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B29" s="65" t="n"/>
+      <c r="C29" s="65" t="n"/>
       <c r="D29" s="64" t="inlineStr">
         <is>
-          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
-        </is>
-      </c>
-      <c r="E29" s="64" t="inlineStr">
-        <is>
-          <t>1 juego</t>
-        </is>
-      </c>
+          <t>Damper de alivio barométrico</t>
+        </is>
+      </c>
+      <c r="E29" s="65" t="n"/>
       <c r="F29" s="64" t="inlineStr">
         <is>
-          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
-        </is>
-      </c>
-      <c r="G29" s="64" t="inlineStr">
-        <is>
-          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
-        </is>
-      </c>
+          <t>Contrapeso ajustable 12-75 Pa (0.05-0.30 in c.a.); set-point +25 Pa; V facial ≤ 2.5 m/s al caudal de alivio; AMCA 500-D</t>
+        </is>
+      </c>
+      <c r="G29" s="65" t="n"/>
+      <c r="H29" s="64" t="inlineStr">
+        <is>
+          <t>Aluminio extruido 6063-T5 o línea severe-environment; no galvanizado</t>
+        </is>
+      </c>
+      <c r="I29" s="65" t="n"/>
+      <c r="J29" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" s="65" t="n"/>
+      <c r="L29" s="64" t="inlineStr">
+        <is>
+          <t>Greenheck SEBR-10; Ruskin CBD6/BD6; Nailor 1390CB-EAF</t>
+        </is>
+      </c>
+      <c r="M29" s="65" t="n"/>
+      <c r="N29" s="64" t="inlineStr">
+        <is>
+          <t>SEBR-10 (PDF) (https://content.greenheck.com/public/DAMProd/Original/10002/SEBR10Series_submittal.pdf); Ruskin BD6 (https://www.ruskin.com/model/bd6); Nailor 1390CB (PDF) (https://nailor.com/sites/default/files/documents/1390CB_B_0_0.pdf)</t>
+        </is>
+      </c>
+      <c r="O29" s="65" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="64" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B30" s="64" t="inlineStr">
-        <is>
-          <t>Rejillas de exfiltración</t>
-        </is>
-      </c>
-      <c r="C30" s="64" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio; área libre ≥ 90 %</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" s="65" t="n"/>
+      <c r="C30" s="65" t="n"/>
       <c r="D30" s="64" t="inlineStr">
         <is>
-          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
-        </is>
-      </c>
-      <c r="E30" s="64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Transmisor de presión diferencial</t>
+        </is>
+      </c>
+      <c r="E30" s="65" t="n"/>
       <c r="F30" s="64" t="inlineStr">
         <is>
-          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
-        </is>
-      </c>
-      <c r="G30" s="64" t="inlineStr">
-        <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
-        </is>
-      </c>
+          <t>Rango 0-62.5 Pa (0-0.25 in c.a.); salida 4-20 mA, 2 hilos; constante de tiempo ajustable</t>
+        </is>
+      </c>
+      <c r="G30" s="65" t="n"/>
+      <c r="H30" s="64" t="inlineStr">
+        <is>
+          <t>Gabinete NEMA 4X (IP66); montaje interior con toma exterior protegida</t>
+        </is>
+      </c>
+      <c r="I30" s="65" t="n"/>
+      <c r="J30" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" s="65" t="n"/>
+      <c r="L30" s="64" t="inlineStr">
+        <is>
+          <t>Dwyer MS-121(-LCD) Magnesense; Setra 264; Siemens QBM2130-1U</t>
+        </is>
+      </c>
+      <c r="M30" s="65" t="n"/>
+      <c r="N30" s="64" t="inlineStr">
+        <is>
+          <t>Dwyer MS (PDF) (https://www.transcat.com/media/pdf/MS_cat.pdf); Setra 264 (PDF) (https://www.setra.com/hubfs/Product_Data_Sheets/Setra_Model_264_Data_Sheet.pdf)</t>
+        </is>
+      </c>
+      <c r="O30" s="65" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="64" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B31" s="64" t="inlineStr">
-        <is>
-          <t>Malla anti-insectos</t>
-        </is>
-      </c>
-      <c r="C31" s="64" t="inlineStr">
-        <is>
-          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B31" s="65" t="n"/>
+      <c r="C31" s="65" t="n"/>
       <c r="D31" s="64" t="inlineStr">
         <is>
-          <t>Inox 316</t>
-        </is>
-      </c>
-      <c r="E31" s="64" t="inlineStr">
-        <is>
-          <t>3 (una por rejilla)</t>
-        </is>
-      </c>
+          <t>Manómetro diferencial de lectura local</t>
+        </is>
+      </c>
+      <c r="E31" s="65" t="n"/>
       <c r="F31" s="64" t="inlineStr">
         <is>
-          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
-        </is>
-      </c>
-      <c r="G31" s="64" t="inlineStr">
-        <is>
-          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
-        </is>
-      </c>
+          <t>Magnehelic 2000-00, rango 0-62 Pa (0-0.25 in c.a.); ±2 % FS</t>
+        </is>
+      </c>
+      <c r="G31" s="65" t="n"/>
+      <c r="H31" s="64" t="inlineStr">
+        <is>
+          <t>Caja aluminio (niebla salina 168 h); opción bisel inox; montaje interior</t>
+        </is>
+      </c>
+      <c r="I31" s="65" t="n"/>
+      <c r="J31" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" s="65" t="n"/>
+      <c r="L31" s="64" t="inlineStr">
+        <is>
+          <t>Dwyer Magnehelic 2000-00 (Vía Industrial, RS Importaciones, SICO Global, Bogotá)</t>
+        </is>
+      </c>
+      <c r="M31" s="65" t="n"/>
+      <c r="N31" s="64" t="inlineStr">
+        <is>
+          <t>Tabla serie 2000 (https://skilltech.com.br/produto/manometro-para-pressao-diferencial-magnehelic-serie-2000/); Vía Industrial (https://www.viaindustrial.com/dwyer/marca/)</t>
+        </is>
+      </c>
+      <c r="O31" s="65" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="64" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B32" s="64" t="inlineStr">
-        <is>
-          <t>Damper de alivio barométrico</t>
-        </is>
-      </c>
-      <c r="C32" s="64" t="inlineStr">
-        <is>
-          <t>Contrapeso ajustable 12-75 Pa (0.05-0.30 in c.a.); set-point +25 Pa; V facial ≤ 2.5 m/s al caudal de alivio; AMCA 500-D</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="65" t="n"/>
+      <c r="C32" s="65" t="n"/>
       <c r="D32" s="64" t="inlineStr">
         <is>
-          <t>Aluminio extruido 6063-T5 o línea severe-environment; no galvanizado</t>
-        </is>
-      </c>
-      <c r="E32" s="64" t="inlineStr">
+          <t>Controlador / lógica de alarmas</t>
+        </is>
+      </c>
+      <c r="E32" s="65" t="n"/>
+      <c r="F32" s="64" t="inlineStr">
+        <is>
+          <t>Alarma baja +12.5 Pa y alta +40 Pa desde la señal 4-20 mA; retardo 30-60 s</t>
+        </is>
+      </c>
+      <c r="G32" s="65" t="n"/>
+      <c r="H32" s="64" t="inlineStr">
+        <is>
+          <t>Integración al PLC/BMS del cliente o relés autónomos</t>
+        </is>
+      </c>
+      <c r="I32" s="65" t="n"/>
+      <c r="J32" s="64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F32" s="64" t="inlineStr">
-        <is>
-          <t>Greenheck SEBR-10; Ruskin CBD6/BD6; Nailor 1390CB-EAF</t>
-        </is>
-      </c>
-      <c r="G32" s="64" t="inlineStr">
-        <is>
-          <t>SEBR-10 (PDF) (https://content.greenheck.com/public/DAMProd/Original/10002/SEBR10Series_submittal.pdf); Ruskin BD6 (https://www.ruskin.com/model/bd6); Nailor 1390CB (PDF) (https://nailor.com/sites/default/files/documents/1390CB_B_0_0.pdf)</t>
-        </is>
-      </c>
+      <c r="K32" s="65" t="n"/>
+      <c r="L32" s="64" t="inlineStr">
+        <is>
+          <t>PLC del cliente (por confirmar); alternativa autónoma Dwyer Photohelic 3000MR-00AV</t>
+        </is>
+      </c>
+      <c r="M32" s="65" t="n"/>
+      <c r="N32" s="64" t="inlineStr">
+        <is>
+          <t>Northeast Controls — Photohelic (https://nciweb.net/pressure1.htm)</t>
+        </is>
+      </c>
+      <c r="O32" s="65" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="64" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B33" s="64" t="inlineStr">
-        <is>
-          <t>Transmisor de presión diferencial</t>
-        </is>
-      </c>
-      <c r="C33" s="64" t="inlineStr">
-        <is>
-          <t>Rango 0-62.5 Pa (0-0.25 in c.a.); salida 4-20 mA, 2 hilos; constante de tiempo ajustable</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B33" s="65" t="n"/>
+      <c r="C33" s="65" t="n"/>
       <c r="D33" s="64" t="inlineStr">
         <is>
-          <t>Gabinete NEMA 4X (IP66); montaje interior con toma exterior protegida</t>
-        </is>
-      </c>
-      <c r="E33" s="64" t="inlineStr">
+          <t>Toma de referencia exterior</t>
+        </is>
+      </c>
+      <c r="E33" s="65" t="n"/>
+      <c r="F33" s="64" t="inlineStr">
+        <is>
+          <t>Caja estática de pared orientada a sotavento; tubo de impulso con purga/filtro de membrana</t>
+        </is>
+      </c>
+      <c r="G33" s="65" t="n"/>
+      <c r="H33" s="64" t="inlineStr">
+        <is>
+          <t>Inox 316; conexiones 1/8 in NPT con sellante compatible</t>
+        </is>
+      </c>
+      <c r="I33" s="65" t="n"/>
+      <c r="J33" s="64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F33" s="64" t="inlineStr">
-        <is>
-          <t>Dwyer MS-121(-LCD) Magnesense; Setra 264; Siemens QBM2130-1U</t>
-        </is>
-      </c>
-      <c r="G33" s="64" t="inlineStr">
-        <is>
-          <t>Dwyer MS (PDF) (https://www.transcat.com/media/pdf/MS_cat.pdf); Setra 264 (PDF) (https://www.setra.com/hubfs/Product_Data_Sheets/Setra_Model_264_Data_Sheet.pdf)</t>
-        </is>
-      </c>
+      <c r="K33" s="65" t="n"/>
+      <c r="L33" s="64" t="inlineStr">
+        <is>
+          <t>Dwyer A-417 o fabricación local inox 316 (dato típico)</t>
+        </is>
+      </c>
+      <c r="M33" s="65" t="n"/>
+      <c r="N33" s="64" t="inlineStr">
+        <is>
+          <t>Dwyer MS (PDF) (https://www.transcat.com/media/pdf/MS_cat.pdf)</t>
+        </is>
+      </c>
+      <c r="O33" s="65" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="64" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B34" s="64" t="inlineStr">
-        <is>
-          <t>Manómetro diferencial de lectura local</t>
-        </is>
-      </c>
-      <c r="C34" s="64" t="inlineStr">
-        <is>
-          <t>Magnehelic 2000-00, rango 0-62 Pa (0-0.25 in c.a.); ±2 % FS</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B34" s="65" t="n"/>
+      <c r="C34" s="65" t="n"/>
       <c r="D34" s="64" t="inlineStr">
         <is>
-          <t>Caja aluminio (niebla salina 168 h); opción bisel inox; montaje interior</t>
-        </is>
-      </c>
-      <c r="E34" s="64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Soportes y ferretería</t>
+        </is>
+      </c>
+      <c r="E34" s="65" t="n"/>
       <c r="F34" s="64" t="inlineStr">
         <is>
-          <t>Dwyer Magnehelic 2000-00 (Vía Industrial, RS Importaciones, SICO Global, Bogotá)</t>
-        </is>
-      </c>
-      <c r="G34" s="64" t="inlineStr">
-        <is>
-          <t>Tabla serie 2000 (https://skilltech.com.br/produto/manometro-para-pressao-diferencial-magnehelic-serie-2000/); Vía Industrial (https://www.viaindustrial.com/dwyer/marca/)</t>
-        </is>
-      </c>
+          <t>Soportes de ventilador, rejillas, damper e instrumentos; pernos, tuercas, arandelas</t>
+        </is>
+      </c>
+      <c r="G34" s="65" t="n"/>
+      <c r="H34" s="64" t="inlineStr">
+        <is>
+          <t>Inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
+        </is>
+      </c>
+      <c r="I34" s="65" t="n"/>
+      <c r="J34" s="64" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="K34" s="65" t="n"/>
+      <c r="L34" s="64" t="inlineStr">
+        <is>
+          <t>Suministro nacional genérico A4</t>
+        </is>
+      </c>
+      <c r="M34" s="65" t="n"/>
+      <c r="N34" s="64" t="inlineStr">
+        <is>
+          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
+        </is>
+      </c>
+      <c r="O34" s="65" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="64" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B35" s="64" t="inlineStr">
-        <is>
-          <t>Controlador / lógica de alarmas</t>
-        </is>
-      </c>
-      <c r="C35" s="64" t="inlineStr">
-        <is>
-          <t>Alarma baja +12.5 Pa y alta +40 Pa desde la señal 4-20 mA; retardo 30-60 s</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B35" s="65" t="n"/>
+      <c r="C35" s="65" t="n"/>
       <c r="D35" s="64" t="inlineStr">
         <is>
-          <t>Integración al PLC/BMS del cliente o relés autónomos</t>
-        </is>
-      </c>
-      <c r="E35" s="64" t="inlineStr">
+          <t>Conexión flexible ventilador-pasamuros</t>
+        </is>
+      </c>
+      <c r="E35" s="65" t="n"/>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>Ancho ≥ 100 mm; bandas de amarre inox 316 cal. 24</t>
+        </is>
+      </c>
+      <c r="G35" s="65" t="n"/>
+      <c r="H35" s="64" t="inlineStr">
+        <is>
+          <t>Hipalón (CSM); alternativa clorobutilo; no PVC estándar</t>
+        </is>
+      </c>
+      <c r="I35" s="65" t="n"/>
+      <c r="J35" s="64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F35" s="64" t="inlineStr">
-        <is>
-          <t>PLC del cliente (por confirmar); alternativa autónoma Dwyer Photohelic 3000MR-00AV</t>
-        </is>
-      </c>
-      <c r="G35" s="64" t="inlineStr">
-        <is>
-          <t>Northeast Controls — Photohelic (https://nciweb.net/pressure1.htm)</t>
-        </is>
-      </c>
+      <c r="K35" s="65" t="n"/>
+      <c r="L35" s="64" t="inlineStr">
+        <is>
+          <t>Hardcast Hypalon; Proco serie 500</t>
+        </is>
+      </c>
+      <c r="M35" s="65" t="n"/>
+      <c r="N35" s="64" t="inlineStr">
+        <is>
+          <t>Hardcast (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf)</t>
+        </is>
+      </c>
+      <c r="O35" s="65" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="64" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B36" s="64" t="inlineStr">
-        <is>
-          <t>Toma de referencia exterior</t>
-        </is>
-      </c>
-      <c r="C36" s="64" t="inlineStr">
-        <is>
-          <t>Caja estática de pared orientada a sotavento; tubo de impulso con purga/filtro de membrana</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B36" s="65" t="n"/>
+      <c r="C36" s="65" t="n"/>
       <c r="D36" s="64" t="inlineStr">
         <is>
-          <t>Inox 316; conexiones 1/8 in NPT con sellante compatible</t>
-        </is>
-      </c>
-      <c r="E36" s="64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Selladores</t>
+        </is>
+      </c>
+      <c r="E36" s="65" t="n"/>
       <c r="F36" s="64" t="inlineStr">
         <is>
-          <t>Dwyer A-417 o fabricación local inox 316 (dato típico)</t>
-        </is>
-      </c>
-      <c r="G36" s="64" t="inlineStr">
-        <is>
-          <t>Dwyer MS (PDF) (https://www.transcat.com/media/pdf/MS_cat.pdf)</t>
-        </is>
-      </c>
+          <t>Sellado de pasamuros, marcos y empalmes</t>
+        </is>
+      </c>
+      <c r="G36" s="65" t="n"/>
+      <c r="H36" s="64" t="inlineStr">
+        <is>
+          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
+        </is>
+      </c>
+      <c r="I36" s="65" t="n"/>
+      <c r="J36" s="64" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="K36" s="65" t="n"/>
+      <c r="L36" s="64" t="inlineStr">
+        <is>
+          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
+        </is>
+      </c>
+      <c r="M36" s="65" t="n"/>
+      <c r="N36" s="64" t="inlineStr">
+        <is>
+          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
+        </is>
+      </c>
+      <c r="O36" s="65" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="64" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B37" s="64" t="inlineStr">
-        <is>
-          <t>Soportes y ferretería</t>
-        </is>
-      </c>
-      <c r="C37" s="64" t="inlineStr">
-        <is>
-          <t>Soportes de ventilador, rejillas, damper e instrumentos; pernos, tuercas, arandelas</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B37" s="65" t="n"/>
+      <c r="C37" s="65" t="n"/>
       <c r="D37" s="64" t="inlineStr">
         <is>
-          <t>Inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
-        </is>
-      </c>
-      <c r="E37" s="64" t="inlineStr">
-        <is>
-          <t>Lote</t>
-        </is>
-      </c>
+          <t>Protecciones eléctricas y tablero</t>
+        </is>
+      </c>
+      <c r="E37" s="65" t="n"/>
       <c r="F37" s="64" t="inlineStr">
         <is>
-          <t>Suministro nacional genérico A4</t>
-        </is>
-      </c>
-      <c r="G37" s="64" t="inlineStr">
-        <is>
-          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
-        </is>
-      </c>
+          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
+        </is>
+      </c>
+      <c r="G37" s="65" t="n"/>
+      <c r="H37" s="64" t="inlineStr">
+        <is>
+          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
+        </is>
+      </c>
+      <c r="I37" s="65" t="n"/>
+      <c r="J37" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" s="65" t="n"/>
+      <c r="L37" s="64" t="inlineStr">
+        <is>
+          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
+        </is>
+      </c>
+      <c r="M37" s="65" t="n"/>
+      <c r="N37" s="64" t="inlineStr">
+        <is>
+          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
+        </is>
+      </c>
+      <c r="O37" s="65" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="64" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B38" s="64" t="inlineStr">
-        <is>
-          <t>Conexión flexible ventilador-pasamuros</t>
-        </is>
-      </c>
-      <c r="C38" s="64" t="inlineStr">
-        <is>
-          <t>Ancho ≥ 100 mm; bandas de amarre inox 316 cal. 24</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B38" s="65" t="n"/>
+      <c r="C38" s="65" t="n"/>
       <c r="D38" s="64" t="inlineStr">
         <is>
-          <t>Hipalón (CSM); alternativa clorobutilo; no PVC estándar</t>
-        </is>
-      </c>
-      <c r="E38" s="64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Cableado y canalización</t>
+        </is>
+      </c>
+      <c r="E38" s="65" t="n"/>
       <c r="F38" s="64" t="inlineStr">
         <is>
-          <t>Hardcast Hypalon; Proco serie 500</t>
-        </is>
-      </c>
-      <c r="G38" s="64" t="inlineStr">
-        <is>
-          <t>Hardcast (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="64" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B39" s="64" t="inlineStr">
-        <is>
-          <t>Selladores</t>
-        </is>
-      </c>
-      <c r="C39" s="64" t="inlineStr">
-        <is>
-          <t>Sellado de pasamuros, marcos y empalmes</t>
-        </is>
-      </c>
-      <c r="D39" s="64" t="inlineStr">
-        <is>
-          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
-        </is>
-      </c>
-      <c r="E39" s="64" t="inlineStr">
+          <t>Circuito motor 1.0 HP + circuito instrumentación 4-20 mA apantallado</t>
+        </is>
+      </c>
+      <c r="G38" s="65" t="n"/>
+      <c r="H38" s="64" t="inlineStr">
+        <is>
+          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
+        </is>
+      </c>
+      <c r="I38" s="65" t="n"/>
+      <c r="J38" s="64" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="F39" s="64" t="inlineStr">
-        <is>
-          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
-        </is>
-      </c>
-      <c r="G39" s="64" t="inlineStr">
-        <is>
-          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="64" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B40" s="64" t="inlineStr">
-        <is>
-          <t>Protecciones eléctricas y tablero</t>
-        </is>
-      </c>
-      <c r="C40" s="64" t="inlineStr">
-        <is>
-          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
-        </is>
-      </c>
-      <c r="D40" s="64" t="inlineStr">
-        <is>
-          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
-        </is>
-      </c>
-      <c r="E40" s="64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F40" s="64" t="inlineStr">
-        <is>
-          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
-        </is>
-      </c>
-      <c r="G40" s="64" t="inlineStr">
-        <is>
-          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
-        </is>
-      </c>
+      <c r="K38" s="65" t="n"/>
+      <c r="L38" s="64" t="inlineStr">
+        <is>
+          <t>Suministro nacional certificado RETIE</t>
+        </is>
+      </c>
+      <c r="M38" s="65" t="n"/>
+      <c r="N38" s="64" t="inlineStr">
+        <is>
+          <t>Requisito RETIE / NTC 2050</t>
+        </is>
+      </c>
+      <c r="O38" s="65" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="64" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B41" s="64" t="inlineStr">
-        <is>
-          <t>Cableado y canalización</t>
-        </is>
-      </c>
-      <c r="C41" s="64" t="inlineStr">
-        <is>
-          <t>Circuito motor 1.0 HP + circuito instrumentación 4-20 mA apantallado</t>
-        </is>
-      </c>
-      <c r="D41" s="64" t="inlineStr">
-        <is>
-          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
-        </is>
-      </c>
-      <c r="E41" s="64" t="inlineStr">
-        <is>
-          <t>Lote</t>
-        </is>
-      </c>
-      <c r="F41" s="64" t="inlineStr">
-        <is>
-          <t>Suministro nacional certificado RETIE</t>
-        </is>
-      </c>
-      <c r="G41" s="64" t="inlineStr">
-        <is>
-          <t>Requisito RETIE / NTC 2050</t>
-        </is>
-      </c>
-    </row>
+      <c r="A41" s="61" t="inlineStr">
+        <is>
+          <t>3. Notas de suministro</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="60" t="inlineStr">
+        <is>
+          <t>3.1. Ítems 1, 4, 8, 9 y 10 requieren cotización formal con submittal: la selección final de tamaño/RPM del ventilador (ítem 1) se confirma con el software del fabricante sobre el punto 3 840 m³/h @ 260 Pa aire estándar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
-      <c r="A44" s="61" t="inlineStr">
-        <is>
-          <t>3. Notas de suministro</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="60" t="inlineStr">
-        <is>
-          <t>3.1. Ítems 1, 4, 8, 9 y 10 requieren cotización formal con submittal: la selección final de tamaño/RPM del ventilador (ítem 1) se confirma con el software del fabricante sobre el punto 3 840 m³/h @ 260 Pa aire estándar.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A44" s="60" t="inlineStr">
+        <is>
+          <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
     <row r="46"/>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="60" t="inlineStr">
-        <is>
-          <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="60" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="60" t="inlineStr">
         <is>
           <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 16-17. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
+    <row r="48"/>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A44:G44"/>
+  <mergeCells count="146">
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="C2:L3"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B1:B5"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A44:O46"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A8:O8"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="A1:A5"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="A42:O43"/>
+    <mergeCell ref="A47:O48"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="F26:G26"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="C2:L3"/>
-    <mergeCell ref="A45:G47"/>
-    <mergeCell ref="A13:G14"/>
-    <mergeCell ref="A48:G52"/>
-    <mergeCell ref="A17:G20"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A53:G56"/>
-    <mergeCell ref="A1:A5"/>
-    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="A16:O17"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="N34:O34"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="B1:B5"/>
-    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="H26:I26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/build/lis/P2437-HV-LIS-001 REV0.xlsx
+++ b/build/lis/P2437-HV-LIS-001 REV0.xlsx
@@ -3517,43 +3517,43 @@
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B21" s="63" t="n"/>
+      <c r="B21" s="63" t="inlineStr">
+        <is>
+          <t>Función</t>
+        </is>
+      </c>
       <c r="C21" s="63" t="n"/>
       <c r="D21" s="63" t="inlineStr">
         <is>
-          <t>Función</t>
+          <t>Especificación clave</t>
         </is>
       </c>
       <c r="E21" s="63" t="n"/>
-      <c r="F21" s="63" t="inlineStr">
-        <is>
-          <t>Especificación clave</t>
-        </is>
-      </c>
-      <c r="G21" s="63" t="n"/>
-      <c r="H21" s="63" t="inlineStr">
+      <c r="F21" s="63" t="n"/>
+      <c r="G21" s="63" t="inlineStr">
         <is>
           <t>Material / compatibilidad corrosiva</t>
         </is>
       </c>
-      <c r="I21" s="63" t="n"/>
+      <c r="H21" s="63" t="n"/>
+      <c r="I21" s="63" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
       <c r="J21" s="63" t="inlineStr">
         <is>
-          <t>Cant.</t>
+          <t>Candidatos comerciales (fabricante/modelo)</t>
         </is>
       </c>
       <c r="K21" s="63" t="n"/>
-      <c r="L21" s="63" t="inlineStr">
-        <is>
-          <t>Candidatos comerciales (fabricante/modelo)</t>
-        </is>
-      </c>
-      <c r="M21" s="63" t="n"/>
-      <c r="N21" s="63" t="inlineStr">
+      <c r="L21" s="63" t="n"/>
+      <c r="M21" s="63" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
+      <c r="N21" s="63" t="n"/>
       <c r="O21" s="63" t="n"/>
     </row>
     <row r="22">
@@ -3562,43 +3562,43 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B22" s="65" t="n"/>
+      <c r="B22" s="64" t="inlineStr">
+        <is>
+          <t>Ventilador de impulsión</t>
+        </is>
+      </c>
       <c r="C22" s="65" t="n"/>
       <c r="D22" s="64" t="inlineStr">
         <is>
-          <t>Ventilador de impulsión</t>
+          <t>Centrífugo álabes curvados atrás; 3 840 m³/h @ 260 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 190 Pa en sitio; AMCA 210; Spark A</t>
         </is>
       </c>
       <c r="E22" s="65" t="n"/>
-      <c r="F22" s="64" t="inlineStr">
-        <is>
-          <t>Centrífugo álabes curvados atrás; 3 840 m³/h @ 260 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 190 Pa en sitio; AMCA 210; Spark A</t>
-        </is>
-      </c>
-      <c r="G22" s="65" t="n"/>
-      <c r="H22" s="64" t="inlineStr">
+      <c r="F22" s="65" t="n"/>
+      <c r="G22" s="64" t="inlineStr">
         <is>
           <t>PRFV viniléster (ASTM C582/D4167); alternativa PP</t>
         </is>
       </c>
-      <c r="I22" s="65" t="n"/>
+      <c r="H22" s="65" t="n"/>
+      <c r="I22" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Greenheck BCSW-FRP (vía Prime Lines HVAC, Bogotá); NYB FRP Fume Exhauster; Sodeca CPV; Plastec 25/30; S&amp;P línea PP</t>
         </is>
       </c>
       <c r="K22" s="65" t="n"/>
-      <c r="L22" s="64" t="inlineStr">
-        <is>
-          <t>Greenheck BCSW-FRP (vía Prime Lines HVAC, Bogotá); NYB FRP Fume Exhauster; Sodeca CPV; Plastec 25/30; S&amp;P línea PP</t>
-        </is>
-      </c>
-      <c r="M22" s="65" t="n"/>
-      <c r="N22" s="64" t="inlineStr">
+      <c r="L22" s="65" t="n"/>
+      <c r="M22" s="64" t="inlineStr">
         <is>
           <t>BCSW-FRP (https://content.greenheck.com/public/DAMProd/Original/10002/BCSWFRP_catalog.pdf); NYB (https://www.nyb.com/frp-fume-exhauster/); Sodeca CPV (https://www.sodeca.com/es/sistemas-de-ventilacion-extraccion/cpv-p1000000071)</t>
         </is>
       </c>
+      <c r="N22" s="65" t="n"/>
       <c r="O22" s="65" t="n"/>
     </row>
     <row r="23">
@@ -3607,43 +3607,43 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B23" s="65" t="n"/>
+      <c r="B23" s="64" t="inlineStr">
+        <is>
+          <t>Motor del ventilador</t>
+        </is>
+      </c>
       <c r="C23" s="65" t="n"/>
       <c r="D23" s="64" t="inlineStr">
         <is>
-          <t>Motor del ventilador</t>
+          <t>1.0 HP, TEFC, 1 800 RPM (4 polos), 60 Hz, clase F, IP55 mín., severe duty epóxico; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
         </is>
       </c>
       <c r="E23" s="65" t="n"/>
-      <c r="F23" s="64" t="inlineStr">
-        <is>
-          <t>1.0 HP, TEFC, 1 800 RPM (4 polos), 60 Hz, clase F, IP55 mín., severe duty epóxico; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
-        </is>
-      </c>
-      <c r="G23" s="65" t="n"/>
-      <c r="H23" s="64" t="inlineStr">
+      <c r="F23" s="65" t="n"/>
+      <c r="G23" s="64" t="inlineStr">
         <is>
           <t>Pintura epóxica + protección interna anticorrosiva; motor fuera de la corriente</t>
         </is>
       </c>
-      <c r="I23" s="65" t="n"/>
+      <c r="H23" s="65" t="n"/>
+      <c r="I23" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
         </is>
       </c>
       <c r="K23" s="65" t="n"/>
-      <c r="L23" s="64" t="inlineStr">
-        <is>
-          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
-        </is>
-      </c>
-      <c r="M23" s="65" t="n"/>
-      <c r="N23" s="64" t="inlineStr">
+      <c r="L23" s="65" t="n"/>
+      <c r="M23" s="64" t="inlineStr">
         <is>
           <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
         </is>
       </c>
+      <c r="N23" s="65" t="n"/>
       <c r="O23" s="65" t="n"/>
     </row>
     <row r="24">
@@ -3652,43 +3652,43 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B24" s="65" t="n"/>
+      <c r="B24" s="64" t="inlineStr">
+        <is>
+          <t>Prefiltro (etapa 1)</t>
+        </is>
+      </c>
       <c r="C24" s="65" t="n"/>
       <c r="D24" s="64" t="inlineStr">
         <is>
-          <t>Prefiltro (etapa 1)</t>
+          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
         </is>
       </c>
       <c r="E24" s="65" t="n"/>
-      <c r="F24" s="64" t="inlineStr">
-        <is>
-          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
-        </is>
-      </c>
-      <c r="G24" s="65" t="n"/>
-      <c r="H24" s="64" t="inlineStr">
+      <c r="F24" s="65" t="n"/>
+      <c r="G24" s="64" t="inlineStr">
         <is>
           <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
         </is>
       </c>
-      <c r="I24" s="65" t="n"/>
+      <c r="H24" s="65" t="n"/>
+      <c r="I24" s="64" t="inlineStr">
+        <is>
+          <t>1 (+ repuestos)</t>
+        </is>
+      </c>
       <c r="J24" s="64" t="inlineStr">
         <is>
-          <t>1 (+ repuestos)</t>
+          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
         </is>
       </c>
       <c r="K24" s="65" t="n"/>
-      <c r="L24" s="64" t="inlineStr">
-        <is>
-          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
-        </is>
-      </c>
-      <c r="M24" s="65" t="n"/>
-      <c r="N24" s="64" t="inlineStr">
+      <c r="L24" s="65" t="n"/>
+      <c r="M24" s="64" t="inlineStr">
         <is>
           <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
         </is>
       </c>
+      <c r="N24" s="65" t="n"/>
       <c r="O24" s="65" t="n"/>
     </row>
     <row r="25">
@@ -3697,43 +3697,43 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B25" s="65" t="n"/>
+      <c r="B25" s="64" t="inlineStr">
+        <is>
+          <t>Filtro final (etapa 2)</t>
+        </is>
+      </c>
       <c r="C25" s="65" t="n"/>
       <c r="D25" s="64" t="inlineStr">
         <is>
-          <t>Filtro final (etapa 2)</t>
+          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
         </is>
       </c>
       <c r="E25" s="65" t="n"/>
-      <c r="F25" s="64" t="inlineStr">
-        <is>
-          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
-        </is>
-      </c>
-      <c r="G25" s="65" t="n"/>
-      <c r="H25" s="64" t="inlineStr">
+      <c r="F25" s="65" t="n"/>
+      <c r="G25" s="64" t="inlineStr">
         <is>
           <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
         </is>
       </c>
-      <c r="I25" s="65" t="n"/>
+      <c r="H25" s="65" t="n"/>
+      <c r="I25" s="64" t="inlineStr">
+        <is>
+          <t>1 (+ repuestos)</t>
+        </is>
+      </c>
       <c r="J25" s="64" t="inlineStr">
         <is>
-          <t>1 (+ repuestos)</t>
+          <t>Camfil Durafil ES2 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
         </is>
       </c>
       <c r="K25" s="65" t="n"/>
-      <c r="L25" s="64" t="inlineStr">
-        <is>
-          <t>Camfil Durafil ES2 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
-        </is>
-      </c>
-      <c r="M25" s="65" t="n"/>
-      <c r="N25" s="64" t="inlineStr">
+      <c r="L25" s="65" t="n"/>
+      <c r="M25" s="64" t="inlineStr">
         <is>
           <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
         </is>
       </c>
+      <c r="N25" s="65" t="n"/>
       <c r="O25" s="65" t="n"/>
     </row>
     <row r="26">
@@ -3742,43 +3742,43 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B26" s="65" t="n"/>
+      <c r="B26" s="64" t="inlineStr">
+        <is>
+          <t>Marcos portafiltros</t>
+        </is>
+      </c>
       <c r="C26" s="65" t="n"/>
       <c r="D26" s="64" t="inlineStr">
         <is>
-          <t>Marcos portafiltros</t>
+          <t>Holding frames para prefiltro + filtro final con junta continua</t>
         </is>
       </c>
       <c r="E26" s="65" t="n"/>
-      <c r="F26" s="64" t="inlineStr">
-        <is>
-          <t>Holding frames para prefiltro + filtro final con junta continua</t>
-        </is>
-      </c>
-      <c r="G26" s="65" t="n"/>
-      <c r="H26" s="64" t="inlineStr">
+      <c r="F26" s="65" t="n"/>
+      <c r="G26" s="64" t="inlineStr">
         <is>
           <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
         </is>
       </c>
-      <c r="I26" s="65" t="n"/>
+      <c r="H26" s="65" t="n"/>
+      <c r="I26" s="64" t="inlineStr">
+        <is>
+          <t>1 juego</t>
+        </is>
+      </c>
       <c r="J26" s="64" t="inlineStr">
         <is>
-          <t>1 juego</t>
+          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
         </is>
       </c>
       <c r="K26" s="65" t="n"/>
-      <c r="L26" s="64" t="inlineStr">
-        <is>
-          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
-        </is>
-      </c>
-      <c r="M26" s="65" t="n"/>
-      <c r="N26" s="64" t="inlineStr">
+      <c r="L26" s="65" t="n"/>
+      <c r="M26" s="64" t="inlineStr">
         <is>
           <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
         </is>
       </c>
+      <c r="N26" s="65" t="n"/>
       <c r="O26" s="65" t="n"/>
     </row>
     <row r="27">
@@ -3787,43 +3787,43 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B27" s="65" t="n"/>
+      <c r="B27" s="64" t="inlineStr">
+        <is>
+          <t>Rejillas de exfiltración</t>
+        </is>
+      </c>
       <c r="C27" s="65" t="n"/>
       <c r="D27" s="64" t="inlineStr">
         <is>
-          <t>Rejillas de exfiltración</t>
+          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio; área libre ≥ 90 %</t>
         </is>
       </c>
       <c r="E27" s="65" t="n"/>
-      <c r="F27" s="64" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio; área libre ≥ 90 %</t>
-        </is>
-      </c>
-      <c r="G27" s="65" t="n"/>
-      <c r="H27" s="64" t="inlineStr">
+      <c r="F27" s="65" t="n"/>
+      <c r="G27" s="64" t="inlineStr">
         <is>
           <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
         </is>
       </c>
-      <c r="I27" s="65" t="n"/>
+      <c r="H27" s="65" t="n"/>
+      <c r="I27" s="64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J27" s="64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
         </is>
       </c>
       <c r="K27" s="65" t="n"/>
-      <c r="L27" s="64" t="inlineStr">
-        <is>
-          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
-        </is>
-      </c>
-      <c r="M27" s="65" t="n"/>
-      <c r="N27" s="64" t="inlineStr">
+      <c r="L27" s="65" t="n"/>
+      <c r="M27" s="64" t="inlineStr">
         <is>
           <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
+      <c r="N27" s="65" t="n"/>
       <c r="O27" s="65" t="n"/>
     </row>
     <row r="28">
@@ -3832,43 +3832,43 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B28" s="65" t="n"/>
+      <c r="B28" s="64" t="inlineStr">
+        <is>
+          <t>Malla anti-insectos</t>
+        </is>
+      </c>
       <c r="C28" s="65" t="n"/>
       <c r="D28" s="64" t="inlineStr">
         <is>
-          <t>Malla anti-insectos</t>
+          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
         </is>
       </c>
       <c r="E28" s="65" t="n"/>
-      <c r="F28" s="64" t="inlineStr">
-        <is>
-          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
-        </is>
-      </c>
-      <c r="G28" s="65" t="n"/>
-      <c r="H28" s="64" t="inlineStr">
+      <c r="F28" s="65" t="n"/>
+      <c r="G28" s="64" t="inlineStr">
         <is>
           <t>Inox 316</t>
         </is>
       </c>
-      <c r="I28" s="65" t="n"/>
+      <c r="H28" s="65" t="n"/>
+      <c r="I28" s="64" t="inlineStr">
+        <is>
+          <t>3 (una por rejilla)</t>
+        </is>
+      </c>
       <c r="J28" s="64" t="inlineStr">
         <is>
-          <t>3 (una por rejilla)</t>
+          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
         </is>
       </c>
       <c r="K28" s="65" t="n"/>
-      <c r="L28" s="64" t="inlineStr">
-        <is>
-          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
-        </is>
-      </c>
-      <c r="M28" s="65" t="n"/>
-      <c r="N28" s="64" t="inlineStr">
+      <c r="L28" s="65" t="n"/>
+      <c r="M28" s="64" t="inlineStr">
         <is>
           <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
         </is>
       </c>
+      <c r="N28" s="65" t="n"/>
       <c r="O28" s="65" t="n"/>
     </row>
     <row r="29">
@@ -3877,43 +3877,43 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B29" s="65" t="n"/>
+      <c r="B29" s="64" t="inlineStr">
+        <is>
+          <t>Damper de alivio barométrico</t>
+        </is>
+      </c>
       <c r="C29" s="65" t="n"/>
       <c r="D29" s="64" t="inlineStr">
         <is>
-          <t>Damper de alivio barométrico</t>
+          <t>Contrapeso ajustable 12-75 Pa (0.05-0.30 in c.a.); set-point +25 Pa; V facial ≤ 2.5 m/s al caudal de alivio; AMCA 500-D</t>
         </is>
       </c>
       <c r="E29" s="65" t="n"/>
-      <c r="F29" s="64" t="inlineStr">
-        <is>
-          <t>Contrapeso ajustable 12-75 Pa (0.05-0.30 in c.a.); set-point +25 Pa; V facial ≤ 2.5 m/s al caudal de alivio; AMCA 500-D</t>
-        </is>
-      </c>
-      <c r="G29" s="65" t="n"/>
-      <c r="H29" s="64" t="inlineStr">
+      <c r="F29" s="65" t="n"/>
+      <c r="G29" s="64" t="inlineStr">
         <is>
           <t>Aluminio extruido 6063-T5 o línea severe-environment; no galvanizado</t>
         </is>
       </c>
-      <c r="I29" s="65" t="n"/>
+      <c r="H29" s="65" t="n"/>
+      <c r="I29" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J29" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Greenheck SEBR-10; Ruskin CBD6/BD6; Nailor 1390CB-EAF</t>
         </is>
       </c>
       <c r="K29" s="65" t="n"/>
-      <c r="L29" s="64" t="inlineStr">
-        <is>
-          <t>Greenheck SEBR-10; Ruskin CBD6/BD6; Nailor 1390CB-EAF</t>
-        </is>
-      </c>
-      <c r="M29" s="65" t="n"/>
-      <c r="N29" s="64" t="inlineStr">
+      <c r="L29" s="65" t="n"/>
+      <c r="M29" s="64" t="inlineStr">
         <is>
           <t>SEBR-10 (PDF) (https://content.greenheck.com/public/DAMProd/Original/10002/SEBR10Series_submittal.pdf); Ruskin BD6 (https://www.ruskin.com/model/bd6); Nailor 1390CB (PDF) (https://nailor.com/sites/default/files/documents/1390CB_B_0_0.pdf)</t>
         </is>
       </c>
+      <c r="N29" s="65" t="n"/>
       <c r="O29" s="65" t="n"/>
     </row>
     <row r="30">
@@ -3922,43 +3922,43 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B30" s="65" t="n"/>
+      <c r="B30" s="64" t="inlineStr">
+        <is>
+          <t>Transmisor de presión diferencial</t>
+        </is>
+      </c>
       <c r="C30" s="65" t="n"/>
       <c r="D30" s="64" t="inlineStr">
         <is>
-          <t>Transmisor de presión diferencial</t>
+          <t>Rango 0-62.5 Pa (0-0.25 in c.a.); salida 4-20 mA, 2 hilos; constante de tiempo ajustable</t>
         </is>
       </c>
       <c r="E30" s="65" t="n"/>
-      <c r="F30" s="64" t="inlineStr">
-        <is>
-          <t>Rango 0-62.5 Pa (0-0.25 in c.a.); salida 4-20 mA, 2 hilos; constante de tiempo ajustable</t>
-        </is>
-      </c>
-      <c r="G30" s="65" t="n"/>
-      <c r="H30" s="64" t="inlineStr">
+      <c r="F30" s="65" t="n"/>
+      <c r="G30" s="64" t="inlineStr">
         <is>
           <t>Gabinete NEMA 4X (IP66); montaje interior con toma exterior protegida</t>
         </is>
       </c>
-      <c r="I30" s="65" t="n"/>
+      <c r="H30" s="65" t="n"/>
+      <c r="I30" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dwyer MS-121(-LCD) Magnesense; Setra 264; Siemens QBM2130-1U</t>
         </is>
       </c>
       <c r="K30" s="65" t="n"/>
-      <c r="L30" s="64" t="inlineStr">
-        <is>
-          <t>Dwyer MS-121(-LCD) Magnesense; Setra 264; Siemens QBM2130-1U</t>
-        </is>
-      </c>
-      <c r="M30" s="65" t="n"/>
-      <c r="N30" s="64" t="inlineStr">
+      <c r="L30" s="65" t="n"/>
+      <c r="M30" s="64" t="inlineStr">
         <is>
           <t>Dwyer MS (PDF) (https://www.transcat.com/media/pdf/MS_cat.pdf); Setra 264 (PDF) (https://www.setra.com/hubfs/Product_Data_Sheets/Setra_Model_264_Data_Sheet.pdf)</t>
         </is>
       </c>
+      <c r="N30" s="65" t="n"/>
       <c r="O30" s="65" t="n"/>
     </row>
     <row r="31">
@@ -3967,43 +3967,43 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B31" s="65" t="n"/>
+      <c r="B31" s="64" t="inlineStr">
+        <is>
+          <t>Manómetro diferencial de lectura local</t>
+        </is>
+      </c>
       <c r="C31" s="65" t="n"/>
       <c r="D31" s="64" t="inlineStr">
         <is>
-          <t>Manómetro diferencial de lectura local</t>
+          <t>Magnehelic 2000-00, rango 0-62 Pa (0-0.25 in c.a.); ±2 % FS</t>
         </is>
       </c>
       <c r="E31" s="65" t="n"/>
-      <c r="F31" s="64" t="inlineStr">
-        <is>
-          <t>Magnehelic 2000-00, rango 0-62 Pa (0-0.25 in c.a.); ±2 % FS</t>
-        </is>
-      </c>
-      <c r="G31" s="65" t="n"/>
-      <c r="H31" s="64" t="inlineStr">
+      <c r="F31" s="65" t="n"/>
+      <c r="G31" s="64" t="inlineStr">
         <is>
           <t>Caja aluminio (niebla salina 168 h); opción bisel inox; montaje interior</t>
         </is>
       </c>
-      <c r="I31" s="65" t="n"/>
+      <c r="H31" s="65" t="n"/>
+      <c r="I31" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dwyer Magnehelic 2000-00 (Vía Industrial, RS Importaciones, SICO Global, Bogotá)</t>
         </is>
       </c>
       <c r="K31" s="65" t="n"/>
-      <c r="L31" s="64" t="inlineStr">
-        <is>
-          <t>Dwyer Magnehelic 2000-00 (Vía Industrial, RS Importaciones, SICO Global, Bogotá)</t>
-        </is>
-      </c>
-      <c r="M31" s="65" t="n"/>
-      <c r="N31" s="64" t="inlineStr">
+      <c r="L31" s="65" t="n"/>
+      <c r="M31" s="64" t="inlineStr">
         <is>
           <t>Tabla serie 2000 (https://skilltech.com.br/produto/manometro-para-pressao-diferencial-magnehelic-serie-2000/); Vía Industrial (https://www.viaindustrial.com/dwyer/marca/)</t>
         </is>
       </c>
+      <c r="N31" s="65" t="n"/>
       <c r="O31" s="65" t="n"/>
     </row>
     <row r="32">
@@ -4012,43 +4012,43 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="65" t="n"/>
+      <c r="B32" s="64" t="inlineStr">
+        <is>
+          <t>Controlador / lógica de alarmas</t>
+        </is>
+      </c>
       <c r="C32" s="65" t="n"/>
       <c r="D32" s="64" t="inlineStr">
         <is>
-          <t>Controlador / lógica de alarmas</t>
+          <t>Alarma baja +12.5 Pa y alta +40 Pa desde la señal 4-20 mA; retardo 30-60 s</t>
         </is>
       </c>
       <c r="E32" s="65" t="n"/>
-      <c r="F32" s="64" t="inlineStr">
-        <is>
-          <t>Alarma baja +12.5 Pa y alta +40 Pa desde la señal 4-20 mA; retardo 30-60 s</t>
-        </is>
-      </c>
-      <c r="G32" s="65" t="n"/>
-      <c r="H32" s="64" t="inlineStr">
+      <c r="F32" s="65" t="n"/>
+      <c r="G32" s="64" t="inlineStr">
         <is>
           <t>Integración al PLC/BMS del cliente o relés autónomos</t>
         </is>
       </c>
-      <c r="I32" s="65" t="n"/>
+      <c r="H32" s="65" t="n"/>
+      <c r="I32" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J32" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PLC del cliente (por confirmar); alternativa autónoma Dwyer Photohelic 3000MR-00AV</t>
         </is>
       </c>
       <c r="K32" s="65" t="n"/>
-      <c r="L32" s="64" t="inlineStr">
-        <is>
-          <t>PLC del cliente (por confirmar); alternativa autónoma Dwyer Photohelic 3000MR-00AV</t>
-        </is>
-      </c>
-      <c r="M32" s="65" t="n"/>
-      <c r="N32" s="64" t="inlineStr">
+      <c r="L32" s="65" t="n"/>
+      <c r="M32" s="64" t="inlineStr">
         <is>
           <t>Northeast Controls — Photohelic (https://nciweb.net/pressure1.htm)</t>
         </is>
       </c>
+      <c r="N32" s="65" t="n"/>
       <c r="O32" s="65" t="n"/>
     </row>
     <row r="33">
@@ -4057,43 +4057,43 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B33" s="65" t="n"/>
+      <c r="B33" s="64" t="inlineStr">
+        <is>
+          <t>Toma de referencia exterior</t>
+        </is>
+      </c>
       <c r="C33" s="65" t="n"/>
       <c r="D33" s="64" t="inlineStr">
         <is>
-          <t>Toma de referencia exterior</t>
+          <t>Caja estática de pared orientada a sotavento; tubo de impulso con purga/filtro de membrana</t>
         </is>
       </c>
       <c r="E33" s="65" t="n"/>
-      <c r="F33" s="64" t="inlineStr">
-        <is>
-          <t>Caja estática de pared orientada a sotavento; tubo de impulso con purga/filtro de membrana</t>
-        </is>
-      </c>
-      <c r="G33" s="65" t="n"/>
-      <c r="H33" s="64" t="inlineStr">
+      <c r="F33" s="65" t="n"/>
+      <c r="G33" s="64" t="inlineStr">
         <is>
           <t>Inox 316; conexiones 1/8 in NPT con sellante compatible</t>
         </is>
       </c>
-      <c r="I33" s="65" t="n"/>
+      <c r="H33" s="65" t="n"/>
+      <c r="I33" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Dwyer A-417 o fabricación local inox 316 (dato típico)</t>
         </is>
       </c>
       <c r="K33" s="65" t="n"/>
-      <c r="L33" s="64" t="inlineStr">
-        <is>
-          <t>Dwyer A-417 o fabricación local inox 316 (dato típico)</t>
-        </is>
-      </c>
-      <c r="M33" s="65" t="n"/>
-      <c r="N33" s="64" t="inlineStr">
+      <c r="L33" s="65" t="n"/>
+      <c r="M33" s="64" t="inlineStr">
         <is>
           <t>Dwyer MS (PDF) (https://www.transcat.com/media/pdf/MS_cat.pdf)</t>
         </is>
       </c>
+      <c r="N33" s="65" t="n"/>
       <c r="O33" s="65" t="n"/>
     </row>
     <row r="34">
@@ -4102,43 +4102,43 @@
           <t>13</t>
         </is>
       </c>
-      <c r="B34" s="65" t="n"/>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>Soportes y ferretería</t>
+        </is>
+      </c>
       <c r="C34" s="65" t="n"/>
       <c r="D34" s="64" t="inlineStr">
         <is>
-          <t>Soportes y ferretería</t>
+          <t>Soportes de ventilador, rejillas, damper e instrumentos; pernos, tuercas, arandelas</t>
         </is>
       </c>
       <c r="E34" s="65" t="n"/>
-      <c r="F34" s="64" t="inlineStr">
-        <is>
-          <t>Soportes de ventilador, rejillas, damper e instrumentos; pernos, tuercas, arandelas</t>
-        </is>
-      </c>
-      <c r="G34" s="65" t="n"/>
-      <c r="H34" s="64" t="inlineStr">
+      <c r="F34" s="65" t="n"/>
+      <c r="G34" s="64" t="inlineStr">
         <is>
           <t>Inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
         </is>
       </c>
-      <c r="I34" s="65" t="n"/>
+      <c r="H34" s="65" t="n"/>
+      <c r="I34" s="64" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
       <c r="J34" s="64" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>Suministro nacional genérico A4</t>
         </is>
       </c>
       <c r="K34" s="65" t="n"/>
-      <c r="L34" s="64" t="inlineStr">
-        <is>
-          <t>Suministro nacional genérico A4</t>
-        </is>
-      </c>
-      <c r="M34" s="65" t="n"/>
-      <c r="N34" s="64" t="inlineStr">
+      <c r="L34" s="65" t="n"/>
+      <c r="M34" s="64" t="inlineStr">
         <is>
           <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
         </is>
       </c>
+      <c r="N34" s="65" t="n"/>
       <c r="O34" s="65" t="n"/>
     </row>
     <row r="35">
@@ -4147,43 +4147,43 @@
           <t>14</t>
         </is>
       </c>
-      <c r="B35" s="65" t="n"/>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>Conexión flexible ventilador-pasamuros</t>
+        </is>
+      </c>
       <c r="C35" s="65" t="n"/>
       <c r="D35" s="64" t="inlineStr">
         <is>
-          <t>Conexión flexible ventilador-pasamuros</t>
+          <t>Ancho ≥ 100 mm; bandas de amarre inox 316 cal. 24</t>
         </is>
       </c>
       <c r="E35" s="65" t="n"/>
-      <c r="F35" s="64" t="inlineStr">
-        <is>
-          <t>Ancho ≥ 100 mm; bandas de amarre inox 316 cal. 24</t>
-        </is>
-      </c>
-      <c r="G35" s="65" t="n"/>
-      <c r="H35" s="64" t="inlineStr">
+      <c r="F35" s="65" t="n"/>
+      <c r="G35" s="64" t="inlineStr">
         <is>
           <t>Hipalón (CSM); alternativa clorobutilo; no PVC estándar</t>
         </is>
       </c>
-      <c r="I35" s="65" t="n"/>
+      <c r="H35" s="65" t="n"/>
+      <c r="I35" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J35" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Hardcast Hypalon; Proco serie 500</t>
         </is>
       </c>
       <c r="K35" s="65" t="n"/>
-      <c r="L35" s="64" t="inlineStr">
-        <is>
-          <t>Hardcast Hypalon; Proco serie 500</t>
-        </is>
-      </c>
-      <c r="M35" s="65" t="n"/>
-      <c r="N35" s="64" t="inlineStr">
+      <c r="L35" s="65" t="n"/>
+      <c r="M35" s="64" t="inlineStr">
         <is>
           <t>Hardcast (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf)</t>
         </is>
       </c>
+      <c r="N35" s="65" t="n"/>
       <c r="O35" s="65" t="n"/>
     </row>
     <row r="36">
@@ -4192,43 +4192,43 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B36" s="65" t="n"/>
+      <c r="B36" s="64" t="inlineStr">
+        <is>
+          <t>Selladores</t>
+        </is>
+      </c>
       <c r="C36" s="65" t="n"/>
       <c r="D36" s="64" t="inlineStr">
         <is>
-          <t>Selladores</t>
+          <t>Sellado de pasamuros, marcos y empalmes</t>
         </is>
       </c>
       <c r="E36" s="65" t="n"/>
-      <c r="F36" s="64" t="inlineStr">
-        <is>
-          <t>Sellado de pasamuros, marcos y empalmes</t>
-        </is>
-      </c>
-      <c r="G36" s="65" t="n"/>
-      <c r="H36" s="64" t="inlineStr">
+      <c r="F36" s="65" t="n"/>
+      <c r="G36" s="64" t="inlineStr">
         <is>
           <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
         </is>
       </c>
-      <c r="I36" s="65" t="n"/>
+      <c r="H36" s="65" t="n"/>
+      <c r="I36" s="64" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
       <c r="J36" s="64" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
         </is>
       </c>
       <c r="K36" s="65" t="n"/>
-      <c r="L36" s="64" t="inlineStr">
-        <is>
-          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
-        </is>
-      </c>
-      <c r="M36" s="65" t="n"/>
-      <c r="N36" s="64" t="inlineStr">
+      <c r="L36" s="65" t="n"/>
+      <c r="M36" s="64" t="inlineStr">
         <is>
           <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
         </is>
       </c>
+      <c r="N36" s="65" t="n"/>
       <c r="O36" s="65" t="n"/>
     </row>
     <row r="37">
@@ -4237,43 +4237,43 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B37" s="65" t="n"/>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>Protecciones eléctricas y tablero</t>
+        </is>
+      </c>
       <c r="C37" s="65" t="n"/>
       <c r="D37" s="64" t="inlineStr">
         <is>
-          <t>Protecciones eléctricas y tablero</t>
+          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
         </is>
       </c>
       <c r="E37" s="65" t="n"/>
-      <c r="F37" s="64" t="inlineStr">
-        <is>
-          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
-        </is>
-      </c>
-      <c r="G37" s="65" t="n"/>
-      <c r="H37" s="64" t="inlineStr">
+      <c r="F37" s="65" t="n"/>
+      <c r="G37" s="64" t="inlineStr">
         <is>
           <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
         </is>
       </c>
-      <c r="I37" s="65" t="n"/>
+      <c r="H37" s="65" t="n"/>
+      <c r="I37" s="64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J37" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
         </is>
       </c>
       <c r="K37" s="65" t="n"/>
-      <c r="L37" s="64" t="inlineStr">
-        <is>
-          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
-        </is>
-      </c>
-      <c r="M37" s="65" t="n"/>
-      <c r="N37" s="64" t="inlineStr">
+      <c r="L37" s="65" t="n"/>
+      <c r="M37" s="64" t="inlineStr">
         <is>
           <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
         </is>
       </c>
+      <c r="N37" s="65" t="n"/>
       <c r="O37" s="65" t="n"/>
     </row>
     <row r="38">
@@ -4282,43 +4282,43 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B38" s="65" t="n"/>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>Cableado y canalización</t>
+        </is>
+      </c>
       <c r="C38" s="65" t="n"/>
       <c r="D38" s="64" t="inlineStr">
         <is>
-          <t>Cableado y canalización</t>
+          <t>Circuito motor 1.0 HP + circuito instrumentación 4-20 mA apantallado</t>
         </is>
       </c>
       <c r="E38" s="65" t="n"/>
-      <c r="F38" s="64" t="inlineStr">
-        <is>
-          <t>Circuito motor 1.0 HP + circuito instrumentación 4-20 mA apantallado</t>
-        </is>
-      </c>
-      <c r="G38" s="65" t="n"/>
-      <c r="H38" s="64" t="inlineStr">
+      <c r="F38" s="65" t="n"/>
+      <c r="G38" s="64" t="inlineStr">
         <is>
           <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
         </is>
       </c>
-      <c r="I38" s="65" t="n"/>
+      <c r="H38" s="65" t="n"/>
+      <c r="I38" s="64" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
       <c r="J38" s="64" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>Suministro nacional certificado RETIE</t>
         </is>
       </c>
       <c r="K38" s="65" t="n"/>
-      <c r="L38" s="64" t="inlineStr">
-        <is>
-          <t>Suministro nacional certificado RETIE</t>
-        </is>
-      </c>
-      <c r="M38" s="65" t="n"/>
-      <c r="N38" s="64" t="inlineStr">
+      <c r="L38" s="65" t="n"/>
+      <c r="M38" s="64" t="inlineStr">
         <is>
           <t>Requisito RETIE / NTC 2050</t>
         </is>
       </c>
+      <c r="N38" s="65" t="n"/>
       <c r="O38" s="65" t="n"/>
     </row>
     <row r="41">
@@ -4354,153 +4354,117 @@
     </row>
     <row r="48"/>
   </sheetData>
-  <mergeCells count="146">
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="A26:C26"/>
+  <mergeCells count="110">
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="J25:L25"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="N5:O5"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="M24:O24"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="J29:L29"/>
     <mergeCell ref="A15:O15"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="G38:H38"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A44:O46"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="J28:L28"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="J30:L30"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="D32:F32"/>
     <mergeCell ref="A41:O41"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="G37:H37"/>
     <mergeCell ref="A8:O8"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A19:O19"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D35:F35"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="J34:L34"/>
     <mergeCell ref="A42:O43"/>
     <mergeCell ref="A47:O48"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J31:L31"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="G28:H28"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="G30:H30"/>
     <mergeCell ref="A16:O17"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="G31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/build/lis/P2437-HV-LIS-001 REV0.xlsx
+++ b/build/lis/P2437-HV-LIS-001 REV0.xlsx
@@ -1412,7 +1412,7 @@
       <c r="Y5" s="54" t="n"/>
       <c r="Z5" s="31" t="inlineStr">
         <is>
-          <t>LISTADO DE EQUIPOS Y MATERIALES (BOQ): SISTEMA DE VENTILACIÓN Y PRESURIZACIÓN POSITIVA</t>
+          <t>LISTADO DE EQUIPOS Y MATERIALES (BOQ): SISTEMA DE VENTILACIÓN DEL LABORATORIO</t>
         </is>
       </c>
       <c r="AA5" s="44" t="n"/>
@@ -3221,7 +3221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.61328125" customWidth="1" min="1" max="1"/>
@@ -3443,14 +3443,14 @@
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="58" t="inlineStr">
         <is>
-          <t>LISTADO DE EQUIPOS Y MATERIALES (BOQ): SISTEMA DE VENTILACIÓN Y PRESURIZACIÓN POSITIVA</t>
+          <t>LISTADO DE EQUIPOS Y MATERIALES (BOQ): SISTEMA DE VENTILACIÓN DEL LABORATORIO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="59" t="inlineStr">
         <is>
-          <t>Listado de equipos y materiales (BOQ): sistema de ventilación y presurización positiva</t>
+          <t>Listado de equipos y materiales (BOQ): sistema de ventilación del laboratorio</t>
         </is>
       </c>
     </row>
@@ -3464,165 +3464,127 @@
     <row r="11">
       <c r="A11" s="60" t="inlineStr">
         <is>
-          <t>Documento: listado_equipos.md — Revisión 0</t>
+          <t>Documento: listado_equipos.md — Revisión 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="60" t="inlineStr">
         <is>
-          <t>Fecha: 2026-07-23</t>
+          <t>Fecha: 2026-07-27 (fuentes consultadas el 2026-07-23; frente de ventiladores axiales ampliado el 2026-07-27)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="60" t="inlineStr">
         <is>
-          <t>Base: informe_investigacion.md (misma revisión); punto de diseño 3 840 m³/h @ 190 Pa en el sitio (260 Pa equivalente de catálogo, ρ = 1.2 kg/m³).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="61" t="inlineStr">
+          <t>Base: informe_investigacion.md (misma revisión); punto de diseño 3 840 m³/h @ 165 Pa en el sitio (225 Pa equivalente de catálogo, ρ = 1.2 kg/m³).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="60" t="inlineStr">
+        <is>
+          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial, sin instrumentación de presión diferencial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="61" t="inlineStr">
         <is>
           <t>1. Alcance del suministro</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="60" t="inlineStr">
-        <is>
-          <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, exfiltración, control de presurización, instrumentación y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="19">
-      <c r="A19" s="61" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="60" t="inlineStr">
+        <is>
+          <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="20">
+      <c r="A20" s="61" t="inlineStr">
         <is>
           <t>2. Tabla de equipos y materiales</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="62" t="inlineStr">
-        <is>
-          <t>Tabla 1. BOQ del sistema de presurización positiva (consulta de fuentes 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" s="63" t="inlineStr">
+      <c r="A21" s="62" t="inlineStr">
+        <is>
+          <t>Tabla 1. BOQ del sistema de ventilación (consulta de fuentes 2026-07-23, ampliada 2026-07-27).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="63" t="inlineStr">
         <is>
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B21" s="63" t="inlineStr">
+      <c r="B22" s="63" t="inlineStr">
         <is>
           <t>Función</t>
         </is>
       </c>
-      <c r="C21" s="63" t="n"/>
-      <c r="D21" s="63" t="inlineStr">
+      <c r="C22" s="63" t="n"/>
+      <c r="D22" s="63" t="inlineStr">
         <is>
           <t>Especificación clave</t>
         </is>
       </c>
-      <c r="E21" s="63" t="n"/>
-      <c r="F21" s="63" t="n"/>
-      <c r="G21" s="63" t="inlineStr">
+      <c r="E22" s="63" t="n"/>
+      <c r="F22" s="63" t="n"/>
+      <c r="G22" s="63" t="inlineStr">
         <is>
           <t>Material / compatibilidad corrosiva</t>
         </is>
       </c>
-      <c r="H21" s="63" t="n"/>
-      <c r="I21" s="63" t="inlineStr">
+      <c r="H22" s="63" t="n"/>
+      <c r="I22" s="63" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="J21" s="63" t="inlineStr">
+      <c r="J22" s="63" t="inlineStr">
         <is>
           <t>Candidatos comerciales (fabricante/modelo)</t>
         </is>
       </c>
-      <c r="K21" s="63" t="n"/>
-      <c r="L21" s="63" t="n"/>
-      <c r="M21" s="63" t="inlineStr">
+      <c r="K22" s="63" t="n"/>
+      <c r="L22" s="63" t="n"/>
+      <c r="M22" s="63" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N21" s="63" t="n"/>
-      <c r="O21" s="63" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B22" s="64" t="inlineStr">
-        <is>
-          <t>Ventilador de impulsión</t>
-        </is>
-      </c>
-      <c r="C22" s="65" t="n"/>
-      <c r="D22" s="64" t="inlineStr">
-        <is>
-          <t>Centrífugo álabes curvados atrás; 3 840 m³/h @ 260 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 190 Pa en sitio; AMCA 210; Spark A</t>
-        </is>
-      </c>
-      <c r="E22" s="65" t="n"/>
-      <c r="F22" s="65" t="n"/>
-      <c r="G22" s="64" t="inlineStr">
-        <is>
-          <t>PRFV viniléster (ASTM C582/D4167); alternativa PP</t>
-        </is>
-      </c>
-      <c r="H22" s="65" t="n"/>
-      <c r="I22" s="64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" s="64" t="inlineStr">
-        <is>
-          <t>Greenheck BCSW-FRP (vía Prime Lines HVAC, Bogotá); NYB FRP Fume Exhauster; Sodeca CPV; Plastec 25/30; S&amp;P línea PP</t>
-        </is>
-      </c>
-      <c r="K22" s="65" t="n"/>
-      <c r="L22" s="65" t="n"/>
-      <c r="M22" s="64" t="inlineStr">
-        <is>
-          <t>BCSW-FRP (https://content.greenheck.com/public/DAMProd/Original/10002/BCSWFRP_catalog.pdf); NYB (https://www.nyb.com/frp-fume-exhauster/); Sodeca CPV (https://www.sodeca.com/es/sistemas-de-ventilacion-extraccion/cpv-p1000000071)</t>
-        </is>
-      </c>
-      <c r="N22" s="65" t="n"/>
-      <c r="O22" s="65" t="n"/>
+      <c r="N22" s="63" t="n"/>
+      <c r="O22" s="63" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B23" s="64" t="inlineStr">
         <is>
-          <t>Motor del ventilador</t>
+          <t>Ventilador de impulsión</t>
         </is>
       </c>
       <c r="C23" s="65" t="n"/>
       <c r="D23" s="64" t="inlineStr">
         <is>
-          <t>1.0 HP, TEFC, 1 800 RPM (4 polos), 60 Hz, clase F, IP55 mín., severe duty epóxico; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
+          <t>Axial tubeaxial, transmisión por bandas; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; tamaño/RPM por confirmar con proveedor</t>
         </is>
       </c>
       <c r="E23" s="65" t="n"/>
       <c r="F23" s="65" t="n"/>
       <c r="G23" s="64" t="inlineStr">
         <is>
-          <t>Pintura epóxica + protección interna anticorrosiva; motor fuera de la corriente</t>
+          <t>PRFV viniléster (ASTM C582/D4167); motor fuera de la corriente de aire</t>
         </is>
       </c>
       <c r="H23" s="65" t="n"/>
@@ -3633,14 +3595,14 @@
       </c>
       <c r="J23" s="64" t="inlineStr">
         <is>
-          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
+          <t>Aerovent FBD (Twin City Fan, Catálogo 185); Greenheck VAB (vaneaxial epóxico, Prime Lines HVAC, Bogotá); Sodeca HCT/HGT anticorrosivo PRFV; NYB FRP tubeaxial; Plastec PP</t>
         </is>
       </c>
       <c r="K23" s="65" t="n"/>
       <c r="L23" s="65" t="n"/>
       <c r="M23" s="64" t="inlineStr">
         <is>
-          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
+          <t>Aerovent Cat. 185 (PDF) (https://www.aerovent.com/wp-content/uploads/sites/2/2024/07/Fiberglass-Fans-Axial-Flow-Model-FBD-FDP-FRV-TFBD-VTFBD-Catalog-185.pdf); Greenheck VAB/VAD (PDF) (https://content.greenheck.com/public/DAMProd/Original/10003/vane_axial_catalog.pdf); Sodeca (https://www.sodeca.com)</t>
         </is>
       </c>
       <c r="N23" s="65" t="n"/>
@@ -3649,43 +3611,43 @@
     <row r="24">
       <c r="A24" s="64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" s="64" t="inlineStr">
         <is>
-          <t>Prefiltro (etapa 1)</t>
+          <t>Motor del ventilador</t>
         </is>
       </c>
       <c r="C24" s="65" t="n"/>
       <c r="D24" s="64" t="inlineStr">
         <is>
-          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
+          <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC, 1 800 RPM (4 polos), 60 Hz, clase F, IP55 mín., severe duty epóxico; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
         </is>
       </c>
       <c r="E24" s="65" t="n"/>
       <c r="F24" s="65" t="n"/>
       <c r="G24" s="64" t="inlineStr">
         <is>
-          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
+          <t>Pintura epóxica + protección interna anticorrosiva; motor fuera de la corriente (transmisión por bandas)</t>
         </is>
       </c>
       <c r="H24" s="65" t="n"/>
       <c r="I24" s="64" t="inlineStr">
         <is>
-          <t>1 (+ repuestos)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" s="64" t="inlineStr">
         <is>
-          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
+          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
         </is>
       </c>
       <c r="K24" s="65" t="n"/>
       <c r="L24" s="65" t="n"/>
       <c r="M24" s="64" t="inlineStr">
         <is>
-          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
+          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
         </is>
       </c>
       <c r="N24" s="65" t="n"/>
@@ -3694,25 +3656,25 @@
     <row r="25">
       <c r="A25" s="64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B25" s="64" t="inlineStr">
         <is>
-          <t>Filtro final (etapa 2)</t>
+          <t>Prefiltro (etapa 1)</t>
         </is>
       </c>
       <c r="C25" s="65" t="n"/>
       <c r="D25" s="64" t="inlineStr">
         <is>
-          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
+          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
         </is>
       </c>
       <c r="E25" s="65" t="n"/>
       <c r="F25" s="65" t="n"/>
       <c r="G25" s="64" t="inlineStr">
         <is>
-          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
+          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
         </is>
       </c>
       <c r="H25" s="65" t="n"/>
@@ -3723,14 +3685,14 @@
       </c>
       <c r="J25" s="64" t="inlineStr">
         <is>
-          <t>Camfil Durafil ES2 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
+          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
         </is>
       </c>
       <c r="K25" s="65" t="n"/>
       <c r="L25" s="65" t="n"/>
       <c r="M25" s="64" t="inlineStr">
         <is>
-          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
+          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
         </is>
       </c>
       <c r="N25" s="65" t="n"/>
@@ -3739,43 +3701,43 @@
     <row r="26">
       <c r="A26" s="64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B26" s="64" t="inlineStr">
         <is>
-          <t>Marcos portafiltros</t>
+          <t>Filtro final (etapa 2)</t>
         </is>
       </c>
       <c r="C26" s="65" t="n"/>
       <c r="D26" s="64" t="inlineStr">
         <is>
-          <t>Holding frames para prefiltro + filtro final con junta continua</t>
+          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
         </is>
       </c>
       <c r="E26" s="65" t="n"/>
       <c r="F26" s="65" t="n"/>
       <c r="G26" s="64" t="inlineStr">
         <is>
-          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
+          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
         </is>
       </c>
       <c r="H26" s="65" t="n"/>
       <c r="I26" s="64" t="inlineStr">
         <is>
-          <t>1 juego</t>
+          <t>1 (+ repuestos)</t>
         </is>
       </c>
       <c r="J26" s="64" t="inlineStr">
         <is>
-          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
+          <t>Camfil Durafil ES2 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
         </is>
       </c>
       <c r="K26" s="65" t="n"/>
       <c r="L26" s="65" t="n"/>
       <c r="M26" s="64" t="inlineStr">
         <is>
-          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
+          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
         </is>
       </c>
       <c r="N26" s="65" t="n"/>
@@ -3784,43 +3746,43 @@
     <row r="27">
       <c r="A27" s="64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B27" s="64" t="inlineStr">
         <is>
-          <t>Rejillas de exfiltración</t>
+          <t>Marcos portafiltros</t>
         </is>
       </c>
       <c r="C27" s="65" t="n"/>
       <c r="D27" s="64" t="inlineStr">
         <is>
-          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio; área libre ≥ 90 %</t>
+          <t>Holding frames para prefiltro + filtro final con junta continua</t>
         </is>
       </c>
       <c r="E27" s="65" t="n"/>
       <c r="F27" s="65" t="n"/>
       <c r="G27" s="64" t="inlineStr">
         <is>
-          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
+          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
         </is>
       </c>
       <c r="H27" s="65" t="n"/>
       <c r="I27" s="64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1 juego</t>
         </is>
       </c>
       <c r="J27" s="64" t="inlineStr">
         <is>
-          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
+          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
         </is>
       </c>
       <c r="K27" s="65" t="n"/>
       <c r="L27" s="65" t="n"/>
       <c r="M27" s="64" t="inlineStr">
         <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
         </is>
       </c>
       <c r="N27" s="65" t="n"/>
@@ -3829,43 +3791,43 @@
     <row r="28">
       <c r="A28" s="64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B28" s="64" t="inlineStr">
         <is>
-          <t>Malla anti-insectos</t>
+          <t>Rejillas de descarga</t>
         </is>
       </c>
       <c r="C28" s="65" t="n"/>
       <c r="D28" s="64" t="inlineStr">
         <is>
-          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
+          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
         </is>
       </c>
       <c r="E28" s="65" t="n"/>
       <c r="F28" s="65" t="n"/>
       <c r="G28" s="64" t="inlineStr">
         <is>
-          <t>Inox 316</t>
+          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
         </is>
       </c>
       <c r="H28" s="65" t="n"/>
       <c r="I28" s="64" t="inlineStr">
         <is>
-          <t>3 (una por rejilla)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" s="64" t="inlineStr">
         <is>
-          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
+          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
         </is>
       </c>
       <c r="K28" s="65" t="n"/>
       <c r="L28" s="65" t="n"/>
       <c r="M28" s="64" t="inlineStr">
         <is>
-          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
       <c r="N28" s="65" t="n"/>
@@ -3874,43 +3836,43 @@
     <row r="29">
       <c r="A29" s="64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B29" s="64" t="inlineStr">
         <is>
-          <t>Damper de alivio barométrico</t>
+          <t>Malla anti-insectos</t>
         </is>
       </c>
       <c r="C29" s="65" t="n"/>
       <c r="D29" s="64" t="inlineStr">
         <is>
-          <t>Contrapeso ajustable 12-75 Pa (0.05-0.30 in c.a.); set-point +25 Pa; V facial ≤ 2.5 m/s al caudal de alivio; AMCA 500-D</t>
+          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
         </is>
       </c>
       <c r="E29" s="65" t="n"/>
       <c r="F29" s="65" t="n"/>
       <c r="G29" s="64" t="inlineStr">
         <is>
-          <t>Aluminio extruido 6063-T5 o línea severe-environment; no galvanizado</t>
+          <t>Inox 316</t>
         </is>
       </c>
       <c r="H29" s="65" t="n"/>
       <c r="I29" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3 (una por rejilla)</t>
         </is>
       </c>
       <c r="J29" s="64" t="inlineStr">
         <is>
-          <t>Greenheck SEBR-10; Ruskin CBD6/BD6; Nailor 1390CB-EAF</t>
+          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
         </is>
       </c>
       <c r="K29" s="65" t="n"/>
       <c r="L29" s="65" t="n"/>
       <c r="M29" s="64" t="inlineStr">
         <is>
-          <t>SEBR-10 (PDF) (https://content.greenheck.com/public/DAMProd/Original/10002/SEBR10Series_submittal.pdf); Ruskin BD6 (https://www.ruskin.com/model/bd6); Nailor 1390CB (PDF) (https://nailor.com/sites/default/files/documents/1390CB_B_0_0.pdf)</t>
+          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
         </is>
       </c>
       <c r="N29" s="65" t="n"/>
@@ -3919,43 +3881,43 @@
     <row r="30">
       <c r="A30" s="64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B30" s="64" t="inlineStr">
         <is>
-          <t>Transmisor de presión diferencial</t>
+          <t>Soportes y ferretería</t>
         </is>
       </c>
       <c r="C30" s="65" t="n"/>
       <c r="D30" s="64" t="inlineStr">
         <is>
-          <t>Rango 0-62.5 Pa (0-0.25 in c.a.); salida 4-20 mA, 2 hilos; constante de tiempo ajustable</t>
+          <t>Soportes de ventilador y rejillas; pernos, tuercas, arandelas</t>
         </is>
       </c>
       <c r="E30" s="65" t="n"/>
       <c r="F30" s="65" t="n"/>
       <c r="G30" s="64" t="inlineStr">
         <is>
-          <t>Gabinete NEMA 4X (IP66); montaje interior con toma exterior protegida</t>
+          <t>Inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
         </is>
       </c>
       <c r="H30" s="65" t="n"/>
       <c r="I30" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="J30" s="64" t="inlineStr">
         <is>
-          <t>Dwyer MS-121(-LCD) Magnesense; Setra 264; Siemens QBM2130-1U</t>
+          <t>Suministro nacional genérico A4</t>
         </is>
       </c>
       <c r="K30" s="65" t="n"/>
       <c r="L30" s="65" t="n"/>
       <c r="M30" s="64" t="inlineStr">
         <is>
-          <t>Dwyer MS (PDF) (https://www.transcat.com/media/pdf/MS_cat.pdf); Setra 264 (PDF) (https://www.setra.com/hubfs/Product_Data_Sheets/Setra_Model_264_Data_Sheet.pdf)</t>
+          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
         </is>
       </c>
       <c r="N30" s="65" t="n"/>
@@ -3964,25 +3926,25 @@
     <row r="31">
       <c r="A31" s="64" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B31" s="64" t="inlineStr">
         <is>
-          <t>Manómetro diferencial de lectura local</t>
+          <t>Conexión flexible ventilador-pasamuros</t>
         </is>
       </c>
       <c r="C31" s="65" t="n"/>
       <c r="D31" s="64" t="inlineStr">
         <is>
-          <t>Magnehelic 2000-00, rango 0-62 Pa (0-0.25 in c.a.); ±2 % FS</t>
+          <t>Ancho ≥ 100 mm; bandas de amarre inox 316 cal. 24</t>
         </is>
       </c>
       <c r="E31" s="65" t="n"/>
       <c r="F31" s="65" t="n"/>
       <c r="G31" s="64" t="inlineStr">
         <is>
-          <t>Caja aluminio (niebla salina 168 h); opción bisel inox; montaje interior</t>
+          <t>Hipalón (CSM); alternativa clorobutilo; no PVC estándar</t>
         </is>
       </c>
       <c r="H31" s="65" t="n"/>
@@ -3993,14 +3955,14 @@
       </c>
       <c r="J31" s="64" t="inlineStr">
         <is>
-          <t>Dwyer Magnehelic 2000-00 (Vía Industrial, RS Importaciones, SICO Global, Bogotá)</t>
+          <t>Hardcast Hypalon; Proco serie 500</t>
         </is>
       </c>
       <c r="K31" s="65" t="n"/>
       <c r="L31" s="65" t="n"/>
       <c r="M31" s="64" t="inlineStr">
         <is>
-          <t>Tabla serie 2000 (https://skilltech.com.br/produto/manometro-para-pressao-diferencial-magnehelic-serie-2000/); Vía Industrial (https://www.viaindustrial.com/dwyer/marca/)</t>
+          <t>Hardcast (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf)</t>
         </is>
       </c>
       <c r="N31" s="65" t="n"/>
@@ -4009,43 +3971,43 @@
     <row r="32">
       <c r="A32" s="64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" s="64" t="inlineStr">
         <is>
-          <t>Controlador / lógica de alarmas</t>
+          <t>Selladores</t>
         </is>
       </c>
       <c r="C32" s="65" t="n"/>
       <c r="D32" s="64" t="inlineStr">
         <is>
-          <t>Alarma baja +12.5 Pa y alta +40 Pa desde la señal 4-20 mA; retardo 30-60 s</t>
+          <t>Sellado de pasamuros, marcos y empalmes</t>
         </is>
       </c>
       <c r="E32" s="65" t="n"/>
       <c r="F32" s="65" t="n"/>
       <c r="G32" s="64" t="inlineStr">
         <is>
-          <t>Integración al PLC/BMS del cliente o relés autónomos</t>
+          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
         </is>
       </c>
       <c r="H32" s="65" t="n"/>
       <c r="I32" s="64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="J32" s="64" t="inlineStr">
         <is>
-          <t>PLC del cliente (por confirmar); alternativa autónoma Dwyer Photohelic 3000MR-00AV</t>
+          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
         </is>
       </c>
       <c r="K32" s="65" t="n"/>
       <c r="L32" s="65" t="n"/>
       <c r="M32" s="64" t="inlineStr">
         <is>
-          <t>Northeast Controls — Photohelic (https://nciweb.net/pressure1.htm)</t>
+          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
         </is>
       </c>
       <c r="N32" s="65" t="n"/>
@@ -4054,25 +4016,25 @@
     <row r="33">
       <c r="A33" s="64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" s="64" t="inlineStr">
         <is>
-          <t>Toma de referencia exterior</t>
+          <t>Protecciones eléctricas y tablero</t>
         </is>
       </c>
       <c r="C33" s="65" t="n"/>
       <c r="D33" s="64" t="inlineStr">
         <is>
-          <t>Caja estática de pared orientada a sotavento; tubo de impulso con purga/filtro de membrana</t>
+          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
         </is>
       </c>
       <c r="E33" s="65" t="n"/>
       <c r="F33" s="65" t="n"/>
       <c r="G33" s="64" t="inlineStr">
         <is>
-          <t>Inox 316; conexiones 1/8 in NPT con sellante compatible</t>
+          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
         </is>
       </c>
       <c r="H33" s="65" t="n"/>
@@ -4083,14 +4045,14 @@
       </c>
       <c r="J33" s="64" t="inlineStr">
         <is>
-          <t>Dwyer A-417 o fabricación local inox 316 (dato típico)</t>
+          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
         </is>
       </c>
       <c r="K33" s="65" t="n"/>
       <c r="L33" s="65" t="n"/>
       <c r="M33" s="64" t="inlineStr">
         <is>
-          <t>Dwyer MS (PDF) (https://www.transcat.com/media/pdf/MS_cat.pdf)</t>
+          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
         </is>
       </c>
       <c r="N33" s="65" t="n"/>
@@ -4099,25 +4061,25 @@
     <row r="34">
       <c r="A34" s="64" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B34" s="64" t="inlineStr">
         <is>
-          <t>Soportes y ferretería</t>
+          <t>Cableado y canalización</t>
         </is>
       </c>
       <c r="C34" s="65" t="n"/>
       <c r="D34" s="64" t="inlineStr">
         <is>
-          <t>Soportes de ventilador, rejillas, damper e instrumentos; pernos, tuercas, arandelas</t>
+          <t>Circuito de alimentación del motor 0.75 HP</t>
         </is>
       </c>
       <c r="E34" s="65" t="n"/>
       <c r="F34" s="65" t="n"/>
       <c r="G34" s="64" t="inlineStr">
         <is>
-          <t>Inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
+          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
         </is>
       </c>
       <c r="H34" s="65" t="n"/>
@@ -4128,310 +4090,114 @@
       </c>
       <c r="J34" s="64" t="inlineStr">
         <is>
-          <t>Suministro nacional genérico A4</t>
+          <t>Suministro nacional certificado RETIE</t>
         </is>
       </c>
       <c r="K34" s="65" t="n"/>
       <c r="L34" s="65" t="n"/>
       <c r="M34" s="64" t="inlineStr">
         <is>
-          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
+          <t>Requisito RETIE / NTC 2050</t>
         </is>
       </c>
       <c r="N34" s="65" t="n"/>
       <c r="O34" s="65" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="64" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B35" s="64" t="inlineStr">
-        <is>
-          <t>Conexión flexible ventilador-pasamuros</t>
-        </is>
-      </c>
-      <c r="C35" s="65" t="n"/>
-      <c r="D35" s="64" t="inlineStr">
-        <is>
-          <t>Ancho ≥ 100 mm; bandas de amarre inox 316 cal. 24</t>
-        </is>
-      </c>
-      <c r="E35" s="65" t="n"/>
-      <c r="F35" s="65" t="n"/>
-      <c r="G35" s="64" t="inlineStr">
-        <is>
-          <t>Hipalón (CSM); alternativa clorobutilo; no PVC estándar</t>
-        </is>
-      </c>
-      <c r="H35" s="65" t="n"/>
-      <c r="I35" s="64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" s="64" t="inlineStr">
-        <is>
-          <t>Hardcast Hypalon; Proco serie 500</t>
-        </is>
-      </c>
-      <c r="K35" s="65" t="n"/>
-      <c r="L35" s="65" t="n"/>
-      <c r="M35" s="64" t="inlineStr">
-        <is>
-          <t>Hardcast (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf)</t>
-        </is>
-      </c>
-      <c r="N35" s="65" t="n"/>
-      <c r="O35" s="65" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="64" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B36" s="64" t="inlineStr">
-        <is>
-          <t>Selladores</t>
-        </is>
-      </c>
-      <c r="C36" s="65" t="n"/>
-      <c r="D36" s="64" t="inlineStr">
-        <is>
-          <t>Sellado de pasamuros, marcos y empalmes</t>
-        </is>
-      </c>
-      <c r="E36" s="65" t="n"/>
-      <c r="F36" s="65" t="n"/>
-      <c r="G36" s="64" t="inlineStr">
-        <is>
-          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
-        </is>
-      </c>
-      <c r="H36" s="65" t="n"/>
-      <c r="I36" s="64" t="inlineStr">
-        <is>
-          <t>Lote</t>
-        </is>
-      </c>
-      <c r="J36" s="64" t="inlineStr">
-        <is>
-          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
-        </is>
-      </c>
-      <c r="K36" s="65" t="n"/>
-      <c r="L36" s="65" t="n"/>
-      <c r="M36" s="64" t="inlineStr">
-        <is>
-          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
-        </is>
-      </c>
-      <c r="N36" s="65" t="n"/>
-      <c r="O36" s="65" t="n"/>
-    </row>
     <row r="37">
-      <c r="A37" s="64" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B37" s="64" t="inlineStr">
-        <is>
-          <t>Protecciones eléctricas y tablero</t>
-        </is>
-      </c>
-      <c r="C37" s="65" t="n"/>
-      <c r="D37" s="64" t="inlineStr">
-        <is>
-          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
-        </is>
-      </c>
-      <c r="E37" s="65" t="n"/>
-      <c r="F37" s="65" t="n"/>
-      <c r="G37" s="64" t="inlineStr">
-        <is>
-          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
-        </is>
-      </c>
-      <c r="H37" s="65" t="n"/>
-      <c r="I37" s="64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" s="64" t="inlineStr">
-        <is>
-          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
-        </is>
-      </c>
-      <c r="K37" s="65" t="n"/>
-      <c r="L37" s="65" t="n"/>
-      <c r="M37" s="64" t="inlineStr">
-        <is>
-          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
-        </is>
-      </c>
-      <c r="N37" s="65" t="n"/>
-      <c r="O37" s="65" t="n"/>
+      <c r="A37" s="61" t="inlineStr">
+        <is>
+          <t>3. Notas de suministro</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="64" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B38" s="64" t="inlineStr">
-        <is>
-          <t>Cableado y canalización</t>
-        </is>
-      </c>
-      <c r="C38" s="65" t="n"/>
-      <c r="D38" s="64" t="inlineStr">
-        <is>
-          <t>Circuito motor 1.0 HP + circuito instrumentación 4-20 mA apantallado</t>
-        </is>
-      </c>
-      <c r="E38" s="65" t="n"/>
-      <c r="F38" s="65" t="n"/>
-      <c r="G38" s="64" t="inlineStr">
-        <is>
-          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
-        </is>
-      </c>
-      <c r="H38" s="65" t="n"/>
-      <c r="I38" s="64" t="inlineStr">
-        <is>
-          <t>Lote</t>
-        </is>
-      </c>
-      <c r="J38" s="64" t="inlineStr">
-        <is>
-          <t>Suministro nacional certificado RETIE</t>
-        </is>
-      </c>
-      <c r="K38" s="65" t="n"/>
-      <c r="L38" s="65" t="n"/>
-      <c r="M38" s="64" t="inlineStr">
-        <is>
-          <t>Requisito RETIE / NTC 2050</t>
-        </is>
-      </c>
-      <c r="N38" s="65" t="n"/>
-      <c r="O38" s="65" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="61" t="inlineStr">
-        <is>
-          <t>3. Notas de suministro</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="60" t="inlineStr">
-        <is>
-          <t>3.1. Ítems 1, 4, 8, 9 y 10 requieren cotización formal con submittal: la selección final de tamaño/RPM del ventilador (ítem 1) se confirma con el software del fabricante sobre el punto 3 840 m³/h @ 260 Pa aire estándar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="60" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr">
+        <is>
+          <t>3.1. Los ítems 1 y 4 requieren cotización formal con submittal: la selección final de tamaño/RPM del ventilador (ítem 1) y la potencia definitiva del motor (ítem 2) se confirman con el software del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="60" t="inlineStr">
-        <is>
-          <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 16-17. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="60" t="inlineStr">
+        <is>
+          <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
   </sheetData>
-  <mergeCells count="110">
-    <mergeCell ref="G21:H21"/>
+  <mergeCells count="85">
     <mergeCell ref="J27:L27"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="J35:L35"/>
     <mergeCell ref="G23:H23"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="M21:O21"/>
     <mergeCell ref="J25:L25"/>
-    <mergeCell ref="B21:C21"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D37:F37"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="M24:O24"/>
     <mergeCell ref="C2:L3"/>
     <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B38:C38"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="D23:F23"/>
     <mergeCell ref="J29:L29"/>
-    <mergeCell ref="A15:O15"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="J38:L38"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A40:O42"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="G22:H22"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B1:B5"/>
+    <mergeCell ref="A17:O18"/>
     <mergeCell ref="J24:L24"/>
+    <mergeCell ref="A16:O16"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="M22:O22"/>
     <mergeCell ref="M31:O31"/>
     <mergeCell ref="J26:L26"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A43:O44"/>
     <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M37:O37"/>
-    <mergeCell ref="G38:H38"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="M26:O26"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="M29:O29"/>
+    <mergeCell ref="A20:O20"/>
     <mergeCell ref="M23:O23"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="J33:L33"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="M38:O38"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A44:O46"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G35:H35"/>
     <mergeCell ref="J28:L28"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="G25:H25"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D21:F21"/>
     <mergeCell ref="J30:L30"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A41:O41"/>
     <mergeCell ref="M25:O25"/>
+    <mergeCell ref="A38:O39"/>
     <mergeCell ref="M30:O30"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="M33:O33"/>
-    <mergeCell ref="G37:H37"/>
     <mergeCell ref="A8:O8"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="M32:O32"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A19:O19"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D35:F35"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
@@ -4439,31 +4205,22 @@
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D36:F36"/>
     <mergeCell ref="J34:L34"/>
-    <mergeCell ref="A42:O43"/>
-    <mergeCell ref="A47:O48"/>
-    <mergeCell ref="J36:L36"/>
     <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="A37:O37"/>
     <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M36:O36"/>
     <mergeCell ref="J22:L22"/>
     <mergeCell ref="J31:L31"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="J21:L21"/>
     <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D38:F38"/>
     <mergeCell ref="G30:H30"/>
-    <mergeCell ref="A16:O17"/>
     <mergeCell ref="J23:L23"/>
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="M34:O34"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="G31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/lis/P2437-HV-LIS-001 REV0.xlsx
+++ b/build/lis/P2437-HV-LIS-001 REV0.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -133,23 +133,81 @@
       <sz val="16"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color rgb="FF00B050"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -337,7 +395,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -455,6 +513,14 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -465,36 +531,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1068,96 +1175,96 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A1" s="29" t="n"/>
-      <c r="B1" s="44" t="n"/>
-      <c r="C1" s="44" t="n"/>
-      <c r="D1" s="44" t="n"/>
-      <c r="E1" s="44" t="n"/>
-      <c r="F1" s="44" t="n"/>
-      <c r="G1" s="44" t="n"/>
-      <c r="H1" s="44" t="n"/>
-      <c r="I1" s="44" t="n"/>
-      <c r="J1" s="44" t="n"/>
-      <c r="K1" s="44" t="n"/>
-      <c r="L1" s="44" t="n"/>
-      <c r="M1" s="45" t="n"/>
-      <c r="N1" s="30" t="n"/>
-      <c r="O1" s="44" t="n"/>
-      <c r="P1" s="44" t="n"/>
-      <c r="Q1" s="44" t="n"/>
-      <c r="R1" s="44" t="n"/>
-      <c r="S1" s="44" t="n"/>
-      <c r="T1" s="44" t="n"/>
-      <c r="U1" s="44" t="n"/>
-      <c r="V1" s="44" t="n"/>
-      <c r="W1" s="44" t="n"/>
-      <c r="X1" s="44" t="n"/>
-      <c r="Y1" s="45" t="n"/>
+      <c r="A1" s="44" t="n"/>
+      <c r="B1" s="45" t="n"/>
+      <c r="C1" s="45" t="n"/>
+      <c r="D1" s="45" t="n"/>
+      <c r="E1" s="45" t="n"/>
+      <c r="F1" s="45" t="n"/>
+      <c r="G1" s="45" t="n"/>
+      <c r="H1" s="45" t="n"/>
+      <c r="I1" s="45" t="n"/>
+      <c r="J1" s="45" t="n"/>
+      <c r="K1" s="45" t="n"/>
+      <c r="L1" s="45" t="n"/>
+      <c r="M1" s="46" t="n"/>
+      <c r="N1" s="47" t="n"/>
+      <c r="O1" s="45" t="n"/>
+      <c r="P1" s="48" t="n"/>
+      <c r="Q1" s="48" t="n"/>
+      <c r="R1" s="48" t="n"/>
+      <c r="S1" s="48" t="n"/>
+      <c r="T1" s="48" t="n"/>
+      <c r="U1" s="48" t="n"/>
+      <c r="V1" s="48" t="n"/>
+      <c r="W1" s="48" t="n"/>
+      <c r="X1" s="48" t="n"/>
+      <c r="Y1" s="49" t="n"/>
       <c r="Z1" s="27" t="inlineStr">
         <is>
           <t>DISEÑO DE INGENIERÍA</t>
         </is>
       </c>
-      <c r="AA1" s="44" t="n"/>
-      <c r="AB1" s="44" t="n"/>
-      <c r="AC1" s="44" t="n"/>
-      <c r="AD1" s="44" t="n"/>
-      <c r="AE1" s="44" t="n"/>
-      <c r="AF1" s="44" t="n"/>
-      <c r="AG1" s="44" t="n"/>
-      <c r="AH1" s="44" t="n"/>
-      <c r="AI1" s="44" t="n"/>
-      <c r="AJ1" s="44" t="n"/>
-      <c r="AK1" s="44" t="n"/>
-      <c r="AL1" s="44" t="n"/>
-      <c r="AM1" s="44" t="n"/>
-      <c r="AN1" s="44" t="n"/>
-      <c r="AO1" s="44" t="n"/>
-      <c r="AP1" s="44" t="n"/>
-      <c r="AQ1" s="44" t="n"/>
-      <c r="AR1" s="44" t="n"/>
-      <c r="AS1" s="44" t="n"/>
-      <c r="AT1" s="44" t="n"/>
-      <c r="AU1" s="44" t="n"/>
-      <c r="AV1" s="44" t="n"/>
-      <c r="AW1" s="44" t="n"/>
-      <c r="AX1" s="44" t="n"/>
-      <c r="AY1" s="44" t="n"/>
-      <c r="AZ1" s="44" t="n"/>
-      <c r="BA1" s="44" t="n"/>
-      <c r="BB1" s="45" t="n"/>
+      <c r="AA1" s="48" t="n"/>
+      <c r="AB1" s="48" t="n"/>
+      <c r="AC1" s="48" t="n"/>
+      <c r="AD1" s="48" t="n"/>
+      <c r="AE1" s="48" t="n"/>
+      <c r="AF1" s="48" t="n"/>
+      <c r="AG1" s="48" t="n"/>
+      <c r="AH1" s="48" t="n"/>
+      <c r="AI1" s="48" t="n"/>
+      <c r="AJ1" s="48" t="n"/>
+      <c r="AK1" s="48" t="n"/>
+      <c r="AL1" s="48" t="n"/>
+      <c r="AM1" s="48" t="n"/>
+      <c r="AN1" s="48" t="n"/>
+      <c r="AO1" s="48" t="n"/>
+      <c r="AP1" s="48" t="n"/>
+      <c r="AQ1" s="48" t="n"/>
+      <c r="AR1" s="48" t="n"/>
+      <c r="AS1" s="48" t="n"/>
+      <c r="AT1" s="48" t="n"/>
+      <c r="AU1" s="48" t="n"/>
+      <c r="AV1" s="48" t="n"/>
+      <c r="AW1" s="48" t="n"/>
+      <c r="AX1" s="48" t="n"/>
+      <c r="AY1" s="48" t="n"/>
+      <c r="AZ1" s="48" t="n"/>
+      <c r="BA1" s="48" t="n"/>
+      <c r="BB1" s="49" t="n"/>
       <c r="BC1" s="26" t="inlineStr">
         <is>
           <t>CODIGO:</t>
         </is>
       </c>
-      <c r="BD1" s="46" t="n"/>
-      <c r="BE1" s="46" t="n"/>
-      <c r="BF1" s="46" t="n"/>
-      <c r="BG1" s="46" t="n"/>
-      <c r="BH1" s="46" t="n"/>
-      <c r="BI1" s="46" t="n"/>
-      <c r="BJ1" s="46" t="n"/>
-      <c r="BK1" s="46" t="n"/>
-      <c r="BL1" s="46" t="n"/>
-      <c r="BM1" s="46" t="n"/>
-      <c r="BN1" s="47" t="n"/>
+      <c r="BD1" s="50" t="n"/>
+      <c r="BE1" s="50" t="n"/>
+      <c r="BF1" s="50" t="n"/>
+      <c r="BG1" s="50" t="n"/>
+      <c r="BH1" s="50" t="n"/>
+      <c r="BI1" s="50" t="n"/>
+      <c r="BJ1" s="50" t="n"/>
+      <c r="BK1" s="50" t="n"/>
+      <c r="BL1" s="50" t="n"/>
+      <c r="BM1" s="50" t="n"/>
+      <c r="BN1" s="51" t="n"/>
       <c r="BO1" s="25" t="inlineStr">
         <is>
           <t>P2437-HV-LIS-001</t>
         </is>
       </c>
-      <c r="BP1" s="48" t="n"/>
-      <c r="BQ1" s="48" t="n"/>
-      <c r="BR1" s="48" t="n"/>
-      <c r="BS1" s="48" t="n"/>
-      <c r="BT1" s="48" t="n"/>
-      <c r="BU1" s="48" t="n"/>
-      <c r="BV1" s="48" t="n"/>
-      <c r="BW1" s="48" t="n"/>
-      <c r="BX1" s="48" t="n"/>
-      <c r="BY1" s="48" t="n"/>
-      <c r="BZ1" s="49" t="n"/>
+      <c r="BP1" s="52" t="n"/>
+      <c r="BQ1" s="52" t="n"/>
+      <c r="BR1" s="52" t="n"/>
+      <c r="BS1" s="52" t="n"/>
+      <c r="BT1" s="52" t="n"/>
+      <c r="BU1" s="52" t="n"/>
+      <c r="BV1" s="52" t="n"/>
+      <c r="BW1" s="52" t="n"/>
+      <c r="BX1" s="52" t="n"/>
+      <c r="BY1" s="52" t="n"/>
+      <c r="BZ1" s="53" t="n"/>
       <c r="CB1" s="15" t="inlineStr">
         <is>
           <t>REVIZADO</t>
@@ -1170,71 +1277,83 @@
       </c>
     </row>
     <row r="2" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="50" t="n"/>
-      <c r="M2" s="51" t="n"/>
-      <c r="N2" s="50" t="n"/>
-      <c r="Y2" s="51" t="n"/>
-      <c r="Z2" s="52" t="n"/>
-      <c r="AA2" s="53" t="n"/>
-      <c r="AB2" s="53" t="n"/>
-      <c r="AC2" s="53" t="n"/>
-      <c r="AD2" s="53" t="n"/>
-      <c r="AE2" s="53" t="n"/>
-      <c r="AF2" s="53" t="n"/>
-      <c r="AG2" s="53" t="n"/>
-      <c r="AH2" s="53" t="n"/>
-      <c r="AI2" s="53" t="n"/>
-      <c r="AJ2" s="53" t="n"/>
-      <c r="AK2" s="53" t="n"/>
-      <c r="AL2" s="53" t="n"/>
-      <c r="AM2" s="53" t="n"/>
-      <c r="AN2" s="53" t="n"/>
-      <c r="AO2" s="53" t="n"/>
-      <c r="AP2" s="53" t="n"/>
-      <c r="AQ2" s="53" t="n"/>
-      <c r="AR2" s="53" t="n"/>
-      <c r="AS2" s="53" t="n"/>
-      <c r="AT2" s="53" t="n"/>
-      <c r="AU2" s="53" t="n"/>
-      <c r="AV2" s="53" t="n"/>
-      <c r="AW2" s="53" t="n"/>
-      <c r="AX2" s="53" t="n"/>
-      <c r="AY2" s="53" t="n"/>
-      <c r="AZ2" s="53" t="n"/>
-      <c r="BA2" s="53" t="n"/>
-      <c r="BB2" s="54" t="n"/>
+      <c r="A2" s="54" t="n"/>
+      <c r="B2" s="55" t="n"/>
+      <c r="C2" s="55" t="n"/>
+      <c r="D2" s="55" t="n"/>
+      <c r="E2" s="55" t="n"/>
+      <c r="F2" s="55" t="n"/>
+      <c r="G2" s="55" t="n"/>
+      <c r="H2" s="55" t="n"/>
+      <c r="I2" s="55" t="n"/>
+      <c r="J2" s="55" t="n"/>
+      <c r="K2" s="55" t="n"/>
+      <c r="L2" s="55" t="n"/>
+      <c r="M2" s="56" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="O2" s="55" t="n"/>
+      <c r="Y2" s="57" t="n"/>
+      <c r="Z2" s="58" t="n"/>
+      <c r="AA2" s="59" t="n"/>
+      <c r="AB2" s="59" t="n"/>
+      <c r="AC2" s="59" t="n"/>
+      <c r="AD2" s="59" t="n"/>
+      <c r="AE2" s="59" t="n"/>
+      <c r="AF2" s="59" t="n"/>
+      <c r="AG2" s="59" t="n"/>
+      <c r="AH2" s="59" t="n"/>
+      <c r="AI2" s="59" t="n"/>
+      <c r="AJ2" s="59" t="n"/>
+      <c r="AK2" s="59" t="n"/>
+      <c r="AL2" s="59" t="n"/>
+      <c r="AM2" s="59" t="n"/>
+      <c r="AN2" s="59" t="n"/>
+      <c r="AO2" s="59" t="n"/>
+      <c r="AP2" s="59" t="n"/>
+      <c r="AQ2" s="59" t="n"/>
+      <c r="AR2" s="59" t="n"/>
+      <c r="AS2" s="59" t="n"/>
+      <c r="AT2" s="59" t="n"/>
+      <c r="AU2" s="59" t="n"/>
+      <c r="AV2" s="59" t="n"/>
+      <c r="AW2" s="59" t="n"/>
+      <c r="AX2" s="59" t="n"/>
+      <c r="AY2" s="59" t="n"/>
+      <c r="AZ2" s="59" t="n"/>
+      <c r="BA2" s="59" t="n"/>
+      <c r="BB2" s="60" t="n"/>
       <c r="BC2" s="26" t="inlineStr">
         <is>
           <t>REVISION:</t>
         </is>
       </c>
-      <c r="BD2" s="46" t="n"/>
-      <c r="BE2" s="46" t="n"/>
-      <c r="BF2" s="46" t="n"/>
-      <c r="BG2" s="46" t="n"/>
-      <c r="BH2" s="46" t="n"/>
-      <c r="BI2" s="46" t="n"/>
-      <c r="BJ2" s="46" t="n"/>
-      <c r="BK2" s="46" t="n"/>
-      <c r="BL2" s="46" t="n"/>
-      <c r="BM2" s="46" t="n"/>
-      <c r="BN2" s="47" t="n"/>
+      <c r="BD2" s="50" t="n"/>
+      <c r="BE2" s="50" t="n"/>
+      <c r="BF2" s="50" t="n"/>
+      <c r="BG2" s="50" t="n"/>
+      <c r="BH2" s="50" t="n"/>
+      <c r="BI2" s="50" t="n"/>
+      <c r="BJ2" s="50" t="n"/>
+      <c r="BK2" s="50" t="n"/>
+      <c r="BL2" s="50" t="n"/>
+      <c r="BM2" s="50" t="n"/>
+      <c r="BN2" s="51" t="n"/>
       <c r="BO2" s="25" t="inlineStr">
         <is>
           <t>CERO (0)</t>
         </is>
       </c>
-      <c r="BP2" s="48" t="n"/>
-      <c r="BQ2" s="48" t="n"/>
-      <c r="BR2" s="48" t="n"/>
-      <c r="BS2" s="48" t="n"/>
-      <c r="BT2" s="48" t="n"/>
-      <c r="BU2" s="48" t="n"/>
-      <c r="BV2" s="48" t="n"/>
-      <c r="BW2" s="48" t="n"/>
-      <c r="BX2" s="48" t="n"/>
-      <c r="BY2" s="48" t="n"/>
-      <c r="BZ2" s="49" t="n"/>
+      <c r="BP2" s="52" t="n"/>
+      <c r="BQ2" s="52" t="n"/>
+      <c r="BR2" s="52" t="n"/>
+      <c r="BS2" s="52" t="n"/>
+      <c r="BT2" s="52" t="n"/>
+      <c r="BU2" s="52" t="n"/>
+      <c r="BV2" s="52" t="n"/>
+      <c r="BW2" s="52" t="n"/>
+      <c r="BX2" s="52" t="n"/>
+      <c r="BY2" s="52" t="n"/>
+      <c r="BZ2" s="53" t="n"/>
       <c r="CB2" s="15" t="inlineStr">
         <is>
           <t>APROBADO</t>
@@ -1247,341 +1366,371 @@
       </c>
     </row>
     <row r="3" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="50" t="n"/>
-      <c r="M3" s="51" t="n"/>
-      <c r="N3" s="50" t="n"/>
-      <c r="Y3" s="51" t="n"/>
+      <c r="A3" s="54" t="n"/>
+      <c r="B3" s="55" t="n"/>
+      <c r="C3" s="55" t="n"/>
+      <c r="D3" s="55" t="n"/>
+      <c r="E3" s="55" t="n"/>
+      <c r="F3" s="55" t="n"/>
+      <c r="G3" s="55" t="n"/>
+      <c r="H3" s="55" t="n"/>
+      <c r="I3" s="55" t="n"/>
+      <c r="J3" s="55" t="n"/>
+      <c r="K3" s="55" t="n"/>
+      <c r="L3" s="55" t="n"/>
+      <c r="M3" s="56" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="55" t="n"/>
+      <c r="Y3" s="57" t="n"/>
       <c r="Z3" s="27" t="inlineStr">
         <is>
           <t>SISTEMA HVAC LABORATORIO BRINSA</t>
         </is>
       </c>
-      <c r="AA3" s="44" t="n"/>
-      <c r="AB3" s="44" t="n"/>
-      <c r="AC3" s="44" t="n"/>
-      <c r="AD3" s="44" t="n"/>
-      <c r="AE3" s="44" t="n"/>
-      <c r="AF3" s="44" t="n"/>
-      <c r="AG3" s="44" t="n"/>
-      <c r="AH3" s="44" t="n"/>
-      <c r="AI3" s="44" t="n"/>
-      <c r="AJ3" s="44" t="n"/>
-      <c r="AK3" s="44" t="n"/>
-      <c r="AL3" s="44" t="n"/>
-      <c r="AM3" s="44" t="n"/>
-      <c r="AN3" s="44" t="n"/>
-      <c r="AO3" s="44" t="n"/>
-      <c r="AP3" s="44" t="n"/>
-      <c r="AQ3" s="44" t="n"/>
-      <c r="AR3" s="44" t="n"/>
-      <c r="AS3" s="44" t="n"/>
-      <c r="AT3" s="44" t="n"/>
-      <c r="AU3" s="44" t="n"/>
-      <c r="AV3" s="44" t="n"/>
-      <c r="AW3" s="44" t="n"/>
-      <c r="AX3" s="44" t="n"/>
-      <c r="AY3" s="44" t="n"/>
-      <c r="AZ3" s="44" t="n"/>
-      <c r="BA3" s="44" t="n"/>
-      <c r="BB3" s="45" t="n"/>
+      <c r="AA3" s="48" t="n"/>
+      <c r="AB3" s="48" t="n"/>
+      <c r="AC3" s="48" t="n"/>
+      <c r="AD3" s="48" t="n"/>
+      <c r="AE3" s="48" t="n"/>
+      <c r="AF3" s="48" t="n"/>
+      <c r="AG3" s="48" t="n"/>
+      <c r="AH3" s="48" t="n"/>
+      <c r="AI3" s="48" t="n"/>
+      <c r="AJ3" s="48" t="n"/>
+      <c r="AK3" s="48" t="n"/>
+      <c r="AL3" s="48" t="n"/>
+      <c r="AM3" s="48" t="n"/>
+      <c r="AN3" s="48" t="n"/>
+      <c r="AO3" s="48" t="n"/>
+      <c r="AP3" s="48" t="n"/>
+      <c r="AQ3" s="48" t="n"/>
+      <c r="AR3" s="48" t="n"/>
+      <c r="AS3" s="48" t="n"/>
+      <c r="AT3" s="48" t="n"/>
+      <c r="AU3" s="48" t="n"/>
+      <c r="AV3" s="48" t="n"/>
+      <c r="AW3" s="48" t="n"/>
+      <c r="AX3" s="48" t="n"/>
+      <c r="AY3" s="48" t="n"/>
+      <c r="AZ3" s="48" t="n"/>
+      <c r="BA3" s="48" t="n"/>
+      <c r="BB3" s="49" t="n"/>
       <c r="BC3" s="26" t="inlineStr">
         <is>
           <t>FECHA:</t>
         </is>
       </c>
-      <c r="BD3" s="46" t="n"/>
-      <c r="BE3" s="46" t="n"/>
-      <c r="BF3" s="46" t="n"/>
-      <c r="BG3" s="46" t="n"/>
-      <c r="BH3" s="46" t="n"/>
-      <c r="BI3" s="46" t="n"/>
-      <c r="BJ3" s="46" t="n"/>
-      <c r="BK3" s="46" t="n"/>
-      <c r="BL3" s="46" t="n"/>
-      <c r="BM3" s="46" t="n"/>
-      <c r="BN3" s="47" t="n"/>
+      <c r="BD3" s="50" t="n"/>
+      <c r="BE3" s="50" t="n"/>
+      <c r="BF3" s="50" t="n"/>
+      <c r="BG3" s="50" t="n"/>
+      <c r="BH3" s="50" t="n"/>
+      <c r="BI3" s="50" t="n"/>
+      <c r="BJ3" s="50" t="n"/>
+      <c r="BK3" s="50" t="n"/>
+      <c r="BL3" s="50" t="n"/>
+      <c r="BM3" s="50" t="n"/>
+      <c r="BN3" s="51" t="n"/>
       <c r="BO3" s="25" t="inlineStr">
         <is>
           <t>JULIO 23 DEL 2026</t>
         </is>
       </c>
-      <c r="BP3" s="48" t="n"/>
-      <c r="BQ3" s="48" t="n"/>
-      <c r="BR3" s="48" t="n"/>
-      <c r="BS3" s="48" t="n"/>
-      <c r="BT3" s="48" t="n"/>
-      <c r="BU3" s="48" t="n"/>
-      <c r="BV3" s="48" t="n"/>
-      <c r="BW3" s="48" t="n"/>
-      <c r="BX3" s="48" t="n"/>
-      <c r="BY3" s="48" t="n"/>
-      <c r="BZ3" s="49" t="n"/>
+      <c r="BP3" s="52" t="n"/>
+      <c r="BQ3" s="52" t="n"/>
+      <c r="BR3" s="52" t="n"/>
+      <c r="BS3" s="52" t="n"/>
+      <c r="BT3" s="52" t="n"/>
+      <c r="BU3" s="52" t="n"/>
+      <c r="BV3" s="52" t="n"/>
+      <c r="BW3" s="52" t="n"/>
+      <c r="BX3" s="52" t="n"/>
+      <c r="BY3" s="52" t="n"/>
+      <c r="BZ3" s="53" t="n"/>
     </row>
     <row r="4" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A4" s="50" t="n"/>
-      <c r="M4" s="51" t="n"/>
-      <c r="N4" s="50" t="n"/>
-      <c r="Y4" s="51" t="n"/>
-      <c r="Z4" s="52" t="n"/>
-      <c r="AA4" s="53" t="n"/>
-      <c r="AB4" s="53" t="n"/>
-      <c r="AC4" s="53" t="n"/>
-      <c r="AD4" s="53" t="n"/>
-      <c r="AE4" s="53" t="n"/>
-      <c r="AF4" s="53" t="n"/>
-      <c r="AG4" s="53" t="n"/>
-      <c r="AH4" s="53" t="n"/>
-      <c r="AI4" s="53" t="n"/>
-      <c r="AJ4" s="53" t="n"/>
-      <c r="AK4" s="53" t="n"/>
-      <c r="AL4" s="53" t="n"/>
-      <c r="AM4" s="53" t="n"/>
-      <c r="AN4" s="53" t="n"/>
-      <c r="AO4" s="53" t="n"/>
-      <c r="AP4" s="53" t="n"/>
-      <c r="AQ4" s="53" t="n"/>
-      <c r="AR4" s="53" t="n"/>
-      <c r="AS4" s="53" t="n"/>
-      <c r="AT4" s="53" t="n"/>
-      <c r="AU4" s="53" t="n"/>
-      <c r="AV4" s="53" t="n"/>
-      <c r="AW4" s="53" t="n"/>
-      <c r="AX4" s="53" t="n"/>
-      <c r="AY4" s="53" t="n"/>
-      <c r="AZ4" s="53" t="n"/>
-      <c r="BA4" s="53" t="n"/>
-      <c r="BB4" s="54" t="n"/>
+      <c r="A4" s="54" t="n"/>
+      <c r="B4" s="55" t="n"/>
+      <c r="C4" s="55" t="n"/>
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="55" t="n"/>
+      <c r="F4" s="55" t="n"/>
+      <c r="G4" s="55" t="n"/>
+      <c r="H4" s="55" t="n"/>
+      <c r="I4" s="55" t="n"/>
+      <c r="J4" s="55" t="n"/>
+      <c r="K4" s="55" t="n"/>
+      <c r="L4" s="55" t="n"/>
+      <c r="M4" s="56" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="55" t="n"/>
+      <c r="Y4" s="57" t="n"/>
+      <c r="Z4" s="58" t="n"/>
+      <c r="AA4" s="59" t="n"/>
+      <c r="AB4" s="59" t="n"/>
+      <c r="AC4" s="59" t="n"/>
+      <c r="AD4" s="59" t="n"/>
+      <c r="AE4" s="59" t="n"/>
+      <c r="AF4" s="59" t="n"/>
+      <c r="AG4" s="59" t="n"/>
+      <c r="AH4" s="59" t="n"/>
+      <c r="AI4" s="59" t="n"/>
+      <c r="AJ4" s="59" t="n"/>
+      <c r="AK4" s="59" t="n"/>
+      <c r="AL4" s="59" t="n"/>
+      <c r="AM4" s="59" t="n"/>
+      <c r="AN4" s="59" t="n"/>
+      <c r="AO4" s="59" t="n"/>
+      <c r="AP4" s="59" t="n"/>
+      <c r="AQ4" s="59" t="n"/>
+      <c r="AR4" s="59" t="n"/>
+      <c r="AS4" s="59" t="n"/>
+      <c r="AT4" s="59" t="n"/>
+      <c r="AU4" s="59" t="n"/>
+      <c r="AV4" s="59" t="n"/>
+      <c r="AW4" s="59" t="n"/>
+      <c r="AX4" s="59" t="n"/>
+      <c r="AY4" s="59" t="n"/>
+      <c r="AZ4" s="59" t="n"/>
+      <c r="BA4" s="59" t="n"/>
+      <c r="BB4" s="60" t="n"/>
       <c r="BC4" s="26" t="inlineStr">
         <is>
           <t>ELABORO:</t>
         </is>
       </c>
-      <c r="BD4" s="46" t="n"/>
-      <c r="BE4" s="46" t="n"/>
-      <c r="BF4" s="46" t="n"/>
-      <c r="BG4" s="46" t="n"/>
-      <c r="BH4" s="46" t="n"/>
-      <c r="BI4" s="46" t="n"/>
-      <c r="BJ4" s="46" t="n"/>
-      <c r="BK4" s="46" t="n"/>
-      <c r="BL4" s="46" t="n"/>
-      <c r="BM4" s="46" t="n"/>
-      <c r="BN4" s="47" t="n"/>
+      <c r="BD4" s="50" t="n"/>
+      <c r="BE4" s="50" t="n"/>
+      <c r="BF4" s="50" t="n"/>
+      <c r="BG4" s="50" t="n"/>
+      <c r="BH4" s="50" t="n"/>
+      <c r="BI4" s="50" t="n"/>
+      <c r="BJ4" s="50" t="n"/>
+      <c r="BK4" s="50" t="n"/>
+      <c r="BL4" s="50" t="n"/>
+      <c r="BM4" s="50" t="n"/>
+      <c r="BN4" s="51" t="n"/>
       <c r="BO4" s="25" t="inlineStr">
         <is>
           <t>J.ARBOLEDA</t>
         </is>
       </c>
-      <c r="BP4" s="48" t="n"/>
-      <c r="BQ4" s="48" t="n"/>
-      <c r="BR4" s="48" t="n"/>
-      <c r="BS4" s="48" t="n"/>
-      <c r="BT4" s="48" t="n"/>
-      <c r="BU4" s="48" t="n"/>
-      <c r="BV4" s="48" t="n"/>
-      <c r="BW4" s="48" t="n"/>
-      <c r="BX4" s="48" t="n"/>
-      <c r="BY4" s="48" t="n"/>
-      <c r="BZ4" s="49" t="n"/>
+      <c r="BP4" s="52" t="n"/>
+      <c r="BQ4" s="52" t="n"/>
+      <c r="BR4" s="52" t="n"/>
+      <c r="BS4" s="52" t="n"/>
+      <c r="BT4" s="52" t="n"/>
+      <c r="BU4" s="52" t="n"/>
+      <c r="BV4" s="52" t="n"/>
+      <c r="BW4" s="52" t="n"/>
+      <c r="BX4" s="52" t="n"/>
+      <c r="BY4" s="52" t="n"/>
+      <c r="BZ4" s="53" t="n"/>
     </row>
     <row r="5" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="52" t="n"/>
-      <c r="B5" s="53" t="n"/>
-      <c r="C5" s="53" t="n"/>
-      <c r="D5" s="53" t="n"/>
-      <c r="E5" s="53" t="n"/>
-      <c r="F5" s="53" t="n"/>
-      <c r="G5" s="53" t="n"/>
-      <c r="H5" s="53" t="n"/>
-      <c r="I5" s="53" t="n"/>
-      <c r="J5" s="53" t="n"/>
-      <c r="K5" s="53" t="n"/>
-      <c r="L5" s="53" t="n"/>
-      <c r="M5" s="54" t="n"/>
-      <c r="N5" s="52" t="n"/>
-      <c r="O5" s="53" t="n"/>
-      <c r="P5" s="53" t="n"/>
-      <c r="Q5" s="53" t="n"/>
-      <c r="R5" s="53" t="n"/>
-      <c r="S5" s="53" t="n"/>
-      <c r="T5" s="53" t="n"/>
-      <c r="U5" s="53" t="n"/>
-      <c r="V5" s="53" t="n"/>
-      <c r="W5" s="53" t="n"/>
-      <c r="X5" s="53" t="n"/>
-      <c r="Y5" s="54" t="n"/>
+      <c r="A5" s="61" t="n"/>
+      <c r="B5" s="62" t="n"/>
+      <c r="C5" s="62" t="n"/>
+      <c r="D5" s="62" t="n"/>
+      <c r="E5" s="62" t="n"/>
+      <c r="F5" s="62" t="n"/>
+      <c r="G5" s="62" t="n"/>
+      <c r="H5" s="62" t="n"/>
+      <c r="I5" s="62" t="n"/>
+      <c r="J5" s="62" t="n"/>
+      <c r="K5" s="62" t="n"/>
+      <c r="L5" s="62" t="n"/>
+      <c r="M5" s="63" t="n"/>
+      <c r="N5" s="61" t="n"/>
+      <c r="O5" s="62" t="n"/>
+      <c r="P5" s="59" t="n"/>
+      <c r="Q5" s="59" t="n"/>
+      <c r="R5" s="59" t="n"/>
+      <c r="S5" s="59" t="n"/>
+      <c r="T5" s="59" t="n"/>
+      <c r="U5" s="59" t="n"/>
+      <c r="V5" s="59" t="n"/>
+      <c r="W5" s="59" t="n"/>
+      <c r="X5" s="59" t="n"/>
+      <c r="Y5" s="60" t="n"/>
       <c r="Z5" s="31" t="inlineStr">
         <is>
           <t>LISTADO DE EQUIPOS Y MATERIALES (BOQ): SISTEMA DE VENTILACIÓN DEL LABORATORIO</t>
         </is>
       </c>
-      <c r="AA5" s="44" t="n"/>
-      <c r="AB5" s="44" t="n"/>
-      <c r="AC5" s="44" t="n"/>
-      <c r="AD5" s="44" t="n"/>
-      <c r="AE5" s="44" t="n"/>
-      <c r="AF5" s="44" t="n"/>
-      <c r="AG5" s="44" t="n"/>
-      <c r="AH5" s="44" t="n"/>
-      <c r="AI5" s="44" t="n"/>
-      <c r="AJ5" s="44" t="n"/>
-      <c r="AK5" s="44" t="n"/>
-      <c r="AL5" s="44" t="n"/>
-      <c r="AM5" s="44" t="n"/>
-      <c r="AN5" s="44" t="n"/>
-      <c r="AO5" s="44" t="n"/>
-      <c r="AP5" s="44" t="n"/>
-      <c r="AQ5" s="44" t="n"/>
-      <c r="AR5" s="44" t="n"/>
-      <c r="AS5" s="44" t="n"/>
-      <c r="AT5" s="44" t="n"/>
-      <c r="AU5" s="44" t="n"/>
-      <c r="AV5" s="44" t="n"/>
-      <c r="AW5" s="44" t="n"/>
-      <c r="AX5" s="44" t="n"/>
-      <c r="AY5" s="44" t="n"/>
-      <c r="AZ5" s="44" t="n"/>
-      <c r="BA5" s="44" t="n"/>
-      <c r="BB5" s="45" t="n"/>
+      <c r="AA5" s="48" t="n"/>
+      <c r="AB5" s="48" t="n"/>
+      <c r="AC5" s="48" t="n"/>
+      <c r="AD5" s="48" t="n"/>
+      <c r="AE5" s="48" t="n"/>
+      <c r="AF5" s="48" t="n"/>
+      <c r="AG5" s="48" t="n"/>
+      <c r="AH5" s="48" t="n"/>
+      <c r="AI5" s="48" t="n"/>
+      <c r="AJ5" s="48" t="n"/>
+      <c r="AK5" s="48" t="n"/>
+      <c r="AL5" s="48" t="n"/>
+      <c r="AM5" s="48" t="n"/>
+      <c r="AN5" s="48" t="n"/>
+      <c r="AO5" s="48" t="n"/>
+      <c r="AP5" s="48" t="n"/>
+      <c r="AQ5" s="48" t="n"/>
+      <c r="AR5" s="48" t="n"/>
+      <c r="AS5" s="48" t="n"/>
+      <c r="AT5" s="48" t="n"/>
+      <c r="AU5" s="48" t="n"/>
+      <c r="AV5" s="48" t="n"/>
+      <c r="AW5" s="48" t="n"/>
+      <c r="AX5" s="48" t="n"/>
+      <c r="AY5" s="48" t="n"/>
+      <c r="AZ5" s="48" t="n"/>
+      <c r="BA5" s="48" t="n"/>
+      <c r="BB5" s="49" t="n"/>
       <c r="BC5" s="26" t="inlineStr">
         <is>
           <t>REVISO:</t>
         </is>
       </c>
-      <c r="BD5" s="46" t="n"/>
-      <c r="BE5" s="46" t="n"/>
-      <c r="BF5" s="46" t="n"/>
-      <c r="BG5" s="46" t="n"/>
-      <c r="BH5" s="46" t="n"/>
-      <c r="BI5" s="46" t="n"/>
-      <c r="BJ5" s="46" t="n"/>
-      <c r="BK5" s="46" t="n"/>
-      <c r="BL5" s="46" t="n"/>
-      <c r="BM5" s="46" t="n"/>
-      <c r="BN5" s="47" t="n"/>
+      <c r="BD5" s="50" t="n"/>
+      <c r="BE5" s="50" t="n"/>
+      <c r="BF5" s="50" t="n"/>
+      <c r="BG5" s="50" t="n"/>
+      <c r="BH5" s="50" t="n"/>
+      <c r="BI5" s="50" t="n"/>
+      <c r="BJ5" s="50" t="n"/>
+      <c r="BK5" s="50" t="n"/>
+      <c r="BL5" s="50" t="n"/>
+      <c r="BM5" s="50" t="n"/>
+      <c r="BN5" s="51" t="n"/>
       <c r="BO5" s="25" t="inlineStr">
         <is>
           <t>F.NAVIA</t>
         </is>
       </c>
-      <c r="BP5" s="48" t="n"/>
-      <c r="BQ5" s="48" t="n"/>
-      <c r="BR5" s="48" t="n"/>
-      <c r="BS5" s="48" t="n"/>
-      <c r="BT5" s="48" t="n"/>
-      <c r="BU5" s="48" t="n"/>
-      <c r="BV5" s="48" t="n"/>
-      <c r="BW5" s="48" t="n"/>
-      <c r="BX5" s="48" t="n"/>
-      <c r="BY5" s="48" t="n"/>
-      <c r="BZ5" s="49" t="n"/>
+      <c r="BP5" s="52" t="n"/>
+      <c r="BQ5" s="52" t="n"/>
+      <c r="BR5" s="52" t="n"/>
+      <c r="BS5" s="52" t="n"/>
+      <c r="BT5" s="52" t="n"/>
+      <c r="BU5" s="52" t="n"/>
+      <c r="BV5" s="52" t="n"/>
+      <c r="BW5" s="52" t="n"/>
+      <c r="BX5" s="52" t="n"/>
+      <c r="BY5" s="52" t="n"/>
+      <c r="BZ5" s="53" t="n"/>
     </row>
     <row r="6" ht="25" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>PROYECTO</t>
         </is>
       </c>
-      <c r="B6" s="46" t="n"/>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="46" t="n"/>
-      <c r="E6" s="46" t="n"/>
-      <c r="F6" s="46" t="n"/>
-      <c r="G6" s="46" t="n"/>
-      <c r="H6" s="46" t="n"/>
-      <c r="I6" s="46" t="n"/>
-      <c r="J6" s="46" t="n"/>
-      <c r="K6" s="46" t="n"/>
-      <c r="L6" s="46" t="n"/>
-      <c r="M6" s="47" t="n"/>
-      <c r="N6" s="28" t="inlineStr">
+      <c r="B6" s="65" t="n"/>
+      <c r="C6" s="65" t="n"/>
+      <c r="D6" s="65" t="n"/>
+      <c r="E6" s="65" t="n"/>
+      <c r="F6" s="65" t="n"/>
+      <c r="G6" s="65" t="n"/>
+      <c r="H6" s="65" t="n"/>
+      <c r="I6" s="65" t="n"/>
+      <c r="J6" s="65" t="n"/>
+      <c r="K6" s="65" t="n"/>
+      <c r="L6" s="65" t="n"/>
+      <c r="M6" s="66" t="n"/>
+      <c r="N6" s="64" t="inlineStr">
         <is>
           <t>P2437</t>
         </is>
       </c>
-      <c r="O6" s="46" t="n"/>
-      <c r="P6" s="46" t="n"/>
-      <c r="Q6" s="46" t="n"/>
-      <c r="R6" s="46" t="n"/>
-      <c r="S6" s="46" t="n"/>
-      <c r="T6" s="46" t="n"/>
-      <c r="U6" s="46" t="n"/>
-      <c r="V6" s="46" t="n"/>
-      <c r="W6" s="46" t="n"/>
-      <c r="X6" s="46" t="n"/>
-      <c r="Y6" s="47" t="n"/>
-      <c r="Z6" s="52" t="n"/>
-      <c r="AA6" s="53" t="n"/>
-      <c r="AB6" s="53" t="n"/>
-      <c r="AC6" s="53" t="n"/>
-      <c r="AD6" s="53" t="n"/>
-      <c r="AE6" s="53" t="n"/>
-      <c r="AF6" s="53" t="n"/>
-      <c r="AG6" s="53" t="n"/>
-      <c r="AH6" s="53" t="n"/>
-      <c r="AI6" s="53" t="n"/>
-      <c r="AJ6" s="53" t="n"/>
-      <c r="AK6" s="53" t="n"/>
-      <c r="AL6" s="53" t="n"/>
-      <c r="AM6" s="53" t="n"/>
-      <c r="AN6" s="53" t="n"/>
-      <c r="AO6" s="53" t="n"/>
-      <c r="AP6" s="53" t="n"/>
-      <c r="AQ6" s="53" t="n"/>
-      <c r="AR6" s="53" t="n"/>
-      <c r="AS6" s="53" t="n"/>
-      <c r="AT6" s="53" t="n"/>
-      <c r="AU6" s="53" t="n"/>
-      <c r="AV6" s="53" t="n"/>
-      <c r="AW6" s="53" t="n"/>
-      <c r="AX6" s="53" t="n"/>
-      <c r="AY6" s="53" t="n"/>
-      <c r="AZ6" s="53" t="n"/>
-      <c r="BA6" s="53" t="n"/>
-      <c r="BB6" s="54" t="n"/>
+      <c r="O6" s="65" t="n"/>
+      <c r="P6" s="50" t="n"/>
+      <c r="Q6" s="50" t="n"/>
+      <c r="R6" s="50" t="n"/>
+      <c r="S6" s="50" t="n"/>
+      <c r="T6" s="50" t="n"/>
+      <c r="U6" s="50" t="n"/>
+      <c r="V6" s="50" t="n"/>
+      <c r="W6" s="50" t="n"/>
+      <c r="X6" s="50" t="n"/>
+      <c r="Y6" s="51" t="n"/>
+      <c r="Z6" s="58" t="n"/>
+      <c r="AA6" s="59" t="n"/>
+      <c r="AB6" s="59" t="n"/>
+      <c r="AC6" s="59" t="n"/>
+      <c r="AD6" s="59" t="n"/>
+      <c r="AE6" s="59" t="n"/>
+      <c r="AF6" s="59" t="n"/>
+      <c r="AG6" s="59" t="n"/>
+      <c r="AH6" s="59" t="n"/>
+      <c r="AI6" s="59" t="n"/>
+      <c r="AJ6" s="59" t="n"/>
+      <c r="AK6" s="59" t="n"/>
+      <c r="AL6" s="59" t="n"/>
+      <c r="AM6" s="59" t="n"/>
+      <c r="AN6" s="59" t="n"/>
+      <c r="AO6" s="59" t="n"/>
+      <c r="AP6" s="59" t="n"/>
+      <c r="AQ6" s="59" t="n"/>
+      <c r="AR6" s="59" t="n"/>
+      <c r="AS6" s="59" t="n"/>
+      <c r="AT6" s="59" t="n"/>
+      <c r="AU6" s="59" t="n"/>
+      <c r="AV6" s="59" t="n"/>
+      <c r="AW6" s="59" t="n"/>
+      <c r="AX6" s="59" t="n"/>
+      <c r="AY6" s="59" t="n"/>
+      <c r="AZ6" s="59" t="n"/>
+      <c r="BA6" s="59" t="n"/>
+      <c r="BB6" s="60" t="n"/>
       <c r="BC6" s="26" t="inlineStr">
         <is>
           <t>APROBO:</t>
         </is>
       </c>
-      <c r="BD6" s="46" t="n"/>
-      <c r="BE6" s="46" t="n"/>
-      <c r="BF6" s="46" t="n"/>
-      <c r="BG6" s="46" t="n"/>
-      <c r="BH6" s="46" t="n"/>
-      <c r="BI6" s="46" t="n"/>
-      <c r="BJ6" s="46" t="n"/>
-      <c r="BK6" s="46" t="n"/>
-      <c r="BL6" s="46" t="n"/>
-      <c r="BM6" s="46" t="n"/>
-      <c r="BN6" s="47" t="n"/>
+      <c r="BD6" s="50" t="n"/>
+      <c r="BE6" s="50" t="n"/>
+      <c r="BF6" s="50" t="n"/>
+      <c r="BG6" s="50" t="n"/>
+      <c r="BH6" s="50" t="n"/>
+      <c r="BI6" s="50" t="n"/>
+      <c r="BJ6" s="50" t="n"/>
+      <c r="BK6" s="50" t="n"/>
+      <c r="BL6" s="50" t="n"/>
+      <c r="BM6" s="50" t="n"/>
+      <c r="BN6" s="51" t="n"/>
       <c r="BO6" s="25" t="inlineStr">
         <is>
           <t>H.ROSERO</t>
         </is>
       </c>
-      <c r="BP6" s="48" t="n"/>
-      <c r="BQ6" s="48" t="n"/>
-      <c r="BR6" s="48" t="n"/>
-      <c r="BS6" s="48" t="n"/>
-      <c r="BT6" s="48" t="n"/>
-      <c r="BU6" s="48" t="n"/>
-      <c r="BV6" s="48" t="n"/>
-      <c r="BW6" s="48" t="n"/>
-      <c r="BX6" s="48" t="n"/>
-      <c r="BY6" s="48" t="n"/>
-      <c r="BZ6" s="49" t="n"/>
+      <c r="BP6" s="52" t="n"/>
+      <c r="BQ6" s="52" t="n"/>
+      <c r="BR6" s="52" t="n"/>
+      <c r="BS6" s="52" t="n"/>
+      <c r="BT6" s="52" t="n"/>
+      <c r="BU6" s="52" t="n"/>
+      <c r="BV6" s="52" t="n"/>
+      <c r="BW6" s="52" t="n"/>
+      <c r="BX6" s="52" t="n"/>
+      <c r="BY6" s="52" t="n"/>
+      <c r="BZ6" s="53" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="21" t="n"/>
+      <c r="A7" s="55" t="n"/>
+      <c r="B7" s="55" t="n"/>
+      <c r="C7" s="55" t="n"/>
+      <c r="D7" s="55" t="n"/>
+      <c r="E7" s="55" t="n"/>
+      <c r="F7" s="55" t="n"/>
+      <c r="G7" s="67" t="n"/>
+      <c r="H7" s="67" t="n"/>
+      <c r="I7" s="67" t="n"/>
+      <c r="J7" s="67" t="n"/>
+      <c r="K7" s="67" t="n"/>
+      <c r="L7" s="67" t="n"/>
+      <c r="M7" s="67" t="n"/>
+      <c r="N7" s="67" t="n"/>
+      <c r="O7" s="67" t="n"/>
       <c r="P7" s="21" t="n"/>
       <c r="Q7" s="21" t="n"/>
       <c r="R7" s="21" t="n"/>
@@ -1602,15 +1751,21 @@
       <c r="CD7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="G8" s="21" t="n"/>
-      <c r="H8" s="21" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
+      <c r="A8" s="55" t="n"/>
+      <c r="B8" s="55" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="55" t="n"/>
+      <c r="F8" s="55" t="n"/>
+      <c r="G8" s="67" t="n"/>
+      <c r="H8" s="67" t="n"/>
+      <c r="I8" s="67" t="n"/>
+      <c r="J8" s="67" t="n"/>
+      <c r="K8" s="67" t="n"/>
+      <c r="L8" s="67" t="n"/>
+      <c r="M8" s="67" t="n"/>
+      <c r="N8" s="67" t="n"/>
+      <c r="O8" s="67" t="n"/>
       <c r="P8" s="21" t="n"/>
       <c r="Q8" s="21" t="n"/>
       <c r="R8" s="21" t="n"/>
@@ -1631,15 +1786,21 @@
       <c r="CD8" s="7" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="21" t="n"/>
+      <c r="A9" s="55" t="n"/>
+      <c r="B9" s="55" t="n"/>
+      <c r="C9" s="55" t="n"/>
+      <c r="D9" s="55" t="n"/>
+      <c r="E9" s="55" t="n"/>
+      <c r="F9" s="55" t="n"/>
+      <c r="G9" s="67" t="n"/>
+      <c r="H9" s="67" t="n"/>
+      <c r="I9" s="67" t="n"/>
+      <c r="J9" s="67" t="n"/>
+      <c r="K9" s="67" t="n"/>
+      <c r="L9" s="67" t="n"/>
+      <c r="M9" s="67" t="n"/>
+      <c r="N9" s="67" t="n"/>
+      <c r="O9" s="67" t="n"/>
       <c r="P9" s="21" t="n"/>
       <c r="Q9" s="21" t="n"/>
       <c r="R9" s="21" t="n"/>
@@ -1660,15 +1821,21 @@
       <c r="CD9" s="7" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="21" t="n"/>
-      <c r="M10" s="21" t="n"/>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="21" t="n"/>
+      <c r="A10" s="55" t="n"/>
+      <c r="B10" s="55" t="n"/>
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="55" t="n"/>
+      <c r="E10" s="55" t="n"/>
+      <c r="F10" s="55" t="n"/>
+      <c r="G10" s="67" t="n"/>
+      <c r="H10" s="67" t="n"/>
+      <c r="I10" s="67" t="n"/>
+      <c r="J10" s="67" t="n"/>
+      <c r="K10" s="67" t="n"/>
+      <c r="L10" s="67" t="n"/>
+      <c r="M10" s="67" t="n"/>
+      <c r="N10" s="67" t="n"/>
+      <c r="O10" s="67" t="n"/>
       <c r="P10" s="21" t="n"/>
       <c r="Q10" s="21" t="n"/>
       <c r="R10" s="21" t="n"/>
@@ -1689,15 +1856,21 @@
       <c r="CD10" s="7" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="21" t="n"/>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="21" t="n"/>
+      <c r="A11" s="55" t="n"/>
+      <c r="B11" s="55" t="n"/>
+      <c r="C11" s="55" t="n"/>
+      <c r="D11" s="55" t="n"/>
+      <c r="E11" s="55" t="n"/>
+      <c r="F11" s="55" t="n"/>
+      <c r="G11" s="67" t="n"/>
+      <c r="H11" s="67" t="n"/>
+      <c r="I11" s="67" t="n"/>
+      <c r="J11" s="67" t="n"/>
+      <c r="K11" s="67" t="n"/>
+      <c r="L11" s="67" t="n"/>
+      <c r="M11" s="67" t="n"/>
+      <c r="N11" s="67" t="n"/>
+      <c r="O11" s="67" t="n"/>
       <c r="P11" s="21" t="n"/>
       <c r="Q11" s="21" t="n"/>
       <c r="R11" s="21" t="n"/>
@@ -1718,15 +1891,21 @@
       <c r="CD11" s="7" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="21" t="n"/>
+      <c r="A12" s="55" t="n"/>
+      <c r="B12" s="55" t="n"/>
+      <c r="C12" s="55" t="n"/>
+      <c r="D12" s="55" t="n"/>
+      <c r="E12" s="55" t="n"/>
+      <c r="F12" s="55" t="n"/>
+      <c r="G12" s="67" t="n"/>
+      <c r="H12" s="67" t="n"/>
+      <c r="I12" s="67" t="n"/>
+      <c r="J12" s="67" t="n"/>
+      <c r="K12" s="67" t="n"/>
+      <c r="L12" s="67" t="n"/>
+      <c r="M12" s="67" t="n"/>
+      <c r="N12" s="67" t="n"/>
+      <c r="O12" s="67" t="n"/>
       <c r="P12" s="21" t="n"/>
       <c r="Q12" s="21" t="n"/>
       <c r="R12" s="21" t="n"/>
@@ -1747,15 +1926,21 @@
       <c r="CD12" s="7" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="21" t="n"/>
+      <c r="A13" s="55" t="n"/>
+      <c r="B13" s="55" t="n"/>
+      <c r="C13" s="55" t="n"/>
+      <c r="D13" s="55" t="n"/>
+      <c r="E13" s="55" t="n"/>
+      <c r="F13" s="55" t="n"/>
+      <c r="G13" s="67" t="n"/>
+      <c r="H13" s="67" t="n"/>
+      <c r="I13" s="67" t="n"/>
+      <c r="J13" s="67" t="n"/>
+      <c r="K13" s="67" t="n"/>
+      <c r="L13" s="67" t="n"/>
+      <c r="M13" s="67" t="n"/>
+      <c r="N13" s="67" t="n"/>
+      <c r="O13" s="67" t="n"/>
       <c r="P13" s="21" t="n"/>
       <c r="Q13" s="21" t="n"/>
       <c r="R13" s="21" t="n"/>
@@ -1776,15 +1961,21 @@
       <c r="CD13" s="7" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="21" t="n"/>
+      <c r="A14" s="55" t="n"/>
+      <c r="B14" s="55" t="n"/>
+      <c r="C14" s="55" t="n"/>
+      <c r="D14" s="55" t="n"/>
+      <c r="E14" s="55" t="n"/>
+      <c r="F14" s="55" t="n"/>
+      <c r="G14" s="67" t="n"/>
+      <c r="H14" s="67" t="n"/>
+      <c r="I14" s="67" t="n"/>
+      <c r="J14" s="67" t="n"/>
+      <c r="K14" s="67" t="n"/>
+      <c r="L14" s="67" t="n"/>
+      <c r="M14" s="67" t="n"/>
+      <c r="N14" s="67" t="n"/>
+      <c r="O14" s="67" t="n"/>
       <c r="P14" s="21" t="n"/>
       <c r="Q14" s="21" t="n"/>
       <c r="R14" s="21" t="n"/>
@@ -1805,15 +1996,21 @@
       <c r="CD14" s="7" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="21" t="n"/>
+      <c r="A15" s="55" t="n"/>
+      <c r="B15" s="55" t="n"/>
+      <c r="C15" s="55" t="n"/>
+      <c r="D15" s="55" t="n"/>
+      <c r="E15" s="55" t="n"/>
+      <c r="F15" s="55" t="n"/>
+      <c r="G15" s="67" t="n"/>
+      <c r="H15" s="67" t="n"/>
+      <c r="I15" s="67" t="n"/>
+      <c r="J15" s="67" t="n"/>
+      <c r="K15" s="67" t="n"/>
+      <c r="L15" s="67" t="n"/>
+      <c r="M15" s="67" t="n"/>
+      <c r="N15" s="67" t="n"/>
+      <c r="O15" s="67" t="n"/>
       <c r="P15" s="21" t="n"/>
       <c r="Q15" s="21" t="n"/>
       <c r="R15" s="21" t="n"/>
@@ -1834,15 +2031,21 @@
       <c r="CD15" s="7" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
+      <c r="A16" s="55" t="n"/>
+      <c r="B16" s="55" t="n"/>
+      <c r="C16" s="55" t="n"/>
+      <c r="D16" s="55" t="n"/>
+      <c r="E16" s="55" t="n"/>
+      <c r="F16" s="55" t="n"/>
+      <c r="G16" s="67" t="n"/>
+      <c r="H16" s="67" t="n"/>
+      <c r="I16" s="67" t="n"/>
+      <c r="J16" s="67" t="n"/>
+      <c r="K16" s="67" t="n"/>
+      <c r="L16" s="67" t="n"/>
+      <c r="M16" s="67" t="n"/>
+      <c r="N16" s="67" t="n"/>
+      <c r="O16" s="67" t="n"/>
       <c r="P16" s="21" t="n"/>
       <c r="Q16" s="21" t="n"/>
       <c r="R16" s="21" t="n"/>
@@ -1863,15 +2066,21 @@
       <c r="CD16" s="7" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
+      <c r="A17" s="55" t="n"/>
+      <c r="B17" s="55" t="n"/>
+      <c r="C17" s="55" t="n"/>
+      <c r="D17" s="55" t="n"/>
+      <c r="E17" s="55" t="n"/>
+      <c r="F17" s="55" t="n"/>
+      <c r="G17" s="67" t="n"/>
+      <c r="H17" s="67" t="n"/>
+      <c r="I17" s="67" t="n"/>
+      <c r="J17" s="67" t="n"/>
+      <c r="K17" s="67" t="n"/>
+      <c r="L17" s="67" t="n"/>
+      <c r="M17" s="67" t="n"/>
+      <c r="N17" s="67" t="n"/>
+      <c r="O17" s="67" t="n"/>
       <c r="P17" s="21" t="n"/>
       <c r="Q17" s="21" t="n"/>
       <c r="R17" s="21" t="n"/>
@@ -1892,15 +2101,21 @@
       <c r="CD17" s="7" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
+      <c r="A18" s="55" t="n"/>
+      <c r="B18" s="55" t="n"/>
+      <c r="C18" s="55" t="n"/>
+      <c r="D18" s="55" t="n"/>
+      <c r="E18" s="55" t="n"/>
+      <c r="F18" s="55" t="n"/>
+      <c r="G18" s="67" t="n"/>
+      <c r="H18" s="67" t="n"/>
+      <c r="I18" s="67" t="n"/>
+      <c r="J18" s="67" t="n"/>
+      <c r="K18" s="67" t="n"/>
+      <c r="L18" s="67" t="n"/>
+      <c r="M18" s="67" t="n"/>
+      <c r="N18" s="67" t="n"/>
+      <c r="O18" s="67" t="n"/>
       <c r="P18" s="21" t="n"/>
       <c r="Q18" s="21" t="n"/>
       <c r="R18" s="21" t="n"/>
@@ -1921,15 +2136,21 @@
       <c r="CD18" s="7" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="21" t="n"/>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
+      <c r="A19" s="55" t="n"/>
+      <c r="B19" s="55" t="n"/>
+      <c r="C19" s="55" t="n"/>
+      <c r="D19" s="55" t="n"/>
+      <c r="E19" s="55" t="n"/>
+      <c r="F19" s="55" t="n"/>
+      <c r="G19" s="67" t="n"/>
+      <c r="H19" s="67" t="n"/>
+      <c r="I19" s="67" t="n"/>
+      <c r="J19" s="67" t="n"/>
+      <c r="K19" s="67" t="n"/>
+      <c r="L19" s="67" t="n"/>
+      <c r="M19" s="67" t="n"/>
+      <c r="N19" s="67" t="n"/>
+      <c r="O19" s="67" t="n"/>
       <c r="P19" s="21" t="n"/>
       <c r="Q19" s="21" t="n"/>
       <c r="R19" s="21" t="n"/>
@@ -1950,15 +2171,21 @@
       <c r="CD19" s="7" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
+      <c r="A20" s="55" t="n"/>
+      <c r="B20" s="55" t="n"/>
+      <c r="C20" s="55" t="n"/>
+      <c r="D20" s="55" t="n"/>
+      <c r="E20" s="55" t="n"/>
+      <c r="F20" s="55" t="n"/>
+      <c r="G20" s="67" t="n"/>
+      <c r="H20" s="67" t="n"/>
+      <c r="I20" s="67" t="n"/>
+      <c r="J20" s="67" t="n"/>
+      <c r="K20" s="67" t="n"/>
+      <c r="L20" s="67" t="n"/>
+      <c r="M20" s="67" t="n"/>
+      <c r="N20" s="67" t="n"/>
+      <c r="O20" s="67" t="n"/>
       <c r="P20" s="21" t="n"/>
       <c r="Q20" s="21" t="n"/>
       <c r="R20" s="21" t="n"/>
@@ -1979,15 +2206,21 @@
       <c r="CD20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="G21" s="21" t="n"/>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="21" t="n"/>
-      <c r="K21" s="21" t="n"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="21" t="n"/>
+      <c r="A21" s="55" t="n"/>
+      <c r="B21" s="55" t="n"/>
+      <c r="C21" s="55" t="n"/>
+      <c r="D21" s="55" t="n"/>
+      <c r="E21" s="55" t="n"/>
+      <c r="F21" s="55" t="n"/>
+      <c r="G21" s="67" t="n"/>
+      <c r="H21" s="67" t="n"/>
+      <c r="I21" s="67" t="n"/>
+      <c r="J21" s="67" t="n"/>
+      <c r="K21" s="67" t="n"/>
+      <c r="L21" s="67" t="n"/>
+      <c r="M21" s="67" t="n"/>
+      <c r="N21" s="67" t="n"/>
+      <c r="O21" s="67" t="n"/>
       <c r="P21" s="21" t="n"/>
       <c r="Q21" s="21" t="n"/>
       <c r="R21" s="41" t="inlineStr">
@@ -1995,140 +2228,158 @@
           <t>Elaborado por:</t>
         </is>
       </c>
-      <c r="S21" s="44" t="n"/>
-      <c r="T21" s="44" t="n"/>
-      <c r="U21" s="44" t="n"/>
-      <c r="V21" s="44" t="n"/>
-      <c r="W21" s="44" t="n"/>
-      <c r="X21" s="44" t="n"/>
-      <c r="Y21" s="44" t="n"/>
-      <c r="Z21" s="44" t="n"/>
-      <c r="AA21" s="44" t="n"/>
-      <c r="AB21" s="44" t="n"/>
-      <c r="AC21" s="44" t="n"/>
-      <c r="AD21" s="44" t="n"/>
-      <c r="AE21" s="45" t="n"/>
+      <c r="S21" s="48" t="n"/>
+      <c r="T21" s="48" t="n"/>
+      <c r="U21" s="48" t="n"/>
+      <c r="V21" s="48" t="n"/>
+      <c r="W21" s="48" t="n"/>
+      <c r="X21" s="48" t="n"/>
+      <c r="Y21" s="48" t="n"/>
+      <c r="Z21" s="48" t="n"/>
+      <c r="AA21" s="48" t="n"/>
+      <c r="AB21" s="48" t="n"/>
+      <c r="AC21" s="48" t="n"/>
+      <c r="AD21" s="48" t="n"/>
+      <c r="AE21" s="49" t="n"/>
       <c r="AF21" s="41" t="inlineStr">
         <is>
           <t>Revisado por:</t>
         </is>
       </c>
-      <c r="AG21" s="44" t="n"/>
-      <c r="AH21" s="44" t="n"/>
-      <c r="AI21" s="44" t="n"/>
-      <c r="AJ21" s="44" t="n"/>
-      <c r="AK21" s="44" t="n"/>
-      <c r="AL21" s="44" t="n"/>
-      <c r="AM21" s="44" t="n"/>
-      <c r="AN21" s="44" t="n"/>
-      <c r="AO21" s="44" t="n"/>
-      <c r="AP21" s="44" t="n"/>
-      <c r="AQ21" s="44" t="n"/>
-      <c r="AR21" s="44" t="n"/>
-      <c r="AS21" s="45" t="n"/>
+      <c r="AG21" s="48" t="n"/>
+      <c r="AH21" s="48" t="n"/>
+      <c r="AI21" s="48" t="n"/>
+      <c r="AJ21" s="48" t="n"/>
+      <c r="AK21" s="48" t="n"/>
+      <c r="AL21" s="48" t="n"/>
+      <c r="AM21" s="48" t="n"/>
+      <c r="AN21" s="48" t="n"/>
+      <c r="AO21" s="48" t="n"/>
+      <c r="AP21" s="48" t="n"/>
+      <c r="AQ21" s="48" t="n"/>
+      <c r="AR21" s="48" t="n"/>
+      <c r="AS21" s="49" t="n"/>
       <c r="AT21" s="41" t="inlineStr">
         <is>
           <t>Aprobado por:</t>
         </is>
       </c>
-      <c r="AU21" s="44" t="n"/>
-      <c r="AV21" s="44" t="n"/>
-      <c r="AW21" s="44" t="n"/>
-      <c r="AX21" s="44" t="n"/>
-      <c r="AY21" s="44" t="n"/>
-      <c r="AZ21" s="44" t="n"/>
-      <c r="BA21" s="44" t="n"/>
-      <c r="BB21" s="44" t="n"/>
-      <c r="BC21" s="44" t="n"/>
-      <c r="BD21" s="44" t="n"/>
-      <c r="BE21" s="44" t="n"/>
-      <c r="BF21" s="44" t="n"/>
-      <c r="BG21" s="45" t="n"/>
+      <c r="AU21" s="48" t="n"/>
+      <c r="AV21" s="48" t="n"/>
+      <c r="AW21" s="48" t="n"/>
+      <c r="AX21" s="48" t="n"/>
+      <c r="AY21" s="48" t="n"/>
+      <c r="AZ21" s="48" t="n"/>
+      <c r="BA21" s="48" t="n"/>
+      <c r="BB21" s="48" t="n"/>
+      <c r="BC21" s="48" t="n"/>
+      <c r="BD21" s="48" t="n"/>
+      <c r="BE21" s="48" t="n"/>
+      <c r="BF21" s="48" t="n"/>
+      <c r="BG21" s="49" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="G22" s="21" t="n"/>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
+      <c r="A22" s="55" t="n"/>
+      <c r="B22" s="55" t="n"/>
+      <c r="C22" s="55" t="n"/>
+      <c r="D22" s="55" t="n"/>
+      <c r="E22" s="55" t="n"/>
+      <c r="F22" s="55" t="n"/>
+      <c r="G22" s="67" t="n"/>
+      <c r="H22" s="67" t="n"/>
+      <c r="I22" s="67" t="n"/>
+      <c r="J22" s="67" t="n"/>
+      <c r="K22" s="67" t="n"/>
+      <c r="L22" s="67" t="n"/>
+      <c r="M22" s="67" t="n"/>
+      <c r="N22" s="67" t="n"/>
+      <c r="O22" s="67" t="n"/>
       <c r="P22" s="21" t="n"/>
       <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="50" t="n"/>
-      <c r="AE22" s="51" t="n"/>
-      <c r="AF22" s="50" t="n"/>
-      <c r="AS22" s="51" t="n"/>
-      <c r="AT22" s="50" t="n"/>
-      <c r="BG22" s="51" t="n"/>
+      <c r="R22" s="68" t="n"/>
+      <c r="AE22" s="57" t="n"/>
+      <c r="AF22" s="68" t="n"/>
+      <c r="AS22" s="57" t="n"/>
+      <c r="AT22" s="68" t="n"/>
+      <c r="BG22" s="57" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
-      <c r="K23" s="21" t="n"/>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="21" t="n"/>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="21" t="n"/>
+      <c r="A23" s="55" t="n"/>
+      <c r="B23" s="55" t="n"/>
+      <c r="C23" s="55" t="n"/>
+      <c r="D23" s="55" t="n"/>
+      <c r="E23" s="55" t="n"/>
+      <c r="F23" s="55" t="n"/>
+      <c r="G23" s="67" t="n"/>
+      <c r="H23" s="67" t="n"/>
+      <c r="I23" s="67" t="n"/>
+      <c r="J23" s="67" t="n"/>
+      <c r="K23" s="67" t="n"/>
+      <c r="L23" s="67" t="n"/>
+      <c r="M23" s="67" t="n"/>
+      <c r="N23" s="67" t="n"/>
+      <c r="O23" s="67" t="n"/>
       <c r="P23" s="21" t="n"/>
       <c r="Q23" s="21" t="n"/>
-      <c r="R23" s="52" t="n"/>
-      <c r="S23" s="53" t="n"/>
-      <c r="T23" s="53" t="n"/>
-      <c r="U23" s="53" t="n"/>
-      <c r="V23" s="53" t="n"/>
-      <c r="W23" s="53" t="n"/>
-      <c r="X23" s="53" t="n"/>
-      <c r="Y23" s="53" t="n"/>
-      <c r="Z23" s="53" t="n"/>
-      <c r="AA23" s="53" t="n"/>
-      <c r="AB23" s="53" t="n"/>
-      <c r="AC23" s="53" t="n"/>
-      <c r="AD23" s="53" t="n"/>
-      <c r="AE23" s="54" t="n"/>
-      <c r="AF23" s="52" t="n"/>
-      <c r="AG23" s="53" t="n"/>
-      <c r="AH23" s="53" t="n"/>
-      <c r="AI23" s="53" t="n"/>
-      <c r="AJ23" s="53" t="n"/>
-      <c r="AK23" s="53" t="n"/>
-      <c r="AL23" s="53" t="n"/>
-      <c r="AM23" s="53" t="n"/>
-      <c r="AN23" s="53" t="n"/>
-      <c r="AO23" s="53" t="n"/>
-      <c r="AP23" s="53" t="n"/>
-      <c r="AQ23" s="53" t="n"/>
-      <c r="AR23" s="53" t="n"/>
-      <c r="AS23" s="54" t="n"/>
-      <c r="AT23" s="52" t="n"/>
-      <c r="AU23" s="53" t="n"/>
-      <c r="AV23" s="53" t="n"/>
-      <c r="AW23" s="53" t="n"/>
-      <c r="AX23" s="53" t="n"/>
-      <c r="AY23" s="53" t="n"/>
-      <c r="AZ23" s="53" t="n"/>
-      <c r="BA23" s="53" t="n"/>
-      <c r="BB23" s="53" t="n"/>
-      <c r="BC23" s="53" t="n"/>
-      <c r="BD23" s="53" t="n"/>
-      <c r="BE23" s="53" t="n"/>
-      <c r="BF23" s="53" t="n"/>
-      <c r="BG23" s="54" t="n"/>
+      <c r="R23" s="58" t="n"/>
+      <c r="S23" s="59" t="n"/>
+      <c r="T23" s="59" t="n"/>
+      <c r="U23" s="59" t="n"/>
+      <c r="V23" s="59" t="n"/>
+      <c r="W23" s="59" t="n"/>
+      <c r="X23" s="59" t="n"/>
+      <c r="Y23" s="59" t="n"/>
+      <c r="Z23" s="59" t="n"/>
+      <c r="AA23" s="59" t="n"/>
+      <c r="AB23" s="59" t="n"/>
+      <c r="AC23" s="59" t="n"/>
+      <c r="AD23" s="59" t="n"/>
+      <c r="AE23" s="60" t="n"/>
+      <c r="AF23" s="58" t="n"/>
+      <c r="AG23" s="59" t="n"/>
+      <c r="AH23" s="59" t="n"/>
+      <c r="AI23" s="59" t="n"/>
+      <c r="AJ23" s="59" t="n"/>
+      <c r="AK23" s="59" t="n"/>
+      <c r="AL23" s="59" t="n"/>
+      <c r="AM23" s="59" t="n"/>
+      <c r="AN23" s="59" t="n"/>
+      <c r="AO23" s="59" t="n"/>
+      <c r="AP23" s="59" t="n"/>
+      <c r="AQ23" s="59" t="n"/>
+      <c r="AR23" s="59" t="n"/>
+      <c r="AS23" s="60" t="n"/>
+      <c r="AT23" s="58" t="n"/>
+      <c r="AU23" s="59" t="n"/>
+      <c r="AV23" s="59" t="n"/>
+      <c r="AW23" s="59" t="n"/>
+      <c r="AX23" s="59" t="n"/>
+      <c r="AY23" s="59" t="n"/>
+      <c r="AZ23" s="59" t="n"/>
+      <c r="BA23" s="59" t="n"/>
+      <c r="BB23" s="59" t="n"/>
+      <c r="BC23" s="59" t="n"/>
+      <c r="BD23" s="59" t="n"/>
+      <c r="BE23" s="59" t="n"/>
+      <c r="BF23" s="59" t="n"/>
+      <c r="BG23" s="60" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
+      <c r="A24" s="55" t="n"/>
+      <c r="B24" s="55" t="n"/>
+      <c r="C24" s="55" t="n"/>
+      <c r="D24" s="55" t="n"/>
+      <c r="E24" s="55" t="n"/>
+      <c r="F24" s="55" t="n"/>
+      <c r="G24" s="67" t="n"/>
+      <c r="H24" s="67" t="n"/>
+      <c r="I24" s="67" t="n"/>
+      <c r="J24" s="67" t="n"/>
+      <c r="K24" s="67" t="n"/>
+      <c r="L24" s="67" t="n"/>
+      <c r="M24" s="67" t="n"/>
+      <c r="N24" s="67" t="n"/>
+      <c r="O24" s="67" t="n"/>
       <c r="P24" s="21" t="n"/>
       <c r="Q24" s="21" t="n"/>
       <c r="R24" s="23" t="inlineStr">
@@ -2136,270 +2387,306 @@
           <t>J.ARBOLEDA</t>
         </is>
       </c>
-      <c r="S24" s="44" t="n"/>
-      <c r="T24" s="44" t="n"/>
-      <c r="U24" s="44" t="n"/>
-      <c r="V24" s="44" t="n"/>
-      <c r="W24" s="44" t="n"/>
-      <c r="X24" s="44" t="n"/>
-      <c r="Y24" s="44" t="n"/>
-      <c r="Z24" s="44" t="n"/>
-      <c r="AA24" s="44" t="n"/>
-      <c r="AB24" s="44" t="n"/>
-      <c r="AC24" s="44" t="n"/>
-      <c r="AD24" s="44" t="n"/>
-      <c r="AE24" s="45" t="n"/>
+      <c r="S24" s="48" t="n"/>
+      <c r="T24" s="48" t="n"/>
+      <c r="U24" s="48" t="n"/>
+      <c r="V24" s="48" t="n"/>
+      <c r="W24" s="48" t="n"/>
+      <c r="X24" s="48" t="n"/>
+      <c r="Y24" s="48" t="n"/>
+      <c r="Z24" s="48" t="n"/>
+      <c r="AA24" s="48" t="n"/>
+      <c r="AB24" s="48" t="n"/>
+      <c r="AC24" s="48" t="n"/>
+      <c r="AD24" s="48" t="n"/>
+      <c r="AE24" s="49" t="n"/>
       <c r="AF24" s="24" t="n"/>
-      <c r="AG24" s="44" t="n"/>
-      <c r="AH24" s="44" t="n"/>
-      <c r="AI24" s="44" t="n"/>
-      <c r="AJ24" s="44" t="n"/>
-      <c r="AK24" s="44" t="n"/>
-      <c r="AL24" s="44" t="n"/>
-      <c r="AM24" s="44" t="n"/>
-      <c r="AN24" s="44" t="n"/>
-      <c r="AO24" s="44" t="n"/>
-      <c r="AP24" s="44" t="n"/>
-      <c r="AQ24" s="44" t="n"/>
-      <c r="AR24" s="44" t="n"/>
-      <c r="AS24" s="45" t="n"/>
+      <c r="AG24" s="48" t="n"/>
+      <c r="AH24" s="48" t="n"/>
+      <c r="AI24" s="48" t="n"/>
+      <c r="AJ24" s="48" t="n"/>
+      <c r="AK24" s="48" t="n"/>
+      <c r="AL24" s="48" t="n"/>
+      <c r="AM24" s="48" t="n"/>
+      <c r="AN24" s="48" t="n"/>
+      <c r="AO24" s="48" t="n"/>
+      <c r="AP24" s="48" t="n"/>
+      <c r="AQ24" s="48" t="n"/>
+      <c r="AR24" s="48" t="n"/>
+      <c r="AS24" s="49" t="n"/>
       <c r="AT24" s="24" t="n"/>
-      <c r="AU24" s="44" t="n"/>
-      <c r="AV24" s="44" t="n"/>
-      <c r="AW24" s="44" t="n"/>
-      <c r="AX24" s="44" t="n"/>
-      <c r="AY24" s="44" t="n"/>
-      <c r="AZ24" s="44" t="n"/>
-      <c r="BA24" s="44" t="n"/>
-      <c r="BB24" s="44" t="n"/>
-      <c r="BC24" s="44" t="n"/>
-      <c r="BD24" s="44" t="n"/>
-      <c r="BE24" s="44" t="n"/>
-      <c r="BF24" s="44" t="n"/>
-      <c r="BG24" s="45" t="n"/>
+      <c r="AU24" s="48" t="n"/>
+      <c r="AV24" s="48" t="n"/>
+      <c r="AW24" s="48" t="n"/>
+      <c r="AX24" s="48" t="n"/>
+      <c r="AY24" s="48" t="n"/>
+      <c r="AZ24" s="48" t="n"/>
+      <c r="BA24" s="48" t="n"/>
+      <c r="BB24" s="48" t="n"/>
+      <c r="BC24" s="48" t="n"/>
+      <c r="BD24" s="48" t="n"/>
+      <c r="BE24" s="48" t="n"/>
+      <c r="BF24" s="48" t="n"/>
+      <c r="BG24" s="49" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="21" t="n"/>
-      <c r="K25" s="21" t="n"/>
-      <c r="L25" s="21" t="n"/>
-      <c r="M25" s="21" t="n"/>
-      <c r="N25" s="21" t="n"/>
-      <c r="O25" s="21" t="n"/>
+      <c r="A25" s="55" t="n"/>
+      <c r="B25" s="55" t="n"/>
+      <c r="C25" s="55" t="n"/>
+      <c r="D25" s="55" t="n"/>
+      <c r="E25" s="55" t="n"/>
+      <c r="F25" s="55" t="n"/>
+      <c r="G25" s="67" t="n"/>
+      <c r="H25" s="67" t="n"/>
+      <c r="I25" s="67" t="n"/>
+      <c r="J25" s="67" t="n"/>
+      <c r="K25" s="67" t="n"/>
+      <c r="L25" s="67" t="n"/>
+      <c r="M25" s="67" t="n"/>
+      <c r="N25" s="67" t="n"/>
+      <c r="O25" s="67" t="n"/>
       <c r="P25" s="21" t="n"/>
       <c r="Q25" s="21" t="n"/>
-      <c r="R25" s="50" t="n"/>
-      <c r="AE25" s="51" t="n"/>
-      <c r="AF25" s="50" t="n"/>
-      <c r="AS25" s="51" t="n"/>
-      <c r="AT25" s="50" t="n"/>
-      <c r="BG25" s="51" t="n"/>
+      <c r="R25" s="68" t="n"/>
+      <c r="AE25" s="57" t="n"/>
+      <c r="AF25" s="68" t="n"/>
+      <c r="AS25" s="57" t="n"/>
+      <c r="AT25" s="68" t="n"/>
+      <c r="BG25" s="57" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="21" t="n"/>
-      <c r="K26" s="21" t="n"/>
-      <c r="L26" s="21" t="n"/>
-      <c r="M26" s="21" t="n"/>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="21" t="n"/>
+      <c r="A26" s="55" t="n"/>
+      <c r="B26" s="55" t="n"/>
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="55" t="n"/>
+      <c r="E26" s="55" t="n"/>
+      <c r="F26" s="55" t="n"/>
+      <c r="G26" s="67" t="n"/>
+      <c r="H26" s="67" t="n"/>
+      <c r="I26" s="67" t="n"/>
+      <c r="J26" s="67" t="n"/>
+      <c r="K26" s="67" t="n"/>
+      <c r="L26" s="67" t="n"/>
+      <c r="M26" s="67" t="n"/>
+      <c r="N26" s="67" t="n"/>
+      <c r="O26" s="67" t="n"/>
       <c r="P26" s="21" t="n"/>
       <c r="Q26" s="21" t="n"/>
-      <c r="R26" s="52" t="n"/>
-      <c r="S26" s="53" t="n"/>
-      <c r="T26" s="53" t="n"/>
-      <c r="U26" s="53" t="n"/>
-      <c r="V26" s="53" t="n"/>
-      <c r="W26" s="53" t="n"/>
-      <c r="X26" s="53" t="n"/>
-      <c r="Y26" s="53" t="n"/>
-      <c r="Z26" s="53" t="n"/>
-      <c r="AA26" s="53" t="n"/>
-      <c r="AB26" s="53" t="n"/>
-      <c r="AC26" s="53" t="n"/>
-      <c r="AD26" s="53" t="n"/>
-      <c r="AE26" s="54" t="n"/>
-      <c r="AF26" s="52" t="n"/>
-      <c r="AG26" s="53" t="n"/>
-      <c r="AH26" s="53" t="n"/>
-      <c r="AI26" s="53" t="n"/>
-      <c r="AJ26" s="53" t="n"/>
-      <c r="AK26" s="53" t="n"/>
-      <c r="AL26" s="53" t="n"/>
-      <c r="AM26" s="53" t="n"/>
-      <c r="AN26" s="53" t="n"/>
-      <c r="AO26" s="53" t="n"/>
-      <c r="AP26" s="53" t="n"/>
-      <c r="AQ26" s="53" t="n"/>
-      <c r="AR26" s="53" t="n"/>
-      <c r="AS26" s="54" t="n"/>
-      <c r="AT26" s="52" t="n"/>
-      <c r="AU26" s="53" t="n"/>
-      <c r="AV26" s="53" t="n"/>
-      <c r="AW26" s="53" t="n"/>
-      <c r="AX26" s="53" t="n"/>
-      <c r="AY26" s="53" t="n"/>
-      <c r="AZ26" s="53" t="n"/>
-      <c r="BA26" s="53" t="n"/>
-      <c r="BB26" s="53" t="n"/>
-      <c r="BC26" s="53" t="n"/>
-      <c r="BD26" s="53" t="n"/>
-      <c r="BE26" s="53" t="n"/>
-      <c r="BF26" s="53" t="n"/>
-      <c r="BG26" s="54" t="n"/>
+      <c r="R26" s="58" t="n"/>
+      <c r="S26" s="59" t="n"/>
+      <c r="T26" s="59" t="n"/>
+      <c r="U26" s="59" t="n"/>
+      <c r="V26" s="59" t="n"/>
+      <c r="W26" s="59" t="n"/>
+      <c r="X26" s="59" t="n"/>
+      <c r="Y26" s="59" t="n"/>
+      <c r="Z26" s="59" t="n"/>
+      <c r="AA26" s="59" t="n"/>
+      <c r="AB26" s="59" t="n"/>
+      <c r="AC26" s="59" t="n"/>
+      <c r="AD26" s="59" t="n"/>
+      <c r="AE26" s="60" t="n"/>
+      <c r="AF26" s="58" t="n"/>
+      <c r="AG26" s="59" t="n"/>
+      <c r="AH26" s="59" t="n"/>
+      <c r="AI26" s="59" t="n"/>
+      <c r="AJ26" s="59" t="n"/>
+      <c r="AK26" s="59" t="n"/>
+      <c r="AL26" s="59" t="n"/>
+      <c r="AM26" s="59" t="n"/>
+      <c r="AN26" s="59" t="n"/>
+      <c r="AO26" s="59" t="n"/>
+      <c r="AP26" s="59" t="n"/>
+      <c r="AQ26" s="59" t="n"/>
+      <c r="AR26" s="59" t="n"/>
+      <c r="AS26" s="60" t="n"/>
+      <c r="AT26" s="58" t="n"/>
+      <c r="AU26" s="59" t="n"/>
+      <c r="AV26" s="59" t="n"/>
+      <c r="AW26" s="59" t="n"/>
+      <c r="AX26" s="59" t="n"/>
+      <c r="AY26" s="59" t="n"/>
+      <c r="AZ26" s="59" t="n"/>
+      <c r="BA26" s="59" t="n"/>
+      <c r="BB26" s="59" t="n"/>
+      <c r="BC26" s="59" t="n"/>
+      <c r="BD26" s="59" t="n"/>
+      <c r="BE26" s="59" t="n"/>
+      <c r="BF26" s="59" t="n"/>
+      <c r="BG26" s="60" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="G27" s="21" t="n"/>
-      <c r="H27" s="21" t="n"/>
-      <c r="I27" s="21" t="n"/>
-      <c r="J27" s="21" t="n"/>
-      <c r="K27" s="21" t="n"/>
-      <c r="L27" s="21" t="n"/>
-      <c r="M27" s="21" t="n"/>
-      <c r="N27" s="21" t="n"/>
-      <c r="O27" s="21" t="n"/>
+      <c r="A27" s="55" t="n"/>
+      <c r="B27" s="55" t="n"/>
+      <c r="C27" s="55" t="n"/>
+      <c r="D27" s="55" t="n"/>
+      <c r="E27" s="55" t="n"/>
+      <c r="F27" s="55" t="n"/>
+      <c r="G27" s="67" t="n"/>
+      <c r="H27" s="67" t="n"/>
+      <c r="I27" s="67" t="n"/>
+      <c r="J27" s="67" t="n"/>
+      <c r="K27" s="67" t="n"/>
+      <c r="L27" s="67" t="n"/>
+      <c r="M27" s="67" t="n"/>
+      <c r="N27" s="67" t="n"/>
+      <c r="O27" s="67" t="n"/>
       <c r="P27" s="21" t="n"/>
       <c r="Q27" s="21" t="n"/>
       <c r="R27" s="24">
         <f>"Fecha :"&amp;BO3</f>
         <v/>
       </c>
-      <c r="S27" s="44" t="n"/>
-      <c r="T27" s="44" t="n"/>
-      <c r="U27" s="44" t="n"/>
-      <c r="V27" s="44" t="n"/>
-      <c r="W27" s="44" t="n"/>
-      <c r="X27" s="44" t="n"/>
-      <c r="Y27" s="44" t="n"/>
-      <c r="Z27" s="44" t="n"/>
-      <c r="AA27" s="44" t="n"/>
-      <c r="AB27" s="44" t="n"/>
-      <c r="AC27" s="44" t="n"/>
-      <c r="AD27" s="44" t="n"/>
-      <c r="AE27" s="45" t="n"/>
+      <c r="S27" s="48" t="n"/>
+      <c r="T27" s="48" t="n"/>
+      <c r="U27" s="48" t="n"/>
+      <c r="V27" s="48" t="n"/>
+      <c r="W27" s="48" t="n"/>
+      <c r="X27" s="48" t="n"/>
+      <c r="Y27" s="48" t="n"/>
+      <c r="Z27" s="48" t="n"/>
+      <c r="AA27" s="48" t="n"/>
+      <c r="AB27" s="48" t="n"/>
+      <c r="AC27" s="48" t="n"/>
+      <c r="AD27" s="48" t="n"/>
+      <c r="AE27" s="49" t="n"/>
       <c r="AF27" s="24">
         <f>"Fecha :"&amp;CC1</f>
         <v/>
       </c>
-      <c r="AG27" s="44" t="n"/>
-      <c r="AH27" s="44" t="n"/>
-      <c r="AI27" s="44" t="n"/>
-      <c r="AJ27" s="44" t="n"/>
-      <c r="AK27" s="44" t="n"/>
-      <c r="AL27" s="44" t="n"/>
-      <c r="AM27" s="44" t="n"/>
-      <c r="AN27" s="44" t="n"/>
-      <c r="AO27" s="44" t="n"/>
-      <c r="AP27" s="44" t="n"/>
-      <c r="AQ27" s="44" t="n"/>
-      <c r="AR27" s="44" t="n"/>
-      <c r="AS27" s="45" t="n"/>
+      <c r="AG27" s="48" t="n"/>
+      <c r="AH27" s="48" t="n"/>
+      <c r="AI27" s="48" t="n"/>
+      <c r="AJ27" s="48" t="n"/>
+      <c r="AK27" s="48" t="n"/>
+      <c r="AL27" s="48" t="n"/>
+      <c r="AM27" s="48" t="n"/>
+      <c r="AN27" s="48" t="n"/>
+      <c r="AO27" s="48" t="n"/>
+      <c r="AP27" s="48" t="n"/>
+      <c r="AQ27" s="48" t="n"/>
+      <c r="AR27" s="48" t="n"/>
+      <c r="AS27" s="49" t="n"/>
       <c r="AT27" s="24">
         <f>"Fecha :"&amp;CC2</f>
         <v/>
       </c>
-      <c r="AU27" s="44" t="n"/>
-      <c r="AV27" s="44" t="n"/>
-      <c r="AW27" s="44" t="n"/>
-      <c r="AX27" s="44" t="n"/>
-      <c r="AY27" s="44" t="n"/>
-      <c r="AZ27" s="44" t="n"/>
-      <c r="BA27" s="44" t="n"/>
-      <c r="BB27" s="44" t="n"/>
-      <c r="BC27" s="44" t="n"/>
-      <c r="BD27" s="44" t="n"/>
-      <c r="BE27" s="44" t="n"/>
-      <c r="BF27" s="44" t="n"/>
-      <c r="BG27" s="45" t="n"/>
+      <c r="AU27" s="48" t="n"/>
+      <c r="AV27" s="48" t="n"/>
+      <c r="AW27" s="48" t="n"/>
+      <c r="AX27" s="48" t="n"/>
+      <c r="AY27" s="48" t="n"/>
+      <c r="AZ27" s="48" t="n"/>
+      <c r="BA27" s="48" t="n"/>
+      <c r="BB27" s="48" t="n"/>
+      <c r="BC27" s="48" t="n"/>
+      <c r="BD27" s="48" t="n"/>
+      <c r="BE27" s="48" t="n"/>
+      <c r="BF27" s="48" t="n"/>
+      <c r="BG27" s="49" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="G28" s="21" t="n"/>
-      <c r="H28" s="21" t="n"/>
-      <c r="I28" s="21" t="n"/>
-      <c r="J28" s="21" t="n"/>
-      <c r="K28" s="21" t="n"/>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="21" t="n"/>
-      <c r="N28" s="21" t="n"/>
-      <c r="O28" s="21" t="n"/>
+      <c r="A28" s="55" t="n"/>
+      <c r="B28" s="55" t="n"/>
+      <c r="C28" s="55" t="n"/>
+      <c r="D28" s="55" t="n"/>
+      <c r="E28" s="55" t="n"/>
+      <c r="F28" s="55" t="n"/>
+      <c r="G28" s="67" t="n"/>
+      <c r="H28" s="67" t="n"/>
+      <c r="I28" s="67" t="n"/>
+      <c r="J28" s="67" t="n"/>
+      <c r="K28" s="67" t="n"/>
+      <c r="L28" s="67" t="n"/>
+      <c r="M28" s="67" t="n"/>
+      <c r="N28" s="67" t="n"/>
+      <c r="O28" s="67" t="n"/>
       <c r="P28" s="21" t="n"/>
       <c r="Q28" s="21" t="n"/>
-      <c r="R28" s="50" t="n"/>
-      <c r="AE28" s="51" t="n"/>
-      <c r="AF28" s="50" t="n"/>
-      <c r="AS28" s="51" t="n"/>
-      <c r="AT28" s="50" t="n"/>
-      <c r="BG28" s="51" t="n"/>
+      <c r="R28" s="68" t="n"/>
+      <c r="AE28" s="57" t="n"/>
+      <c r="AF28" s="68" t="n"/>
+      <c r="AS28" s="57" t="n"/>
+      <c r="AT28" s="68" t="n"/>
+      <c r="BG28" s="57" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="G29" s="21" t="n"/>
-      <c r="H29" s="21" t="n"/>
-      <c r="I29" s="21" t="n"/>
-      <c r="J29" s="21" t="n"/>
-      <c r="K29" s="21" t="n"/>
-      <c r="L29" s="21" t="n"/>
-      <c r="M29" s="21" t="n"/>
-      <c r="N29" s="21" t="n"/>
-      <c r="O29" s="21" t="n"/>
+      <c r="A29" s="55" t="n"/>
+      <c r="B29" s="55" t="n"/>
+      <c r="C29" s="55" t="n"/>
+      <c r="D29" s="55" t="n"/>
+      <c r="E29" s="55" t="n"/>
+      <c r="F29" s="55" t="n"/>
+      <c r="G29" s="67" t="n"/>
+      <c r="H29" s="67" t="n"/>
+      <c r="I29" s="67" t="n"/>
+      <c r="J29" s="67" t="n"/>
+      <c r="K29" s="67" t="n"/>
+      <c r="L29" s="67" t="n"/>
+      <c r="M29" s="67" t="n"/>
+      <c r="N29" s="67" t="n"/>
+      <c r="O29" s="67" t="n"/>
       <c r="P29" s="21" t="n"/>
       <c r="Q29" s="21" t="n"/>
-      <c r="R29" s="52" t="n"/>
-      <c r="S29" s="53" t="n"/>
-      <c r="T29" s="53" t="n"/>
-      <c r="U29" s="53" t="n"/>
-      <c r="V29" s="53" t="n"/>
-      <c r="W29" s="53" t="n"/>
-      <c r="X29" s="53" t="n"/>
-      <c r="Y29" s="53" t="n"/>
-      <c r="Z29" s="53" t="n"/>
-      <c r="AA29" s="53" t="n"/>
-      <c r="AB29" s="53" t="n"/>
-      <c r="AC29" s="53" t="n"/>
-      <c r="AD29" s="53" t="n"/>
-      <c r="AE29" s="54" t="n"/>
-      <c r="AF29" s="52" t="n"/>
-      <c r="AG29" s="53" t="n"/>
-      <c r="AH29" s="53" t="n"/>
-      <c r="AI29" s="53" t="n"/>
-      <c r="AJ29" s="53" t="n"/>
-      <c r="AK29" s="53" t="n"/>
-      <c r="AL29" s="53" t="n"/>
-      <c r="AM29" s="53" t="n"/>
-      <c r="AN29" s="53" t="n"/>
-      <c r="AO29" s="53" t="n"/>
-      <c r="AP29" s="53" t="n"/>
-      <c r="AQ29" s="53" t="n"/>
-      <c r="AR29" s="53" t="n"/>
-      <c r="AS29" s="54" t="n"/>
-      <c r="AT29" s="52" t="n"/>
-      <c r="AU29" s="53" t="n"/>
-      <c r="AV29" s="53" t="n"/>
-      <c r="AW29" s="53" t="n"/>
-      <c r="AX29" s="53" t="n"/>
-      <c r="AY29" s="53" t="n"/>
-      <c r="AZ29" s="53" t="n"/>
-      <c r="BA29" s="53" t="n"/>
-      <c r="BB29" s="53" t="n"/>
-      <c r="BC29" s="53" t="n"/>
-      <c r="BD29" s="53" t="n"/>
-      <c r="BE29" s="53" t="n"/>
-      <c r="BF29" s="53" t="n"/>
-      <c r="BG29" s="54" t="n"/>
+      <c r="R29" s="58" t="n"/>
+      <c r="S29" s="59" t="n"/>
+      <c r="T29" s="59" t="n"/>
+      <c r="U29" s="59" t="n"/>
+      <c r="V29" s="59" t="n"/>
+      <c r="W29" s="59" t="n"/>
+      <c r="X29" s="59" t="n"/>
+      <c r="Y29" s="59" t="n"/>
+      <c r="Z29" s="59" t="n"/>
+      <c r="AA29" s="59" t="n"/>
+      <c r="AB29" s="59" t="n"/>
+      <c r="AC29" s="59" t="n"/>
+      <c r="AD29" s="59" t="n"/>
+      <c r="AE29" s="60" t="n"/>
+      <c r="AF29" s="58" t="n"/>
+      <c r="AG29" s="59" t="n"/>
+      <c r="AH29" s="59" t="n"/>
+      <c r="AI29" s="59" t="n"/>
+      <c r="AJ29" s="59" t="n"/>
+      <c r="AK29" s="59" t="n"/>
+      <c r="AL29" s="59" t="n"/>
+      <c r="AM29" s="59" t="n"/>
+      <c r="AN29" s="59" t="n"/>
+      <c r="AO29" s="59" t="n"/>
+      <c r="AP29" s="59" t="n"/>
+      <c r="AQ29" s="59" t="n"/>
+      <c r="AR29" s="59" t="n"/>
+      <c r="AS29" s="60" t="n"/>
+      <c r="AT29" s="58" t="n"/>
+      <c r="AU29" s="59" t="n"/>
+      <c r="AV29" s="59" t="n"/>
+      <c r="AW29" s="59" t="n"/>
+      <c r="AX29" s="59" t="n"/>
+      <c r="AY29" s="59" t="n"/>
+      <c r="AZ29" s="59" t="n"/>
+      <c r="BA29" s="59" t="n"/>
+      <c r="BB29" s="59" t="n"/>
+      <c r="BC29" s="59" t="n"/>
+      <c r="BD29" s="59" t="n"/>
+      <c r="BE29" s="59" t="n"/>
+      <c r="BF29" s="59" t="n"/>
+      <c r="BG29" s="60" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="G30" s="21" t="n"/>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
-      <c r="J30" s="21" t="n"/>
-      <c r="K30" s="21" t="n"/>
-      <c r="L30" s="21" t="n"/>
-      <c r="M30" s="21" t="n"/>
-      <c r="N30" s="21" t="n"/>
-      <c r="O30" s="21" t="n"/>
+      <c r="A30" s="55" t="n"/>
+      <c r="B30" s="55" t="n"/>
+      <c r="C30" s="55" t="n"/>
+      <c r="D30" s="55" t="n"/>
+      <c r="E30" s="55" t="n"/>
+      <c r="F30" s="55" t="n"/>
+      <c r="G30" s="67" t="n"/>
+      <c r="H30" s="67" t="n"/>
+      <c r="I30" s="67" t="n"/>
+      <c r="J30" s="67" t="n"/>
+      <c r="K30" s="67" t="n"/>
+      <c r="L30" s="67" t="n"/>
+      <c r="M30" s="67" t="n"/>
+      <c r="N30" s="67" t="n"/>
+      <c r="O30" s="67" t="n"/>
       <c r="P30" s="21" t="n"/>
       <c r="Q30" s="21" t="n"/>
       <c r="R30" s="21" t="n"/>
@@ -2419,15 +2706,21 @@
       <c r="AF30" s="21" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="G31" s="21" t="n"/>
-      <c r="H31" s="21" t="n"/>
-      <c r="I31" s="21" t="n"/>
-      <c r="J31" s="21" t="n"/>
-      <c r="K31" s="21" t="n"/>
-      <c r="L31" s="21" t="n"/>
-      <c r="M31" s="21" t="n"/>
-      <c r="N31" s="21" t="n"/>
-      <c r="O31" s="21" t="n"/>
+      <c r="A31" s="55" t="n"/>
+      <c r="B31" s="55" t="n"/>
+      <c r="C31" s="55" t="n"/>
+      <c r="D31" s="55" t="n"/>
+      <c r="E31" s="55" t="n"/>
+      <c r="F31" s="55" t="n"/>
+      <c r="G31" s="67" t="n"/>
+      <c r="H31" s="67" t="n"/>
+      <c r="I31" s="67" t="n"/>
+      <c r="J31" s="67" t="n"/>
+      <c r="K31" s="67" t="n"/>
+      <c r="L31" s="67" t="n"/>
+      <c r="M31" s="67" t="n"/>
+      <c r="N31" s="67" t="n"/>
+      <c r="O31" s="67" t="n"/>
       <c r="P31" s="21" t="n"/>
       <c r="Q31" s="21" t="n"/>
       <c r="R31" s="21" t="n"/>
@@ -2447,15 +2740,21 @@
       <c r="AF31" s="21" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="G32" s="21" t="n"/>
-      <c r="H32" s="21" t="n"/>
-      <c r="I32" s="21" t="n"/>
-      <c r="J32" s="21" t="n"/>
-      <c r="K32" s="21" t="n"/>
-      <c r="L32" s="21" t="n"/>
-      <c r="M32" s="21" t="n"/>
-      <c r="N32" s="21" t="n"/>
-      <c r="O32" s="21" t="n"/>
+      <c r="A32" s="55" t="n"/>
+      <c r="B32" s="55" t="n"/>
+      <c r="C32" s="55" t="n"/>
+      <c r="D32" s="55" t="n"/>
+      <c r="E32" s="55" t="n"/>
+      <c r="F32" s="55" t="n"/>
+      <c r="G32" s="67" t="n"/>
+      <c r="H32" s="67" t="n"/>
+      <c r="I32" s="67" t="n"/>
+      <c r="J32" s="67" t="n"/>
+      <c r="K32" s="67" t="n"/>
+      <c r="L32" s="67" t="n"/>
+      <c r="M32" s="67" t="n"/>
+      <c r="N32" s="67" t="n"/>
+      <c r="O32" s="67" t="n"/>
       <c r="P32" s="21" t="n"/>
       <c r="Q32" s="21" t="n"/>
       <c r="R32" s="21" t="n"/>
@@ -2475,15 +2774,21 @@
       <c r="AF32" s="21" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-      <c r="I33" s="21" t="n"/>
-      <c r="J33" s="21" t="n"/>
-      <c r="K33" s="21" t="n"/>
-      <c r="L33" s="21" t="n"/>
-      <c r="M33" s="21" t="n"/>
-      <c r="N33" s="21" t="n"/>
-      <c r="O33" s="21" t="n"/>
+      <c r="A33" s="55" t="n"/>
+      <c r="B33" s="55" t="n"/>
+      <c r="C33" s="55" t="n"/>
+      <c r="D33" s="55" t="n"/>
+      <c r="E33" s="55" t="n"/>
+      <c r="F33" s="55" t="n"/>
+      <c r="G33" s="67" t="n"/>
+      <c r="H33" s="67" t="n"/>
+      <c r="I33" s="67" t="n"/>
+      <c r="J33" s="67" t="n"/>
+      <c r="K33" s="67" t="n"/>
+      <c r="L33" s="67" t="n"/>
+      <c r="M33" s="67" t="n"/>
+      <c r="N33" s="67" t="n"/>
+      <c r="O33" s="67" t="n"/>
       <c r="P33" s="21" t="n"/>
       <c r="Q33" s="21" t="n"/>
       <c r="R33" s="21" t="n"/>
@@ -2503,15 +2808,21 @@
       <c r="AF33" s="21" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="21" t="n"/>
-      <c r="I34" s="21" t="n"/>
-      <c r="J34" s="21" t="n"/>
-      <c r="K34" s="21" t="n"/>
-      <c r="L34" s="21" t="n"/>
-      <c r="M34" s="21" t="n"/>
-      <c r="N34" s="21" t="n"/>
-      <c r="O34" s="21" t="n"/>
+      <c r="A34" s="55" t="n"/>
+      <c r="B34" s="55" t="n"/>
+      <c r="C34" s="55" t="n"/>
+      <c r="D34" s="55" t="n"/>
+      <c r="E34" s="55" t="n"/>
+      <c r="F34" s="55" t="n"/>
+      <c r="G34" s="67" t="n"/>
+      <c r="H34" s="67" t="n"/>
+      <c r="I34" s="67" t="n"/>
+      <c r="J34" s="67" t="n"/>
+      <c r="K34" s="67" t="n"/>
+      <c r="L34" s="67" t="n"/>
+      <c r="M34" s="67" t="n"/>
+      <c r="N34" s="67" t="n"/>
+      <c r="O34" s="67" t="n"/>
       <c r="P34" s="21" t="n"/>
       <c r="Q34" s="21" t="n"/>
       <c r="R34" s="21" t="n"/>
@@ -2531,15 +2842,21 @@
       <c r="AF34" s="21" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="G35" s="21" t="n"/>
-      <c r="H35" s="21" t="n"/>
-      <c r="I35" s="21" t="n"/>
-      <c r="J35" s="21" t="n"/>
-      <c r="K35" s="21" t="n"/>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="21" t="n"/>
-      <c r="O35" s="21" t="n"/>
+      <c r="A35" s="55" t="n"/>
+      <c r="B35" s="55" t="n"/>
+      <c r="C35" s="55" t="n"/>
+      <c r="D35" s="55" t="n"/>
+      <c r="E35" s="55" t="n"/>
+      <c r="F35" s="55" t="n"/>
+      <c r="G35" s="67" t="n"/>
+      <c r="H35" s="67" t="n"/>
+      <c r="I35" s="67" t="n"/>
+      <c r="J35" s="67" t="n"/>
+      <c r="K35" s="67" t="n"/>
+      <c r="L35" s="67" t="n"/>
+      <c r="M35" s="67" t="n"/>
+      <c r="N35" s="67" t="n"/>
+      <c r="O35" s="67" t="n"/>
       <c r="P35" s="21" t="n"/>
       <c r="Q35" s="21" t="n"/>
       <c r="R35" s="21" t="n"/>
@@ -2559,15 +2876,21 @@
       <c r="AF35" s="21" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="G36" s="21" t="n"/>
-      <c r="H36" s="21" t="n"/>
-      <c r="I36" s="21" t="n"/>
-      <c r="J36" s="21" t="n"/>
-      <c r="K36" s="21" t="n"/>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="21" t="n"/>
-      <c r="N36" s="21" t="n"/>
-      <c r="O36" s="21" t="n"/>
+      <c r="A36" s="55" t="n"/>
+      <c r="B36" s="55" t="n"/>
+      <c r="C36" s="55" t="n"/>
+      <c r="D36" s="55" t="n"/>
+      <c r="E36" s="55" t="n"/>
+      <c r="F36" s="55" t="n"/>
+      <c r="G36" s="67" t="n"/>
+      <c r="H36" s="67" t="n"/>
+      <c r="I36" s="67" t="n"/>
+      <c r="J36" s="67" t="n"/>
+      <c r="K36" s="67" t="n"/>
+      <c r="L36" s="67" t="n"/>
+      <c r="M36" s="67" t="n"/>
+      <c r="N36" s="67" t="n"/>
+      <c r="O36" s="67" t="n"/>
       <c r="P36" s="21" t="n"/>
       <c r="Q36" s="21" t="n"/>
       <c r="R36" s="21" t="n"/>
@@ -2588,15 +2911,21 @@
       <c r="BK36" s="21" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="G37" s="21" t="n"/>
-      <c r="H37" s="21" t="n"/>
-      <c r="I37" s="21" t="n"/>
-      <c r="J37" s="21" t="n"/>
-      <c r="K37" s="21" t="n"/>
-      <c r="L37" s="21" t="n"/>
-      <c r="M37" s="21" t="n"/>
-      <c r="N37" s="21" t="n"/>
-      <c r="O37" s="21" t="n"/>
+      <c r="A37" s="55" t="n"/>
+      <c r="B37" s="55" t="n"/>
+      <c r="C37" s="55" t="n"/>
+      <c r="D37" s="55" t="n"/>
+      <c r="E37" s="55" t="n"/>
+      <c r="F37" s="55" t="n"/>
+      <c r="G37" s="67" t="n"/>
+      <c r="H37" s="67" t="n"/>
+      <c r="I37" s="67" t="n"/>
+      <c r="J37" s="67" t="n"/>
+      <c r="K37" s="67" t="n"/>
+      <c r="L37" s="67" t="n"/>
+      <c r="M37" s="67" t="n"/>
+      <c r="N37" s="67" t="n"/>
+      <c r="O37" s="67" t="n"/>
       <c r="P37" s="21" t="n"/>
       <c r="Q37" s="21" t="n"/>
       <c r="R37" s="21" t="n"/>
@@ -2616,15 +2945,21 @@
       <c r="AF37" s="21" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="G38" s="21" t="n"/>
-      <c r="H38" s="21" t="n"/>
-      <c r="I38" s="21" t="n"/>
-      <c r="J38" s="21" t="n"/>
-      <c r="K38" s="21" t="n"/>
-      <c r="L38" s="21" t="n"/>
-      <c r="M38" s="21" t="n"/>
-      <c r="N38" s="21" t="n"/>
-      <c r="O38" s="21" t="n"/>
+      <c r="A38" s="55" t="n"/>
+      <c r="B38" s="55" t="n"/>
+      <c r="C38" s="55" t="n"/>
+      <c r="D38" s="55" t="n"/>
+      <c r="E38" s="55" t="n"/>
+      <c r="F38" s="55" t="n"/>
+      <c r="G38" s="67" t="n"/>
+      <c r="H38" s="67" t="n"/>
+      <c r="I38" s="67" t="n"/>
+      <c r="J38" s="67" t="n"/>
+      <c r="K38" s="67" t="n"/>
+      <c r="L38" s="67" t="n"/>
+      <c r="M38" s="67" t="n"/>
+      <c r="N38" s="67" t="n"/>
+      <c r="O38" s="67" t="n"/>
       <c r="P38" s="21" t="n"/>
       <c r="Q38" s="21" t="n"/>
       <c r="R38" s="21" t="n"/>
@@ -2644,476 +2979,608 @@
       <c r="AF38" s="21" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
-      <c r="J39" s="21" t="n"/>
-      <c r="K39" s="21" t="n"/>
-      <c r="L39" s="21" t="n"/>
-      <c r="M39" s="21" t="n"/>
-      <c r="N39" s="21" t="n"/>
-      <c r="O39" s="42" t="inlineStr">
+      <c r="A39" s="55" t="n"/>
+      <c r="B39" s="55" t="n"/>
+      <c r="C39" s="55" t="n"/>
+      <c r="D39" s="55" t="n"/>
+      <c r="E39" s="55" t="n"/>
+      <c r="F39" s="55" t="n"/>
+      <c r="G39" s="67" t="n"/>
+      <c r="H39" s="67" t="n"/>
+      <c r="I39" s="67" t="n"/>
+      <c r="J39" s="67" t="n"/>
+      <c r="K39" s="67" t="n"/>
+      <c r="L39" s="67" t="n"/>
+      <c r="M39" s="67" t="n"/>
+      <c r="N39" s="67" t="n"/>
+      <c r="O39" s="69" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="P39" s="44" t="n"/>
-      <c r="Q39" s="44" t="n"/>
-      <c r="R39" s="44" t="n"/>
-      <c r="S39" s="44" t="n"/>
-      <c r="T39" s="44" t="n"/>
-      <c r="U39" s="45" t="n"/>
+      <c r="P39" s="48" t="n"/>
+      <c r="Q39" s="48" t="n"/>
+      <c r="R39" s="48" t="n"/>
+      <c r="S39" s="48" t="n"/>
+      <c r="T39" s="48" t="n"/>
+      <c r="U39" s="49" t="n"/>
       <c r="V39" s="42" t="inlineStr">
         <is>
           <t>Autor</t>
         </is>
       </c>
-      <c r="W39" s="44" t="n"/>
-      <c r="X39" s="44" t="n"/>
-      <c r="Y39" s="44" t="n"/>
-      <c r="Z39" s="44" t="n"/>
-      <c r="AA39" s="44" t="n"/>
-      <c r="AB39" s="45" t="n"/>
+      <c r="W39" s="48" t="n"/>
+      <c r="X39" s="48" t="n"/>
+      <c r="Y39" s="48" t="n"/>
+      <c r="Z39" s="48" t="n"/>
+      <c r="AA39" s="48" t="n"/>
+      <c r="AB39" s="49" t="n"/>
       <c r="AC39" s="43" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="AD39" s="44" t="n"/>
-      <c r="AE39" s="44" t="n"/>
-      <c r="AF39" s="44" t="n"/>
-      <c r="AG39" s="44" t="n"/>
-      <c r="AH39" s="44" t="n"/>
-      <c r="AI39" s="44" t="n"/>
-      <c r="AJ39" s="44" t="n"/>
-      <c r="AK39" s="44" t="n"/>
-      <c r="AL39" s="44" t="n"/>
-      <c r="AM39" s="44" t="n"/>
-      <c r="AN39" s="44" t="n"/>
-      <c r="AO39" s="45" t="n"/>
+      <c r="AD39" s="48" t="n"/>
+      <c r="AE39" s="48" t="n"/>
+      <c r="AF39" s="48" t="n"/>
+      <c r="AG39" s="48" t="n"/>
+      <c r="AH39" s="48" t="n"/>
+      <c r="AI39" s="48" t="n"/>
+      <c r="AJ39" s="48" t="n"/>
+      <c r="AK39" s="48" t="n"/>
+      <c r="AL39" s="48" t="n"/>
+      <c r="AM39" s="48" t="n"/>
+      <c r="AN39" s="48" t="n"/>
+      <c r="AO39" s="49" t="n"/>
       <c r="AP39" s="42" t="inlineStr">
         <is>
           <t>Fecha de elaboración</t>
         </is>
       </c>
-      <c r="AQ39" s="44" t="n"/>
-      <c r="AR39" s="44" t="n"/>
-      <c r="AS39" s="44" t="n"/>
-      <c r="AT39" s="44" t="n"/>
-      <c r="AU39" s="44" t="n"/>
-      <c r="AV39" s="45" t="n"/>
+      <c r="AQ39" s="48" t="n"/>
+      <c r="AR39" s="48" t="n"/>
+      <c r="AS39" s="48" t="n"/>
+      <c r="AT39" s="48" t="n"/>
+      <c r="AU39" s="48" t="n"/>
+      <c r="AV39" s="49" t="n"/>
       <c r="AW39" s="42" t="inlineStr">
         <is>
           <t>Fecha de revisión</t>
         </is>
       </c>
-      <c r="AX39" s="44" t="n"/>
-      <c r="AY39" s="44" t="n"/>
-      <c r="AZ39" s="44" t="n"/>
-      <c r="BA39" s="44" t="n"/>
-      <c r="BB39" s="44" t="n"/>
-      <c r="BC39" s="45" t="n"/>
+      <c r="AX39" s="48" t="n"/>
+      <c r="AY39" s="48" t="n"/>
+      <c r="AZ39" s="48" t="n"/>
+      <c r="BA39" s="48" t="n"/>
+      <c r="BB39" s="48" t="n"/>
+      <c r="BC39" s="49" t="n"/>
       <c r="BD39" s="42" t="inlineStr">
         <is>
           <t>Revisado por</t>
         </is>
       </c>
-      <c r="BE39" s="44" t="n"/>
-      <c r="BF39" s="44" t="n"/>
-      <c r="BG39" s="44" t="n"/>
-      <c r="BH39" s="44" t="n"/>
-      <c r="BI39" s="44" t="n"/>
-      <c r="BJ39" s="45" t="n"/>
+      <c r="BE39" s="48" t="n"/>
+      <c r="BF39" s="48" t="n"/>
+      <c r="BG39" s="48" t="n"/>
+      <c r="BH39" s="48" t="n"/>
+      <c r="BI39" s="48" t="n"/>
+      <c r="BJ39" s="49" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
-      <c r="I40" s="21" t="n"/>
-      <c r="J40" s="21" t="n"/>
-      <c r="K40" s="21" t="n"/>
-      <c r="L40" s="21" t="n"/>
-      <c r="M40" s="21" t="n"/>
-      <c r="N40" s="21" t="n"/>
-      <c r="O40" s="50" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="50" t="n"/>
-      <c r="AB40" s="51" t="n"/>
-      <c r="AC40" s="50" t="n"/>
-      <c r="AO40" s="51" t="n"/>
-      <c r="AP40" s="50" t="n"/>
-      <c r="AV40" s="51" t="n"/>
-      <c r="AW40" s="50" t="n"/>
-      <c r="BC40" s="51" t="n"/>
-      <c r="BD40" s="50" t="n"/>
-      <c r="BJ40" s="51" t="n"/>
+      <c r="A40" s="55" t="n"/>
+      <c r="B40" s="55" t="n"/>
+      <c r="C40" s="55" t="n"/>
+      <c r="D40" s="55" t="n"/>
+      <c r="E40" s="55" t="n"/>
+      <c r="F40" s="55" t="n"/>
+      <c r="G40" s="67" t="n"/>
+      <c r="H40" s="67" t="n"/>
+      <c r="I40" s="67" t="n"/>
+      <c r="J40" s="67" t="n"/>
+      <c r="K40" s="67" t="n"/>
+      <c r="L40" s="67" t="n"/>
+      <c r="M40" s="67" t="n"/>
+      <c r="N40" s="67" t="n"/>
+      <c r="O40" s="54" t="n"/>
+      <c r="U40" s="57" t="n"/>
+      <c r="V40" s="68" t="n"/>
+      <c r="AB40" s="57" t="n"/>
+      <c r="AC40" s="68" t="n"/>
+      <c r="AO40" s="57" t="n"/>
+      <c r="AP40" s="68" t="n"/>
+      <c r="AV40" s="57" t="n"/>
+      <c r="AW40" s="68" t="n"/>
+      <c r="BC40" s="57" t="n"/>
+      <c r="BD40" s="68" t="n"/>
+      <c r="BJ40" s="57" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="21" t="n"/>
-      <c r="I41" s="21" t="n"/>
-      <c r="J41" s="21" t="n"/>
-      <c r="K41" s="21" t="n"/>
-      <c r="L41" s="21" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="N41" s="21" t="n"/>
-      <c r="O41" s="52" t="n"/>
-      <c r="P41" s="53" t="n"/>
-      <c r="Q41" s="53" t="n"/>
-      <c r="R41" s="53" t="n"/>
-      <c r="S41" s="53" t="n"/>
-      <c r="T41" s="53" t="n"/>
-      <c r="U41" s="54" t="n"/>
-      <c r="V41" s="52" t="n"/>
-      <c r="W41" s="53" t="n"/>
-      <c r="X41" s="53" t="n"/>
-      <c r="Y41" s="53" t="n"/>
-      <c r="Z41" s="53" t="n"/>
-      <c r="AA41" s="53" t="n"/>
-      <c r="AB41" s="54" t="n"/>
-      <c r="AC41" s="52" t="n"/>
-      <c r="AD41" s="53" t="n"/>
-      <c r="AE41" s="53" t="n"/>
-      <c r="AF41" s="53" t="n"/>
-      <c r="AG41" s="53" t="n"/>
-      <c r="AH41" s="53" t="n"/>
-      <c r="AI41" s="53" t="n"/>
-      <c r="AJ41" s="53" t="n"/>
-      <c r="AK41" s="53" t="n"/>
-      <c r="AL41" s="53" t="n"/>
-      <c r="AM41" s="53" t="n"/>
-      <c r="AN41" s="53" t="n"/>
-      <c r="AO41" s="54" t="n"/>
-      <c r="AP41" s="52" t="n"/>
-      <c r="AQ41" s="53" t="n"/>
-      <c r="AR41" s="53" t="n"/>
-      <c r="AS41" s="53" t="n"/>
-      <c r="AT41" s="53" t="n"/>
-      <c r="AU41" s="53" t="n"/>
-      <c r="AV41" s="54" t="n"/>
-      <c r="AW41" s="52" t="n"/>
-      <c r="AX41" s="53" t="n"/>
-      <c r="AY41" s="53" t="n"/>
-      <c r="AZ41" s="53" t="n"/>
-      <c r="BA41" s="53" t="n"/>
-      <c r="BB41" s="53" t="n"/>
-      <c r="BC41" s="54" t="n"/>
-      <c r="BD41" s="52" t="n"/>
-      <c r="BE41" s="53" t="n"/>
-      <c r="BF41" s="53" t="n"/>
-      <c r="BG41" s="53" t="n"/>
-      <c r="BH41" s="53" t="n"/>
-      <c r="BI41" s="53" t="n"/>
-      <c r="BJ41" s="54" t="n"/>
+      <c r="A41" s="55" t="n"/>
+      <c r="B41" s="55" t="n"/>
+      <c r="C41" s="55" t="n"/>
+      <c r="D41" s="55" t="n"/>
+      <c r="E41" s="55" t="n"/>
+      <c r="F41" s="55" t="n"/>
+      <c r="G41" s="67" t="n"/>
+      <c r="H41" s="67" t="n"/>
+      <c r="I41" s="67" t="n"/>
+      <c r="J41" s="67" t="n"/>
+      <c r="K41" s="67" t="n"/>
+      <c r="L41" s="67" t="n"/>
+      <c r="M41" s="67" t="n"/>
+      <c r="N41" s="67" t="n"/>
+      <c r="O41" s="61" t="n"/>
+      <c r="P41" s="59" t="n"/>
+      <c r="Q41" s="59" t="n"/>
+      <c r="R41" s="59" t="n"/>
+      <c r="S41" s="59" t="n"/>
+      <c r="T41" s="59" t="n"/>
+      <c r="U41" s="60" t="n"/>
+      <c r="V41" s="58" t="n"/>
+      <c r="W41" s="59" t="n"/>
+      <c r="X41" s="59" t="n"/>
+      <c r="Y41" s="59" t="n"/>
+      <c r="Z41" s="59" t="n"/>
+      <c r="AA41" s="59" t="n"/>
+      <c r="AB41" s="60" t="n"/>
+      <c r="AC41" s="58" t="n"/>
+      <c r="AD41" s="59" t="n"/>
+      <c r="AE41" s="59" t="n"/>
+      <c r="AF41" s="59" t="n"/>
+      <c r="AG41" s="59" t="n"/>
+      <c r="AH41" s="59" t="n"/>
+      <c r="AI41" s="59" t="n"/>
+      <c r="AJ41" s="59" t="n"/>
+      <c r="AK41" s="59" t="n"/>
+      <c r="AL41" s="59" t="n"/>
+      <c r="AM41" s="59" t="n"/>
+      <c r="AN41" s="59" t="n"/>
+      <c r="AO41" s="60" t="n"/>
+      <c r="AP41" s="58" t="n"/>
+      <c r="AQ41" s="59" t="n"/>
+      <c r="AR41" s="59" t="n"/>
+      <c r="AS41" s="59" t="n"/>
+      <c r="AT41" s="59" t="n"/>
+      <c r="AU41" s="59" t="n"/>
+      <c r="AV41" s="60" t="n"/>
+      <c r="AW41" s="58" t="n"/>
+      <c r="AX41" s="59" t="n"/>
+      <c r="AY41" s="59" t="n"/>
+      <c r="AZ41" s="59" t="n"/>
+      <c r="BA41" s="59" t="n"/>
+      <c r="BB41" s="59" t="n"/>
+      <c r="BC41" s="60" t="n"/>
+      <c r="BD41" s="58" t="n"/>
+      <c r="BE41" s="59" t="n"/>
+      <c r="BF41" s="59" t="n"/>
+      <c r="BG41" s="59" t="n"/>
+      <c r="BH41" s="59" t="n"/>
+      <c r="BI41" s="59" t="n"/>
+      <c r="BJ41" s="60" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="21" t="n"/>
-      <c r="I42" s="21" t="n"/>
-      <c r="J42" s="21" t="n"/>
-      <c r="K42" s="21" t="n"/>
-      <c r="L42" s="21" t="n"/>
-      <c r="M42" s="21" t="n"/>
-      <c r="N42" s="21" t="n"/>
-      <c r="O42" s="37" t="inlineStr">
+      <c r="A42" s="55" t="n"/>
+      <c r="B42" s="55" t="n"/>
+      <c r="C42" s="55" t="n"/>
+      <c r="D42" s="55" t="n"/>
+      <c r="E42" s="55" t="n"/>
+      <c r="F42" s="55" t="n"/>
+      <c r="G42" s="67" t="n"/>
+      <c r="H42" s="67" t="n"/>
+      <c r="I42" s="67" t="n"/>
+      <c r="J42" s="67" t="n"/>
+      <c r="K42" s="67" t="n"/>
+      <c r="L42" s="67" t="n"/>
+      <c r="M42" s="67" t="n"/>
+      <c r="N42" s="67" t="n"/>
+      <c r="O42" s="70" t="inlineStr">
         <is>
           <t>CERO (0)</t>
         </is>
       </c>
-      <c r="P42" s="44" t="n"/>
-      <c r="Q42" s="44" t="n"/>
-      <c r="R42" s="44" t="n"/>
-      <c r="S42" s="44" t="n"/>
-      <c r="T42" s="44" t="n"/>
-      <c r="U42" s="45" t="n"/>
+      <c r="P42" s="48" t="n"/>
+      <c r="Q42" s="48" t="n"/>
+      <c r="R42" s="48" t="n"/>
+      <c r="S42" s="48" t="n"/>
+      <c r="T42" s="48" t="n"/>
+      <c r="U42" s="49" t="n"/>
       <c r="V42" s="37" t="inlineStr">
         <is>
           <t>J.ARBOLEDA</t>
         </is>
       </c>
-      <c r="W42" s="44" t="n"/>
-      <c r="X42" s="44" t="n"/>
-      <c r="Y42" s="44" t="n"/>
-      <c r="Z42" s="44" t="n"/>
-      <c r="AA42" s="44" t="n"/>
-      <c r="AB42" s="45" t="n"/>
+      <c r="W42" s="48" t="n"/>
+      <c r="X42" s="48" t="n"/>
+      <c r="Y42" s="48" t="n"/>
+      <c r="Z42" s="48" t="n"/>
+      <c r="AA42" s="48" t="n"/>
+      <c r="AB42" s="49" t="n"/>
       <c r="AC42" s="38" t="inlineStr">
         <is>
           <t>Emitido para cotizacion</t>
         </is>
       </c>
-      <c r="AD42" s="44" t="n"/>
-      <c r="AE42" s="44" t="n"/>
-      <c r="AF42" s="44" t="n"/>
-      <c r="AG42" s="44" t="n"/>
-      <c r="AH42" s="44" t="n"/>
-      <c r="AI42" s="44" t="n"/>
-      <c r="AJ42" s="44" t="n"/>
-      <c r="AK42" s="44" t="n"/>
-      <c r="AL42" s="44" t="n"/>
-      <c r="AM42" s="44" t="n"/>
-      <c r="AN42" s="44" t="n"/>
-      <c r="AO42" s="45" t="n"/>
+      <c r="AD42" s="48" t="n"/>
+      <c r="AE42" s="48" t="n"/>
+      <c r="AF42" s="48" t="n"/>
+      <c r="AG42" s="48" t="n"/>
+      <c r="AH42" s="48" t="n"/>
+      <c r="AI42" s="48" t="n"/>
+      <c r="AJ42" s="48" t="n"/>
+      <c r="AK42" s="48" t="n"/>
+      <c r="AL42" s="48" t="n"/>
+      <c r="AM42" s="48" t="n"/>
+      <c r="AN42" s="48" t="n"/>
+      <c r="AO42" s="49" t="n"/>
       <c r="AP42" s="39">
         <f>BO3</f>
         <v/>
       </c>
-      <c r="AQ42" s="44" t="n"/>
-      <c r="AR42" s="44" t="n"/>
-      <c r="AS42" s="44" t="n"/>
-      <c r="AT42" s="44" t="n"/>
-      <c r="AU42" s="44" t="n"/>
-      <c r="AV42" s="45" t="n"/>
+      <c r="AQ42" s="48" t="n"/>
+      <c r="AR42" s="48" t="n"/>
+      <c r="AS42" s="48" t="n"/>
+      <c r="AT42" s="48" t="n"/>
+      <c r="AU42" s="48" t="n"/>
+      <c r="AV42" s="49" t="n"/>
       <c r="AW42" s="39">
         <f>AT27</f>
         <v/>
       </c>
-      <c r="AX42" s="44" t="n"/>
-      <c r="AY42" s="44" t="n"/>
-      <c r="AZ42" s="44" t="n"/>
-      <c r="BA42" s="44" t="n"/>
-      <c r="BB42" s="44" t="n"/>
-      <c r="BC42" s="45" t="n"/>
+      <c r="AX42" s="48" t="n"/>
+      <c r="AY42" s="48" t="n"/>
+      <c r="AZ42" s="48" t="n"/>
+      <c r="BA42" s="48" t="n"/>
+      <c r="BB42" s="48" t="n"/>
+      <c r="BC42" s="49" t="n"/>
       <c r="BD42" s="40">
         <f>BO5</f>
         <v/>
       </c>
-      <c r="BE42" s="44" t="n"/>
-      <c r="BF42" s="44" t="n"/>
-      <c r="BG42" s="44" t="n"/>
-      <c r="BH42" s="44" t="n"/>
-      <c r="BI42" s="44" t="n"/>
-      <c r="BJ42" s="45" t="n"/>
+      <c r="BE42" s="48" t="n"/>
+      <c r="BF42" s="48" t="n"/>
+      <c r="BG42" s="48" t="n"/>
+      <c r="BH42" s="48" t="n"/>
+      <c r="BI42" s="48" t="n"/>
+      <c r="BJ42" s="49" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="G43" s="21" t="n"/>
-      <c r="H43" s="21" t="n"/>
-      <c r="I43" s="21" t="n"/>
-      <c r="J43" s="21" t="n"/>
-      <c r="K43" s="21" t="n"/>
-      <c r="L43" s="21" t="n"/>
-      <c r="M43" s="21" t="n"/>
-      <c r="N43" s="21" t="n"/>
-      <c r="O43" s="50" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="50" t="n"/>
-      <c r="AB43" s="51" t="n"/>
-      <c r="AC43" s="50" t="n"/>
-      <c r="AO43" s="51" t="n"/>
-      <c r="AP43" s="50" t="n"/>
-      <c r="AV43" s="51" t="n"/>
-      <c r="AW43" s="50" t="n"/>
-      <c r="BC43" s="51" t="n"/>
-      <c r="BD43" s="50" t="n"/>
-      <c r="BJ43" s="51" t="n"/>
+      <c r="A43" s="55" t="n"/>
+      <c r="B43" s="55" t="n"/>
+      <c r="C43" s="55" t="n"/>
+      <c r="D43" s="55" t="n"/>
+      <c r="E43" s="55" t="n"/>
+      <c r="F43" s="55" t="n"/>
+      <c r="G43" s="67" t="n"/>
+      <c r="H43" s="67" t="n"/>
+      <c r="I43" s="67" t="n"/>
+      <c r="J43" s="67" t="n"/>
+      <c r="K43" s="67" t="n"/>
+      <c r="L43" s="67" t="n"/>
+      <c r="M43" s="67" t="n"/>
+      <c r="N43" s="67" t="n"/>
+      <c r="O43" s="54" t="n"/>
+      <c r="U43" s="57" t="n"/>
+      <c r="V43" s="68" t="n"/>
+      <c r="AB43" s="57" t="n"/>
+      <c r="AC43" s="68" t="n"/>
+      <c r="AO43" s="57" t="n"/>
+      <c r="AP43" s="68" t="n"/>
+      <c r="AV43" s="57" t="n"/>
+      <c r="AW43" s="68" t="n"/>
+      <c r="BC43" s="57" t="n"/>
+      <c r="BD43" s="68" t="n"/>
+      <c r="BJ43" s="57" t="n"/>
       <c r="BP43" s="21" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="G44" s="21" t="n"/>
-      <c r="H44" s="21" t="n"/>
-      <c r="I44" s="21" t="n"/>
-      <c r="J44" s="21" t="n"/>
-      <c r="K44" s="21" t="n"/>
-      <c r="L44" s="21" t="n"/>
-      <c r="M44" s="21" t="n"/>
-      <c r="N44" s="21" t="n"/>
-      <c r="O44" s="52" t="n"/>
-      <c r="P44" s="53" t="n"/>
-      <c r="Q44" s="53" t="n"/>
-      <c r="R44" s="53" t="n"/>
-      <c r="S44" s="53" t="n"/>
-      <c r="T44" s="53" t="n"/>
-      <c r="U44" s="54" t="n"/>
-      <c r="V44" s="52" t="n"/>
-      <c r="W44" s="53" t="n"/>
-      <c r="X44" s="53" t="n"/>
-      <c r="Y44" s="53" t="n"/>
-      <c r="Z44" s="53" t="n"/>
-      <c r="AA44" s="53" t="n"/>
-      <c r="AB44" s="54" t="n"/>
-      <c r="AC44" s="52" t="n"/>
-      <c r="AD44" s="53" t="n"/>
-      <c r="AE44" s="53" t="n"/>
-      <c r="AF44" s="53" t="n"/>
-      <c r="AG44" s="53" t="n"/>
-      <c r="AH44" s="53" t="n"/>
-      <c r="AI44" s="53" t="n"/>
-      <c r="AJ44" s="53" t="n"/>
-      <c r="AK44" s="53" t="n"/>
-      <c r="AL44" s="53" t="n"/>
-      <c r="AM44" s="53" t="n"/>
-      <c r="AN44" s="53" t="n"/>
-      <c r="AO44" s="54" t="n"/>
-      <c r="AP44" s="52" t="n"/>
-      <c r="AQ44" s="53" t="n"/>
-      <c r="AR44" s="53" t="n"/>
-      <c r="AS44" s="53" t="n"/>
-      <c r="AT44" s="53" t="n"/>
-      <c r="AU44" s="53" t="n"/>
-      <c r="AV44" s="54" t="n"/>
-      <c r="AW44" s="52" t="n"/>
-      <c r="AX44" s="53" t="n"/>
-      <c r="AY44" s="53" t="n"/>
-      <c r="AZ44" s="53" t="n"/>
-      <c r="BA44" s="53" t="n"/>
-      <c r="BB44" s="53" t="n"/>
-      <c r="BC44" s="54" t="n"/>
-      <c r="BD44" s="52" t="n"/>
-      <c r="BE44" s="53" t="n"/>
-      <c r="BF44" s="53" t="n"/>
-      <c r="BG44" s="53" t="n"/>
-      <c r="BH44" s="53" t="n"/>
-      <c r="BI44" s="53" t="n"/>
-      <c r="BJ44" s="54" t="n"/>
+      <c r="A44" s="55" t="n"/>
+      <c r="B44" s="55" t="n"/>
+      <c r="C44" s="55" t="n"/>
+      <c r="D44" s="55" t="n"/>
+      <c r="E44" s="55" t="n"/>
+      <c r="F44" s="55" t="n"/>
+      <c r="G44" s="67" t="n"/>
+      <c r="H44" s="67" t="n"/>
+      <c r="I44" s="67" t="n"/>
+      <c r="J44" s="67" t="n"/>
+      <c r="K44" s="67" t="n"/>
+      <c r="L44" s="67" t="n"/>
+      <c r="M44" s="67" t="n"/>
+      <c r="N44" s="67" t="n"/>
+      <c r="O44" s="61" t="n"/>
+      <c r="P44" s="59" t="n"/>
+      <c r="Q44" s="59" t="n"/>
+      <c r="R44" s="59" t="n"/>
+      <c r="S44" s="59" t="n"/>
+      <c r="T44" s="59" t="n"/>
+      <c r="U44" s="60" t="n"/>
+      <c r="V44" s="58" t="n"/>
+      <c r="W44" s="59" t="n"/>
+      <c r="X44" s="59" t="n"/>
+      <c r="Y44" s="59" t="n"/>
+      <c r="Z44" s="59" t="n"/>
+      <c r="AA44" s="59" t="n"/>
+      <c r="AB44" s="60" t="n"/>
+      <c r="AC44" s="58" t="n"/>
+      <c r="AD44" s="59" t="n"/>
+      <c r="AE44" s="59" t="n"/>
+      <c r="AF44" s="59" t="n"/>
+      <c r="AG44" s="59" t="n"/>
+      <c r="AH44" s="59" t="n"/>
+      <c r="AI44" s="59" t="n"/>
+      <c r="AJ44" s="59" t="n"/>
+      <c r="AK44" s="59" t="n"/>
+      <c r="AL44" s="59" t="n"/>
+      <c r="AM44" s="59" t="n"/>
+      <c r="AN44" s="59" t="n"/>
+      <c r="AO44" s="60" t="n"/>
+      <c r="AP44" s="58" t="n"/>
+      <c r="AQ44" s="59" t="n"/>
+      <c r="AR44" s="59" t="n"/>
+      <c r="AS44" s="59" t="n"/>
+      <c r="AT44" s="59" t="n"/>
+      <c r="AU44" s="59" t="n"/>
+      <c r="AV44" s="60" t="n"/>
+      <c r="AW44" s="58" t="n"/>
+      <c r="AX44" s="59" t="n"/>
+      <c r="AY44" s="59" t="n"/>
+      <c r="AZ44" s="59" t="n"/>
+      <c r="BA44" s="59" t="n"/>
+      <c r="BB44" s="59" t="n"/>
+      <c r="BC44" s="60" t="n"/>
+      <c r="BD44" s="58" t="n"/>
+      <c r="BE44" s="59" t="n"/>
+      <c r="BF44" s="59" t="n"/>
+      <c r="BG44" s="59" t="n"/>
+      <c r="BH44" s="59" t="n"/>
+      <c r="BI44" s="59" t="n"/>
+      <c r="BJ44" s="60" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="21" t="n"/>
-      <c r="I45" s="21" t="n"/>
-      <c r="J45" s="21" t="n"/>
-      <c r="K45" s="21" t="n"/>
-      <c r="L45" s="21" t="n"/>
-      <c r="M45" s="21" t="n"/>
-      <c r="N45" s="21" t="n"/>
-      <c r="O45" s="20" t="n"/>
-      <c r="P45" s="44" t="n"/>
-      <c r="Q45" s="44" t="n"/>
-      <c r="R45" s="44" t="n"/>
-      <c r="S45" s="44" t="n"/>
-      <c r="T45" s="44" t="n"/>
-      <c r="U45" s="45" t="n"/>
+      <c r="A45" s="55" t="n"/>
+      <c r="B45" s="55" t="n"/>
+      <c r="C45" s="55" t="n"/>
+      <c r="D45" s="55" t="n"/>
+      <c r="E45" s="55" t="n"/>
+      <c r="F45" s="55" t="n"/>
+      <c r="G45" s="67" t="n"/>
+      <c r="H45" s="67" t="n"/>
+      <c r="I45" s="67" t="n"/>
+      <c r="J45" s="67" t="n"/>
+      <c r="K45" s="67" t="n"/>
+      <c r="L45" s="67" t="n"/>
+      <c r="M45" s="67" t="n"/>
+      <c r="N45" s="67" t="n"/>
+      <c r="O45" s="71" t="n"/>
+      <c r="P45" s="48" t="n"/>
+      <c r="Q45" s="48" t="n"/>
+      <c r="R45" s="48" t="n"/>
+      <c r="S45" s="48" t="n"/>
+      <c r="T45" s="48" t="n"/>
+      <c r="U45" s="49" t="n"/>
       <c r="V45" s="20" t="n"/>
-      <c r="W45" s="44" t="n"/>
-      <c r="X45" s="44" t="n"/>
-      <c r="Y45" s="44" t="n"/>
-      <c r="Z45" s="44" t="n"/>
-      <c r="AA45" s="44" t="n"/>
-      <c r="AB45" s="45" t="n"/>
+      <c r="W45" s="48" t="n"/>
+      <c r="X45" s="48" t="n"/>
+      <c r="Y45" s="48" t="n"/>
+      <c r="Z45" s="48" t="n"/>
+      <c r="AA45" s="48" t="n"/>
+      <c r="AB45" s="49" t="n"/>
       <c r="AC45" s="22" t="n"/>
-      <c r="AD45" s="44" t="n"/>
-      <c r="AE45" s="44" t="n"/>
-      <c r="AF45" s="44" t="n"/>
-      <c r="AG45" s="44" t="n"/>
-      <c r="AH45" s="44" t="n"/>
-      <c r="AI45" s="44" t="n"/>
-      <c r="AJ45" s="44" t="n"/>
-      <c r="AK45" s="44" t="n"/>
-      <c r="AL45" s="44" t="n"/>
-      <c r="AM45" s="44" t="n"/>
-      <c r="AN45" s="44" t="n"/>
-      <c r="AO45" s="45" t="n"/>
+      <c r="AD45" s="48" t="n"/>
+      <c r="AE45" s="48" t="n"/>
+      <c r="AF45" s="48" t="n"/>
+      <c r="AG45" s="48" t="n"/>
+      <c r="AH45" s="48" t="n"/>
+      <c r="AI45" s="48" t="n"/>
+      <c r="AJ45" s="48" t="n"/>
+      <c r="AK45" s="48" t="n"/>
+      <c r="AL45" s="48" t="n"/>
+      <c r="AM45" s="48" t="n"/>
+      <c r="AN45" s="48" t="n"/>
+      <c r="AO45" s="49" t="n"/>
       <c r="AP45" s="20" t="n"/>
-      <c r="AQ45" s="44" t="n"/>
-      <c r="AR45" s="44" t="n"/>
-      <c r="AS45" s="44" t="n"/>
-      <c r="AT45" s="44" t="n"/>
-      <c r="AU45" s="44" t="n"/>
-      <c r="AV45" s="45" t="n"/>
+      <c r="AQ45" s="48" t="n"/>
+      <c r="AR45" s="48" t="n"/>
+      <c r="AS45" s="48" t="n"/>
+      <c r="AT45" s="48" t="n"/>
+      <c r="AU45" s="48" t="n"/>
+      <c r="AV45" s="49" t="n"/>
       <c r="AW45" s="20" t="n"/>
-      <c r="AX45" s="44" t="n"/>
-      <c r="AY45" s="44" t="n"/>
-      <c r="AZ45" s="44" t="n"/>
-      <c r="BA45" s="44" t="n"/>
-      <c r="BB45" s="44" t="n"/>
-      <c r="BC45" s="45" t="n"/>
+      <c r="AX45" s="48" t="n"/>
+      <c r="AY45" s="48" t="n"/>
+      <c r="AZ45" s="48" t="n"/>
+      <c r="BA45" s="48" t="n"/>
+      <c r="BB45" s="48" t="n"/>
+      <c r="BC45" s="49" t="n"/>
       <c r="BD45" s="20" t="n"/>
-      <c r="BE45" s="44" t="n"/>
-      <c r="BF45" s="44" t="n"/>
-      <c r="BG45" s="44" t="n"/>
-      <c r="BH45" s="44" t="n"/>
-      <c r="BI45" s="44" t="n"/>
-      <c r="BJ45" s="45" t="n"/>
+      <c r="BE45" s="48" t="n"/>
+      <c r="BF45" s="48" t="n"/>
+      <c r="BG45" s="48" t="n"/>
+      <c r="BH45" s="48" t="n"/>
+      <c r="BI45" s="48" t="n"/>
+      <c r="BJ45" s="49" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="G46" s="21" t="n"/>
-      <c r="H46" s="21" t="n"/>
-      <c r="I46" s="21" t="n"/>
-      <c r="J46" s="21" t="n"/>
-      <c r="K46" s="21" t="n"/>
-      <c r="L46" s="21" t="n"/>
-      <c r="M46" s="21" t="n"/>
-      <c r="N46" s="21" t="n"/>
-      <c r="O46" s="50" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="50" t="n"/>
-      <c r="AB46" s="51" t="n"/>
-      <c r="AC46" s="50" t="n"/>
-      <c r="AO46" s="51" t="n"/>
-      <c r="AP46" s="50" t="n"/>
-      <c r="AV46" s="51" t="n"/>
-      <c r="AW46" s="50" t="n"/>
-      <c r="BC46" s="51" t="n"/>
-      <c r="BD46" s="50" t="n"/>
-      <c r="BJ46" s="51" t="n"/>
+      <c r="A46" s="55" t="n"/>
+      <c r="B46" s="55" t="n"/>
+      <c r="C46" s="55" t="n"/>
+      <c r="D46" s="55" t="n"/>
+      <c r="E46" s="55" t="n"/>
+      <c r="F46" s="55" t="n"/>
+      <c r="G46" s="67" t="n"/>
+      <c r="H46" s="67" t="n"/>
+      <c r="I46" s="67" t="n"/>
+      <c r="J46" s="67" t="n"/>
+      <c r="K46" s="67" t="n"/>
+      <c r="L46" s="67" t="n"/>
+      <c r="M46" s="67" t="n"/>
+      <c r="N46" s="67" t="n"/>
+      <c r="O46" s="54" t="n"/>
+      <c r="U46" s="57" t="n"/>
+      <c r="V46" s="68" t="n"/>
+      <c r="AB46" s="57" t="n"/>
+      <c r="AC46" s="68" t="n"/>
+      <c r="AO46" s="57" t="n"/>
+      <c r="AP46" s="68" t="n"/>
+      <c r="AV46" s="57" t="n"/>
+      <c r="AW46" s="68" t="n"/>
+      <c r="BC46" s="57" t="n"/>
+      <c r="BD46" s="68" t="n"/>
+      <c r="BJ46" s="57" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="21" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="J47" s="21" t="n"/>
-      <c r="K47" s="21" t="n"/>
-      <c r="L47" s="21" t="n"/>
-      <c r="M47" s="21" t="n"/>
-      <c r="N47" s="21" t="n"/>
-      <c r="O47" s="52" t="n"/>
-      <c r="P47" s="53" t="n"/>
-      <c r="Q47" s="53" t="n"/>
-      <c r="R47" s="53" t="n"/>
-      <c r="S47" s="53" t="n"/>
-      <c r="T47" s="53" t="n"/>
-      <c r="U47" s="54" t="n"/>
-      <c r="V47" s="52" t="n"/>
-      <c r="W47" s="53" t="n"/>
-      <c r="X47" s="53" t="n"/>
-      <c r="Y47" s="53" t="n"/>
-      <c r="Z47" s="53" t="n"/>
-      <c r="AA47" s="53" t="n"/>
-      <c r="AB47" s="54" t="n"/>
-      <c r="AC47" s="52" t="n"/>
-      <c r="AD47" s="53" t="n"/>
-      <c r="AE47" s="53" t="n"/>
-      <c r="AF47" s="53" t="n"/>
-      <c r="AG47" s="53" t="n"/>
-      <c r="AH47" s="53" t="n"/>
-      <c r="AI47" s="53" t="n"/>
-      <c r="AJ47" s="53" t="n"/>
-      <c r="AK47" s="53" t="n"/>
-      <c r="AL47" s="53" t="n"/>
-      <c r="AM47" s="53" t="n"/>
-      <c r="AN47" s="53" t="n"/>
-      <c r="AO47" s="54" t="n"/>
-      <c r="AP47" s="52" t="n"/>
-      <c r="AQ47" s="53" t="n"/>
-      <c r="AR47" s="53" t="n"/>
-      <c r="AS47" s="53" t="n"/>
-      <c r="AT47" s="53" t="n"/>
-      <c r="AU47" s="53" t="n"/>
-      <c r="AV47" s="54" t="n"/>
-      <c r="AW47" s="52" t="n"/>
-      <c r="AX47" s="53" t="n"/>
-      <c r="AY47" s="53" t="n"/>
-      <c r="AZ47" s="53" t="n"/>
-      <c r="BA47" s="53" t="n"/>
-      <c r="BB47" s="53" t="n"/>
-      <c r="BC47" s="54" t="n"/>
-      <c r="BD47" s="52" t="n"/>
-      <c r="BE47" s="53" t="n"/>
-      <c r="BF47" s="53" t="n"/>
-      <c r="BG47" s="53" t="n"/>
-      <c r="BH47" s="53" t="n"/>
-      <c r="BI47" s="53" t="n"/>
-      <c r="BJ47" s="54" t="n"/>
+      <c r="A47" s="55" t="n"/>
+      <c r="B47" s="55" t="n"/>
+      <c r="C47" s="55" t="n"/>
+      <c r="D47" s="55" t="n"/>
+      <c r="E47" s="55" t="n"/>
+      <c r="F47" s="55" t="n"/>
+      <c r="G47" s="67" t="n"/>
+      <c r="H47" s="67" t="n"/>
+      <c r="I47" s="67" t="n"/>
+      <c r="J47" s="67" t="n"/>
+      <c r="K47" s="67" t="n"/>
+      <c r="L47" s="67" t="n"/>
+      <c r="M47" s="67" t="n"/>
+      <c r="N47" s="67" t="n"/>
+      <c r="O47" s="61" t="n"/>
+      <c r="P47" s="59" t="n"/>
+      <c r="Q47" s="59" t="n"/>
+      <c r="R47" s="59" t="n"/>
+      <c r="S47" s="59" t="n"/>
+      <c r="T47" s="59" t="n"/>
+      <c r="U47" s="60" t="n"/>
+      <c r="V47" s="58" t="n"/>
+      <c r="W47" s="59" t="n"/>
+      <c r="X47" s="59" t="n"/>
+      <c r="Y47" s="59" t="n"/>
+      <c r="Z47" s="59" t="n"/>
+      <c r="AA47" s="59" t="n"/>
+      <c r="AB47" s="60" t="n"/>
+      <c r="AC47" s="58" t="n"/>
+      <c r="AD47" s="59" t="n"/>
+      <c r="AE47" s="59" t="n"/>
+      <c r="AF47" s="59" t="n"/>
+      <c r="AG47" s="59" t="n"/>
+      <c r="AH47" s="59" t="n"/>
+      <c r="AI47" s="59" t="n"/>
+      <c r="AJ47" s="59" t="n"/>
+      <c r="AK47" s="59" t="n"/>
+      <c r="AL47" s="59" t="n"/>
+      <c r="AM47" s="59" t="n"/>
+      <c r="AN47" s="59" t="n"/>
+      <c r="AO47" s="60" t="n"/>
+      <c r="AP47" s="58" t="n"/>
+      <c r="AQ47" s="59" t="n"/>
+      <c r="AR47" s="59" t="n"/>
+      <c r="AS47" s="59" t="n"/>
+      <c r="AT47" s="59" t="n"/>
+      <c r="AU47" s="59" t="n"/>
+      <c r="AV47" s="60" t="n"/>
+      <c r="AW47" s="58" t="n"/>
+      <c r="AX47" s="59" t="n"/>
+      <c r="AY47" s="59" t="n"/>
+      <c r="AZ47" s="59" t="n"/>
+      <c r="BA47" s="59" t="n"/>
+      <c r="BB47" s="59" t="n"/>
+      <c r="BC47" s="60" t="n"/>
+      <c r="BD47" s="58" t="n"/>
+      <c r="BE47" s="59" t="n"/>
+      <c r="BF47" s="59" t="n"/>
+      <c r="BG47" s="59" t="n"/>
+      <c r="BH47" s="59" t="n"/>
+      <c r="BI47" s="59" t="n"/>
+      <c r="BJ47" s="60" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="O48" s="19" t="n"/>
+      <c r="A48" s="55" t="n"/>
+      <c r="B48" s="55" t="n"/>
+      <c r="C48" s="55" t="n"/>
+      <c r="D48" s="55" t="n"/>
+      <c r="E48" s="55" t="n"/>
+      <c r="F48" s="55" t="n"/>
+      <c r="G48" s="55" t="n"/>
+      <c r="H48" s="55" t="n"/>
+      <c r="I48" s="55" t="n"/>
+      <c r="J48" s="55" t="n"/>
+      <c r="K48" s="55" t="n"/>
+      <c r="L48" s="55" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="72" t="n"/>
       <c r="V48" s="19" t="n"/>
       <c r="AC48" s="19" t="n"/>
       <c r="AP48" s="19" t="n"/>
       <c r="AW48" s="19" t="n"/>
       <c r="BD48" s="19" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1"/>
-    <row r="50" ht="15" customHeight="1"/>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="55" t="n"/>
+      <c r="B49" s="55" t="n"/>
+      <c r="C49" s="55" t="n"/>
+      <c r="D49" s="55" t="n"/>
+      <c r="E49" s="55" t="n"/>
+      <c r="F49" s="55" t="n"/>
+      <c r="G49" s="55" t="n"/>
+      <c r="H49" s="55" t="n"/>
+      <c r="I49" s="55" t="n"/>
+      <c r="J49" s="55" t="n"/>
+      <c r="K49" s="55" t="n"/>
+      <c r="L49" s="55" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="55" t="n"/>
+      <c r="B50" s="55" t="n"/>
+      <c r="C50" s="55" t="n"/>
+      <c r="D50" s="55" t="n"/>
+      <c r="E50" s="55" t="n"/>
+      <c r="F50" s="55" t="n"/>
+      <c r="G50" s="55" t="n"/>
+      <c r="H50" s="55" t="n"/>
+      <c r="I50" s="55" t="n"/>
+      <c r="J50" s="55" t="n"/>
+      <c r="K50" s="55" t="n"/>
+      <c r="L50" s="55" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="55" t="n"/>
+      <c r="B51" s="55" t="n"/>
+      <c r="C51" s="55" t="n"/>
+      <c r="D51" s="55" t="n"/>
+      <c r="E51" s="55" t="n"/>
+      <c r="F51" s="55" t="n"/>
+      <c r="G51" s="55" t="n"/>
+      <c r="H51" s="55" t="n"/>
+      <c r="I51" s="55" t="n"/>
+      <c r="J51" s="55" t="n"/>
+      <c r="K51" s="55" t="n"/>
+      <c r="L51" s="55" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+    </row>
     <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="55" t="n"/>
+      <c r="B52" s="55" t="n"/>
+      <c r="C52" s="55" t="n"/>
+      <c r="D52" s="55" t="n"/>
+      <c r="E52" s="55" t="n"/>
+      <c r="F52" s="55" t="n"/>
+      <c r="G52" s="55" t="n"/>
+      <c r="H52" s="55" t="n"/>
+      <c r="I52" s="55" t="n"/>
+      <c r="J52" s="55" t="n"/>
+      <c r="K52" s="55" t="n"/>
+      <c r="L52" s="55" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
       <c r="BH52" s="8" t="n"/>
       <c r="BI52" s="8" t="n"/>
       <c r="BJ52" s="8" t="n"/>
@@ -3126,22 +3593,54 @@
       <c r="BQ52" s="9" t="n"/>
       <c r="BR52" s="9" t="n"/>
     </row>
+    <row r="53">
+      <c r="A53" s="55" t="n"/>
+      <c r="B53" s="55" t="n"/>
+      <c r="C53" s="55" t="n"/>
+      <c r="D53" s="55" t="n"/>
+      <c r="E53" s="55" t="n"/>
+      <c r="F53" s="55" t="n"/>
+      <c r="G53" s="55" t="n"/>
+      <c r="H53" s="55" t="n"/>
+      <c r="I53" s="55" t="n"/>
+      <c r="J53" s="55" t="n"/>
+      <c r="K53" s="55" t="n"/>
+      <c r="L53" s="55" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+    </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="AA54" s="55" t="n"/>
-      <c r="AB54" s="55" t="n"/>
-      <c r="AC54" s="55" t="n"/>
-      <c r="AD54" s="55" t="n"/>
-      <c r="AE54" s="55" t="n"/>
-      <c r="AF54" s="55" t="n"/>
-      <c r="AG54" s="55" t="n"/>
-      <c r="AH54" s="55" t="n"/>
-      <c r="AI54" s="55" t="n"/>
-      <c r="AJ54" s="55" t="n"/>
-      <c r="AK54" s="55" t="n"/>
-      <c r="AL54" s="55" t="n"/>
-      <c r="AM54" s="55" t="n"/>
-      <c r="AN54" s="55" t="n"/>
-      <c r="AO54" s="55" t="n"/>
+      <c r="A54" s="55" t="n"/>
+      <c r="B54" s="55" t="n"/>
+      <c r="C54" s="55" t="n"/>
+      <c r="D54" s="55" t="n"/>
+      <c r="E54" s="55" t="n"/>
+      <c r="F54" s="55" t="n"/>
+      <c r="G54" s="55" t="n"/>
+      <c r="H54" s="55" t="n"/>
+      <c r="I54" s="55" t="n"/>
+      <c r="J54" s="55" t="n"/>
+      <c r="K54" s="55" t="n"/>
+      <c r="L54" s="55" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="AA54" s="73" t="n"/>
+      <c r="AB54" s="73" t="n"/>
+      <c r="AC54" s="73" t="n"/>
+      <c r="AD54" s="73" t="n"/>
+      <c r="AE54" s="73" t="n"/>
+      <c r="AF54" s="73" t="n"/>
+      <c r="AG54" s="73" t="n"/>
+      <c r="AH54" s="73" t="n"/>
+      <c r="AI54" s="73" t="n"/>
+      <c r="AJ54" s="73" t="n"/>
+      <c r="AK54" s="73" t="n"/>
+      <c r="AL54" s="73" t="n"/>
+      <c r="AM54" s="73" t="n"/>
+      <c r="AN54" s="73" t="n"/>
+      <c r="AO54" s="73" t="n"/>
       <c r="AP54" s="11" t="n"/>
       <c r="AQ54" s="11" t="n"/>
       <c r="AR54" s="11" t="n"/>
@@ -3221,1007 +3720,1105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.61328125" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="30.6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
+    <col width="13" customWidth="1" min="50" max="50"/>
+    <col width="13" customWidth="1" min="51" max="51"/>
+    <col width="13" customWidth="1" min="52" max="52"/>
+    <col width="13" customWidth="1" min="53" max="53"/>
+    <col width="13" customWidth="1" min="54" max="54"/>
+    <col width="13" customWidth="1" min="55" max="55"/>
+    <col width="13" customWidth="1" min="56" max="56"/>
+    <col width="13" customWidth="1" min="57" max="57"/>
+    <col width="13" customWidth="1" min="58" max="58"/>
+    <col width="13" customWidth="1" min="59" max="59"/>
+    <col width="13" customWidth="1" min="60" max="60"/>
+    <col width="13" customWidth="1" min="61" max="61"/>
+    <col width="13" customWidth="1" min="62" max="62"/>
+    <col width="13" customWidth="1" min="63" max="63"/>
+    <col width="13" customWidth="1" min="64" max="64"/>
+    <col width="13" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
-      <c r="A1" s="35" t="n"/>
-      <c r="B1" s="36" t="n"/>
-      <c r="C1" s="35">
+      <c r="A1" s="74" t="n"/>
+      <c r="B1" s="75" t="n"/>
+      <c r="C1" s="74">
         <f>PORTADA!Z1</f>
         <v/>
       </c>
-      <c r="D1" s="46" t="n"/>
-      <c r="E1" s="46" t="n"/>
-      <c r="F1" s="46" t="n"/>
-      <c r="G1" s="46" t="n"/>
-      <c r="H1" s="46" t="n"/>
-      <c r="I1" s="46" t="n"/>
-      <c r="J1" s="46" t="n"/>
-      <c r="K1" s="46" t="n"/>
-      <c r="L1" s="47" t="n"/>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="D1" s="65" t="n"/>
+      <c r="E1" s="65" t="n"/>
+      <c r="F1" s="65" t="n"/>
+      <c r="G1" s="65" t="n"/>
+      <c r="H1" s="65" t="n"/>
+      <c r="I1" s="65" t="n"/>
+      <c r="J1" s="65" t="n"/>
+      <c r="K1" s="65" t="n"/>
+      <c r="L1" s="66" t="n"/>
+      <c r="M1" s="76" t="inlineStr">
         <is>
           <t>CODIGO:</t>
         </is>
       </c>
-      <c r="N1" s="32">
+      <c r="N1" s="77">
         <f>PORTADA!BO1</f>
         <v/>
       </c>
-      <c r="O1" s="47" t="n"/>
+      <c r="O1" s="66" t="n"/>
     </row>
     <row r="2" ht="29.25" customHeight="1">
-      <c r="A2" s="56" t="n"/>
-      <c r="B2" s="56" t="n"/>
-      <c r="C2" s="35">
+      <c r="A2" s="78" t="n"/>
+      <c r="B2" s="78" t="n"/>
+      <c r="C2" s="74">
         <f>PORTADA!Z3</f>
         <v/>
       </c>
-      <c r="D2" s="44" t="n"/>
-      <c r="E2" s="44" t="n"/>
-      <c r="F2" s="44" t="n"/>
-      <c r="G2" s="44" t="n"/>
-      <c r="H2" s="44" t="n"/>
-      <c r="I2" s="44" t="n"/>
-      <c r="J2" s="44" t="n"/>
-      <c r="K2" s="44" t="n"/>
-      <c r="L2" s="45" t="n"/>
-      <c r="M2" s="12" t="inlineStr">
+      <c r="D2" s="45" t="n"/>
+      <c r="E2" s="45" t="n"/>
+      <c r="F2" s="45" t="n"/>
+      <c r="G2" s="45" t="n"/>
+      <c r="H2" s="45" t="n"/>
+      <c r="I2" s="45" t="n"/>
+      <c r="J2" s="45" t="n"/>
+      <c r="K2" s="45" t="n"/>
+      <c r="L2" s="46" t="n"/>
+      <c r="M2" s="76" t="inlineStr">
         <is>
           <t>REVISION:</t>
         </is>
       </c>
-      <c r="N2" s="32">
+      <c r="N2" s="77">
         <f>PORTADA!BO2</f>
         <v/>
       </c>
-      <c r="O2" s="47" t="n"/>
+      <c r="O2" s="66" t="n"/>
     </row>
     <row r="3" ht="29.25" customHeight="1">
-      <c r="A3" s="56" t="n"/>
-      <c r="B3" s="56" t="n"/>
-      <c r="C3" s="52" t="n"/>
-      <c r="D3" s="53" t="n"/>
-      <c r="E3" s="53" t="n"/>
-      <c r="F3" s="53" t="n"/>
-      <c r="G3" s="53" t="n"/>
-      <c r="H3" s="53" t="n"/>
-      <c r="I3" s="53" t="n"/>
-      <c r="J3" s="53" t="n"/>
-      <c r="K3" s="53" t="n"/>
-      <c r="L3" s="54" t="n"/>
-      <c r="M3" s="12" t="inlineStr">
+      <c r="A3" s="78" t="n"/>
+      <c r="B3" s="78" t="n"/>
+      <c r="C3" s="61" t="n"/>
+      <c r="D3" s="62" t="n"/>
+      <c r="E3" s="62" t="n"/>
+      <c r="F3" s="62" t="n"/>
+      <c r="G3" s="62" t="n"/>
+      <c r="H3" s="62" t="n"/>
+      <c r="I3" s="62" t="n"/>
+      <c r="J3" s="62" t="n"/>
+      <c r="K3" s="62" t="n"/>
+      <c r="L3" s="63" t="n"/>
+      <c r="M3" s="76" t="inlineStr">
         <is>
           <t>FECHA:</t>
         </is>
       </c>
-      <c r="N3" s="32">
+      <c r="N3" s="77">
         <f>PORTADA!BO3</f>
         <v/>
       </c>
-      <c r="O3" s="47" t="n"/>
+      <c r="O3" s="66" t="n"/>
     </row>
     <row r="4" ht="29.25" customHeight="1">
-      <c r="A4" s="56" t="n"/>
-      <c r="B4" s="56" t="n"/>
-      <c r="C4" s="35">
+      <c r="A4" s="78" t="n"/>
+      <c r="B4" s="78" t="n"/>
+      <c r="C4" s="74">
         <f>PORTADA!Z5</f>
         <v/>
       </c>
-      <c r="D4" s="44" t="n"/>
-      <c r="E4" s="44" t="n"/>
-      <c r="F4" s="44" t="n"/>
-      <c r="G4" s="44" t="n"/>
-      <c r="H4" s="44" t="n"/>
-      <c r="I4" s="44" t="n"/>
-      <c r="J4" s="44" t="n"/>
-      <c r="K4" s="44" t="n"/>
-      <c r="L4" s="45" t="n"/>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="D4" s="45" t="n"/>
+      <c r="E4" s="45" t="n"/>
+      <c r="F4" s="45" t="n"/>
+      <c r="G4" s="45" t="n"/>
+      <c r="H4" s="45" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="45" t="n"/>
+      <c r="K4" s="45" t="n"/>
+      <c r="L4" s="46" t="n"/>
+      <c r="M4" s="76" t="inlineStr">
         <is>
           <t>ELABORO:</t>
         </is>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="77">
         <f>PORTADA!BO4</f>
         <v/>
       </c>
-      <c r="O4" s="47" t="n"/>
+      <c r="O4" s="66" t="n"/>
     </row>
     <row r="5" ht="29.25" customHeight="1">
-      <c r="A5" s="57" t="n"/>
-      <c r="B5" s="57" t="n"/>
-      <c r="C5" s="50" t="n"/>
-      <c r="L5" s="51" t="n"/>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="A5" s="79" t="n"/>
+      <c r="B5" s="79" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="55" t="n"/>
+      <c r="E5" s="55" t="n"/>
+      <c r="F5" s="55" t="n"/>
+      <c r="G5" s="55" t="n"/>
+      <c r="H5" s="55" t="n"/>
+      <c r="I5" s="55" t="n"/>
+      <c r="J5" s="55" t="n"/>
+      <c r="K5" s="55" t="n"/>
+      <c r="L5" s="56" t="n"/>
+      <c r="M5" s="76" t="inlineStr">
         <is>
           <t xml:space="preserve">REVISO:      </t>
         </is>
       </c>
-      <c r="N5" s="32">
+      <c r="N5" s="77">
         <f>PORTADA!BO5</f>
         <v/>
       </c>
-      <c r="O5" s="47" t="n"/>
+      <c r="O5" s="66" t="n"/>
     </row>
     <row r="6" ht="29.25" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="76" t="inlineStr">
         <is>
           <t>PROYECTO:</t>
         </is>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="74">
         <f>PORTADA!N6</f>
         <v/>
       </c>
-      <c r="C6" s="52" t="n"/>
-      <c r="D6" s="53" t="n"/>
-      <c r="E6" s="53" t="n"/>
-      <c r="F6" s="53" t="n"/>
-      <c r="G6" s="53" t="n"/>
-      <c r="H6" s="53" t="n"/>
-      <c r="I6" s="53" t="n"/>
-      <c r="J6" s="53" t="n"/>
-      <c r="K6" s="53" t="n"/>
-      <c r="L6" s="54" t="n"/>
-      <c r="M6" s="12" t="inlineStr">
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="62" t="n"/>
+      <c r="E6" s="62" t="n"/>
+      <c r="F6" s="62" t="n"/>
+      <c r="G6" s="62" t="n"/>
+      <c r="H6" s="62" t="n"/>
+      <c r="I6" s="62" t="n"/>
+      <c r="J6" s="62" t="n"/>
+      <c r="K6" s="62" t="n"/>
+      <c r="L6" s="63" t="n"/>
+      <c r="M6" s="76" t="inlineStr">
         <is>
           <t>APROBO:</t>
         </is>
       </c>
-      <c r="N6" s="32">
+      <c r="N6" s="77">
         <f>PORTADA!BO6</f>
         <v/>
       </c>
-      <c r="O6" s="47" t="n"/>
+      <c r="O6" s="66" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="80" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="80" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="80" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="80" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="80" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="80" t="n">
         <v>8</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="80" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="80" t="n">
         <v>10</v>
       </c>
-      <c r="K7" s="18" t="n">
+      <c r="K7" s="80" t="n">
         <v>11</v>
       </c>
-      <c r="L7" s="18" t="n">
+      <c r="L7" s="80" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="18" t="n">
+      <c r="M7" s="80" t="n">
         <v>13</v>
       </c>
-      <c r="N7" s="18" t="n">
+      <c r="N7" s="80" t="n">
         <v>14</v>
       </c>
-      <c r="O7" s="18" t="n">
+      <c r="O7" s="80" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="A8" s="81" t="inlineStr">
         <is>
           <t>LISTADO DE EQUIPOS Y MATERIALES (BOQ): SISTEMA DE VENTILACIÓN DEL LABORATORIO</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="59" t="inlineStr">
+      <c r="B8" s="55" t="n"/>
+      <c r="C8" s="55" t="n"/>
+      <c r="D8" s="55" t="n"/>
+      <c r="E8" s="55" t="n"/>
+      <c r="F8" s="55" t="n"/>
+      <c r="G8" s="55" t="n"/>
+      <c r="H8" s="55" t="n"/>
+      <c r="I8" s="55" t="n"/>
+      <c r="J8" s="55" t="n"/>
+      <c r="K8" s="55" t="n"/>
+      <c r="L8" s="55" t="n"/>
+      <c r="M8" s="55" t="n"/>
+      <c r="N8" s="55" t="n"/>
+      <c r="O8" s="55" t="n"/>
+    </row>
+    <row r="9" ht="450" customHeight="1">
+      <c r="A9" s="82" t="inlineStr">
         <is>
           <t>Listado de equipos y materiales (BOQ): sistema de ventilación del laboratorio</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="60" t="inlineStr">
+    <row r="10" ht="210" customHeight="1">
+      <c r="A10" s="83" t="inlineStr">
         <is>
           <t>Proyecto: P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá (Cundinamarca)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="60" t="inlineStr">
+    <row r="11" ht="15" customHeight="1"/>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Documento: listado_equipos.md — Revisión 1</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="60" t="inlineStr">
+    <row r="13" ht="195" customHeight="1">
+      <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Fecha: 2026-07-27 (fuentes consultadas el 2026-07-23; frente de ventiladores axiales ampliado el 2026-07-27)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="60" t="inlineStr">
+    <row r="14" ht="15" customHeight="1"/>
+    <row r="15" ht="150" customHeight="1">
+      <c r="A15" s="83" t="inlineStr">
         <is>
           <t>Base: informe_investigacion.md (misma revisión); punto de diseño 3 840 m³/h @ 165 Pa en el sitio (225 Pa equivalente de catálogo, ρ = 1.2 kg/m³).</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="60" t="inlineStr">
+    <row r="16" ht="15" customHeight="1"/>
+    <row r="17" ht="15" customHeight="1"/>
+    <row r="18" ht="150" customHeight="1">
+      <c r="A18" s="83" t="inlineStr">
         <is>
           <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial, sin instrumentación de presión diferencial.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="61" t="inlineStr">
+    <row r="19" ht="15" customHeight="1"/>
+    <row r="20" ht="15" customHeight="1"/>
+    <row r="21" ht="15" customHeight="1"/>
+    <row r="22" ht="75" customHeight="1">
+      <c r="A22" s="84" t="inlineStr">
         <is>
           <t>1. Alcance del suministro</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="60" t="inlineStr">
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="83" t="inlineStr">
         <is>
           <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="20">
-      <c r="A20" s="61" t="inlineStr">
+    <row r="24" ht="15" customHeight="1"/>
+    <row r="25" ht="15" customHeight="1"/>
+    <row r="26" ht="15" customHeight="1"/>
+    <row r="27" ht="15" customHeight="1"/>
+    <row r="28" ht="15" customHeight="1"/>
+    <row r="29" ht="15" customHeight="1"/>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="84" t="inlineStr">
         <is>
           <t>2. Tabla de equipos y materiales</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="62" t="inlineStr">
+    <row r="31" ht="135" customHeight="1">
+      <c r="A31" s="85" t="inlineStr">
         <is>
           <t>Tabla 1. BOQ del sistema de ventilación (consulta de fuentes 2026-07-23, ampliada 2026-07-27).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="63" t="inlineStr">
+    <row r="32" ht="15" customHeight="1"/>
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="86" t="inlineStr">
         <is>
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B22" s="63" t="inlineStr">
+      <c r="B33" s="86" t="inlineStr">
         <is>
           <t>Función</t>
         </is>
       </c>
-      <c r="C22" s="63" t="n"/>
-      <c r="D22" s="63" t="inlineStr">
+      <c r="C33" s="86" t="n"/>
+      <c r="D33" s="86" t="inlineStr">
         <is>
           <t>Especificación clave</t>
         </is>
       </c>
-      <c r="E22" s="63" t="n"/>
-      <c r="F22" s="63" t="n"/>
-      <c r="G22" s="63" t="inlineStr">
+      <c r="E33" s="86" t="n"/>
+      <c r="F33" s="86" t="n"/>
+      <c r="G33" s="86" t="inlineStr">
         <is>
           <t>Material / compatibilidad corrosiva</t>
         </is>
       </c>
-      <c r="H22" s="63" t="n"/>
-      <c r="I22" s="63" t="inlineStr">
+      <c r="H33" s="86" t="n"/>
+      <c r="I33" s="86" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="J22" s="63" t="inlineStr">
+      <c r="J33" s="86" t="inlineStr">
         <is>
           <t>Candidatos comerciales (fabricante/modelo)</t>
         </is>
       </c>
-      <c r="K22" s="63" t="n"/>
-      <c r="L22" s="63" t="n"/>
-      <c r="M22" s="63" t="inlineStr">
+      <c r="K33" s="86" t="n"/>
+      <c r="L33" s="86" t="n"/>
+      <c r="M33" s="86" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N22" s="63" t="n"/>
-      <c r="O22" s="63" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="64" t="inlineStr">
+      <c r="N33" s="86" t="n"/>
+      <c r="O33" s="86" t="n"/>
+    </row>
+    <row r="34" ht="810" customHeight="1">
+      <c r="A34" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B23" s="64" t="inlineStr">
+      <c r="B34" s="87" t="inlineStr">
         <is>
           <t>Ventilador de impulsión</t>
         </is>
       </c>
-      <c r="C23" s="65" t="n"/>
-      <c r="D23" s="64" t="inlineStr">
+      <c r="C34" s="88" t="n"/>
+      <c r="D34" s="87" t="inlineStr">
         <is>
           <t>Axial tubeaxial, transmisión por bandas; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; tamaño/RPM por confirmar con proveedor</t>
         </is>
       </c>
-      <c r="E23" s="65" t="n"/>
-      <c r="F23" s="65" t="n"/>
-      <c r="G23" s="64" t="inlineStr">
+      <c r="E34" s="88" t="n"/>
+      <c r="F34" s="88" t="n"/>
+      <c r="G34" s="87" t="inlineStr">
         <is>
           <t>PRFV viniléster (ASTM C582/D4167); motor fuera de la corriente de aire</t>
         </is>
       </c>
-      <c r="H23" s="65" t="n"/>
-      <c r="I23" s="64" t="inlineStr">
+      <c r="H34" s="88" t="n"/>
+      <c r="I34" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J23" s="64" t="inlineStr">
+      <c r="J34" s="87" t="inlineStr">
         <is>
           <t>Aerovent FBD (Twin City Fan, Catálogo 185); Greenheck VAB (vaneaxial epóxico, Prime Lines HVAC, Bogotá); Sodeca HCT/HGT anticorrosivo PRFV; NYB FRP tubeaxial; Plastec PP</t>
         </is>
       </c>
-      <c r="K23" s="65" t="n"/>
-      <c r="L23" s="65" t="n"/>
-      <c r="M23" s="64" t="inlineStr">
+      <c r="K34" s="88" t="n"/>
+      <c r="L34" s="88" t="n"/>
+      <c r="M34" s="87" t="inlineStr">
         <is>
           <t>Aerovent Cat. 185 (PDF) (https://www.aerovent.com/wp-content/uploads/sites/2/2024/07/Fiberglass-Fans-Axial-Flow-Model-FBD-FDP-FRV-TFBD-VTFBD-Catalog-185.pdf); Greenheck VAB/VAD (PDF) (https://content.greenheck.com/public/DAMProd/Original/10003/vane_axial_catalog.pdf); Sodeca (https://www.sodeca.com)</t>
         </is>
       </c>
-      <c r="N23" s="65" t="n"/>
-      <c r="O23" s="65" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="64" t="inlineStr">
+      <c r="N34" s="88" t="n"/>
+      <c r="O34" s="88" t="n"/>
+    </row>
+    <row r="35" ht="525" customHeight="1">
+      <c r="A35" s="87" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B24" s="64" t="inlineStr">
+      <c r="B35" s="87" t="inlineStr">
         <is>
           <t>Motor del ventilador</t>
         </is>
       </c>
-      <c r="C24" s="65" t="n"/>
-      <c r="D24" s="64" t="inlineStr">
+      <c r="C35" s="88" t="n"/>
+      <c r="D35" s="87" t="inlineStr">
         <is>
           <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC, 1 800 RPM (4 polos), 60 Hz, clase F, IP55 mín., severe duty epóxico; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
         </is>
       </c>
-      <c r="E24" s="65" t="n"/>
-      <c r="F24" s="65" t="n"/>
-      <c r="G24" s="64" t="inlineStr">
+      <c r="E35" s="88" t="n"/>
+      <c r="F35" s="88" t="n"/>
+      <c r="G35" s="87" t="inlineStr">
         <is>
           <t>Pintura epóxica + protección interna anticorrosiva; motor fuera de la corriente (transmisión por bandas)</t>
         </is>
       </c>
-      <c r="H24" s="65" t="n"/>
-      <c r="I24" s="64" t="inlineStr">
+      <c r="H35" s="88" t="n"/>
+      <c r="I35" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J24" s="64" t="inlineStr">
+      <c r="J35" s="87" t="inlineStr">
         <is>
           <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
         </is>
       </c>
-      <c r="K24" s="65" t="n"/>
-      <c r="L24" s="65" t="n"/>
-      <c r="M24" s="64" t="inlineStr">
+      <c r="K35" s="88" t="n"/>
+      <c r="L35" s="88" t="n"/>
+      <c r="M35" s="87" t="inlineStr">
         <is>
           <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
         </is>
       </c>
-      <c r="N24" s="65" t="n"/>
-      <c r="O24" s="65" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="N35" s="88" t="n"/>
+      <c r="O35" s="88" t="n"/>
+    </row>
+    <row r="36" ht="465" customHeight="1">
+      <c r="A36" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B25" s="64" t="inlineStr">
+      <c r="B36" s="87" t="inlineStr">
         <is>
           <t>Prefiltro (etapa 1)</t>
         </is>
       </c>
-      <c r="C25" s="65" t="n"/>
-      <c r="D25" s="64" t="inlineStr">
+      <c r="C36" s="88" t="n"/>
+      <c r="D36" s="87" t="inlineStr">
         <is>
           <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
         </is>
       </c>
-      <c r="E25" s="65" t="n"/>
-      <c r="F25" s="65" t="n"/>
-      <c r="G25" s="64" t="inlineStr">
+      <c r="E36" s="88" t="n"/>
+      <c r="F36" s="88" t="n"/>
+      <c r="G36" s="87" t="inlineStr">
         <is>
           <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
         </is>
       </c>
-      <c r="H25" s="65" t="n"/>
-      <c r="I25" s="64" t="inlineStr">
+      <c r="H36" s="88" t="n"/>
+      <c r="I36" s="87" t="inlineStr">
         <is>
           <t>1 (+ repuestos)</t>
         </is>
       </c>
-      <c r="J25" s="64" t="inlineStr">
+      <c r="J36" s="87" t="inlineStr">
         <is>
           <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
         </is>
       </c>
-      <c r="K25" s="65" t="n"/>
-      <c r="L25" s="65" t="n"/>
-      <c r="M25" s="64" t="inlineStr">
+      <c r="K36" s="88" t="n"/>
+      <c r="L36" s="88" t="n"/>
+      <c r="M36" s="87" t="inlineStr">
         <is>
           <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
         </is>
       </c>
-      <c r="N25" s="65" t="n"/>
-      <c r="O25" s="65" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="64" t="inlineStr">
+      <c r="N36" s="88" t="n"/>
+      <c r="O36" s="88" t="n"/>
+    </row>
+    <row r="37" ht="660" customHeight="1">
+      <c r="A37" s="87" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B26" s="64" t="inlineStr">
+      <c r="B37" s="87" t="inlineStr">
         <is>
           <t>Filtro final (etapa 2)</t>
         </is>
       </c>
-      <c r="C26" s="65" t="n"/>
-      <c r="D26" s="64" t="inlineStr">
+      <c r="C37" s="88" t="n"/>
+      <c r="D37" s="87" t="inlineStr">
         <is>
           <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
         </is>
       </c>
-      <c r="E26" s="65" t="n"/>
-      <c r="F26" s="65" t="n"/>
-      <c r="G26" s="64" t="inlineStr">
+      <c r="E37" s="88" t="n"/>
+      <c r="F37" s="88" t="n"/>
+      <c r="G37" s="87" t="inlineStr">
         <is>
           <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
         </is>
       </c>
-      <c r="H26" s="65" t="n"/>
-      <c r="I26" s="64" t="inlineStr">
+      <c r="H37" s="88" t="n"/>
+      <c r="I37" s="87" t="inlineStr">
         <is>
           <t>1 (+ repuestos)</t>
         </is>
       </c>
-      <c r="J26" s="64" t="inlineStr">
+      <c r="J37" s="87" t="inlineStr">
         <is>
           <t>Camfil Durafil ES2 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
         </is>
       </c>
-      <c r="K26" s="65" t="n"/>
-      <c r="L26" s="65" t="n"/>
-      <c r="M26" s="64" t="inlineStr">
+      <c r="K37" s="88" t="n"/>
+      <c r="L37" s="88" t="n"/>
+      <c r="M37" s="87" t="inlineStr">
         <is>
           <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
         </is>
       </c>
-      <c r="N26" s="65" t="n"/>
-      <c r="O26" s="65" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="N37" s="88" t="n"/>
+      <c r="O37" s="88" t="n"/>
+    </row>
+    <row r="38" ht="420" customHeight="1">
+      <c r="A38" s="87" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B27" s="64" t="inlineStr">
+      <c r="B38" s="87" t="inlineStr">
         <is>
           <t>Marcos portafiltros</t>
         </is>
       </c>
-      <c r="C27" s="65" t="n"/>
-      <c r="D27" s="64" t="inlineStr">
+      <c r="C38" s="88" t="n"/>
+      <c r="D38" s="87" t="inlineStr">
         <is>
           <t>Holding frames para prefiltro + filtro final con junta continua</t>
         </is>
       </c>
-      <c r="E27" s="65" t="n"/>
-      <c r="F27" s="65" t="n"/>
-      <c r="G27" s="64" t="inlineStr">
+      <c r="E38" s="88" t="n"/>
+      <c r="F38" s="88" t="n"/>
+      <c r="G38" s="87" t="inlineStr">
         <is>
           <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
         </is>
       </c>
-      <c r="H27" s="65" t="n"/>
-      <c r="I27" s="64" t="inlineStr">
+      <c r="H38" s="88" t="n"/>
+      <c r="I38" s="87" t="inlineStr">
         <is>
           <t>1 juego</t>
         </is>
       </c>
-      <c r="J27" s="64" t="inlineStr">
+      <c r="J38" s="87" t="inlineStr">
         <is>
           <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
         </is>
       </c>
-      <c r="K27" s="65" t="n"/>
-      <c r="L27" s="65" t="n"/>
-      <c r="M27" s="64" t="inlineStr">
+      <c r="K38" s="88" t="n"/>
+      <c r="L38" s="88" t="n"/>
+      <c r="M38" s="87" t="inlineStr">
         <is>
           <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
         </is>
       </c>
-      <c r="N27" s="65" t="n"/>
-      <c r="O27" s="65" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="64" t="inlineStr">
+      <c r="N38" s="88" t="n"/>
+      <c r="O38" s="88" t="n"/>
+    </row>
+    <row r="39" ht="450" customHeight="1">
+      <c r="A39" s="87" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B28" s="64" t="inlineStr">
+      <c r="B39" s="87" t="inlineStr">
         <is>
           <t>Rejillas de descarga</t>
         </is>
       </c>
-      <c r="C28" s="65" t="n"/>
-      <c r="D28" s="64" t="inlineStr">
+      <c r="C39" s="88" t="n"/>
+      <c r="D39" s="87" t="inlineStr">
         <is>
           <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
         </is>
       </c>
-      <c r="E28" s="65" t="n"/>
-      <c r="F28" s="65" t="n"/>
-      <c r="G28" s="64" t="inlineStr">
+      <c r="E39" s="88" t="n"/>
+      <c r="F39" s="88" t="n"/>
+      <c r="G39" s="87" t="inlineStr">
         <is>
           <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
         </is>
       </c>
-      <c r="H28" s="65" t="n"/>
-      <c r="I28" s="64" t="inlineStr">
+      <c r="H39" s="88" t="n"/>
+      <c r="I39" s="87" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J28" s="64" t="inlineStr">
+      <c r="J39" s="87" t="inlineStr">
         <is>
           <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
         </is>
       </c>
-      <c r="K28" s="65" t="n"/>
-      <c r="L28" s="65" t="n"/>
-      <c r="M28" s="64" t="inlineStr">
+      <c r="K39" s="88" t="n"/>
+      <c r="L39" s="88" t="n"/>
+      <c r="M39" s="87" t="inlineStr">
         <is>
           <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
-      <c r="N28" s="65" t="n"/>
-      <c r="O28" s="65" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="64" t="inlineStr">
+      <c r="N39" s="88" t="n"/>
+      <c r="O39" s="88" t="n"/>
+    </row>
+    <row r="40" ht="375" customHeight="1">
+      <c r="A40" s="87" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B29" s="64" t="inlineStr">
+      <c r="B40" s="87" t="inlineStr">
         <is>
           <t>Malla anti-insectos</t>
         </is>
       </c>
-      <c r="C29" s="65" t="n"/>
-      <c r="D29" s="64" t="inlineStr">
+      <c r="C40" s="88" t="n"/>
+      <c r="D40" s="87" t="inlineStr">
         <is>
           <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
         </is>
       </c>
-      <c r="E29" s="65" t="n"/>
-      <c r="F29" s="65" t="n"/>
-      <c r="G29" s="64" t="inlineStr">
+      <c r="E40" s="88" t="n"/>
+      <c r="F40" s="88" t="n"/>
+      <c r="G40" s="87" t="inlineStr">
         <is>
           <t>Inox 316</t>
         </is>
       </c>
-      <c r="H29" s="65" t="n"/>
-      <c r="I29" s="64" t="inlineStr">
+      <c r="H40" s="88" t="n"/>
+      <c r="I40" s="87" t="inlineStr">
         <is>
           <t>3 (una por rejilla)</t>
         </is>
       </c>
-      <c r="J29" s="64" t="inlineStr">
+      <c r="J40" s="87" t="inlineStr">
         <is>
           <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
         </is>
       </c>
-      <c r="K29" s="65" t="n"/>
-      <c r="L29" s="65" t="n"/>
-      <c r="M29" s="64" t="inlineStr">
+      <c r="K40" s="88" t="n"/>
+      <c r="L40" s="88" t="n"/>
+      <c r="M40" s="87" t="inlineStr">
         <is>
           <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
         </is>
       </c>
-      <c r="N29" s="65" t="n"/>
-      <c r="O29" s="65" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="64" t="inlineStr">
+      <c r="N40" s="88" t="n"/>
+      <c r="O40" s="88" t="n"/>
+    </row>
+    <row r="41" ht="270" customHeight="1">
+      <c r="A41" s="87" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B30" s="64" t="inlineStr">
+      <c r="B41" s="87" t="inlineStr">
         <is>
           <t>Soportes y ferretería</t>
         </is>
       </c>
-      <c r="C30" s="65" t="n"/>
-      <c r="D30" s="64" t="inlineStr">
+      <c r="C41" s="88" t="n"/>
+      <c r="D41" s="87" t="inlineStr">
         <is>
           <t>Soportes de ventilador y rejillas; pernos, tuercas, arandelas</t>
         </is>
       </c>
-      <c r="E30" s="65" t="n"/>
-      <c r="F30" s="65" t="n"/>
-      <c r="G30" s="64" t="inlineStr">
+      <c r="E41" s="88" t="n"/>
+      <c r="F41" s="88" t="n"/>
+      <c r="G41" s="87" t="inlineStr">
         <is>
           <t>Inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
         </is>
       </c>
-      <c r="H30" s="65" t="n"/>
-      <c r="I30" s="64" t="inlineStr">
+      <c r="H41" s="88" t="n"/>
+      <c r="I41" s="87" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="J30" s="64" t="inlineStr">
+      <c r="J41" s="87" t="inlineStr">
         <is>
           <t>Suministro nacional genérico A4</t>
         </is>
       </c>
-      <c r="K30" s="65" t="n"/>
-      <c r="L30" s="65" t="n"/>
-      <c r="M30" s="64" t="inlineStr">
+      <c r="K41" s="88" t="n"/>
+      <c r="L41" s="88" t="n"/>
+      <c r="M41" s="87" t="inlineStr">
         <is>
           <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
         </is>
       </c>
-      <c r="N30" s="65" t="n"/>
-      <c r="O30" s="65" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="64" t="inlineStr">
+      <c r="N41" s="88" t="n"/>
+      <c r="O41" s="88" t="n"/>
+    </row>
+    <row r="42" ht="360" customHeight="1">
+      <c r="A42" s="87" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B31" s="64" t="inlineStr">
+      <c r="B42" s="87" t="inlineStr">
         <is>
           <t>Conexión flexible ventilador-pasamuros</t>
         </is>
       </c>
-      <c r="C31" s="65" t="n"/>
-      <c r="D31" s="64" t="inlineStr">
+      <c r="C42" s="88" t="n"/>
+      <c r="D42" s="87" t="inlineStr">
         <is>
           <t>Ancho ≥ 100 mm; bandas de amarre inox 316 cal. 24</t>
         </is>
       </c>
-      <c r="E31" s="65" t="n"/>
-      <c r="F31" s="65" t="n"/>
-      <c r="G31" s="64" t="inlineStr">
+      <c r="E42" s="88" t="n"/>
+      <c r="F42" s="88" t="n"/>
+      <c r="G42" s="87" t="inlineStr">
         <is>
           <t>Hipalón (CSM); alternativa clorobutilo; no PVC estándar</t>
         </is>
       </c>
-      <c r="H31" s="65" t="n"/>
-      <c r="I31" s="64" t="inlineStr">
+      <c r="H42" s="88" t="n"/>
+      <c r="I42" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J31" s="64" t="inlineStr">
+      <c r="J42" s="87" t="inlineStr">
         <is>
           <t>Hardcast Hypalon; Proco serie 500</t>
         </is>
       </c>
-      <c r="K31" s="65" t="n"/>
-      <c r="L31" s="65" t="n"/>
-      <c r="M31" s="64" t="inlineStr">
+      <c r="K42" s="88" t="n"/>
+      <c r="L42" s="88" t="n"/>
+      <c r="M42" s="87" t="inlineStr">
         <is>
           <t>Hardcast (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf)</t>
         </is>
       </c>
-      <c r="N31" s="65" t="n"/>
-      <c r="O31" s="65" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="64" t="inlineStr">
+      <c r="N42" s="88" t="n"/>
+      <c r="O42" s="88" t="n"/>
+    </row>
+    <row r="43" ht="600" customHeight="1">
+      <c r="A43" s="87" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B32" s="64" t="inlineStr">
+      <c r="B43" s="87" t="inlineStr">
         <is>
           <t>Selladores</t>
         </is>
       </c>
-      <c r="C32" s="65" t="n"/>
-      <c r="D32" s="64" t="inlineStr">
+      <c r="C43" s="88" t="n"/>
+      <c r="D43" s="87" t="inlineStr">
         <is>
           <t>Sellado de pasamuros, marcos y empalmes</t>
         </is>
       </c>
-      <c r="E32" s="65" t="n"/>
-      <c r="F32" s="65" t="n"/>
-      <c r="G32" s="64" t="inlineStr">
+      <c r="E43" s="88" t="n"/>
+      <c r="F43" s="88" t="n"/>
+      <c r="G43" s="87" t="inlineStr">
         <is>
           <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
         </is>
       </c>
-      <c r="H32" s="65" t="n"/>
-      <c r="I32" s="64" t="inlineStr">
+      <c r="H43" s="88" t="n"/>
+      <c r="I43" s="87" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="J32" s="64" t="inlineStr">
+      <c r="J43" s="87" t="inlineStr">
         <is>
           <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
         </is>
       </c>
-      <c r="K32" s="65" t="n"/>
-      <c r="L32" s="65" t="n"/>
-      <c r="M32" s="64" t="inlineStr">
+      <c r="K43" s="88" t="n"/>
+      <c r="L43" s="88" t="n"/>
+      <c r="M43" s="87" t="inlineStr">
         <is>
           <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
         </is>
       </c>
-      <c r="N32" s="65" t="n"/>
-      <c r="O32" s="65" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="64" t="inlineStr">
+      <c r="N43" s="88" t="n"/>
+      <c r="O43" s="88" t="n"/>
+    </row>
+    <row r="44" ht="240" customHeight="1">
+      <c r="A44" s="87" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B33" s="64" t="inlineStr">
+      <c r="B44" s="87" t="inlineStr">
         <is>
           <t>Protecciones eléctricas y tablero</t>
         </is>
       </c>
-      <c r="C33" s="65" t="n"/>
-      <c r="D33" s="64" t="inlineStr">
+      <c r="C44" s="88" t="n"/>
+      <c r="D44" s="87" t="inlineStr">
         <is>
           <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
         </is>
       </c>
-      <c r="E33" s="65" t="n"/>
-      <c r="F33" s="65" t="n"/>
-      <c r="G33" s="64" t="inlineStr">
+      <c r="E44" s="88" t="n"/>
+      <c r="F44" s="88" t="n"/>
+      <c r="G44" s="87" t="inlineStr">
         <is>
           <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
         </is>
       </c>
-      <c r="H33" s="65" t="n"/>
-      <c r="I33" s="64" t="inlineStr">
+      <c r="H44" s="88" t="n"/>
+      <c r="I44" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J33" s="64" t="inlineStr">
+      <c r="J44" s="87" t="inlineStr">
         <is>
           <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
         </is>
       </c>
-      <c r="K33" s="65" t="n"/>
-      <c r="L33" s="65" t="n"/>
-      <c r="M33" s="64" t="inlineStr">
+      <c r="K44" s="88" t="n"/>
+      <c r="L44" s="88" t="n"/>
+      <c r="M44" s="87" t="inlineStr">
         <is>
           <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
         </is>
       </c>
-      <c r="N33" s="65" t="n"/>
-      <c r="O33" s="65" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="64" t="inlineStr">
+      <c r="N44" s="88" t="n"/>
+      <c r="O44" s="88" t="n"/>
+    </row>
+    <row r="45" ht="210" customHeight="1">
+      <c r="A45" s="87" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B34" s="64" t="inlineStr">
+      <c r="B45" s="87" t="inlineStr">
         <is>
           <t>Cableado y canalización</t>
         </is>
       </c>
-      <c r="C34" s="65" t="n"/>
-      <c r="D34" s="64" t="inlineStr">
+      <c r="C45" s="88" t="n"/>
+      <c r="D45" s="87" t="inlineStr">
         <is>
           <t>Circuito de alimentación del motor 0.75 HP</t>
         </is>
       </c>
-      <c r="E34" s="65" t="n"/>
-      <c r="F34" s="65" t="n"/>
-      <c r="G34" s="64" t="inlineStr">
+      <c r="E45" s="88" t="n"/>
+      <c r="F45" s="88" t="n"/>
+      <c r="G45" s="87" t="inlineStr">
         <is>
           <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
         </is>
       </c>
-      <c r="H34" s="65" t="n"/>
-      <c r="I34" s="64" t="inlineStr">
+      <c r="H45" s="88" t="n"/>
+      <c r="I45" s="87" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="J34" s="64" t="inlineStr">
+      <c r="J45" s="87" t="inlineStr">
         <is>
           <t>Suministro nacional certificado RETIE</t>
         </is>
       </c>
-      <c r="K34" s="65" t="n"/>
-      <c r="L34" s="65" t="n"/>
-      <c r="M34" s="64" t="inlineStr">
+      <c r="K45" s="88" t="n"/>
+      <c r="L45" s="88" t="n"/>
+      <c r="M45" s="87" t="inlineStr">
         <is>
           <t>Requisito RETIE / NTC 2050</t>
         </is>
       </c>
-      <c r="N34" s="65" t="n"/>
-      <c r="O34" s="65" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="61" t="inlineStr">
+      <c r="N45" s="88" t="n"/>
+      <c r="O45" s="88" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1"/>
+    <row r="47" ht="15" customHeight="1"/>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="84" t="inlineStr">
         <is>
           <t>3. Notas de suministro</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="60" t="inlineStr">
+    <row r="49" ht="150" customHeight="1">
+      <c r="A49" s="83" t="inlineStr">
         <is>
           <t>3.1. Los ítems 1 y 4 requieren cotización formal con submittal: la selección final de tamaño/RPM del ventilador (ítem 1) y la potencia definitiva del motor (ítem 2) se confirman con el software del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar.</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" s="60" t="inlineStr">
+    <row r="50" ht="15" customHeight="1"/>
+    <row r="51" ht="15" customHeight="1"/>
+    <row r="52" ht="15" customHeight="1"/>
+    <row r="53" ht="15" customHeight="1"/>
+    <row r="54" ht="150" customHeight="1">
+      <c r="A54" s="83" t="inlineStr">
         <is>
           <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="60" t="inlineStr">
+    <row r="55" ht="15" customHeight="1"/>
+    <row r="56" ht="15" customHeight="1"/>
+    <row r="57" ht="15" customHeight="1"/>
+    <row r="58" ht="15" customHeight="1"/>
+    <row r="59" ht="15" customHeight="1"/>
+    <row r="60" ht="15" customHeight="1"/>
+    <row r="61" ht="165" customHeight="1">
+      <c r="A61" s="83" t="inlineStr">
         <is>
           <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
+    <row r="62" ht="15" customHeight="1"/>
+    <row r="63" ht="15" customHeight="1"/>
+    <row r="64" ht="15" customHeight="1"/>
+    <row r="65" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="85">
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="J25:L25"/>
+  <mergeCells count="90">
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="J35:L35"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="M41:O41"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="D39:F39"/>
     <mergeCell ref="C2:L3"/>
     <mergeCell ref="G34:H34"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="J38:L38"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A40:O42"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="A17:O18"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="A16:O16"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="A43:O44"/>
-    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="A10:O11"/>
+    <mergeCell ref="A23:O28"/>
+    <mergeCell ref="A54:O60"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="G38:H38"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="A20:O20"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A18:O20"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="A22:O22"/>
     <mergeCell ref="J33:L33"/>
-    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="J42:L42"/>
     <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="A48:O48"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="G35:H35"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="M35:O35"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="A38:O39"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="A13:O14"/>
+    <mergeCell ref="A61:O65"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="M33:O33"/>
+    <mergeCell ref="A31:O32"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="G37:H37"/>
     <mergeCell ref="A8:O8"/>
     <mergeCell ref="D33:F33"/>
-    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D44:F44"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
     <mergeCell ref="D34:F34"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="A49:O53"/>
+    <mergeCell ref="D45:F45"/>
     <mergeCell ref="J34:L34"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J31:L31"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="M45:O45"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="G45:H45"/>
     <mergeCell ref="M34:O34"/>
-    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="A15:O17"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="G40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/build/lis/P2437-HV-LIS-001 REV0.xlsx
+++ b/build/lis/P2437-HV-LIS-001 REV0.xlsx
@@ -3720,7 +3720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.6" customWidth="1" min="1" max="1"/>
@@ -3766,7 +3766,7 @@
     <col width="13" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="13" customWidth="1" min="46" max="46"/>
     <col width="13" customWidth="1" min="49" max="49"/>
     <col width="13" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
@@ -3784,6 +3784,8 @@
     <col width="13" customWidth="1" min="63" max="63"/>
     <col width="13" customWidth="1" min="64" max="64"/>
     <col width="13" customWidth="1" min="65" max="65"/>
+    <col width="13" customWidth="1" min="66" max="66"/>
+    <col width="13" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -4683,52 +4685,98 @@
       <c r="N45" s="88" t="n"/>
       <c r="O45" s="88" t="n"/>
     </row>
-    <row r="46" ht="15" customHeight="1"/>
+    <row r="46" ht="345" customHeight="1">
+      <c r="A46" s="87" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B46" s="87" t="inlineStr">
+        <is>
+          <t>Caja/housing de filtración y transición</t>
+        </is>
+      </c>
+      <c r="C46" s="88" t="n"/>
+      <c r="D46" s="87" t="inlineStr">
+        <is>
+          <t>Alojar portafiltros, malla anti-insectos y adaptar la boca cuadrada 24×24 in del filtro a la boca circular del ventilador axial</t>
+        </is>
+      </c>
+      <c r="E46" s="88" t="n"/>
+      <c r="F46" s="88" t="n"/>
+      <c r="G46" s="87" t="inlineStr">
+        <is>
+          <t>Inox 316L o PRFV viniléster (mismo criterio anticorrosivo del ventilador); tapas de inspección, juntas PU</t>
+        </is>
+      </c>
+      <c r="H46" s="88" t="n"/>
+      <c r="I46" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" s="87" t="inlineStr">
+        <is>
+          <t>Fabricación local a partir de planos del submittal del ventilador</t>
+        </is>
+      </c>
+      <c r="K46" s="88" t="n"/>
+      <c r="L46" s="88" t="n"/>
+      <c r="M46" s="87" t="inlineStr">
+        <is>
+          <t>Derivado de HD-FILT-001 §7.3</t>
+        </is>
+      </c>
+      <c r="N46" s="88" t="n"/>
+      <c r="O46" s="88" t="n"/>
+    </row>
     <row r="47" ht="15" customHeight="1"/>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="84" t="inlineStr">
+    <row r="48" ht="15" customHeight="1"/>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="84" t="inlineStr">
         <is>
           <t>3. Notas de suministro</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="150" customHeight="1">
-      <c r="A49" s="83" t="inlineStr">
-        <is>
-          <t>3.1. Los ítems 1 y 4 requieren cotización formal con submittal: la selección final de tamaño/RPM del ventilador (ítem 1) y la potencia definitiva del motor (ítem 2) se confirman con el software del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1"/>
+    <row r="50" ht="165" customHeight="1">
+      <c r="A50" s="83" t="inlineStr">
+        <is>
+          <t>3.1. Los ítems 1, 4 y 13 requieren cotización formal con submittal: la selección final de tamaño/RPM del ventilador (ítem 1), la potencia definitiva del motor (ítem 2) y las dimensiones de la caja de filtración/transición cuadrado-circular (ítem 13) se confirman con el software o planos del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar.</t>
+        </is>
+      </c>
+    </row>
     <row r="51" ht="15" customHeight="1"/>
     <row r="52" ht="15" customHeight="1"/>
     <row r="53" ht="15" customHeight="1"/>
-    <row r="54" ht="150" customHeight="1">
-      <c r="A54" s="83" t="inlineStr">
+    <row r="54" ht="15" customHeight="1"/>
+    <row r="55" ht="15" customHeight="1"/>
+    <row r="56" ht="150" customHeight="1">
+      <c r="A56" s="83" t="inlineStr">
         <is>
           <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1"/>
-    <row r="56" ht="15" customHeight="1"/>
     <row r="57" ht="15" customHeight="1"/>
     <row r="58" ht="15" customHeight="1"/>
     <row r="59" ht="15" customHeight="1"/>
     <row r="60" ht="15" customHeight="1"/>
-    <row r="61" ht="165" customHeight="1">
-      <c r="A61" s="83" t="inlineStr">
+    <row r="61" ht="15" customHeight="1"/>
+    <row r="62" ht="15" customHeight="1"/>
+    <row r="63" ht="165" customHeight="1">
+      <c r="A63" s="83" t="inlineStr">
         <is>
           <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1"/>
-    <row r="63" ht="15" customHeight="1"/>
     <row r="64" ht="15" customHeight="1"/>
     <row r="65" ht="15" customHeight="1"/>
+    <row r="66" ht="15" customHeight="1"/>
+    <row r="67" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="90">
+  <mergeCells count="95">
     <mergeCell ref="M40:O40"/>
     <mergeCell ref="J35:L35"/>
     <mergeCell ref="N3:O3"/>
@@ -4737,12 +4785,14 @@
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="C2:L3"/>
+    <mergeCell ref="J46:L46"/>
     <mergeCell ref="G34:H34"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="J39:L39"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="J38:L38"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A50:O55"/>
     <mergeCell ref="M39:O39"/>
     <mergeCell ref="G44:H44"/>
     <mergeCell ref="J40:L40"/>
@@ -4752,7 +4802,6 @@
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="A10:O11"/>
     <mergeCell ref="A23:O28"/>
-    <mergeCell ref="A54:O60"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="J41:L41"/>
     <mergeCell ref="M37:O37"/>
@@ -4768,19 +4817,19 @@
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="M43:O43"/>
     <mergeCell ref="J44:L44"/>
-    <mergeCell ref="A48:O48"/>
     <mergeCell ref="A30:O30"/>
     <mergeCell ref="G35:H35"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="J37:L37"/>
+    <mergeCell ref="D46:F46"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="M35:O35"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="A13:O14"/>
-    <mergeCell ref="A61:O65"/>
     <mergeCell ref="G42:H42"/>
     <mergeCell ref="G39:H39"/>
     <mergeCell ref="B43:C43"/>
+    <mergeCell ref="M46:O46"/>
     <mergeCell ref="M33:O33"/>
     <mergeCell ref="A31:O32"/>
     <mergeCell ref="M42:O42"/>
@@ -4788,10 +4837,12 @@
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="A8:O8"/>
     <mergeCell ref="D33:F33"/>
+    <mergeCell ref="A56:O62"/>
     <mergeCell ref="D42:F42"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="D35:F35"/>
+    <mergeCell ref="A63:O67"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
@@ -4801,12 +4852,12 @@
     <mergeCell ref="G41:H41"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="D36:F36"/>
-    <mergeCell ref="A49:O53"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="J34:L34"/>
     <mergeCell ref="G43:H43"/>
     <mergeCell ref="J36:L36"/>
     <mergeCell ref="J45:L45"/>
+    <mergeCell ref="B46:C46"/>
     <mergeCell ref="G36:H36"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="M36:O36"/>
@@ -4817,7 +4868,9 @@
     <mergeCell ref="M34:O34"/>
     <mergeCell ref="A15:O17"/>
     <mergeCell ref="C4:L6"/>
+    <mergeCell ref="A49:O49"/>
     <mergeCell ref="B36:C36"/>
+    <mergeCell ref="G46:H46"/>
     <mergeCell ref="G40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/build/lis/P2437-HV-LIS-001 REV0.xlsx
+++ b/build/lis/P2437-HV-LIS-001 REV0.xlsx
@@ -3720,7 +3720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.6" customWidth="1" min="1" max="1"/>
@@ -3743,20 +3743,20 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
     <col width="13" customWidth="1" min="37" max="37"/>
     <col width="13" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
@@ -3767,13 +3767,13 @@
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="13" customWidth="1" min="45" max="45"/>
     <col width="13" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
     <col width="13" customWidth="1" min="49" max="49"/>
     <col width="13" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
     <col width="13" customWidth="1" min="52" max="52"/>
     <col width="13" customWidth="1" min="53" max="53"/>
-    <col width="13" customWidth="1" min="54" max="54"/>
-    <col width="13" customWidth="1" min="55" max="55"/>
     <col width="13" customWidth="1" min="56" max="56"/>
     <col width="13" customWidth="1" min="57" max="57"/>
     <col width="13" customWidth="1" min="58" max="58"/>
@@ -3786,6 +3786,14 @@
     <col width="13" customWidth="1" min="65" max="65"/>
     <col width="13" customWidth="1" min="66" max="66"/>
     <col width="13" customWidth="1" min="67" max="67"/>
+    <col width="13" customWidth="1" min="68" max="68"/>
+    <col width="13" customWidth="1" min="69" max="69"/>
+    <col width="13" customWidth="1" min="70" max="70"/>
+    <col width="13" customWidth="1" min="71" max="71"/>
+    <col width="13" customWidth="1" min="72" max="72"/>
+    <col width="13" customWidth="1" min="73" max="73"/>
+    <col width="13" customWidth="1" min="74" max="74"/>
+    <col width="13" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -4055,478 +4063,176 @@
     </row>
     <row r="16" ht="15" customHeight="1"/>
     <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="150" customHeight="1">
+    <row r="18" ht="165" customHeight="1">
       <c r="A18" s="83" t="inlineStr">
         <is>
-          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial, sin instrumentación de presión diferencial.</t>
+          <t>Nota de revisión REV2 — 2026-07-27: actualización por uniformidad con el montaje típico instalado en la planta (Montaje/DISENOFINAL.png): ventilador axial mural Ø560 mm de transmisión directa, banco de filtración alojado en la cubierta intemperie, estructura de unión pernada al muro y malla de protección interior. Se eliminan la conexión flexible y la caja/housing con transición cuadrado/circular (REV1).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1"/>
     <row r="20" ht="15" customHeight="1"/>
     <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="75" customHeight="1">
-      <c r="A22" s="84" t="inlineStr">
-        <is>
-          <t>1. Alcance del suministro</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="83" t="inlineStr">
-        <is>
-          <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
-        </is>
-      </c>
-    </row>
+    <row r="22" ht="15" customHeight="1"/>
+    <row r="23" ht="15" customHeight="1"/>
     <row r="24" ht="15" customHeight="1"/>
-    <row r="25" ht="15" customHeight="1"/>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="83" t="inlineStr">
+        <is>
+          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial, sin instrumentación de presión diferencial.</t>
+        </is>
+      </c>
+    </row>
     <row r="26" ht="15" customHeight="1"/>
     <row r="27" ht="15" customHeight="1"/>
     <row r="28" ht="15" customHeight="1"/>
-    <row r="29" ht="15" customHeight="1"/>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="84" t="inlineStr">
+    <row r="29" ht="75" customHeight="1">
+      <c r="A29" s="84" t="inlineStr">
+        <is>
+          <t>1. Alcance del suministro</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="83" t="inlineStr">
+        <is>
+          <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1"/>
+    <row r="32" ht="15" customHeight="1"/>
+    <row r="33" ht="15" customHeight="1"/>
+    <row r="34" ht="15" customHeight="1"/>
+    <row r="35" ht="15" customHeight="1"/>
+    <row r="36" ht="15" customHeight="1"/>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="84" t="inlineStr">
         <is>
           <t>2. Tabla de equipos y materiales</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="135" customHeight="1">
-      <c r="A31" s="85" t="inlineStr">
+    <row r="38" ht="135" customHeight="1">
+      <c r="A38" s="85" t="inlineStr">
         <is>
           <t>Tabla 1. BOQ del sistema de ventilación (consulta de fuentes 2026-07-23, ampliada 2026-07-27).</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="120" customHeight="1">
-      <c r="A33" s="86" t="inlineStr">
+    <row r="39" ht="15" customHeight="1"/>
+    <row r="40" ht="120" customHeight="1">
+      <c r="A40" s="86" t="inlineStr">
         <is>
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B33" s="86" t="inlineStr">
+      <c r="B40" s="86" t="inlineStr">
         <is>
           <t>Función</t>
         </is>
       </c>
-      <c r="C33" s="86" t="n"/>
-      <c r="D33" s="86" t="inlineStr">
+      <c r="C40" s="86" t="n"/>
+      <c r="D40" s="86" t="inlineStr">
         <is>
           <t>Especificación clave</t>
         </is>
       </c>
-      <c r="E33" s="86" t="n"/>
-      <c r="F33" s="86" t="n"/>
-      <c r="G33" s="86" t="inlineStr">
+      <c r="E40" s="86" t="n"/>
+      <c r="F40" s="86" t="n"/>
+      <c r="G40" s="86" t="inlineStr">
         <is>
           <t>Material / compatibilidad corrosiva</t>
         </is>
       </c>
-      <c r="H33" s="86" t="n"/>
-      <c r="I33" s="86" t="inlineStr">
+      <c r="H40" s="86" t="n"/>
+      <c r="I40" s="86" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="J33" s="86" t="inlineStr">
+      <c r="J40" s="86" t="inlineStr">
         <is>
           <t>Candidatos comerciales (fabricante/modelo)</t>
         </is>
       </c>
-      <c r="K33" s="86" t="n"/>
-      <c r="L33" s="86" t="n"/>
-      <c r="M33" s="86" t="inlineStr">
+      <c r="K40" s="86" t="n"/>
+      <c r="L40" s="86" t="n"/>
+      <c r="M40" s="86" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N33" s="86" t="n"/>
-      <c r="O33" s="86" t="n"/>
-    </row>
-    <row r="34" ht="810" customHeight="1">
-      <c r="A34" s="87" t="inlineStr">
+      <c r="N40" s="86" t="n"/>
+      <c r="O40" s="86" t="n"/>
+    </row>
+    <row r="41" ht="510" customHeight="1">
+      <c r="A41" s="87" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B34" s="87" t="inlineStr">
-        <is>
-          <t>Ventilador de impulsión</t>
-        </is>
-      </c>
-      <c r="C34" s="88" t="n"/>
-      <c r="D34" s="87" t="inlineStr">
-        <is>
-          <t>Axial tubeaxial, transmisión por bandas; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; tamaño/RPM por confirmar con proveedor</t>
-        </is>
-      </c>
-      <c r="E34" s="88" t="n"/>
-      <c r="F34" s="88" t="n"/>
-      <c r="G34" s="87" t="inlineStr">
-        <is>
-          <t>PRFV viniléster (ASTM C582/D4167); motor fuera de la corriente de aire</t>
-        </is>
-      </c>
-      <c r="H34" s="88" t="n"/>
-      <c r="I34" s="87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" s="87" t="inlineStr">
-        <is>
-          <t>Aerovent FBD (Twin City Fan, Catálogo 185); Greenheck VAB (vaneaxial epóxico, Prime Lines HVAC, Bogotá); Sodeca HCT/HGT anticorrosivo PRFV; NYB FRP tubeaxial; Plastec PP</t>
-        </is>
-      </c>
-      <c r="K34" s="88" t="n"/>
-      <c r="L34" s="88" t="n"/>
-      <c r="M34" s="87" t="inlineStr">
-        <is>
-          <t>Aerovent Cat. 185 (PDF) (https://www.aerovent.com/wp-content/uploads/sites/2/2024/07/Fiberglass-Fans-Axial-Flow-Model-FBD-FDP-FRV-TFBD-VTFBD-Catalog-185.pdf); Greenheck VAB/VAD (PDF) (https://content.greenheck.com/public/DAMProd/Original/10003/vane_axial_catalog.pdf); Sodeca (https://www.sodeca.com)</t>
-        </is>
-      </c>
-      <c r="N34" s="88" t="n"/>
-      <c r="O34" s="88" t="n"/>
-    </row>
-    <row r="35" ht="525" customHeight="1">
-      <c r="A35" s="87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B35" s="87" t="inlineStr">
-        <is>
-          <t>Motor del ventilador</t>
-        </is>
-      </c>
-      <c r="C35" s="88" t="n"/>
-      <c r="D35" s="87" t="inlineStr">
-        <is>
-          <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC, 1 800 RPM (4 polos), 60 Hz, clase F, IP55 mín., severe duty epóxico; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
-        </is>
-      </c>
-      <c r="E35" s="88" t="n"/>
-      <c r="F35" s="88" t="n"/>
-      <c r="G35" s="87" t="inlineStr">
-        <is>
-          <t>Pintura epóxica + protección interna anticorrosiva; motor fuera de la corriente (transmisión por bandas)</t>
-        </is>
-      </c>
-      <c r="H35" s="88" t="n"/>
-      <c r="I35" s="87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" s="87" t="inlineStr">
-        <is>
-          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
-        </is>
-      </c>
-      <c r="K35" s="88" t="n"/>
-      <c r="L35" s="88" t="n"/>
-      <c r="M35" s="87" t="inlineStr">
-        <is>
-          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
-        </is>
-      </c>
-      <c r="N35" s="88" t="n"/>
-      <c r="O35" s="88" t="n"/>
-    </row>
-    <row r="36" ht="465" customHeight="1">
-      <c r="A36" s="87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B36" s="87" t="inlineStr">
-        <is>
-          <t>Prefiltro (etapa 1)</t>
-        </is>
-      </c>
-      <c r="C36" s="88" t="n"/>
-      <c r="D36" s="87" t="inlineStr">
-        <is>
-          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
-        </is>
-      </c>
-      <c r="E36" s="88" t="n"/>
-      <c r="F36" s="88" t="n"/>
-      <c r="G36" s="87" t="inlineStr">
-        <is>
-          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
-        </is>
-      </c>
-      <c r="H36" s="88" t="n"/>
-      <c r="I36" s="87" t="inlineStr">
-        <is>
-          <t>1 (+ repuestos)</t>
-        </is>
-      </c>
-      <c r="J36" s="87" t="inlineStr">
-        <is>
-          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
-        </is>
-      </c>
-      <c r="K36" s="88" t="n"/>
-      <c r="L36" s="88" t="n"/>
-      <c r="M36" s="87" t="inlineStr">
-        <is>
-          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
-        </is>
-      </c>
-      <c r="N36" s="88" t="n"/>
-      <c r="O36" s="88" t="n"/>
-    </row>
-    <row r="37" ht="660" customHeight="1">
-      <c r="A37" s="87" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B37" s="87" t="inlineStr">
-        <is>
-          <t>Filtro final (etapa 2)</t>
-        </is>
-      </c>
-      <c r="C37" s="88" t="n"/>
-      <c r="D37" s="87" t="inlineStr">
-        <is>
-          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
-        </is>
-      </c>
-      <c r="E37" s="88" t="n"/>
-      <c r="F37" s="88" t="n"/>
-      <c r="G37" s="87" t="inlineStr">
-        <is>
-          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
-        </is>
-      </c>
-      <c r="H37" s="88" t="n"/>
-      <c r="I37" s="87" t="inlineStr">
-        <is>
-          <t>1 (+ repuestos)</t>
-        </is>
-      </c>
-      <c r="J37" s="87" t="inlineStr">
-        <is>
-          <t>Camfil Durafil ES2 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
-        </is>
-      </c>
-      <c r="K37" s="88" t="n"/>
-      <c r="L37" s="88" t="n"/>
-      <c r="M37" s="87" t="inlineStr">
-        <is>
-          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
-        </is>
-      </c>
-      <c r="N37" s="88" t="n"/>
-      <c r="O37" s="88" t="n"/>
-    </row>
-    <row r="38" ht="420" customHeight="1">
-      <c r="A38" s="87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B38" s="87" t="inlineStr">
-        <is>
-          <t>Marcos portafiltros</t>
-        </is>
-      </c>
-      <c r="C38" s="88" t="n"/>
-      <c r="D38" s="87" t="inlineStr">
-        <is>
-          <t>Holding frames para prefiltro + filtro final con junta continua</t>
-        </is>
-      </c>
-      <c r="E38" s="88" t="n"/>
-      <c r="F38" s="88" t="n"/>
-      <c r="G38" s="87" t="inlineStr">
-        <is>
-          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
-        </is>
-      </c>
-      <c r="H38" s="88" t="n"/>
-      <c r="I38" s="87" t="inlineStr">
-        <is>
-          <t>1 juego</t>
-        </is>
-      </c>
-      <c r="J38" s="87" t="inlineStr">
-        <is>
-          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
-        </is>
-      </c>
-      <c r="K38" s="88" t="n"/>
-      <c r="L38" s="88" t="n"/>
-      <c r="M38" s="87" t="inlineStr">
-        <is>
-          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
-        </is>
-      </c>
-      <c r="N38" s="88" t="n"/>
-      <c r="O38" s="88" t="n"/>
-    </row>
-    <row r="39" ht="450" customHeight="1">
-      <c r="A39" s="87" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B39" s="87" t="inlineStr">
-        <is>
-          <t>Rejillas de descarga</t>
-        </is>
-      </c>
-      <c r="C39" s="88" t="n"/>
-      <c r="D39" s="87" t="inlineStr">
-        <is>
-          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
-        </is>
-      </c>
-      <c r="E39" s="88" t="n"/>
-      <c r="F39" s="88" t="n"/>
-      <c r="G39" s="87" t="inlineStr">
-        <is>
-          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
-        </is>
-      </c>
-      <c r="H39" s="88" t="n"/>
-      <c r="I39" s="87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" s="87" t="inlineStr">
-        <is>
-          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
-        </is>
-      </c>
-      <c r="K39" s="88" t="n"/>
-      <c r="L39" s="88" t="n"/>
-      <c r="M39" s="87" t="inlineStr">
-        <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
-        </is>
-      </c>
-      <c r="N39" s="88" t="n"/>
-      <c r="O39" s="88" t="n"/>
-    </row>
-    <row r="40" ht="375" customHeight="1">
-      <c r="A40" s="87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B40" s="87" t="inlineStr">
-        <is>
-          <t>Malla anti-insectos</t>
-        </is>
-      </c>
-      <c r="C40" s="88" t="n"/>
-      <c r="D40" s="87" t="inlineStr">
-        <is>
-          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
-        </is>
-      </c>
-      <c r="E40" s="88" t="n"/>
-      <c r="F40" s="88" t="n"/>
-      <c r="G40" s="87" t="inlineStr">
-        <is>
-          <t>Inox 316</t>
-        </is>
-      </c>
-      <c r="H40" s="88" t="n"/>
-      <c r="I40" s="87" t="inlineStr">
-        <is>
-          <t>3 (una por rejilla)</t>
-        </is>
-      </c>
-      <c r="J40" s="87" t="inlineStr">
-        <is>
-          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
-        </is>
-      </c>
-      <c r="K40" s="88" t="n"/>
-      <c r="L40" s="88" t="n"/>
-      <c r="M40" s="87" t="inlineStr">
-        <is>
-          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
-        </is>
-      </c>
-      <c r="N40" s="88" t="n"/>
-      <c r="O40" s="88" t="n"/>
-    </row>
-    <row r="41" ht="270" customHeight="1">
-      <c r="A41" s="87" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="B41" s="87" t="inlineStr">
         <is>
-          <t>Soportes y ferretería</t>
+          <t>Ventilador de inyección</t>
         </is>
       </c>
       <c r="C41" s="88" t="n"/>
       <c r="D41" s="87" t="inlineStr">
         <is>
-          <t>Soportes de ventilador y rejillas; pernos, tuercas, arandelas</t>
+          <t>Axial mural (placa mural) Ø560 mm, transmisión directa; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; RPM por confirmar con proveedor</t>
         </is>
       </c>
       <c r="E41" s="88" t="n"/>
       <c r="F41" s="88" t="n"/>
       <c r="G41" s="87" t="inlineStr">
         <is>
-          <t>Inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
+          <t>PRFV viniléster (ASTM C582/D4167) o acero con epóxico anticorrosivo; motor encapsulado en la corriente</t>
         </is>
       </c>
       <c r="H41" s="88" t="n"/>
       <c r="I41" s="87" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" s="87" t="inlineStr">
         <is>
-          <t>Suministro nacional genérico A4</t>
+          <t>Sodeca HQD/HGT mural anticorrosivo (primera opción por uniformidad y canal local); Greenheck mural epóxico (Prime Lines HVAC, Bogotá); Aerovent/Twin City mural FRP; NYB FRP mural; Plastec PP</t>
         </is>
       </c>
       <c r="K41" s="88" t="n"/>
       <c r="L41" s="88" t="n"/>
       <c r="M41" s="87" t="inlineStr">
         <is>
-          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
+          <t>Sodeca (https://www.sodeca.com); catálogo Sodeca CO (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf); Greenheck (https://www.greenheck.com)</t>
         </is>
       </c>
       <c r="N41" s="88" t="n"/>
       <c r="O41" s="88" t="n"/>
     </row>
-    <row r="42" ht="360" customHeight="1">
+    <row r="42" ht="570" customHeight="1">
       <c r="A42" s="87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B42" s="87" t="inlineStr">
         <is>
-          <t>Conexión flexible ventilador-pasamuros</t>
+          <t>Motor del ventilador (integrado en el cubo)</t>
         </is>
       </c>
       <c r="C42" s="88" t="n"/>
       <c r="D42" s="87" t="inlineStr">
         <is>
-          <t>Ancho ≥ 100 mm; bandas de amarre inox 316 cal. 24</t>
+          <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC encapsulado, clase F (H preferible), IP56 mín. (IP66 preferible), severe duty epóxico, eje inox; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
         </is>
       </c>
       <c r="E42" s="88" t="n"/>
       <c r="F42" s="88" t="n"/>
       <c r="G42" s="87" t="inlineStr">
         <is>
-          <t>Hipalón (CSM); alternativa clorobutilo; no PVC estándar</t>
+          <t>Pintura epóxica + protección interna anticorrosiva; motor dentro de la corriente (transmisión directa) — ejecución reforzada</t>
         </is>
       </c>
       <c r="H42" s="88" t="n"/>
@@ -4537,341 +4243,658 @@
       </c>
       <c r="J42" s="87" t="inlineStr">
         <is>
-          <t>Hardcast Hypalon; Proco serie 500</t>
+          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
         </is>
       </c>
       <c r="K42" s="88" t="n"/>
       <c r="L42" s="88" t="n"/>
       <c r="M42" s="87" t="inlineStr">
         <is>
-          <t>Hardcast (PDF) (https://6c2bd45d09da3c66a408-2b16a407535c695c8a76f8b06a56f342.ssl.cf2.rackcdn.com/GWB%20%20eCatalog%2006-25-16.pdf)</t>
+          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
         </is>
       </c>
       <c r="N42" s="88" t="n"/>
       <c r="O42" s="88" t="n"/>
     </row>
-    <row r="43" ht="600" customHeight="1">
+    <row r="43" ht="465" customHeight="1">
       <c r="A43" s="87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B43" s="87" t="inlineStr">
         <is>
-          <t>Selladores</t>
+          <t>Prefiltro (etapa 1)</t>
         </is>
       </c>
       <c r="C43" s="88" t="n"/>
       <c r="D43" s="87" t="inlineStr">
         <is>
-          <t>Sellado de pasamuros, marcos y empalmes</t>
+          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
         </is>
       </c>
       <c r="E43" s="88" t="n"/>
       <c r="F43" s="88" t="n"/>
       <c r="G43" s="87" t="inlineStr">
         <is>
-          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
+          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
         </is>
       </c>
       <c r="H43" s="88" t="n"/>
       <c r="I43" s="87" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>1 (+ repuestos)</t>
         </is>
       </c>
       <c r="J43" s="87" t="inlineStr">
         <is>
-          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
+          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
         </is>
       </c>
       <c r="K43" s="88" t="n"/>
       <c r="L43" s="88" t="n"/>
       <c r="M43" s="87" t="inlineStr">
         <is>
-          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
+          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
         </is>
       </c>
       <c r="N43" s="88" t="n"/>
       <c r="O43" s="88" t="n"/>
     </row>
-    <row r="44" ht="240" customHeight="1">
+    <row r="44" ht="660" customHeight="1">
       <c r="A44" s="87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B44" s="87" t="inlineStr">
         <is>
-          <t>Protecciones eléctricas y tablero</t>
+          <t>Filtro final (etapa 2)</t>
         </is>
       </c>
       <c r="C44" s="88" t="n"/>
       <c r="D44" s="87" t="inlineStr">
         <is>
-          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
+          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
         </is>
       </c>
       <c r="E44" s="88" t="n"/>
       <c r="F44" s="88" t="n"/>
       <c r="G44" s="87" t="inlineStr">
         <is>
-          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
+          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
         </is>
       </c>
       <c r="H44" s="88" t="n"/>
       <c r="I44" s="87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 (+ repuestos)</t>
         </is>
       </c>
       <c r="J44" s="87" t="inlineStr">
         <is>
-          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
+          <t>Camfil Durafil ES2/ES3 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
         </is>
       </c>
       <c r="K44" s="88" t="n"/>
       <c r="L44" s="88" t="n"/>
       <c r="M44" s="87" t="inlineStr">
         <is>
-          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
+          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
         </is>
       </c>
       <c r="N44" s="88" t="n"/>
       <c r="O44" s="88" t="n"/>
     </row>
-    <row r="45" ht="210" customHeight="1">
+    <row r="45" ht="420" customHeight="1">
       <c r="A45" s="87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B45" s="87" t="inlineStr">
         <is>
-          <t>Cableado y canalización</t>
+          <t>Marcos portafiltros</t>
         </is>
       </c>
       <c r="C45" s="88" t="n"/>
       <c r="D45" s="87" t="inlineStr">
         <is>
-          <t>Circuito de alimentación del motor 0.75 HP</t>
+          <t>Holding frames para prefiltro + filtro final con junta continua, dentro de la cubierta</t>
         </is>
       </c>
       <c r="E45" s="88" t="n"/>
       <c r="F45" s="88" t="n"/>
       <c r="G45" s="87" t="inlineStr">
         <is>
-          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
+          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
         </is>
       </c>
       <c r="H45" s="88" t="n"/>
       <c r="I45" s="87" t="inlineStr">
         <is>
-          <t>Lote</t>
+          <t>1 juego</t>
         </is>
       </c>
       <c r="J45" s="87" t="inlineStr">
         <is>
-          <t>Suministro nacional certificado RETIE</t>
+          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
         </is>
       </c>
       <c r="K45" s="88" t="n"/>
       <c r="L45" s="88" t="n"/>
       <c r="M45" s="87" t="inlineStr">
         <is>
-          <t>Requisito RETIE / NTC 2050</t>
+          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
         </is>
       </c>
       <c r="N45" s="88" t="n"/>
       <c r="O45" s="88" t="n"/>
     </row>
-    <row r="46" ht="345" customHeight="1">
+    <row r="46" ht="450" customHeight="1">
       <c r="A46" s="87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B46" s="87" t="inlineStr">
         <is>
-          <t>Caja/housing de filtración y transición</t>
+          <t>Rejillas de descarga</t>
         </is>
       </c>
       <c r="C46" s="88" t="n"/>
       <c r="D46" s="87" t="inlineStr">
         <is>
-          <t>Alojar portafiltros, malla anti-insectos y adaptar la boca cuadrada 24×24 in del filtro a la boca circular del ventilador axial</t>
+          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
         </is>
       </c>
       <c r="E46" s="88" t="n"/>
       <c r="F46" s="88" t="n"/>
       <c r="G46" s="87" t="inlineStr">
         <is>
-          <t>Inox 316L o PRFV viniléster (mismo criterio anticorrosivo del ventilador); tapas de inspección, juntas PU</t>
+          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
         </is>
       </c>
       <c r="H46" s="88" t="n"/>
       <c r="I46" s="87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" s="87" t="inlineStr">
         <is>
-          <t>Fabricación local a partir de planos del submittal del ventilador</t>
+          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
         </is>
       </c>
       <c r="K46" s="88" t="n"/>
       <c r="L46" s="88" t="n"/>
       <c r="M46" s="87" t="inlineStr">
         <is>
-          <t>Derivado de HD-FILT-001 §7.3</t>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
       <c r="N46" s="88" t="n"/>
       <c r="O46" s="88" t="n"/>
     </row>
-    <row r="47" ht="15" customHeight="1"/>
-    <row r="48" ht="15" customHeight="1"/>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="84" t="inlineStr">
-        <is>
-          <t>3. Notas de suministro</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="165" customHeight="1">
-      <c r="A50" s="83" t="inlineStr">
-        <is>
-          <t>3.1. Los ítems 1, 4 y 13 requieren cotización formal con submittal: la selección final de tamaño/RPM del ventilador (ítem 1), la potencia definitiva del motor (ítem 2) y las dimensiones de la caja de filtración/transición cuadrado-circular (ítem 13) se confirman con el software o planos del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1"/>
-    <row r="52" ht="15" customHeight="1"/>
-    <row r="53" ht="15" customHeight="1"/>
+    <row r="47" ht="375" customHeight="1">
+      <c r="A47" s="87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B47" s="87" t="inlineStr">
+        <is>
+          <t>Malla anti-insectos</t>
+        </is>
+      </c>
+      <c r="C47" s="88" t="n"/>
+      <c r="D47" s="87" t="inlineStr">
+        <is>
+          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
+        </is>
+      </c>
+      <c r="E47" s="88" t="n"/>
+      <c r="F47" s="88" t="n"/>
+      <c r="G47" s="87" t="inlineStr">
+        <is>
+          <t>Inox 316</t>
+        </is>
+      </c>
+      <c r="H47" s="88" t="n"/>
+      <c r="I47" s="87" t="inlineStr">
+        <is>
+          <t>3 (una por rejilla) + 1 (boca de la cubierta)</t>
+        </is>
+      </c>
+      <c r="J47" s="87" t="inlineStr">
+        <is>
+          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
+        </is>
+      </c>
+      <c r="K47" s="88" t="n"/>
+      <c r="L47" s="88" t="n"/>
+      <c r="M47" s="87" t="inlineStr">
+        <is>
+          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
+        </is>
+      </c>
+      <c r="N47" s="88" t="n"/>
+      <c r="O47" s="88" t="n"/>
+    </row>
+    <row r="48" ht="435" customHeight="1">
+      <c r="A48" s="87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B48" s="87" t="inlineStr">
+        <is>
+          <t>Estructura de unión y soportes</t>
+        </is>
+      </c>
+      <c r="C48" s="88" t="n"/>
+      <c r="D48" s="87" t="inlineStr">
+        <is>
+          <t>Marco de soporte pernado al muro para fijación del ventilador; soporta cargas estáticas, dinámicas y vibraciones; soportes de rejillas; pernos, tuercas, arandelas</t>
+        </is>
+      </c>
+      <c r="E48" s="88" t="n"/>
+      <c r="F48" s="88" t="n"/>
+      <c r="G48" s="87" t="inlineStr">
+        <is>
+          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
+        </is>
+      </c>
+      <c r="H48" s="88" t="n"/>
+      <c r="I48" s="87" t="inlineStr">
+        <is>
+          <t>1 + Lote</t>
+        </is>
+      </c>
+      <c r="J48" s="87" t="inlineStr">
+        <is>
+          <t>Fabricación local a partir de planos del submittal del ventilador</t>
+        </is>
+      </c>
+      <c r="K48" s="88" t="n"/>
+      <c r="L48" s="88" t="n"/>
+      <c r="M48" s="87" t="inlineStr">
+        <is>
+          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
+        </is>
+      </c>
+      <c r="N48" s="88" t="n"/>
+      <c r="O48" s="88" t="n"/>
+    </row>
+    <row r="49" ht="525" customHeight="1">
+      <c r="A49" s="87" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B49" s="87" t="inlineStr">
+        <is>
+          <t>Cubierta intemperie</t>
+        </is>
+      </c>
+      <c r="C49" s="88" t="n"/>
+      <c r="D49" s="87" t="inlineStr">
+        <is>
+          <t>Protección contra lluvia/sol/ingreso de agua; aloja el banco de filtración (ítems 3-5 y malla); embridado directo a la placa mural del ventilador; acceso frontal/superior para cambio de filtros</t>
+        </is>
+      </c>
+      <c r="E49" s="88" t="n"/>
+      <c r="F49" s="88" t="n"/>
+      <c r="G49" s="87" t="inlineStr">
+        <is>
+          <t>PRFV viniléster o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L; drenaje inferior</t>
+        </is>
+      </c>
+      <c r="H49" s="88" t="n"/>
+      <c r="I49" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" s="87" t="inlineStr">
+        <is>
+          <t>Suministrada por el fabricante del ventilador o fabricación local según submittal</t>
+        </is>
+      </c>
+      <c r="K49" s="88" t="n"/>
+      <c r="L49" s="88" t="n"/>
+      <c r="M49" s="87" t="inlineStr">
+        <is>
+          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
+        </is>
+      </c>
+      <c r="N49" s="88" t="n"/>
+      <c r="O49" s="88" t="n"/>
+    </row>
+    <row r="50" ht="270" customHeight="1">
+      <c r="A50" s="87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B50" s="87" t="inlineStr">
+        <is>
+          <t>Malla de protección interior</t>
+        </is>
+      </c>
+      <c r="C50" s="88" t="n"/>
+      <c r="D50" s="87" t="inlineStr">
+        <is>
+          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor; desmontable</t>
+        </is>
+      </c>
+      <c r="E50" s="88" t="n"/>
+      <c r="F50" s="88" t="n"/>
+      <c r="G50" s="87" t="inlineStr">
+        <is>
+          <t>Malla inox 316 o galvanizada con pintura epóxica; marco rígido</t>
+        </is>
+      </c>
+      <c r="H50" s="88" t="n"/>
+      <c r="I50" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" s="87" t="inlineStr">
+        <is>
+          <t>Fabricación local según submittal</t>
+        </is>
+      </c>
+      <c r="K50" s="88" t="n"/>
+      <c r="L50" s="88" t="n"/>
+      <c r="M50" s="87" t="inlineStr">
+        <is>
+          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
+        </is>
+      </c>
+      <c r="N50" s="88" t="n"/>
+      <c r="O50" s="88" t="n"/>
+    </row>
+    <row r="51" ht="600" customHeight="1">
+      <c r="A51" s="87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B51" s="87" t="inlineStr">
+        <is>
+          <t>Selladores</t>
+        </is>
+      </c>
+      <c r="C51" s="88" t="n"/>
+      <c r="D51" s="87" t="inlineStr">
+        <is>
+          <t>Sellado de pasamuros, marcos y empalmes</t>
+        </is>
+      </c>
+      <c r="E51" s="88" t="n"/>
+      <c r="F51" s="88" t="n"/>
+      <c r="G51" s="87" t="inlineStr">
+        <is>
+          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
+        </is>
+      </c>
+      <c r="H51" s="88" t="n"/>
+      <c r="I51" s="87" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="J51" s="87" t="inlineStr">
+        <is>
+          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
+        </is>
+      </c>
+      <c r="K51" s="88" t="n"/>
+      <c r="L51" s="88" t="n"/>
+      <c r="M51" s="87" t="inlineStr">
+        <is>
+          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
+        </is>
+      </c>
+      <c r="N51" s="88" t="n"/>
+      <c r="O51" s="88" t="n"/>
+    </row>
+    <row r="52" ht="240" customHeight="1">
+      <c r="A52" s="87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B52" s="87" t="inlineStr">
+        <is>
+          <t>Protecciones eléctricas y tablero</t>
+        </is>
+      </c>
+      <c r="C52" s="88" t="n"/>
+      <c r="D52" s="87" t="inlineStr">
+        <is>
+          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
+        </is>
+      </c>
+      <c r="E52" s="88" t="n"/>
+      <c r="F52" s="88" t="n"/>
+      <c r="G52" s="87" t="inlineStr">
+        <is>
+          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
+        </is>
+      </c>
+      <c r="H52" s="88" t="n"/>
+      <c r="I52" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" s="87" t="inlineStr">
+        <is>
+          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
+        </is>
+      </c>
+      <c r="K52" s="88" t="n"/>
+      <c r="L52" s="88" t="n"/>
+      <c r="M52" s="87" t="inlineStr">
+        <is>
+          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
+        </is>
+      </c>
+      <c r="N52" s="88" t="n"/>
+      <c r="O52" s="88" t="n"/>
+    </row>
+    <row r="53" ht="210" customHeight="1">
+      <c r="A53" s="87" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B53" s="87" t="inlineStr">
+        <is>
+          <t>Cableado y canalización</t>
+        </is>
+      </c>
+      <c r="C53" s="88" t="n"/>
+      <c r="D53" s="87" t="inlineStr">
+        <is>
+          <t>Circuito de alimentación del motor 0.75 HP</t>
+        </is>
+      </c>
+      <c r="E53" s="88" t="n"/>
+      <c r="F53" s="88" t="n"/>
+      <c r="G53" s="87" t="inlineStr">
+        <is>
+          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
+        </is>
+      </c>
+      <c r="H53" s="88" t="n"/>
+      <c r="I53" s="87" t="inlineStr">
+        <is>
+          <t>Lote</t>
+        </is>
+      </c>
+      <c r="J53" s="87" t="inlineStr">
+        <is>
+          <t>Suministro nacional certificado RETIE</t>
+        </is>
+      </c>
+      <c r="K53" s="88" t="n"/>
+      <c r="L53" s="88" t="n"/>
+      <c r="M53" s="87" t="inlineStr">
+        <is>
+          <t>Requisito RETIE / NTC 2050</t>
+        </is>
+      </c>
+      <c r="N53" s="88" t="n"/>
+      <c r="O53" s="88" t="n"/>
+    </row>
     <row r="54" ht="15" customHeight="1"/>
     <row r="55" ht="15" customHeight="1"/>
-    <row r="56" ht="150" customHeight="1">
-      <c r="A56" s="83" t="inlineStr">
-        <is>
-          <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1"/>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="84" t="inlineStr">
+        <is>
+          <t>3. Notas de suministro</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="165" customHeight="1">
+      <c r="A57" s="83" t="inlineStr">
+        <is>
+          <t>3.1. Los ítems 1, 4, 8 y 9 requieren cotización formal con submittal: la selección final de RPM del ventilador mural Ø560 mm (ítem 1) y la potencia definitiva del motor (ítem 2) se confirman con el software del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar; las dimensiones de la estructura de unión (ítem 8) y de la cubierta intemperie (ítem 9) se definen con los planos del submittal del ventilador.</t>
+        </is>
+      </c>
+    </row>
     <row r="58" ht="15" customHeight="1"/>
     <row r="59" ht="15" customHeight="1"/>
     <row r="60" ht="15" customHeight="1"/>
     <row r="61" ht="15" customHeight="1"/>
     <row r="62" ht="15" customHeight="1"/>
-    <row r="63" ht="165" customHeight="1">
-      <c r="A63" s="83" t="inlineStr">
-        <is>
-          <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1"/>
+    <row r="63" ht="15" customHeight="1"/>
+    <row r="64" ht="150" customHeight="1">
+      <c r="A64" s="83" t="inlineStr">
+        <is>
+          <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
     <row r="65" ht="15" customHeight="1"/>
     <row r="66" ht="15" customHeight="1"/>
     <row r="67" ht="15" customHeight="1"/>
+    <row r="68" ht="15" customHeight="1"/>
+    <row r="69" ht="15" customHeight="1"/>
+    <row r="70" ht="15" customHeight="1"/>
+    <row r="71" ht="165" customHeight="1">
+      <c r="A71" s="83" t="inlineStr">
+        <is>
+          <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1"/>
+    <row r="73" ht="15" customHeight="1"/>
+    <row r="74" ht="15" customHeight="1"/>
+    <row r="75" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="96">
     <mergeCell ref="M40:O40"/>
-    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D47:F47"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="D37:F37"/>
     <mergeCell ref="M41:O41"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="J50:L50"/>
     <mergeCell ref="C2:L3"/>
+    <mergeCell ref="A29:O29"/>
     <mergeCell ref="J46:L46"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J52:L52"/>
+    <mergeCell ref="A18:O24"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="J48:L48"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A50:O55"/>
-    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="M52:O52"/>
     <mergeCell ref="G44:H44"/>
     <mergeCell ref="J40:L40"/>
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B1:B5"/>
     <mergeCell ref="D41:F41"/>
     <mergeCell ref="A10:O11"/>
-    <mergeCell ref="A23:O28"/>
+    <mergeCell ref="G48:H48"/>
     <mergeCell ref="D43:F43"/>
+    <mergeCell ref="A25:O27"/>
     <mergeCell ref="J41:L41"/>
-    <mergeCell ref="M37:O37"/>
-    <mergeCell ref="G38:H38"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="A18:O20"/>
     <mergeCell ref="J43:L43"/>
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="G49:H49"/>
     <mergeCell ref="J42:L42"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="M43:O43"/>
     <mergeCell ref="J44:L44"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="G35:H35"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="J37:L37"/>
     <mergeCell ref="D46:F46"/>
     <mergeCell ref="D40:F40"/>
-    <mergeCell ref="M35:O35"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="A13:O14"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="A64:O70"/>
     <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A38:O39"/>
+    <mergeCell ref="A56:O56"/>
     <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="A31:O32"/>
     <mergeCell ref="M42:O42"/>
     <mergeCell ref="B42:C42"/>
-    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="J47:L47"/>
     <mergeCell ref="A8:O8"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="A56:O62"/>
     <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D51:F51"/>
     <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="A63:O67"/>
+    <mergeCell ref="A71:O75"/>
+    <mergeCell ref="A30:O35"/>
+    <mergeCell ref="D50:F50"/>
     <mergeCell ref="D44:F44"/>
+    <mergeCell ref="A57:O63"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="D34:F34"/>
     <mergeCell ref="M44:O44"/>
+    <mergeCell ref="G51:H51"/>
     <mergeCell ref="G41:H41"/>
     <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G50:H50"/>
     <mergeCell ref="D45:F45"/>
-    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="M51:O51"/>
     <mergeCell ref="G43:H43"/>
-    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="J49:L49"/>
+    <mergeCell ref="G52:H52"/>
     <mergeCell ref="J45:L45"/>
     <mergeCell ref="B46:C46"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="B48:C48"/>
     <mergeCell ref="M45:O45"/>
+    <mergeCell ref="G53:H53"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="J51:L51"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="M50:O50"/>
     <mergeCell ref="G45:H45"/>
-    <mergeCell ref="M34:O34"/>
     <mergeCell ref="A15:O17"/>
+    <mergeCell ref="M49:O49"/>
+    <mergeCell ref="G47:H47"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="A49:O49"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="M48:O48"/>
     <mergeCell ref="G46:H46"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D52:F52"/>
     <mergeCell ref="G40:H40"/>
+    <mergeCell ref="D49:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/build/lis/P2437-HV-LIS-001 REV0.xlsx
+++ b/build/lis/P2437-HV-LIS-001 REV0.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000000000000"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -164,29 +164,17 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="12"/>
+      <color rgb="00375623"/>
+      <sz val="28"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="Times New Roman"/>
@@ -237,8 +225,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="00C6E0B4"/>
+        <bgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -395,7 +383,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -513,12 +501,12 @@
     <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -541,25 +529,25 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -585,22 +573,19 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3718,38 +3703,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30.6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
     <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="13" customWidth="1" min="31" max="31"/>
@@ -3757,8 +3739,8 @@
     <col width="13" customWidth="1" min="33" max="33"/>
     <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
     <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
     <col width="13" customWidth="1" min="39" max="39"/>
     <col width="13" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
@@ -3766,34 +3748,6 @@
     <col width="13" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
     <col width="13" customWidth="1" min="45" max="45"/>
-    <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
-    <col width="13" customWidth="1" min="48" max="48"/>
-    <col width="13" customWidth="1" min="49" max="49"/>
-    <col width="13" customWidth="1" min="50" max="50"/>
-    <col width="13" customWidth="1" min="51" max="51"/>
-    <col width="13" customWidth="1" min="52" max="52"/>
-    <col width="13" customWidth="1" min="53" max="53"/>
-    <col width="13" customWidth="1" min="56" max="56"/>
-    <col width="13" customWidth="1" min="57" max="57"/>
-    <col width="13" customWidth="1" min="58" max="58"/>
-    <col width="13" customWidth="1" min="59" max="59"/>
-    <col width="13" customWidth="1" min="60" max="60"/>
-    <col width="13" customWidth="1" min="61" max="61"/>
-    <col width="13" customWidth="1" min="62" max="62"/>
-    <col width="13" customWidth="1" min="63" max="63"/>
-    <col width="13" customWidth="1" min="64" max="64"/>
-    <col width="13" customWidth="1" min="65" max="65"/>
-    <col width="13" customWidth="1" min="66" max="66"/>
-    <col width="13" customWidth="1" min="67" max="67"/>
-    <col width="13" customWidth="1" min="68" max="68"/>
-    <col width="13" customWidth="1" min="69" max="69"/>
-    <col width="13" customWidth="1" min="70" max="70"/>
-    <col width="13" customWidth="1" min="71" max="71"/>
-    <col width="13" customWidth="1" min="72" max="72"/>
-    <col width="13" customWidth="1" min="73" max="73"/>
-    <col width="13" customWidth="1" min="74" max="74"/>
-    <col width="13" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -4003,7 +3957,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="38" customHeight="1">
       <c r="A8" s="81" t="inlineStr">
         <is>
           <t>LISTADO DE EQUIPOS Y MATERIALES (BOQ): SISTEMA DE VENTILACIÓN DEL LABORATORIO</t>
@@ -4024,879 +3978,845 @@
       <c r="N8" s="55" t="n"/>
       <c r="O8" s="55" t="n"/>
     </row>
-    <row r="9" ht="450" customHeight="1">
+    <row r="9" ht="266" customHeight="1">
       <c r="A9" s="82" t="inlineStr">
         <is>
           <t>Listado de equipos y materiales (BOQ): sistema de ventilación del laboratorio</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="210" customHeight="1">
+    <row r="10" ht="76" customHeight="1">
       <c r="A10" s="83" t="inlineStr">
         <is>
           <t>Proyecto: P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá (Cundinamarca)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1"/>
-    <row r="12" ht="60" customHeight="1">
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="83" t="inlineStr">
+        <is>
+          <t>Documento: listado_equipos.md — Revisión 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1">
       <c r="A12" s="83" t="inlineStr">
         <is>
-          <t>Documento: listado_equipos.md — Revisión 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="195" customHeight="1">
+          <t>Fecha: 2026-07-27 (fuentes consultadas el 2026-07-23; frente de ventiladores axiales ampliado el 2026-07-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="114" customHeight="1">
       <c r="A13" s="83" t="inlineStr">
         <is>
-          <t>Fecha: 2026-07-27 (fuentes consultadas el 2026-07-23; frente de ventiladores axiales ampliado el 2026-07-27)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1"/>
-    <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="83" t="inlineStr">
-        <is>
           <t>Base: informe_investigacion.md (misma revisión); punto de diseño 3 840 m³/h @ 165 Pa en el sitio (225 Pa equivalente de catálogo, ρ = 1.2 kg/m³).</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1"/>
-    <row r="17" ht="15" customHeight="1"/>
-    <row r="18" ht="165" customHeight="1">
-      <c r="A18" s="83" t="inlineStr">
+    <row r="14" ht="456" customHeight="1">
+      <c r="A14" s="83" t="inlineStr">
         <is>
           <t>Nota de revisión REV2 — 2026-07-27: actualización por uniformidad con el montaje típico instalado en la planta (Montaje/DISENOFINAL.png): ventilador axial mural Ø560 mm de transmisión directa, banco de filtración alojado en la cubierta intemperie, estructura de unión pernada al muro y malla de protección interior. Se eliminan la conexión flexible y la caja/housing con transición cuadrado/circular (REV1).</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1"/>
-    <row r="20" ht="15" customHeight="1"/>
-    <row r="21" ht="15" customHeight="1"/>
-    <row r="22" ht="15" customHeight="1"/>
-    <row r="23" ht="15" customHeight="1"/>
-    <row r="24" ht="15" customHeight="1"/>
-    <row r="25" ht="150" customHeight="1">
-      <c r="A25" s="83" t="inlineStr">
+    <row r="15" ht="38" customHeight="1"/>
+    <row r="16" ht="114" customHeight="1">
+      <c r="A16" s="83" t="inlineStr">
         <is>
           <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial, sin instrumentación de presión diferencial.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1"/>
-    <row r="27" ht="15" customHeight="1"/>
-    <row r="28" ht="15" customHeight="1"/>
-    <row r="29" ht="75" customHeight="1">
-      <c r="A29" s="84" t="inlineStr">
+    <row r="17" ht="38" customHeight="1"/>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="82" t="inlineStr">
         <is>
           <t>1. Alcance del suministro</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="150" customHeight="1">
-      <c r="A30" s="83" t="inlineStr">
+    <row r="19" ht="418" customHeight="1">
+      <c r="A19" s="83" t="inlineStr">
         <is>
           <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1"/>
-    <row r="32" ht="15" customHeight="1"/>
-    <row r="33" ht="15" customHeight="1"/>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="84" t="inlineStr">
+    <row r="20" ht="38" customHeight="1"/>
+    <row r="21" ht="38" customHeight="1"/>
+    <row r="22" ht="114" customHeight="1">
+      <c r="A22" s="82" t="inlineStr">
         <is>
           <t>2. Tabla de equipos y materiales</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="135" customHeight="1">
-      <c r="A38" s="85" t="inlineStr">
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="84" t="inlineStr">
         <is>
           <t>Tabla 1. BOQ del sistema de ventilación (consulta de fuentes 2026-07-23, ampliada 2026-07-27).</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="120" customHeight="1">
-      <c r="A40" s="86" t="inlineStr">
+    <row r="24" ht="114" customHeight="1">
+      <c r="A24" s="85" t="inlineStr">
         <is>
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B40" s="86" t="inlineStr">
+      <c r="B24" s="85" t="inlineStr">
         <is>
           <t>Función</t>
         </is>
       </c>
-      <c r="C40" s="86" t="n"/>
-      <c r="D40" s="86" t="inlineStr">
+      <c r="C24" s="85" t="n"/>
+      <c r="D24" s="85" t="inlineStr">
         <is>
           <t>Especificación clave</t>
         </is>
       </c>
-      <c r="E40" s="86" t="n"/>
-      <c r="F40" s="86" t="n"/>
-      <c r="G40" s="86" t="inlineStr">
+      <c r="E24" s="85" t="n"/>
+      <c r="F24" s="85" t="n"/>
+      <c r="G24" s="85" t="inlineStr">
         <is>
           <t>Material / compatibilidad corrosiva</t>
         </is>
       </c>
-      <c r="H40" s="86" t="n"/>
-      <c r="I40" s="86" t="inlineStr">
+      <c r="H24" s="85" t="n"/>
+      <c r="I24" s="85" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="J40" s="86" t="inlineStr">
+      <c r="J24" s="85" t="inlineStr">
         <is>
           <t>Candidatos comerciales (fabricante/modelo)</t>
         </is>
       </c>
-      <c r="K40" s="86" t="n"/>
-      <c r="L40" s="86" t="n"/>
-      <c r="M40" s="86" t="inlineStr">
+      <c r="K24" s="85" t="n"/>
+      <c r="L24" s="85" t="n"/>
+      <c r="M24" s="85" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N40" s="86" t="n"/>
-      <c r="O40" s="86" t="n"/>
-    </row>
-    <row r="41" ht="510" customHeight="1">
-      <c r="A41" s="87" t="inlineStr">
+      <c r="N24" s="85" t="n"/>
+      <c r="O24" s="85" t="n"/>
+    </row>
+    <row r="25" ht="532" customHeight="1">
+      <c r="A25" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B41" s="87" t="inlineStr">
+      <c r="B25" s="86" t="inlineStr">
         <is>
           <t>Ventilador de inyección</t>
         </is>
       </c>
-      <c r="C41" s="88" t="n"/>
-      <c r="D41" s="87" t="inlineStr">
+      <c r="C25" s="87" t="n"/>
+      <c r="D25" s="86" t="inlineStr">
         <is>
           <t>Axial mural (placa mural) Ø560 mm, transmisión directa; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; RPM por confirmar con proveedor</t>
         </is>
       </c>
-      <c r="E41" s="88" t="n"/>
-      <c r="F41" s="88" t="n"/>
-      <c r="G41" s="87" t="inlineStr">
+      <c r="E25" s="87" t="n"/>
+      <c r="F25" s="87" t="n"/>
+      <c r="G25" s="86" t="inlineStr">
         <is>
           <t>PRFV viniléster (ASTM C582/D4167) o acero con epóxico anticorrosivo; motor encapsulado en la corriente</t>
         </is>
       </c>
-      <c r="H41" s="88" t="n"/>
-      <c r="I41" s="87" t="inlineStr">
+      <c r="H25" s="87" t="n"/>
+      <c r="I25" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J41" s="87" t="inlineStr">
+      <c r="J25" s="86" t="inlineStr">
         <is>
           <t>Sodeca HQD/HGT mural anticorrosivo (primera opción por uniformidad y canal local); Greenheck mural epóxico (Prime Lines HVAC, Bogotá); Aerovent/Twin City mural FRP; NYB FRP mural; Plastec PP</t>
         </is>
       </c>
-      <c r="K41" s="88" t="n"/>
-      <c r="L41" s="88" t="n"/>
-      <c r="M41" s="87" t="inlineStr">
+      <c r="K25" s="87" t="n"/>
+      <c r="L25" s="87" t="n"/>
+      <c r="M25" s="86" t="inlineStr">
         <is>
           <t>Sodeca (https://www.sodeca.com); catálogo Sodeca CO (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf); Greenheck (https://www.greenheck.com)</t>
         </is>
       </c>
-      <c r="N41" s="88" t="n"/>
-      <c r="O41" s="88" t="n"/>
-    </row>
-    <row r="42" ht="570" customHeight="1">
-      <c r="A42" s="87" t="inlineStr">
+      <c r="N25" s="87" t="n"/>
+      <c r="O25" s="87" t="n"/>
+    </row>
+    <row r="26" ht="570" customHeight="1">
+      <c r="A26" s="86" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B42" s="87" t="inlineStr">
+      <c r="B26" s="86" t="inlineStr">
         <is>
           <t>Motor del ventilador (integrado en el cubo)</t>
         </is>
       </c>
-      <c r="C42" s="88" t="n"/>
-      <c r="D42" s="87" t="inlineStr">
+      <c r="C26" s="87" t="n"/>
+      <c r="D26" s="86" t="inlineStr">
         <is>
           <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC encapsulado, clase F (H preferible), IP56 mín. (IP66 preferible), severe duty epóxico, eje inox; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
         </is>
       </c>
-      <c r="E42" s="88" t="n"/>
-      <c r="F42" s="88" t="n"/>
-      <c r="G42" s="87" t="inlineStr">
+      <c r="E26" s="87" t="n"/>
+      <c r="F26" s="87" t="n"/>
+      <c r="G26" s="86" t="inlineStr">
         <is>
           <t>Pintura epóxica + protección interna anticorrosiva; motor dentro de la corriente (transmisión directa) — ejecución reforzada</t>
         </is>
       </c>
-      <c r="H42" s="88" t="n"/>
-      <c r="I42" s="87" t="inlineStr">
+      <c r="H26" s="87" t="n"/>
+      <c r="I26" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J42" s="87" t="inlineStr">
+      <c r="J26" s="86" t="inlineStr">
         <is>
           <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
         </is>
       </c>
-      <c r="K42" s="88" t="n"/>
-      <c r="L42" s="88" t="n"/>
-      <c r="M42" s="87" t="inlineStr">
+      <c r="K26" s="87" t="n"/>
+      <c r="L26" s="87" t="n"/>
+      <c r="M26" s="86" t="inlineStr">
         <is>
           <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
         </is>
       </c>
-      <c r="N42" s="88" t="n"/>
-      <c r="O42" s="88" t="n"/>
-    </row>
-    <row r="43" ht="465" customHeight="1">
-      <c r="A43" s="87" t="inlineStr">
+      <c r="N26" s="87" t="n"/>
+      <c r="O26" s="87" t="n"/>
+    </row>
+    <row r="27" ht="456" customHeight="1">
+      <c r="A27" s="86" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B43" s="87" t="inlineStr">
+      <c r="B27" s="86" t="inlineStr">
         <is>
           <t>Prefiltro (etapa 1)</t>
         </is>
       </c>
-      <c r="C43" s="88" t="n"/>
-      <c r="D43" s="87" t="inlineStr">
+      <c r="C27" s="87" t="n"/>
+      <c r="D27" s="86" t="inlineStr">
         <is>
           <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
         </is>
       </c>
-      <c r="E43" s="88" t="n"/>
-      <c r="F43" s="88" t="n"/>
-      <c r="G43" s="87" t="inlineStr">
+      <c r="E27" s="87" t="n"/>
+      <c r="F27" s="87" t="n"/>
+      <c r="G27" s="86" t="inlineStr">
         <is>
           <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
         </is>
       </c>
-      <c r="H43" s="88" t="n"/>
-      <c r="I43" s="87" t="inlineStr">
+      <c r="H27" s="87" t="n"/>
+      <c r="I27" s="86" t="inlineStr">
         <is>
           <t>1 (+ repuestos)</t>
         </is>
       </c>
-      <c r="J43" s="87" t="inlineStr">
+      <c r="J27" s="86" t="inlineStr">
         <is>
           <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
         </is>
       </c>
-      <c r="K43" s="88" t="n"/>
-      <c r="L43" s="88" t="n"/>
-      <c r="M43" s="87" t="inlineStr">
+      <c r="K27" s="87" t="n"/>
+      <c r="L27" s="87" t="n"/>
+      <c r="M27" s="86" t="inlineStr">
         <is>
           <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
         </is>
       </c>
-      <c r="N43" s="88" t="n"/>
-      <c r="O43" s="88" t="n"/>
-    </row>
-    <row r="44" ht="660" customHeight="1">
-      <c r="A44" s="87" t="inlineStr">
+      <c r="N27" s="87" t="n"/>
+      <c r="O27" s="87" t="n"/>
+    </row>
+    <row r="28" ht="684" customHeight="1">
+      <c r="A28" s="86" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B44" s="87" t="inlineStr">
+      <c r="B28" s="86" t="inlineStr">
         <is>
           <t>Filtro final (etapa 2)</t>
         </is>
       </c>
-      <c r="C44" s="88" t="n"/>
-      <c r="D44" s="87" t="inlineStr">
+      <c r="C28" s="87" t="n"/>
+      <c r="D28" s="86" t="inlineStr">
         <is>
           <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
         </is>
       </c>
-      <c r="E44" s="88" t="n"/>
-      <c r="F44" s="88" t="n"/>
-      <c r="G44" s="87" t="inlineStr">
+      <c r="E28" s="87" t="n"/>
+      <c r="F28" s="87" t="n"/>
+      <c r="G28" s="86" t="inlineStr">
         <is>
           <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
         </is>
       </c>
-      <c r="H44" s="88" t="n"/>
-      <c r="I44" s="87" t="inlineStr">
+      <c r="H28" s="87" t="n"/>
+      <c r="I28" s="86" t="inlineStr">
         <is>
           <t>1 (+ repuestos)</t>
         </is>
       </c>
-      <c r="J44" s="87" t="inlineStr">
+      <c r="J28" s="86" t="inlineStr">
         <is>
           <t>Camfil Durafil ES2/ES3 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
         </is>
       </c>
-      <c r="K44" s="88" t="n"/>
-      <c r="L44" s="88" t="n"/>
-      <c r="M44" s="87" t="inlineStr">
+      <c r="K28" s="87" t="n"/>
+      <c r="L28" s="87" t="n"/>
+      <c r="M28" s="86" t="inlineStr">
         <is>
           <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
         </is>
       </c>
-      <c r="N44" s="88" t="n"/>
-      <c r="O44" s="88" t="n"/>
-    </row>
-    <row r="45" ht="420" customHeight="1">
-      <c r="A45" s="87" t="inlineStr">
+      <c r="N28" s="87" t="n"/>
+      <c r="O28" s="87" t="n"/>
+    </row>
+    <row r="29" ht="418" customHeight="1">
+      <c r="A29" s="86" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B45" s="87" t="inlineStr">
+      <c r="B29" s="86" t="inlineStr">
         <is>
           <t>Marcos portafiltros</t>
         </is>
       </c>
-      <c r="C45" s="88" t="n"/>
-      <c r="D45" s="87" t="inlineStr">
+      <c r="C29" s="87" t="n"/>
+      <c r="D29" s="86" t="inlineStr">
         <is>
           <t>Holding frames para prefiltro + filtro final con junta continua, dentro de la cubierta</t>
         </is>
       </c>
-      <c r="E45" s="88" t="n"/>
-      <c r="F45" s="88" t="n"/>
-      <c r="G45" s="87" t="inlineStr">
+      <c r="E29" s="87" t="n"/>
+      <c r="F29" s="87" t="n"/>
+      <c r="G29" s="86" t="inlineStr">
         <is>
           <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
         </is>
       </c>
-      <c r="H45" s="88" t="n"/>
-      <c r="I45" s="87" t="inlineStr">
+      <c r="H29" s="87" t="n"/>
+      <c r="I29" s="86" t="inlineStr">
         <is>
           <t>1 juego</t>
         </is>
       </c>
-      <c r="J45" s="87" t="inlineStr">
+      <c r="J29" s="86" t="inlineStr">
         <is>
           <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
         </is>
       </c>
-      <c r="K45" s="88" t="n"/>
-      <c r="L45" s="88" t="n"/>
-      <c r="M45" s="87" t="inlineStr">
+      <c r="K29" s="87" t="n"/>
+      <c r="L29" s="87" t="n"/>
+      <c r="M29" s="86" t="inlineStr">
         <is>
           <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
         </is>
       </c>
-      <c r="N45" s="88" t="n"/>
-      <c r="O45" s="88" t="n"/>
-    </row>
-    <row r="46" ht="450" customHeight="1">
-      <c r="A46" s="87" t="inlineStr">
+      <c r="N29" s="87" t="n"/>
+      <c r="O29" s="87" t="n"/>
+    </row>
+    <row r="30" ht="456" customHeight="1">
+      <c r="A30" s="86" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B46" s="87" t="inlineStr">
+      <c r="B30" s="86" t="inlineStr">
         <is>
           <t>Rejillas de descarga</t>
         </is>
       </c>
-      <c r="C46" s="88" t="n"/>
-      <c r="D46" s="87" t="inlineStr">
+      <c r="C30" s="87" t="n"/>
+      <c r="D30" s="86" t="inlineStr">
         <is>
           <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
         </is>
       </c>
-      <c r="E46" s="88" t="n"/>
-      <c r="F46" s="88" t="n"/>
-      <c r="G46" s="87" t="inlineStr">
+      <c r="E30" s="87" t="n"/>
+      <c r="F30" s="87" t="n"/>
+      <c r="G30" s="86" t="inlineStr">
         <is>
           <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
         </is>
       </c>
-      <c r="H46" s="88" t="n"/>
-      <c r="I46" s="87" t="inlineStr">
+      <c r="H30" s="87" t="n"/>
+      <c r="I30" s="86" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J46" s="87" t="inlineStr">
+      <c r="J30" s="86" t="inlineStr">
         <is>
           <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
         </is>
       </c>
-      <c r="K46" s="88" t="n"/>
-      <c r="L46" s="88" t="n"/>
-      <c r="M46" s="87" t="inlineStr">
+      <c r="K30" s="87" t="n"/>
+      <c r="L30" s="87" t="n"/>
+      <c r="M30" s="86" t="inlineStr">
         <is>
           <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
-      <c r="N46" s="88" t="n"/>
-      <c r="O46" s="88" t="n"/>
-    </row>
-    <row r="47" ht="375" customHeight="1">
-      <c r="A47" s="87" t="inlineStr">
+      <c r="N30" s="87" t="n"/>
+      <c r="O30" s="87" t="n"/>
+    </row>
+    <row r="31" ht="380" customHeight="1">
+      <c r="A31" s="86" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B47" s="87" t="inlineStr">
+      <c r="B31" s="86" t="inlineStr">
         <is>
           <t>Malla anti-insectos</t>
         </is>
       </c>
-      <c r="C47" s="88" t="n"/>
-      <c r="D47" s="87" t="inlineStr">
+      <c r="C31" s="87" t="n"/>
+      <c r="D31" s="86" t="inlineStr">
         <is>
           <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
         </is>
       </c>
-      <c r="E47" s="88" t="n"/>
-      <c r="F47" s="88" t="n"/>
-      <c r="G47" s="87" t="inlineStr">
+      <c r="E31" s="87" t="n"/>
+      <c r="F31" s="87" t="n"/>
+      <c r="G31" s="86" t="inlineStr">
         <is>
           <t>Inox 316</t>
         </is>
       </c>
-      <c r="H47" s="88" t="n"/>
-      <c r="I47" s="87" t="inlineStr">
+      <c r="H31" s="87" t="n"/>
+      <c r="I31" s="86" t="inlineStr">
         <is>
           <t>3 (una por rejilla) + 1 (boca de la cubierta)</t>
         </is>
       </c>
-      <c r="J47" s="87" t="inlineStr">
+      <c r="J31" s="86" t="inlineStr">
         <is>
           <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
         </is>
       </c>
-      <c r="K47" s="88" t="n"/>
-      <c r="L47" s="88" t="n"/>
-      <c r="M47" s="87" t="inlineStr">
+      <c r="K31" s="87" t="n"/>
+      <c r="L31" s="87" t="n"/>
+      <c r="M31" s="86" t="inlineStr">
         <is>
           <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
         </is>
       </c>
-      <c r="N47" s="88" t="n"/>
-      <c r="O47" s="88" t="n"/>
-    </row>
-    <row r="48" ht="435" customHeight="1">
-      <c r="A48" s="87" t="inlineStr">
+      <c r="N31" s="87" t="n"/>
+      <c r="O31" s="87" t="n"/>
+    </row>
+    <row r="32" ht="456" customHeight="1">
+      <c r="A32" s="86" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B48" s="87" t="inlineStr">
+      <c r="B32" s="86" t="inlineStr">
         <is>
           <t>Estructura de unión y soportes</t>
         </is>
       </c>
-      <c r="C48" s="88" t="n"/>
-      <c r="D48" s="87" t="inlineStr">
+      <c r="C32" s="87" t="n"/>
+      <c r="D32" s="86" t="inlineStr">
         <is>
           <t>Marco de soporte pernado al muro para fijación del ventilador; soporta cargas estáticas, dinámicas y vibraciones; soportes de rejillas; pernos, tuercas, arandelas</t>
         </is>
       </c>
-      <c r="E48" s="88" t="n"/>
-      <c r="F48" s="88" t="n"/>
-      <c r="G48" s="87" t="inlineStr">
+      <c r="E32" s="87" t="n"/>
+      <c r="F32" s="87" t="n"/>
+      <c r="G32" s="86" t="inlineStr">
         <is>
           <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
         </is>
       </c>
-      <c r="H48" s="88" t="n"/>
-      <c r="I48" s="87" t="inlineStr">
+      <c r="H32" s="87" t="n"/>
+      <c r="I32" s="86" t="inlineStr">
         <is>
           <t>1 + Lote</t>
         </is>
       </c>
-      <c r="J48" s="87" t="inlineStr">
+      <c r="J32" s="86" t="inlineStr">
         <is>
           <t>Fabricación local a partir de planos del submittal del ventilador</t>
         </is>
       </c>
-      <c r="K48" s="88" t="n"/>
-      <c r="L48" s="88" t="n"/>
-      <c r="M48" s="87" t="inlineStr">
+      <c r="K32" s="87" t="n"/>
+      <c r="L32" s="87" t="n"/>
+      <c r="M32" s="86" t="inlineStr">
         <is>
           <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
         </is>
       </c>
-      <c r="N48" s="88" t="n"/>
-      <c r="O48" s="88" t="n"/>
-    </row>
-    <row r="49" ht="525" customHeight="1">
-      <c r="A49" s="87" t="inlineStr">
+      <c r="N32" s="87" t="n"/>
+      <c r="O32" s="87" t="n"/>
+    </row>
+    <row r="33" ht="532" customHeight="1">
+      <c r="A33" s="86" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B49" s="87" t="inlineStr">
+      <c r="B33" s="86" t="inlineStr">
         <is>
           <t>Cubierta intemperie</t>
         </is>
       </c>
-      <c r="C49" s="88" t="n"/>
-      <c r="D49" s="87" t="inlineStr">
+      <c r="C33" s="87" t="n"/>
+      <c r="D33" s="86" t="inlineStr">
         <is>
           <t>Protección contra lluvia/sol/ingreso de agua; aloja el banco de filtración (ítems 3-5 y malla); embridado directo a la placa mural del ventilador; acceso frontal/superior para cambio de filtros</t>
         </is>
       </c>
-      <c r="E49" s="88" t="n"/>
-      <c r="F49" s="88" t="n"/>
-      <c r="G49" s="87" t="inlineStr">
+      <c r="E33" s="87" t="n"/>
+      <c r="F33" s="87" t="n"/>
+      <c r="G33" s="86" t="inlineStr">
         <is>
           <t>PRFV viniléster o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L; drenaje inferior</t>
         </is>
       </c>
-      <c r="H49" s="88" t="n"/>
-      <c r="I49" s="87" t="inlineStr">
+      <c r="H33" s="87" t="n"/>
+      <c r="I33" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J49" s="87" t="inlineStr">
+      <c r="J33" s="86" t="inlineStr">
         <is>
           <t>Suministrada por el fabricante del ventilador o fabricación local según submittal</t>
         </is>
       </c>
-      <c r="K49" s="88" t="n"/>
-      <c r="L49" s="88" t="n"/>
-      <c r="M49" s="87" t="inlineStr">
+      <c r="K33" s="87" t="n"/>
+      <c r="L33" s="87" t="n"/>
+      <c r="M33" s="86" t="inlineStr">
         <is>
           <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
         </is>
       </c>
-      <c r="N49" s="88" t="n"/>
-      <c r="O49" s="88" t="n"/>
-    </row>
-    <row r="50" ht="270" customHeight="1">
-      <c r="A50" s="87" t="inlineStr">
+      <c r="N33" s="87" t="n"/>
+      <c r="O33" s="87" t="n"/>
+    </row>
+    <row r="34" ht="266" customHeight="1">
+      <c r="A34" s="86" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B50" s="87" t="inlineStr">
+      <c r="B34" s="86" t="inlineStr">
         <is>
           <t>Malla de protección interior</t>
         </is>
       </c>
-      <c r="C50" s="88" t="n"/>
-      <c r="D50" s="87" t="inlineStr">
+      <c r="C34" s="87" t="n"/>
+      <c r="D34" s="86" t="inlineStr">
         <is>
           <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor; desmontable</t>
         </is>
       </c>
-      <c r="E50" s="88" t="n"/>
-      <c r="F50" s="88" t="n"/>
-      <c r="G50" s="87" t="inlineStr">
+      <c r="E34" s="87" t="n"/>
+      <c r="F34" s="87" t="n"/>
+      <c r="G34" s="86" t="inlineStr">
         <is>
           <t>Malla inox 316 o galvanizada con pintura epóxica; marco rígido</t>
         </is>
       </c>
-      <c r="H50" s="88" t="n"/>
-      <c r="I50" s="87" t="inlineStr">
+      <c r="H34" s="87" t="n"/>
+      <c r="I34" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J50" s="87" t="inlineStr">
+      <c r="J34" s="86" t="inlineStr">
         <is>
           <t>Fabricación local según submittal</t>
         </is>
       </c>
-      <c r="K50" s="88" t="n"/>
-      <c r="L50" s="88" t="n"/>
-      <c r="M50" s="87" t="inlineStr">
+      <c r="K34" s="87" t="n"/>
+      <c r="L34" s="87" t="n"/>
+      <c r="M34" s="86" t="inlineStr">
         <is>
           <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
         </is>
       </c>
-      <c r="N50" s="88" t="n"/>
-      <c r="O50" s="88" t="n"/>
-    </row>
-    <row r="51" ht="600" customHeight="1">
-      <c r="A51" s="87" t="inlineStr">
+      <c r="N34" s="87" t="n"/>
+      <c r="O34" s="87" t="n"/>
+    </row>
+    <row r="35" ht="608" customHeight="1">
+      <c r="A35" s="86" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B51" s="87" t="inlineStr">
+      <c r="B35" s="86" t="inlineStr">
         <is>
           <t>Selladores</t>
         </is>
       </c>
-      <c r="C51" s="88" t="n"/>
-      <c r="D51" s="87" t="inlineStr">
+      <c r="C35" s="87" t="n"/>
+      <c r="D35" s="86" t="inlineStr">
         <is>
           <t>Sellado de pasamuros, marcos y empalmes</t>
         </is>
       </c>
-      <c r="E51" s="88" t="n"/>
-      <c r="F51" s="88" t="n"/>
-      <c r="G51" s="87" t="inlineStr">
+      <c r="E35" s="87" t="n"/>
+      <c r="F35" s="87" t="n"/>
+      <c r="G35" s="86" t="inlineStr">
         <is>
           <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
         </is>
       </c>
-      <c r="H51" s="88" t="n"/>
-      <c r="I51" s="87" t="inlineStr">
+      <c r="H35" s="87" t="n"/>
+      <c r="I35" s="86" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="J51" s="87" t="inlineStr">
+      <c r="J35" s="86" t="inlineStr">
         <is>
           <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
         </is>
       </c>
-      <c r="K51" s="88" t="n"/>
-      <c r="L51" s="88" t="n"/>
-      <c r="M51" s="87" t="inlineStr">
+      <c r="K35" s="87" t="n"/>
+      <c r="L35" s="87" t="n"/>
+      <c r="M35" s="86" t="inlineStr">
         <is>
           <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
         </is>
       </c>
-      <c r="N51" s="88" t="n"/>
-      <c r="O51" s="88" t="n"/>
-    </row>
-    <row r="52" ht="240" customHeight="1">
-      <c r="A52" s="87" t="inlineStr">
+      <c r="N35" s="87" t="n"/>
+      <c r="O35" s="87" t="n"/>
+    </row>
+    <row r="36" ht="266" customHeight="1">
+      <c r="A36" s="86" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B52" s="87" t="inlineStr">
+      <c r="B36" s="86" t="inlineStr">
         <is>
           <t>Protecciones eléctricas y tablero</t>
         </is>
       </c>
-      <c r="C52" s="88" t="n"/>
-      <c r="D52" s="87" t="inlineStr">
+      <c r="C36" s="87" t="n"/>
+      <c r="D36" s="86" t="inlineStr">
         <is>
           <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
         </is>
       </c>
-      <c r="E52" s="88" t="n"/>
-      <c r="F52" s="88" t="n"/>
-      <c r="G52" s="87" t="inlineStr">
+      <c r="E36" s="87" t="n"/>
+      <c r="F36" s="87" t="n"/>
+      <c r="G36" s="86" t="inlineStr">
         <is>
           <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
         </is>
       </c>
-      <c r="H52" s="88" t="n"/>
-      <c r="I52" s="87" t="inlineStr">
+      <c r="H36" s="87" t="n"/>
+      <c r="I36" s="86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J52" s="87" t="inlineStr">
+      <c r="J36" s="86" t="inlineStr">
         <is>
           <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
         </is>
       </c>
-      <c r="K52" s="88" t="n"/>
-      <c r="L52" s="88" t="n"/>
-      <c r="M52" s="87" t="inlineStr">
+      <c r="K36" s="87" t="n"/>
+      <c r="L36" s="87" t="n"/>
+      <c r="M36" s="86" t="inlineStr">
         <is>
           <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
         </is>
       </c>
-      <c r="N52" s="88" t="n"/>
-      <c r="O52" s="88" t="n"/>
-    </row>
-    <row r="53" ht="210" customHeight="1">
-      <c r="A53" s="87" t="inlineStr">
+      <c r="N36" s="87" t="n"/>
+      <c r="O36" s="87" t="n"/>
+    </row>
+    <row r="37" ht="228" customHeight="1">
+      <c r="A37" s="86" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B53" s="87" t="inlineStr">
+      <c r="B37" s="86" t="inlineStr">
         <is>
           <t>Cableado y canalización</t>
         </is>
       </c>
-      <c r="C53" s="88" t="n"/>
-      <c r="D53" s="87" t="inlineStr">
+      <c r="C37" s="87" t="n"/>
+      <c r="D37" s="86" t="inlineStr">
         <is>
           <t>Circuito de alimentación del motor 0.75 HP</t>
         </is>
       </c>
-      <c r="E53" s="88" t="n"/>
-      <c r="F53" s="88" t="n"/>
-      <c r="G53" s="87" t="inlineStr">
+      <c r="E37" s="87" t="n"/>
+      <c r="F37" s="87" t="n"/>
+      <c r="G37" s="86" t="inlineStr">
         <is>
           <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
         </is>
       </c>
-      <c r="H53" s="88" t="n"/>
-      <c r="I53" s="87" t="inlineStr">
+      <c r="H37" s="87" t="n"/>
+      <c r="I37" s="86" t="inlineStr">
         <is>
           <t>Lote</t>
         </is>
       </c>
-      <c r="J53" s="87" t="inlineStr">
+      <c r="J37" s="86" t="inlineStr">
         <is>
           <t>Suministro nacional certificado RETIE</t>
         </is>
       </c>
-      <c r="K53" s="88" t="n"/>
-      <c r="L53" s="88" t="n"/>
-      <c r="M53" s="87" t="inlineStr">
+      <c r="K37" s="87" t="n"/>
+      <c r="L37" s="87" t="n"/>
+      <c r="M37" s="86" t="inlineStr">
         <is>
           <t>Requisito RETIE / NTC 2050</t>
         </is>
       </c>
-      <c r="N53" s="88" t="n"/>
-      <c r="O53" s="88" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1"/>
-    <row r="55" ht="15" customHeight="1"/>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" s="84" t="inlineStr">
+      <c r="N37" s="87" t="n"/>
+      <c r="O37" s="87" t="n"/>
+    </row>
+    <row r="38" ht="38" customHeight="1"/>
+    <row r="39" ht="76" customHeight="1">
+      <c r="A39" s="82" t="inlineStr">
         <is>
           <t>3. Notas de suministro</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="165" customHeight="1">
-      <c r="A57" s="83" t="inlineStr">
+    <row r="40" ht="570" customHeight="1">
+      <c r="A40" s="83" t="inlineStr">
         <is>
           <t>3.1. Los ítems 1, 4, 8 y 9 requieren cotización formal con submittal: la selección final de RPM del ventilador mural Ø560 mm (ítem 1) y la potencia definitiva del motor (ítem 2) se confirman con el software del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar; las dimensiones de la estructura de unión (ítem 8) y de la cubierta intemperie (ítem 9) se definen con los planos del submittal del ventilador.</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1"/>
-    <row r="59" ht="15" customHeight="1"/>
-    <row r="60" ht="15" customHeight="1"/>
-    <row r="61" ht="15" customHeight="1"/>
-    <row r="62" ht="15" customHeight="1"/>
-    <row r="63" ht="15" customHeight="1"/>
-    <row r="64" ht="150" customHeight="1">
-      <c r="A64" s="83" t="inlineStr">
+    <row r="41" ht="38" customHeight="1"/>
+    <row r="42" ht="532" customHeight="1">
+      <c r="A42" s="83" t="inlineStr">
         <is>
           <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1"/>
-    <row r="66" ht="15" customHeight="1"/>
-    <row r="67" ht="15" customHeight="1"/>
-    <row r="68" ht="15" customHeight="1"/>
-    <row r="69" ht="15" customHeight="1"/>
-    <row r="70" ht="15" customHeight="1"/>
-    <row r="71" ht="165" customHeight="1">
-      <c r="A71" s="83" t="inlineStr">
+    <row r="43" ht="38" customHeight="1"/>
+    <row r="44" ht="418" customHeight="1">
+      <c r="A44" s="83" t="inlineStr">
         <is>
           <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1"/>
-    <row r="73" ht="15" customHeight="1"/>
-    <row r="74" ht="15" customHeight="1"/>
-    <row r="75" ht="15" customHeight="1"/>
+    <row r="45" ht="38" customHeight="1"/>
   </sheetData>
-  <mergeCells count="96">
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D47:F47"/>
+  <mergeCells count="91">
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="J25:L25"/>
     <mergeCell ref="N3:O3"/>
-    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="N5:O5"/>
-    <mergeCell ref="J50:L50"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="M24:O24"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="J46:L46"/>
-    <mergeCell ref="J52:L52"/>
-    <mergeCell ref="A18:O24"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="J48:L48"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="M52:O52"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B1:B5"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="A10:O11"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="A25:O27"/>
-    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A19:O20"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M37:O37"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="J42:L42"/>
-    <mergeCell ref="M43:O43"/>
-    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="A22:O22"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="J28:L28"/>
     <mergeCell ref="N6:O6"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="A14:O15"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="J30:L30"/>
     <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A13:O14"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="A64:O70"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="A38:O39"/>
-    <mergeCell ref="A56:O56"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="A40:O41"/>
+    <mergeCell ref="G37:H37"/>
     <mergeCell ref="A8:O8"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A71:O75"/>
-    <mergeCell ref="A30:O35"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="A57:O63"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D35:F35"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="M44:O44"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="M51:O51"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="J49:L49"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="A39:O39"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="A42:O43"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="A44:O45"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="J31:L31"/>
+    <mergeCell ref="G28:H28"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="J51:L51"/>
-    <mergeCell ref="M47:O47"/>
-    <mergeCell ref="M50:O50"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="A15:O17"/>
-    <mergeCell ref="M49:O49"/>
-    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="G29:H29"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="M48:O48"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="G31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/build/lis/P2437-HV-LIS-001 REV0.xlsx
+++ b/build/lis/P2437-HV-LIS-001 REV0.xlsx
@@ -3705,28 +3705,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
@@ -3737,17 +3738,7 @@
     <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
     <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="39" max="39"/>
-    <col width="13" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="13" customWidth="1" min="42" max="42"/>
-    <col width="13" customWidth="1" min="43" max="43"/>
-    <col width="13" customWidth="1" min="44" max="44"/>
-    <col width="13" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
@@ -3957,7 +3948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="38" customHeight="1">
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="81" t="inlineStr">
         <is>
           <t>LISTADO DE EQUIPOS Y MATERIALES (BOQ): SISTEMA DE VENTILACIÓN DEL LABORATORIO</t>
@@ -3978,800 +3969,782 @@
       <c r="N8" s="55" t="n"/>
       <c r="O8" s="55" t="n"/>
     </row>
-    <row r="9" ht="266" customHeight="1">
+    <row r="9" ht="100" customHeight="1">
       <c r="A9" s="82" t="inlineStr">
         <is>
           <t>Listado de equipos y materiales (BOQ): sistema de ventilación del laboratorio</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="76" customHeight="1">
+    <row r="10" ht="150" customHeight="1">
       <c r="A10" s="83" t="inlineStr">
         <is>
           <t>Proyecto: P2437-HV-INF-001 — BRINSA, laboratorio de análisis industrial, Cajicá (Cundinamarca)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="100" customHeight="1">
       <c r="A11" s="83" t="inlineStr">
         <is>
-          <t>Documento: listado_equipos.md — Revisión 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="76" customHeight="1">
+          <t>Documento: listado_equipos.md — Revisión 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="150" customHeight="1">
       <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Fecha: 2026-07-27 (fuentes consultadas el 2026-07-23; frente de ventiladores axiales ampliado el 2026-07-27)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="114" customHeight="1">
+    <row r="13" ht="200" customHeight="1">
       <c r="A13" s="83" t="inlineStr">
         <is>
           <t>Base: informe_investigacion.md (misma revisión); punto de diseño 3 840 m³/h @ 165 Pa en el sitio (225 Pa equivalente de catálogo, ρ = 1.2 kg/m³).</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="456" customHeight="1">
-      <c r="A14" s="83" t="inlineStr">
-        <is>
-          <t>Nota de revisión REV2 — 2026-07-27: actualización por uniformidad con el montaje típico instalado en la planta (Montaje/DISENOFINAL.png): ventilador axial mural Ø560 mm de transmisión directa, banco de filtración alojado en la cubierta intemperie, estructura de unión pernada al muro y malla de protección interior. Se eliminan la conexión flexible y la caja/housing con transición cuadrado/circular (REV1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="38" customHeight="1"/>
-    <row r="16" ht="114" customHeight="1">
+    <row r="14" ht="50" customHeight="1"/>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>1. Alcance del suministro</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="450" customHeight="1">
       <c r="A16" s="83" t="inlineStr">
         <is>
-          <t>Nota de revisión REV1 — 2026-07-27: cambio de alcance del cliente — sistema sin presurización, ventilador axial, sin instrumentación de presión diferencial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="38" customHeight="1"/>
-    <row r="18" ht="76" customHeight="1">
+          <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1"/>
+    <row r="18" ht="150" customHeight="1">
       <c r="A18" s="82" t="inlineStr">
         <is>
-          <t>1. Alcance del suministro</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="418" customHeight="1">
-      <c r="A19" s="83" t="inlineStr">
-        <is>
-          <t>1.1. El listado cubre todo lo necesario para que el sistema sea funcional: máquina de impulsión, etapa filtrante, rejillas de descarga y montaje, incluidas las protecciones eléctricas exigidas por RETIE/NTC 2050. Las cantidades corresponden a un (1) sistema completo para el laboratorio de 320 m³ (12 renovaciones/h).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="38" customHeight="1"/>
-    <row r="21" ht="38" customHeight="1"/>
-    <row r="22" ht="114" customHeight="1">
-      <c r="A22" s="82" t="inlineStr">
-        <is>
           <t>2. Tabla de equipos y materiales</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="76" customHeight="1">
-      <c r="A23" s="84" t="inlineStr">
+    <row r="19" ht="150" customHeight="1">
+      <c r="A19" s="84" t="inlineStr">
         <is>
           <t>Tabla 1. BOQ del sistema de ventilación (consulta de fuentes 2026-07-23, ampliada 2026-07-27).</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="114" customHeight="1">
-      <c r="A24" s="85" t="inlineStr">
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="85" t="inlineStr">
         <is>
           <t>Ítem</t>
         </is>
       </c>
-      <c r="B24" s="85" t="inlineStr">
+      <c r="B20" s="85" t="inlineStr">
         <is>
           <t>Función</t>
         </is>
       </c>
-      <c r="C24" s="85" t="n"/>
-      <c r="D24" s="85" t="inlineStr">
+      <c r="C20" s="85" t="n"/>
+      <c r="D20" s="85" t="inlineStr">
         <is>
           <t>Especificación clave</t>
         </is>
       </c>
-      <c r="E24" s="85" t="n"/>
-      <c r="F24" s="85" t="n"/>
-      <c r="G24" s="85" t="inlineStr">
+      <c r="E20" s="85" t="n"/>
+      <c r="F20" s="85" t="n"/>
+      <c r="G20" s="85" t="inlineStr">
         <is>
           <t>Material / compatibilidad corrosiva</t>
         </is>
       </c>
-      <c r="H24" s="85" t="n"/>
-      <c r="I24" s="85" t="inlineStr">
+      <c r="H20" s="85" t="n"/>
+      <c r="I20" s="85" t="inlineStr">
         <is>
           <t>Cant.</t>
         </is>
       </c>
-      <c r="J24" s="85" t="inlineStr">
+      <c r="J20" s="85" t="inlineStr">
         <is>
           <t>Candidatos comerciales (fabricante/modelo)</t>
         </is>
       </c>
-      <c r="K24" s="85" t="n"/>
-      <c r="L24" s="85" t="n"/>
-      <c r="M24" s="85" t="inlineStr">
+      <c r="K20" s="85" t="n"/>
+      <c r="L20" s="85" t="n"/>
+      <c r="M20" s="85" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="N24" s="85" t="n"/>
-      <c r="O24" s="85" t="n"/>
-    </row>
-    <row r="25" ht="532" customHeight="1">
+      <c r="N20" s="85" t="n"/>
+      <c r="O20" s="85" t="n"/>
+    </row>
+    <row r="21" ht="700" customHeight="1">
+      <c r="A21" s="86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="86" t="inlineStr">
+        <is>
+          <t>Ventilador de inyección</t>
+        </is>
+      </c>
+      <c r="C21" s="87" t="n"/>
+      <c r="D21" s="86" t="inlineStr">
+        <is>
+          <t>Axial mural (placa mural) Ø560 mm, transmisión directa; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; RPM por confirmar con proveedor</t>
+        </is>
+      </c>
+      <c r="E21" s="87" t="n"/>
+      <c r="F21" s="87" t="n"/>
+      <c r="G21" s="86" t="inlineStr">
+        <is>
+          <t>PRFV viniléster (ASTM C582/D4167) o acero con epóxico anticorrosivo; motor encapsulado en la corriente</t>
+        </is>
+      </c>
+      <c r="H21" s="87" t="n"/>
+      <c r="I21" s="86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" s="86" t="inlineStr">
+        <is>
+          <t>Sodeca HQD/HGT mural anticorrosivo (primera opción por uniformidad y canal local); Greenheck mural epóxico (Prime Lines HVAC, Bogotá); Aerovent/Twin City mural FRP; NYB FRP mural; Plastec PP</t>
+        </is>
+      </c>
+      <c r="K21" s="87" t="n"/>
+      <c r="L21" s="87" t="n"/>
+      <c r="M21" s="86" t="inlineStr">
+        <is>
+          <t>Sodeca (https://www.sodeca.com); catálogo Sodeca CO (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf); Greenheck (https://www.greenheck.com)</t>
+        </is>
+      </c>
+      <c r="N21" s="87" t="n"/>
+      <c r="O21" s="87" t="n"/>
+    </row>
+    <row r="22" ht="750" customHeight="1">
+      <c r="A22" s="86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" s="86" t="inlineStr">
+        <is>
+          <t>Motor del ventilador (integrado en el cubo)</t>
+        </is>
+      </c>
+      <c r="C22" s="87" t="n"/>
+      <c r="D22" s="86" t="inlineStr">
+        <is>
+          <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC encapsulado, clase F (H preferible), IP56 mín. (IP66 preferible), severe duty epóxico, eje inox; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
+        </is>
+      </c>
+      <c r="E22" s="87" t="n"/>
+      <c r="F22" s="87" t="n"/>
+      <c r="G22" s="86" t="inlineStr">
+        <is>
+          <t>Pintura epóxica + protección interna anticorrosiva; motor dentro de la corriente (transmisión directa) — ejecución reforzada</t>
+        </is>
+      </c>
+      <c r="H22" s="87" t="n"/>
+      <c r="I22" s="86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="86" t="inlineStr">
+        <is>
+          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
+        </is>
+      </c>
+      <c r="K22" s="87" t="n"/>
+      <c r="L22" s="87" t="n"/>
+      <c r="M22" s="86" t="inlineStr">
+        <is>
+          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
+        </is>
+      </c>
+      <c r="N22" s="87" t="n"/>
+      <c r="O22" s="87" t="n"/>
+    </row>
+    <row r="23" ht="600" customHeight="1">
+      <c r="A23" s="86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" s="86" t="inlineStr">
+        <is>
+          <t>Prefiltro (etapa 1)</t>
+        </is>
+      </c>
+      <c r="C23" s="87" t="n"/>
+      <c r="D23" s="86" t="inlineStr">
+        <is>
+          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
+        </is>
+      </c>
+      <c r="E23" s="87" t="n"/>
+      <c r="F23" s="87" t="n"/>
+      <c r="G23" s="86" t="inlineStr">
+        <is>
+          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
+        </is>
+      </c>
+      <c r="H23" s="87" t="n"/>
+      <c r="I23" s="86" t="inlineStr">
+        <is>
+          <t>1 (+ repuestos)</t>
+        </is>
+      </c>
+      <c r="J23" s="86" t="inlineStr">
+        <is>
+          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
+        </is>
+      </c>
+      <c r="K23" s="87" t="n"/>
+      <c r="L23" s="87" t="n"/>
+      <c r="M23" s="86" t="inlineStr">
+        <is>
+          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
+        </is>
+      </c>
+      <c r="N23" s="87" t="n"/>
+      <c r="O23" s="87" t="n"/>
+    </row>
+    <row r="24" ht="900" customHeight="1">
+      <c r="A24" s="86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B24" s="86" t="inlineStr">
+        <is>
+          <t>Filtro final (etapa 2)</t>
+        </is>
+      </c>
+      <c r="C24" s="87" t="n"/>
+      <c r="D24" s="86" t="inlineStr">
+        <is>
+          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
+        </is>
+      </c>
+      <c r="E24" s="87" t="n"/>
+      <c r="F24" s="87" t="n"/>
+      <c r="G24" s="86" t="inlineStr">
+        <is>
+          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
+        </is>
+      </c>
+      <c r="H24" s="87" t="n"/>
+      <c r="I24" s="86" t="inlineStr">
+        <is>
+          <t>1 (+ repuestos)</t>
+        </is>
+      </c>
+      <c r="J24" s="86" t="inlineStr">
+        <is>
+          <t>Camfil Durafil ES2/ES3 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
+        </is>
+      </c>
+      <c r="K24" s="87" t="n"/>
+      <c r="L24" s="87" t="n"/>
+      <c r="M24" s="86" t="inlineStr">
+        <is>
+          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
+        </is>
+      </c>
+      <c r="N24" s="87" t="n"/>
+      <c r="O24" s="87" t="n"/>
+    </row>
+    <row r="25" ht="550" customHeight="1">
       <c r="A25" s="86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B25" s="86" t="inlineStr">
         <is>
-          <t>Ventilador de inyección</t>
+          <t>Marcos portafiltros</t>
         </is>
       </c>
       <c r="C25" s="87" t="n"/>
       <c r="D25" s="86" t="inlineStr">
         <is>
-          <t>Axial mural (placa mural) Ø560 mm, transmisión directa; 3 840 m³/h @ 225 Pa (catálogo, ρ = 1.2 kg/m³) ≡ 165 Pa en sitio; AMCA 210; RPM por confirmar con proveedor</t>
+          <t>Holding frames para prefiltro + filtro final con junta continua, dentro de la cubierta</t>
         </is>
       </c>
       <c r="E25" s="87" t="n"/>
       <c r="F25" s="87" t="n"/>
       <c r="G25" s="86" t="inlineStr">
         <is>
-          <t>PRFV viniléster (ASTM C582/D4167) o acero con epóxico anticorrosivo; motor encapsulado en la corriente</t>
+          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
         </is>
       </c>
       <c r="H25" s="87" t="n"/>
       <c r="I25" s="86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 juego</t>
         </is>
       </c>
       <c r="J25" s="86" t="inlineStr">
         <is>
-          <t>Sodeca HQD/HGT mural anticorrosivo (primera opción por uniformidad y canal local); Greenheck mural epóxico (Prime Lines HVAC, Bogotá); Aerovent/Twin City mural FRP; NYB FRP mural; Plastec PP</t>
+          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
         </is>
       </c>
       <c r="K25" s="87" t="n"/>
       <c r="L25" s="87" t="n"/>
       <c r="M25" s="86" t="inlineStr">
         <is>
-          <t>Sodeca (https://www.sodeca.com); catálogo Sodeca CO (PDF) (https://www.sodeca.co/files/catalogs/es/SODECA_CT18_catalogo_resumen_CO.pdf); Greenheck (https://www.greenheck.com)</t>
+          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
         </is>
       </c>
       <c r="N25" s="87" t="n"/>
       <c r="O25" s="87" t="n"/>
     </row>
-    <row r="26" ht="570" customHeight="1">
+    <row r="26" ht="600" customHeight="1">
       <c r="A26" s="86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B26" s="86" t="inlineStr">
         <is>
-          <t>Motor del ventilador (integrado en el cubo)</t>
+          <t>Rejillas de descarga</t>
         </is>
       </c>
       <c r="C26" s="87" t="n"/>
       <c r="D26" s="86" t="inlineStr">
         <is>
-          <t>0.75 HP (provisional, confirmar con curva de selección final), TEFC encapsulado, clase F (H preferible), IP56 mín. (IP66 preferible), severe duty epóxico, eje inox; 440 V 3φ (confirmado por el cliente, 2026-07-23)</t>
+          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
         </is>
       </c>
       <c r="E26" s="87" t="n"/>
       <c r="F26" s="87" t="n"/>
       <c r="G26" s="86" t="inlineStr">
         <is>
-          <t>Pintura epóxica + protección interna anticorrosiva; motor dentro de la corriente (transmisión directa) — ejecución reforzada</t>
+          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
         </is>
       </c>
       <c r="H26" s="87" t="n"/>
       <c r="I26" s="86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" s="86" t="inlineStr">
         <is>
-          <t>Leeson/Regal Severe Duty; Baldor-Reliance IEEE 841XL; WEG W22 IEEE 841</t>
+          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
         </is>
       </c>
       <c r="K26" s="87" t="n"/>
       <c r="L26" s="87" t="n"/>
       <c r="M26" s="86" t="inlineStr">
         <is>
-          <t>Leeson (PDF) (https://www.regalrexnord.com/-/media/documents/brands/literature/industries/leeson_product_catalog_1050.pdf); Baldor 841XL (https://www.baldor.com/mvc/DownloadCenter/Files/9AKK108319)</t>
+          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
         </is>
       </c>
       <c r="N26" s="87" t="n"/>
       <c r="O26" s="87" t="n"/>
     </row>
-    <row r="27" ht="456" customHeight="1">
+    <row r="27" ht="500" customHeight="1">
       <c r="A27" s="86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B27" s="86" t="inlineStr">
         <is>
-          <t>Prefiltro (etapa 1)</t>
+          <t>Malla anti-insectos</t>
         </is>
       </c>
       <c r="C27" s="87" t="n"/>
       <c r="D27" s="86" t="inlineStr">
         <is>
-          <t>Plisado MERV 8 (ASHRAE 52.2); ΔP limpio 50-75 Pa, final 250 Pa (catálogo); 24×24 in</t>
+          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
         </is>
       </c>
       <c r="E27" s="87" t="n"/>
       <c r="F27" s="87" t="n"/>
       <c r="G27" s="86" t="inlineStr">
         <is>
-          <t>Marco cartón hidrófugo; inspección de corrosión de la rejilla soporte en el primer año</t>
+          <t>Inox 316</t>
         </is>
       </c>
       <c r="H27" s="87" t="n"/>
       <c r="I27" s="86" t="inlineStr">
         <is>
-          <t>1 (+ repuestos)</t>
+          <t>3 (una por rejilla) + 1 (boca de la cubierta)</t>
         </is>
       </c>
       <c r="J27" s="86" t="inlineStr">
         <is>
-          <t>Camfil 30/30 / Dual 9; Koch Multi-Pleat XL8</t>
+          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
         </is>
       </c>
       <c r="K27" s="87" t="n"/>
       <c r="L27" s="87" t="n"/>
       <c r="M27" s="86" t="inlineStr">
         <is>
-          <t>Camfil 30/30 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/406331002-SPS.pdf); Koch XL8 (PDF) (https://fsifiltration.com/wp-content/uploads/2020/08/Pleated-MERV8.pdf)</t>
+          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
         </is>
       </c>
       <c r="N27" s="87" t="n"/>
       <c r="O27" s="87" t="n"/>
     </row>
-    <row r="28" ht="684" customHeight="1">
+    <row r="28" ht="600" customHeight="1">
       <c r="A28" s="86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" s="86" t="inlineStr">
         <is>
-          <t>Filtro final (etapa 2)</t>
+          <t>Estructura de unión y soportes</t>
         </is>
       </c>
       <c r="C28" s="87" t="n"/>
       <c r="D28" s="86" t="inlineStr">
         <is>
-          <t>V-bank MERV 13-14 (52.2) ≡ ePM1 50-70 % (ISO 16890); ΔP limpio 80 Pa / final 210 Pa (catálogo) ≡ 59/154 Pa en sitio; 24×24 in</t>
+          <t>Marco de soporte pernado al muro para fijación del ventilador; soporta cargas estáticas, dinámicas y vibraciones; soportes de rejillas; pernos, tuercas, arandelas</t>
         </is>
       </c>
       <c r="E28" s="87" t="n"/>
       <c r="F28" s="87" t="n"/>
       <c r="G28" s="86" t="inlineStr">
         <is>
-          <t>Marco 100 % plástico (ABS/HIPS), sin metal; juntas PU</t>
+          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
         </is>
       </c>
       <c r="H28" s="87" t="n"/>
       <c r="I28" s="86" t="inlineStr">
         <is>
-          <t>1 (+ repuestos)</t>
+          <t>1 + Lote</t>
         </is>
       </c>
       <c r="J28" s="86" t="inlineStr">
         <is>
-          <t>Camfil Durafil ES2/ES3 (MERV 14); AAF VariCel VXL; Freudenberg MaxiPleat MX 85</t>
+          <t>Fabricación local a partir de planos del submittal del ventilador</t>
         </is>
       </c>
       <c r="K28" s="87" t="n"/>
       <c r="L28" s="87" t="n"/>
       <c r="M28" s="86" t="inlineStr">
         <is>
-          <t>Durafil ES2 (PDF) (https://cdn.lsicloud.net/pandhwhsal/documents/855080-003.pdf); AAF VXL (PDF) (https://aafterms.aafintl.com/-/media/files/aaf/commercial-and-industrial/us-products/box-filters/varicel-vxl/varicel-vxl_prod_mark_sht_afp-1-162.pdf)</t>
+          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
         </is>
       </c>
       <c r="N28" s="87" t="n"/>
       <c r="O28" s="87" t="n"/>
     </row>
-    <row r="29" ht="418" customHeight="1">
+    <row r="29" ht="700" customHeight="1">
       <c r="A29" s="86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" s="86" t="inlineStr">
         <is>
-          <t>Marcos portafiltros</t>
+          <t>Cubierta intemperie</t>
         </is>
       </c>
       <c r="C29" s="87" t="n"/>
       <c r="D29" s="86" t="inlineStr">
         <is>
-          <t>Holding frames para prefiltro + filtro final con junta continua, dentro de la cubierta</t>
+          <t>Protección contra lluvia/sol/ingreso de agua; aloja el banco de filtración (ítems 3-5 y malla); embridado directo a la placa mural del ventilador; acceso frontal/superior para cambio de filtros</t>
         </is>
       </c>
       <c r="E29" s="87" t="n"/>
       <c r="F29" s="87" t="n"/>
       <c r="G29" s="86" t="inlineStr">
         <is>
-          <t>Inox 304/316 (no galvanizado); junta PU/EPDM</t>
+          <t>PRFV viniléster o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L; drenaje inferior</t>
         </is>
       </c>
       <c r="H29" s="87" t="n"/>
       <c r="I29" s="86" t="inlineStr">
         <is>
-          <t>1 juego</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" s="86" t="inlineStr">
         <is>
-          <t>Camfil MagnaFrame II (opción inox 304); Camfil Universal Holding Frame (inox)</t>
+          <t>Suministrada por el fabricante del ventilador o fabricación local según submittal</t>
         </is>
       </c>
       <c r="K29" s="87" t="n"/>
       <c r="L29" s="87" t="n"/>
       <c r="M29" s="86" t="inlineStr">
         <is>
-          <t>MagnaFrame II (https://www.camfil.com/en-ca/products/housings-frames--louvers/filter-holding-frames/filter-holding-frames/magnaframe-ii-gasket-seal-_-47771)</t>
+          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
         </is>
       </c>
       <c r="N29" s="87" t="n"/>
       <c r="O29" s="87" t="n"/>
     </row>
-    <row r="30" ht="456" customHeight="1">
+    <row r="30" ht="350" customHeight="1">
       <c r="A30" s="86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" s="86" t="inlineStr">
         <is>
-          <t>Rejillas de descarga</t>
+          <t>Malla de protección interior</t>
         </is>
       </c>
       <c r="C30" s="87" t="n"/>
       <c r="D30" s="86" t="inlineStr">
         <is>
-          <t>Eggcrate ½ in, 353×336 mm facial; velocidad facial 3 m/s; ΔP 11 Pa en sitio (descarga libre); área libre ≥ 90 %</t>
+          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor; desmontable</t>
         </is>
       </c>
       <c r="E30" s="87" t="n"/>
       <c r="F30" s="87" t="n"/>
       <c r="G30" s="86" t="inlineStr">
         <is>
-          <t>Inox 316L (alternativa: aluminio anodizado 6063-T5); ensayo ASHRAE 70</t>
+          <t>Malla inox 316 o galvanizada con pintura epóxica; marco rígido</t>
         </is>
       </c>
       <c r="H30" s="87" t="n"/>
       <c r="I30" s="86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" s="86" t="inlineStr">
         <is>
-          <t>Titus 50F (versión inox); fabricación local ProAire S.A.S (corte láser inox); Laminaire</t>
+          <t>Fabricación local según submittal</t>
         </is>
       </c>
       <c r="K30" s="87" t="n"/>
       <c r="L30" s="87" t="n"/>
       <c r="M30" s="86" t="inlineStr">
         <is>
-          <t>Titus 50F (PDF) (https://www.titus-hvac.com/file/1228/50F_50Rrprod_specialized_2017.pdf); ProAire (https://www.proairecolombia.com/productos/rejillas-y-difusores.html)</t>
+          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
         </is>
       </c>
       <c r="N30" s="87" t="n"/>
       <c r="O30" s="87" t="n"/>
     </row>
-    <row r="31" ht="380" customHeight="1">
+    <row r="31" ht="800" customHeight="1">
       <c r="A31" s="86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B31" s="86" t="inlineStr">
         <is>
-          <t>Malla anti-insectos</t>
+          <t>Selladores</t>
         </is>
       </c>
       <c r="C31" s="87" t="n"/>
       <c r="D31" s="86" t="inlineStr">
         <is>
-          <t>Tejido 18×18, abertura ≈1 mm, área abierta ≥ 48 %; marco desmontable para limpieza</t>
+          <t>Sellado de pasamuros, marcos y empalmes</t>
         </is>
       </c>
       <c r="E31" s="87" t="n"/>
       <c r="F31" s="87" t="n"/>
       <c r="G31" s="86" t="inlineStr">
         <is>
-          <t>Inox 316</t>
+          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
         </is>
       </c>
       <c r="H31" s="87" t="n"/>
       <c r="I31" s="86" t="inlineStr">
         <is>
-          <t>3 (una por rejilla) + 1 (boca de la cubierta)</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="J31" s="86" t="inlineStr">
         <is>
-          <t>Proveedores de malla inox tejida (especificación genérica 18×18, alambre 0.45 mm)</t>
+          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
         </is>
       </c>
       <c r="K31" s="87" t="n"/>
       <c r="L31" s="87" t="n"/>
       <c r="M31" s="86" t="inlineStr">
         <is>
-          <t>Tabla área abierta (https://www.industrialmetalmesh.com/sale-54819921-micron-304-316l-stainless-steel-wire-mesh-screen-filter-mesh.html)</t>
+          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
         </is>
       </c>
       <c r="N31" s="87" t="n"/>
       <c r="O31" s="87" t="n"/>
     </row>
-    <row r="32" ht="456" customHeight="1">
+    <row r="32" ht="350" customHeight="1">
       <c r="A32" s="86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B32" s="86" t="inlineStr">
         <is>
-          <t>Estructura de unión y soportes</t>
+          <t>Protecciones eléctricas y tablero</t>
         </is>
       </c>
       <c r="C32" s="87" t="n"/>
       <c r="D32" s="86" t="inlineStr">
         <is>
-          <t>Marco de soporte pernado al muro para fijación del ventilador; soporta cargas estáticas, dinámicas y vibraciones; soportes de rejillas; pernos, tuercas, arandelas</t>
+          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
         </is>
       </c>
       <c r="E32" s="87" t="n"/>
       <c r="F32" s="87" t="n"/>
       <c r="G32" s="86" t="inlineStr">
         <is>
-          <t>Perfiles ASTM A36 galvanizados en caliente + pintura epóxica; ferretería inox 316 (clase A4); aislamiento dieléctrico frente a galvanizado</t>
+          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
         </is>
       </c>
       <c r="H32" s="87" t="n"/>
       <c r="I32" s="86" t="inlineStr">
         <is>
-          <t>1 + Lote</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" s="86" t="inlineStr">
         <is>
-          <t>Fabricación local a partir de planos del submittal del ventilador</t>
+          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
         </is>
       </c>
       <c r="K32" s="87" t="n"/>
       <c r="L32" s="87" t="n"/>
       <c r="M32" s="86" t="inlineStr">
         <is>
-          <t>Marsh Fasteners (criterio 304 vs 316) (https://marshfasteners.com/304-vs-316-stainless-steel-bolts/)</t>
+          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
         </is>
       </c>
       <c r="N32" s="87" t="n"/>
       <c r="O32" s="87" t="n"/>
     </row>
-    <row r="33" ht="532" customHeight="1">
+    <row r="33" ht="300" customHeight="1">
       <c r="A33" s="86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B33" s="86" t="inlineStr">
         <is>
-          <t>Cubierta intemperie</t>
+          <t>Cableado y canalización</t>
         </is>
       </c>
       <c r="C33" s="87" t="n"/>
       <c r="D33" s="86" t="inlineStr">
         <is>
-          <t>Protección contra lluvia/sol/ingreso de agua; aloja el banco de filtración (ítems 3-5 y malla); embridado directo a la placa mural del ventilador; acceso frontal/superior para cambio de filtros</t>
+          <t>Circuito de alimentación del motor 0.75 HP</t>
         </is>
       </c>
       <c r="E33" s="87" t="n"/>
       <c r="F33" s="87" t="n"/>
       <c r="G33" s="86" t="inlineStr">
         <is>
-          <t>PRFV viniléster o acero galvanizado G90 con pintura electrostática epóxica; alternativa inox 316L; drenaje inferior</t>
+          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
         </is>
       </c>
       <c r="H33" s="87" t="n"/>
       <c r="I33" s="86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Lote</t>
         </is>
       </c>
       <c r="J33" s="86" t="inlineStr">
         <is>
-          <t>Suministrada por el fabricante del ventilador o fabricación local según submittal</t>
+          <t>Suministro nacional certificado RETIE</t>
         </is>
       </c>
       <c r="K33" s="87" t="n"/>
       <c r="L33" s="87" t="n"/>
       <c r="M33" s="86" t="inlineStr">
         <is>
-          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
+          <t>Requisito RETIE / NTC 2050</t>
         </is>
       </c>
       <c r="N33" s="87" t="n"/>
       <c r="O33" s="87" t="n"/>
     </row>
-    <row r="34" ht="266" customHeight="1">
-      <c r="A34" s="86" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B34" s="86" t="inlineStr">
-        <is>
-          <t>Malla de protección interior</t>
-        </is>
-      </c>
-      <c r="C34" s="87" t="n"/>
-      <c r="D34" s="86" t="inlineStr">
-        <is>
-          <t>Jaula de seguridad en la descarga interior; evita contacto accidental con el impulsor; desmontable</t>
-        </is>
-      </c>
-      <c r="E34" s="87" t="n"/>
-      <c r="F34" s="87" t="n"/>
-      <c r="G34" s="86" t="inlineStr">
-        <is>
-          <t>Malla inox 316 o galvanizada con pintura epóxica; marco rígido</t>
-        </is>
-      </c>
-      <c r="H34" s="87" t="n"/>
-      <c r="I34" s="86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" s="86" t="inlineStr">
-        <is>
-          <t>Fabricación local según submittal</t>
-        </is>
-      </c>
-      <c r="K34" s="87" t="n"/>
-      <c r="L34" s="87" t="n"/>
-      <c r="M34" s="86" t="inlineStr">
-        <is>
-          <t>Montaje típico de planta (Montaje/DISENOFINAL.png)</t>
-        </is>
-      </c>
-      <c r="N34" s="87" t="n"/>
-      <c r="O34" s="87" t="n"/>
-    </row>
-    <row r="35" ht="608" customHeight="1">
-      <c r="A35" s="86" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B35" s="86" t="inlineStr">
-        <is>
-          <t>Selladores</t>
-        </is>
-      </c>
-      <c r="C35" s="87" t="n"/>
-      <c r="D35" s="86" t="inlineStr">
-        <is>
-          <t>Sellado de pasamuros, marcos y empalmes</t>
-        </is>
-      </c>
-      <c r="E35" s="87" t="n"/>
-      <c r="F35" s="87" t="n"/>
-      <c r="G35" s="86" t="inlineStr">
-        <is>
-          <t>Silicona RTV neutra (no acetoxi); PU solo en zonas sin cloro gaseoso directo</t>
-        </is>
-      </c>
-      <c r="H35" s="87" t="n"/>
-      <c r="I35" s="86" t="inlineStr">
-        <is>
-          <t>Lote</t>
-        </is>
-      </c>
-      <c r="J35" s="86" t="inlineStr">
-        <is>
-          <t>Sikaflex / silicona neutra grado industrial (suministro nacional)</t>
-        </is>
-      </c>
-      <c r="K35" s="87" t="n"/>
-      <c r="L35" s="87" t="n"/>
-      <c r="M35" s="86" t="inlineStr">
-        <is>
-          <t>RTV silicone (PDF) (https://irp.cdn-website.com/63168859/files/uploaded/Chemical%20Resistance%20of%20RTV%20Silicone%20Sealants%20Chart.pdf); Tabla PU (PDF) (https://www.apachepipe.com/assets/chemical-resistance-table.pdf)</t>
-        </is>
-      </c>
-      <c r="N35" s="87" t="n"/>
-      <c r="O35" s="87" t="n"/>
-    </row>
-    <row r="36" ht="266" customHeight="1">
-      <c r="A36" s="86" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B36" s="86" t="inlineStr">
-        <is>
-          <t>Protecciones eléctricas y tablero</t>
-        </is>
-      </c>
-      <c r="C36" s="87" t="n"/>
-      <c r="D36" s="86" t="inlineStr">
-        <is>
-          <t>Guardamotor, contactor, seccionador, puesta a tierra; tablero IP55/IP66 según ubicación</t>
-        </is>
-      </c>
-      <c r="E36" s="87" t="n"/>
-      <c r="F36" s="87" t="n"/>
-      <c r="G36" s="86" t="inlineStr">
-        <is>
-          <t>Gabinete con tratamiento anticorrosivo; prensaestopas niquelados o inox</t>
-        </is>
-      </c>
-      <c r="H36" s="87" t="n"/>
-      <c r="I36" s="86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J36" s="86" t="inlineStr">
-        <is>
-          <t>Fabricación local certificada RETIE; componentes Siemens/ABB/WEG</t>
-        </is>
-      </c>
-      <c r="K36" s="87" t="n"/>
-      <c r="L36" s="87" t="n"/>
-      <c r="M36" s="86" t="inlineStr">
-        <is>
-          <t>Requisito RETIE / NTC 2050 (normativo, no de catálogo)</t>
-        </is>
-      </c>
-      <c r="N36" s="87" t="n"/>
-      <c r="O36" s="87" t="n"/>
-    </row>
-    <row r="37" ht="228" customHeight="1">
-      <c r="A37" s="86" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B37" s="86" t="inlineStr">
-        <is>
-          <t>Cableado y canalización</t>
-        </is>
-      </c>
-      <c r="C37" s="87" t="n"/>
-      <c r="D37" s="86" t="inlineStr">
-        <is>
-          <t>Circuito de alimentación del motor 0.75 HP</t>
-        </is>
-      </c>
-      <c r="E37" s="87" t="n"/>
-      <c r="F37" s="87" t="n"/>
-      <c r="G37" s="86" t="inlineStr">
-        <is>
-          <t>Canalización PVC Schedule 80 o conduit inox; no conduit galvanizado expuesto</t>
-        </is>
-      </c>
-      <c r="H37" s="87" t="n"/>
-      <c r="I37" s="86" t="inlineStr">
-        <is>
-          <t>Lote</t>
-        </is>
-      </c>
-      <c r="J37" s="86" t="inlineStr">
-        <is>
-          <t>Suministro nacional certificado RETIE</t>
-        </is>
-      </c>
-      <c r="K37" s="87" t="n"/>
-      <c r="L37" s="87" t="n"/>
-      <c r="M37" s="86" t="inlineStr">
-        <is>
-          <t>Requisito RETIE / NTC 2050</t>
-        </is>
-      </c>
-      <c r="N37" s="87" t="n"/>
-      <c r="O37" s="87" t="n"/>
-    </row>
-    <row r="38" ht="38" customHeight="1"/>
-    <row r="39" ht="76" customHeight="1">
-      <c r="A39" s="82" t="inlineStr">
+    <row r="34" ht="50" customHeight="1"/>
+    <row r="35" ht="100" customHeight="1">
+      <c r="A35" s="82" t="inlineStr">
         <is>
           <t>3. Notas de suministro</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="570" customHeight="1">
-      <c r="A40" s="83" t="inlineStr">
+    <row r="36" ht="550" customHeight="1">
+      <c r="A36" s="83" t="inlineStr">
         <is>
           <t>3.1. Los ítems 1, 4, 8 y 9 requieren cotización formal con submittal: la selección final de RPM del ventilador mural Ø560 mm (ítem 1) y la potencia definitiva del motor (ítem 2) se confirman con el software del fabricante sobre el punto 3 840 m³/h @ 225 Pa aire estándar; las dimensiones de la estructura de unión (ítem 8) y de la cubierta intemperie (ítem 9) se definen con los planos del submittal del ventilador.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="38" customHeight="1"/>
-    <row r="42" ht="532" customHeight="1">
-      <c r="A42" s="83" t="inlineStr">
+    <row r="37" ht="500" customHeight="1">
+      <c r="A37" s="83" t="inlineStr">
         <is>
           <t>3.2. Ítems 3 y 4 son consumibles: se recomienda incluir en la compra inicial un juego de repuestos (un prefiltro y un filtro final) y congelar la especificación en términos MERV/ePM1 + 24×24 in para habilitar segunda fuente nacional (CARVEL S.A./Workclean; carvel.com.co (https://carvel.com.co/catalogo-workclean/filtros-de-aire-acondicionado-tipo-cartucho-fdcjm/), consulta 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="38" customHeight="1"/>
-    <row r="44" ht="418" customHeight="1">
-      <c r="A44" s="83" t="inlineStr">
+    <row r="38" ht="400" customHeight="1">
+      <c r="A38" s="83" t="inlineStr">
         <is>
           <t>3.3. La tensión de alimentación del motor es 440 V, 3φ, 60 Hz (confirmada por el cliente el 2026-07-23); de ella dependen el guardamotor y el cableado de los ítems 11-12. Los plazos de entrega de los equipos e importaciones se presupuestan con un máximo de 3 meses (dato del cliente, 2026-07-23).</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="38" customHeight="1"/>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="86">
+    <mergeCell ref="G21:H21"/>
     <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="G23:H23"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="M21:O21"/>
     <mergeCell ref="J25:L25"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D37:F37"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="M24:O24"/>
     <mergeCell ref="C2:L3"/>
-    <mergeCell ref="G34:H34"/>
     <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D23:F23"/>
     <mergeCell ref="J29:L29"/>
+    <mergeCell ref="A15:O15"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="M20:O20"/>
     <mergeCell ref="B1:B5"/>
     <mergeCell ref="J24:L24"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A19:O20"/>
+    <mergeCell ref="M22:O22"/>
     <mergeCell ref="M31:O31"/>
     <mergeCell ref="J26:L26"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="A18:O18"/>
     <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M37:O37"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="M26:O26"/>
-    <mergeCell ref="A22:O22"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M23:O23"/>
     <mergeCell ref="J33:L33"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G35:H35"/>
     <mergeCell ref="J28:L28"/>
     <mergeCell ref="N6:O6"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="G25:H25"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="A14:O15"/>
-    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D21:F21"/>
     <mergeCell ref="J30:L30"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="D32:F32"/>
@@ -4779,40 +4752,34 @@
     <mergeCell ref="M30:O30"/>
     <mergeCell ref="J32:L32"/>
     <mergeCell ref="M33:O33"/>
-    <mergeCell ref="A40:O41"/>
-    <mergeCell ref="G37:H37"/>
     <mergeCell ref="A8:O8"/>
     <mergeCell ref="D33:F33"/>
+    <mergeCell ref="A35:O35"/>
     <mergeCell ref="M32:O32"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D35:F35"/>
     <mergeCell ref="A1:A5"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="A9:O9"/>
     <mergeCell ref="C1:L1"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="A39:O39"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="G32:H32"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="A42:O43"/>
-    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D22:F22"/>
     <mergeCell ref="G27:H27"/>
-    <mergeCell ref="A44:O45"/>
-    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="J20:L20"/>
     <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="J22:L22"/>
     <mergeCell ref="J31:L31"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="N1:O1"/>
+    <mergeCell ref="J21:L21"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G30:H30"/>
+    <mergeCell ref="J23:L23"/>
     <mergeCell ref="D26:F26"/>
-    <mergeCell ref="M34:O34"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="C4:L6"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="G31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
